--- a/gm/resources/sample/global.xlsx
+++ b/gm/resources/sample/global.xlsx
@@ -194,10 +194,10 @@
     <t>最多连续坐庄次数</t>
   </si>
   <si>
-    <t>我的赌场清除CD价值，每X秒需要Y钻石</t>
-  </si>
-  <si>
-    <t>60_1</t>
+    <t>我的赌场清除CD价值，每X秒需要Y钻石（道具ID_道具数量_单位时间秒）</t>
+  </si>
+  <si>
+    <t>1980000_1_60</t>
   </si>
   <si>
     <t>默认邮件有效期（秒）</t>
@@ -1215,7 +1215,7 @@
   <dimension ref="A1:G23"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="6"/>
   <cols>
-    <col min="2" max="2" width="60.25" customWidth="1"/>
+    <col min="2" max="2" width="65.375" customWidth="1"/>
     <col min="3" max="3" width="22" customWidth="1"/>
     <col min="4" max="4" width="9.375" customWidth="1"/>
     <col min="5" max="5" width="9.5" customWidth="1"/>

--- a/gm/resources/sample/global.xlsx
+++ b/gm/resources/sample/global.xlsx
@@ -26,44 +26,8 @@
 </workbook>
 </file>
 
-<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>Administrator</author>
-  </authors>
-  <commentList>
-    <comment ref="B18" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>Administrator:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">
-0：头像
-1：头像边框
-2：国旗
-3：头衔/称号
-</t>
-        </r>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="58">
   <si>
     <t>sid</t>
   </si>
@@ -110,7 +74,7 @@
     <t>boolValue</t>
   </si>
   <si>
-    <t>VIP开放最大等级</t>
+    <t>玩家最大等级</t>
   </si>
   <si>
     <t>基础经验倍率</t>
@@ -176,16 +140,16 @@
     <t>每局结束从赢方获得的奖金中扣除此比例金额提供给创建房间的玩家</t>
   </si>
   <si>
-    <t>创建房间-邀请码刷新间隔（分钟）</t>
+    <t>创建房间-【邀请码每日0点重置后获得次数】</t>
   </si>
   <si>
     <t>默认装扮</t>
   </si>
   <si>
-    <t>1:1001:2001:3001</t>
-  </si>
-  <si>
-    <t>（类型0的值：类型1的值：类型2的值：类型3的值）</t>
+    <t>1:1001:2001:3001:4001:5001:6001</t>
+  </si>
+  <si>
+    <t>avatar表的ID</t>
   </si>
   <si>
     <t>牌局开启后需要的等待时间（分钟）</t>
@@ -206,7 +170,37 @@
     <t>我的赌场购买一键领取的消耗（道具ID_道具数量_持续时间分钟）</t>
   </si>
   <si>
-    <t>1980000_20_60</t>
+    <t>1980000_200_1440</t>
+  </si>
+  <si>
+    <t>收藏游戏数量上限</t>
+  </si>
+  <si>
+    <t>摇钱树活动增长金额</t>
+  </si>
+  <si>
+    <t>0_3_200_500|3_12_50_150|12_18_100_300|18_24_200_500</t>
+  </si>
+  <si>
+    <t>开始时间/时_结束时间/时（左闭右开）_每次增长值_每次增长下限|</t>
+  </si>
+  <si>
+    <t>摇钱树活动增加频率</t>
+  </si>
+  <si>
+    <t>2_1000</t>
+  </si>
+  <si>
+    <t>增长间隔（秒）_增长触发概率万分比</t>
+  </si>
+  <si>
+    <t>摇钱树活动当前奖金累计进入下一期的万分比比例</t>
+  </si>
+  <si>
+    <t>摇钱树活动当玩家产生有效打码量的金额万分比进入奖池</t>
+  </si>
+  <si>
+    <t>摇钱树活动每日免费获得的抽奖次数（重置时间跟随系统）</t>
   </si>
 </sst>
 </file>
@@ -219,7 +213,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -383,17 +377,6 @@
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
     </font>
   </fonts>
   <fills count="33">
@@ -1212,7 +1195,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G23"/>
+  <dimension ref="A1:G29"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="6"/>
   <cols>
     <col min="2" max="2" width="65.375" customWidth="1"/>
@@ -1295,10 +1278,9 @@
       <c r="B5" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="C5" s="4">
+      <c r="D5" s="4">
         <v>200</v>
       </c>
-      <c r="D5" s="4"/>
       <c r="E5" s="4"/>
       <c r="F5" s="4"/>
       <c r="G5" s="4"/>
@@ -1310,10 +1292,9 @@
       <c r="B6" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="C6" s="4">
+      <c r="D6" s="4">
         <v>10000</v>
       </c>
-      <c r="D6" s="4"/>
       <c r="E6" s="4"/>
       <c r="F6" s="4"/>
       <c r="G6" s="4" t="s">
@@ -1327,10 +1308,9 @@
       <c r="B7" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="C7" s="4">
+      <c r="D7" s="4">
         <v>10000</v>
       </c>
-      <c r="D7" s="4"/>
       <c r="E7" s="4"/>
       <c r="F7" s="4"/>
       <c r="G7" s="4" t="s">
@@ -1560,10 +1540,81 @@
         <v>47</v>
       </c>
     </row>
+    <row r="24" spans="1:4">
+      <c r="A24">
+        <v>20</v>
+      </c>
+      <c r="B24" t="s">
+        <v>48</v>
+      </c>
+      <c r="D24">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
+      <c r="A25">
+        <v>21</v>
+      </c>
+      <c r="B25" t="s">
+        <v>49</v>
+      </c>
+      <c r="C25" t="s">
+        <v>50</v>
+      </c>
+      <c r="G25" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7">
+      <c r="A26">
+        <v>22</v>
+      </c>
+      <c r="B26" t="s">
+        <v>52</v>
+      </c>
+      <c r="C26" t="s">
+        <v>53</v>
+      </c>
+      <c r="G26" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4">
+      <c r="A27">
+        <v>23</v>
+      </c>
+      <c r="B27" t="s">
+        <v>55</v>
+      </c>
+      <c r="D27">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4">
+      <c r="A28">
+        <v>24</v>
+      </c>
+      <c r="B28" t="s">
+        <v>56</v>
+      </c>
+      <c r="D28">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="29" customFormat="1" spans="1:4">
+      <c r="A29">
+        <v>25</v>
+      </c>
+      <c r="B29" t="s">
+        <v>57</v>
+      </c>
+      <c r="D29">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
-  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/gm/resources/sample/global.xlsx
+++ b/gm/resources/sample/global.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="59">
   <si>
     <t>sid</t>
   </si>
@@ -201,6 +201,9 @@
   </si>
   <si>
     <t>摇钱树活动每日免费获得的抽奖次数（重置时间跟随系统）</t>
+  </si>
+  <si>
+    <t>每次下注金币的万分比飞入储钱罐</t>
   </si>
 </sst>
 </file>
@@ -842,7 +845,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -870,6 +873,9 @@
     </xf>
     <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" quotePrefix="1">
       <alignment vertical="center"/>
     </xf>
@@ -1195,7 +1201,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G29"/>
+  <dimension ref="A1:G30"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="6"/>
   <cols>
     <col min="2" max="2" width="65.375" customWidth="1"/>
@@ -1355,7 +1361,7 @@
       <c r="B10" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="C10" s="11" t="s">
+      <c r="C10" s="12" t="s">
         <v>24</v>
       </c>
       <c r="D10" s="7"/>
@@ -1372,7 +1378,7 @@
       <c r="B11" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="C11" s="12" t="s">
+      <c r="C11" s="13" t="s">
         <v>27</v>
       </c>
       <c r="D11" s="8"/>
@@ -1389,7 +1395,7 @@
       <c r="B12" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C12" s="12" t="s">
+      <c r="C12" s="13" t="s">
         <v>29</v>
       </c>
       <c r="D12" s="8"/>
@@ -1406,7 +1412,7 @@
       <c r="B13" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="C13" s="12" t="s">
+      <c r="C13" s="13" t="s">
         <v>31</v>
       </c>
       <c r="D13" s="8"/>
@@ -1423,7 +1429,7 @@
       <c r="B14" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="C14" s="12" t="s">
+      <c r="C14" s="13" t="s">
         <v>33</v>
       </c>
       <c r="D14" s="8"/>
@@ -1610,6 +1616,18 @@
       </c>
       <c r="D29">
         <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4">
+      <c r="A30">
+        <v>26</v>
+      </c>
+      <c r="B30" t="s">
+        <v>58</v>
+      </c>
+      <c r="C30" s="11"/>
+      <c r="D30">
+        <v>500</v>
       </c>
     </row>
   </sheetData>

--- a/gm/resources/sample/global.xlsx
+++ b/gm/resources/sample/global.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="61">
   <si>
     <t>sid</t>
   </si>
@@ -204,6 +204,12 @@
   </si>
   <si>
     <t>每次下注金币的万分比飞入储钱罐</t>
+  </si>
+  <si>
+    <t>创建房间-房间销毁时房主获得实际准备金的万分比</t>
+  </si>
+  <si>
+    <t>不得超过10000</t>
   </si>
 </sst>
 </file>
@@ -1201,7 +1207,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G30"/>
+  <dimension ref="A1:G31"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="6"/>
   <cols>
     <col min="2" max="2" width="65.375" customWidth="1"/>
@@ -1630,6 +1636,20 @@
         <v>500</v>
       </c>
     </row>
+    <row r="31" spans="1:7">
+      <c r="A31">
+        <v>27</v>
+      </c>
+      <c r="B31" t="s">
+        <v>59</v>
+      </c>
+      <c r="D31">
+        <v>9900</v>
+      </c>
+      <c r="G31" t="s">
+        <v>60</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/gm/resources/sample/global.xlsx
+++ b/gm/resources/sample/global.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="64">
   <si>
     <t>sid</t>
   </si>
@@ -200,7 +200,10 @@
     <t>摇钱树活动当玩家产生有效打码量的金额万分比进入奖池</t>
   </si>
   <si>
-    <t>摇钱树活动每日免费获得的抽奖次数（重置时间跟随系统）</t>
+    <t>摇钱树活动每日免费获得一个祈福卡道具（重置时间跟随系统）</t>
+  </si>
+  <si>
+    <t>1022501_1</t>
   </si>
   <si>
     <t>每次下注金币的万分比飞入储钱罐</t>
@@ -210,6 +213,12 @@
   </si>
   <si>
     <t>不得超过10000</t>
+  </si>
+  <si>
+    <t>刮刮奖活动每次消耗道具数量</t>
+  </si>
+  <si>
+    <t>1022502_1</t>
   </si>
 </sst>
 </file>
@@ -1207,7 +1216,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G31"/>
+  <dimension ref="A1:G32"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="6"/>
   <cols>
     <col min="2" max="2" width="65.375" customWidth="1"/>
@@ -1613,15 +1622,15 @@
         <v>100</v>
       </c>
     </row>
-    <row r="29" customFormat="1" spans="1:4">
+    <row r="29" customFormat="1" spans="1:3">
       <c r="A29">
         <v>25</v>
       </c>
       <c r="B29" t="s">
         <v>57</v>
       </c>
-      <c r="D29">
-        <v>1</v>
+      <c r="C29" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -1629,7 +1638,7 @@
         <v>26</v>
       </c>
       <c r="B30" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C30" s="11"/>
       <c r="D30">
@@ -1641,13 +1650,24 @@
         <v>27</v>
       </c>
       <c r="B31" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D31">
         <v>9900</v>
       </c>
       <c r="G31" t="s">
-        <v>60</v>
+        <v>61</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3">
+      <c r="A32">
+        <v>28</v>
+      </c>
+      <c r="B32" t="s">
+        <v>62</v>
+      </c>
+      <c r="C32" t="s">
+        <v>63</v>
       </c>
     </row>
   </sheetData>

--- a/gm/resources/sample/global.xlsx
+++ b/gm/resources/sample/global.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="65">
   <si>
     <t>sid</t>
   </si>
@@ -219,6 +219,9 @@
   </si>
   <si>
     <t>1022502_1</t>
+  </si>
+  <si>
+    <t>幸运夺宝(一元购)能配置商品数量上限</t>
   </si>
 </sst>
 </file>
@@ -1216,7 +1219,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G32"/>
+  <dimension ref="A1:G33"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="6"/>
   <cols>
     <col min="2" max="2" width="65.375" customWidth="1"/>
@@ -1670,6 +1673,17 @@
         <v>63</v>
       </c>
     </row>
+    <row r="33" spans="1:4">
+      <c r="A33">
+        <v>29</v>
+      </c>
+      <c r="B33" t="s">
+        <v>64</v>
+      </c>
+      <c r="D33">
+        <v>6</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/gm/resources/sample/global.xlsx
+++ b/gm/resources/sample/global.xlsx
@@ -26,8 +26,42 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Administrator</author>
+  </authors>
+  <commentList>
+    <comment ref="E35" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+总量 ÷ 平均中奖金额 = 中奖次数
+1000000000 ÷ 718000 = 1392.7577
+初始天数30天</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="84">
   <si>
     <t>sid</t>
   </si>
@@ -222,6 +256,63 @@
   </si>
   <si>
     <t>幸运夺宝(一元购)能配置商品数量上限</t>
+  </si>
+  <si>
+    <t>官方派奖每个转盘需求积分：初、中、高</t>
+  </si>
+  <si>
+    <t>1000_3000_5000</t>
+  </si>
+  <si>
+    <t>官方派奖转盘奖池金币数量</t>
+  </si>
+  <si>
+    <t>从OfficialAwards表中取平均中奖金额</t>
+  </si>
+  <si>
+    <t>活动时间</t>
+  </si>
+  <si>
+    <t>天</t>
+  </si>
+  <si>
+    <t>毫秒</t>
+  </si>
+  <si>
+    <t>官方派奖：有效下注转换积分比例 ：有效下注 = X积分</t>
+  </si>
+  <si>
+    <t>100000_1</t>
+  </si>
+  <si>
+    <t>官方派奖：充值转换积分比例 ：充值金额 = X积分</t>
+  </si>
+  <si>
+    <t>10_1</t>
+  </si>
+  <si>
+    <t>官方派奖：真人和机器人奖池比例(百分比)</t>
+  </si>
+  <si>
+    <t>10_90</t>
+  </si>
+  <si>
+    <t>机器人奖池比例</t>
+  </si>
+  <si>
+    <t>官方派奖：机器人中奖间隔（毫秒_权重|毫秒_权重）</t>
+  </si>
+  <si>
+    <t>平均中奖间隔</t>
+  </si>
+  <si>
+    <t>共5档</t>
+  </si>
+  <si>
+    <t>每档偏移</t>
+  </si>
+  <si>
+    <t>每档时间</t>
   </si>
 </sst>
 </file>
@@ -234,7 +325,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -398,6 +489,17 @@
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="33">
@@ -863,7 +965,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -894,6 +996,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" quotePrefix="1">
       <alignment vertical="center"/>
     </xf>
@@ -1219,15 +1322,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G33"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="6"/>
+  <dimension ref="A1:W39"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="2" max="2" width="65.375" customWidth="1"/>
-    <col min="3" max="3" width="22" customWidth="1"/>
+    <col min="3" max="3" width="37.625" customWidth="1"/>
     <col min="4" max="4" width="9.375" customWidth="1"/>
-    <col min="5" max="5" width="9.5" customWidth="1"/>
+    <col min="5" max="5" width="11.5" customWidth="1"/>
     <col min="6" max="6" width="9.625" customWidth="1"/>
     <col min="7" max="7" width="23.375" customWidth="1"/>
+    <col min="10" max="10" width="11.5"/>
+    <col min="12" max="12" width="11.5"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
@@ -1379,7 +1484,7 @@
       <c r="B10" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="C10" s="12" t="s">
+      <c r="C10" s="13" t="s">
         <v>24</v>
       </c>
       <c r="D10" s="7"/>
@@ -1396,7 +1501,7 @@
       <c r="B11" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="C11" s="13" t="s">
+      <c r="C11" s="14" t="s">
         <v>27</v>
       </c>
       <c r="D11" s="8"/>
@@ -1413,7 +1518,7 @@
       <c r="B12" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C12" s="13" t="s">
+      <c r="C12" s="14" t="s">
         <v>29</v>
       </c>
       <c r="D12" s="8"/>
@@ -1430,7 +1535,7 @@
       <c r="B13" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="C13" s="13" t="s">
+      <c r="C13" s="14" t="s">
         <v>31</v>
       </c>
       <c r="D13" s="8"/>
@@ -1447,7 +1552,7 @@
       <c r="B14" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="C14" s="13" t="s">
+      <c r="C14" s="14" t="s">
         <v>33</v>
       </c>
       <c r="D14" s="8"/>
@@ -1684,9 +1789,168 @@
         <v>6</v>
       </c>
     </row>
+    <row r="34" customFormat="1" spans="1:3">
+      <c r="A34">
+        <v>30</v>
+      </c>
+      <c r="B34" t="s">
+        <v>65</v>
+      </c>
+      <c r="C34" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="35" customFormat="1" spans="1:13">
+      <c r="A35">
+        <v>31</v>
+      </c>
+      <c r="B35" t="s">
+        <v>67</v>
+      </c>
+      <c r="E35">
+        <v>1000000000</v>
+      </c>
+      <c r="G35" t="s">
+        <v>68</v>
+      </c>
+      <c r="H35">
+        <v>718000</v>
+      </c>
+      <c r="I35" t="s">
+        <v>69</v>
+      </c>
+      <c r="J35">
+        <v>30</v>
+      </c>
+      <c r="K35" t="s">
+        <v>70</v>
+      </c>
+      <c r="L35">
+        <f>J35*24*60*60*1000</f>
+        <v>2592000000</v>
+      </c>
+      <c r="M35" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3">
+      <c r="A36">
+        <v>32</v>
+      </c>
+      <c r="B36" t="s">
+        <v>72</v>
+      </c>
+      <c r="C36" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3">
+      <c r="A37">
+        <v>33</v>
+      </c>
+      <c r="B37" t="s">
+        <v>74</v>
+      </c>
+      <c r="C37" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8">
+      <c r="A38">
+        <v>34</v>
+      </c>
+      <c r="B38" t="s">
+        <v>76</v>
+      </c>
+      <c r="C38" t="s">
+        <v>77</v>
+      </c>
+      <c r="G38" t="s">
+        <v>78</v>
+      </c>
+      <c r="H38">
+        <f>VALUE(MID(C38,FIND("_",C38)+1,4))</f>
+        <v>90</v>
+      </c>
+    </row>
+    <row r="39" spans="1:23">
+      <c r="A39">
+        <v>35</v>
+      </c>
+      <c r="B39" t="s">
+        <v>79</v>
+      </c>
+      <c r="C39" t="str">
+        <f>_xlfn.TEXTJOIN("|",TRUE,S39:W39)</f>
+        <v>3101760_1000|2584800_1000|2067840_1000|1550880_1000|1033920_1000</v>
+      </c>
+      <c r="G39" t="s">
+        <v>80</v>
+      </c>
+      <c r="H39">
+        <f>ROUND(L35/(E35*H38/100/H35),0)</f>
+        <v>2067840</v>
+      </c>
+      <c r="I39" t="s">
+        <v>71</v>
+      </c>
+      <c r="J39" t="s">
+        <v>81</v>
+      </c>
+      <c r="K39" s="12" t="s">
+        <v>82</v>
+      </c>
+      <c r="L39" s="12">
+        <v>0.25</v>
+      </c>
+      <c r="M39" t="s">
+        <v>83</v>
+      </c>
+      <c r="N39">
+        <f>ROUND(P39*(1+2*L39),0)</f>
+        <v>3101760</v>
+      </c>
+      <c r="O39">
+        <f>ROUND(P39*(1+1*L39),0)</f>
+        <v>2584800</v>
+      </c>
+      <c r="P39">
+        <f>H39</f>
+        <v>2067840</v>
+      </c>
+      <c r="Q39">
+        <f>ROUND(P39*(1-1*L39),0)</f>
+        <v>1550880</v>
+      </c>
+      <c r="R39">
+        <f>ROUND(P39*(1-2*L39),0)</f>
+        <v>1033920</v>
+      </c>
+      <c r="S39" t="str">
+        <f>_xlfn.TEXTJOIN("_",TRUE,N39,1000)</f>
+        <v>3101760_1000</v>
+      </c>
+      <c r="T39" t="str">
+        <f>_xlfn.TEXTJOIN("_",TRUE,O39,1000)</f>
+        <v>2584800_1000</v>
+      </c>
+      <c r="U39" t="str">
+        <f>_xlfn.TEXTJOIN("_",TRUE,P39,1000)</f>
+        <v>2067840_1000</v>
+      </c>
+      <c r="V39" t="str">
+        <f>_xlfn.TEXTJOIN("_",TRUE,Q39,1000)</f>
+        <v>1550880_1000</v>
+      </c>
+      <c r="W39" t="str">
+        <f>_xlfn.TEXTJOIN("_",TRUE,R39,1000)</f>
+        <v>1033920_1000</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/gm/resources/sample/global.xlsx
+++ b/gm/resources/sample/global.xlsx
@@ -26,42 +26,8 @@
 </workbook>
 </file>
 
-<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>Administrator</author>
-  </authors>
-  <commentList>
-    <comment ref="E35" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>Administrator:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">
-总量 ÷ 平均中奖金额 = 中奖次数
-1000000000 ÷ 718000 = 1392.7577
-初始天数30天</t>
-        </r>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="74">
   <si>
     <t>sid</t>
   </si>
@@ -267,18 +233,6 @@
     <t>官方派奖转盘奖池金币数量</t>
   </si>
   <si>
-    <t>从OfficialAwards表中取平均中奖金额</t>
-  </si>
-  <si>
-    <t>活动时间</t>
-  </si>
-  <si>
-    <t>天</t>
-  </si>
-  <si>
-    <t>毫秒</t>
-  </si>
-  <si>
     <t>官方派奖：有效下注转换积分比例 ：有效下注 = X积分</t>
   </si>
   <si>
@@ -295,24 +249,6 @@
   </si>
   <si>
     <t>10_90</t>
-  </si>
-  <si>
-    <t>机器人奖池比例</t>
-  </si>
-  <si>
-    <t>官方派奖：机器人中奖间隔（毫秒_权重|毫秒_权重）</t>
-  </si>
-  <si>
-    <t>平均中奖间隔</t>
-  </si>
-  <si>
-    <t>共5档</t>
-  </si>
-  <si>
-    <t>每档偏移</t>
-  </si>
-  <si>
-    <t>每档时间</t>
   </si>
 </sst>
 </file>
@@ -325,7 +261,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -489,17 +425,6 @@
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
     </font>
   </fonts>
   <fills count="33">
@@ -965,7 +890,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -996,7 +921,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" quotePrefix="1">
       <alignment vertical="center"/>
     </xf>
@@ -1322,17 +1246,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:W39"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
+  <dimension ref="A1:G38"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="6"/>
   <cols>
     <col min="2" max="2" width="65.375" customWidth="1"/>
-    <col min="3" max="3" width="37.625" customWidth="1"/>
+    <col min="3" max="3" width="22" customWidth="1"/>
     <col min="4" max="4" width="9.375" customWidth="1"/>
     <col min="5" max="5" width="11.5" customWidth="1"/>
     <col min="6" max="6" width="9.625" customWidth="1"/>
     <col min="7" max="7" width="23.375" customWidth="1"/>
-    <col min="10" max="10" width="11.5"/>
-    <col min="12" max="12" width="11.5"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
@@ -1484,7 +1406,7 @@
       <c r="B10" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="C10" s="13" t="s">
+      <c r="C10" s="12" t="s">
         <v>24</v>
       </c>
       <c r="D10" s="7"/>
@@ -1501,7 +1423,7 @@
       <c r="B11" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="C11" s="14" t="s">
+      <c r="C11" s="13" t="s">
         <v>27</v>
       </c>
       <c r="D11" s="8"/>
@@ -1518,7 +1440,7 @@
       <c r="B12" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C12" s="14" t="s">
+      <c r="C12" s="13" t="s">
         <v>29</v>
       </c>
       <c r="D12" s="8"/>
@@ -1535,7 +1457,7 @@
       <c r="B13" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="C13" s="14" t="s">
+      <c r="C13" s="13" t="s">
         <v>31</v>
       </c>
       <c r="D13" s="8"/>
@@ -1552,7 +1474,7 @@
       <c r="B14" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="C14" s="14" t="s">
+      <c r="C14" s="13" t="s">
         <v>33</v>
       </c>
       <c r="D14" s="8"/>
@@ -1800,7 +1722,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="35" customFormat="1" spans="1:13">
+    <row r="35" customFormat="1" spans="1:5">
       <c r="A35">
         <v>31</v>
       </c>
@@ -1809,28 +1731,6 @@
       </c>
       <c r="E35">
         <v>1000000000</v>
-      </c>
-      <c r="G35" t="s">
-        <v>68</v>
-      </c>
-      <c r="H35">
-        <v>718000</v>
-      </c>
-      <c r="I35" t="s">
-        <v>69</v>
-      </c>
-      <c r="J35">
-        <v>30</v>
-      </c>
-      <c r="K35" t="s">
-        <v>70</v>
-      </c>
-      <c r="L35">
-        <f>J35*24*60*60*1000</f>
-        <v>2592000000</v>
-      </c>
-      <c r="M35" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="36" spans="1:3">
@@ -1838,10 +1738,10 @@
         <v>32</v>
       </c>
       <c r="B36" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="C36" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
     </row>
     <row r="37" spans="1:3">
@@ -1849,108 +1749,26 @@
         <v>33</v>
       </c>
       <c r="B37" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="C37" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="38" spans="1:8">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3">
       <c r="A38">
         <v>34</v>
       </c>
       <c r="B38" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="C38" t="s">
-        <v>77</v>
-      </c>
-      <c r="G38" t="s">
-        <v>78</v>
-      </c>
-      <c r="H38">
-        <f>VALUE(MID(C38,FIND("_",C38)+1,4))</f>
-        <v>90</v>
-      </c>
-    </row>
-    <row r="39" spans="1:23">
-      <c r="A39">
-        <v>35</v>
-      </c>
-      <c r="B39" t="s">
-        <v>79</v>
-      </c>
-      <c r="C39" t="str">
-        <f>_xlfn.TEXTJOIN("|",TRUE,S39:W39)</f>
-        <v>3101760_1000|2584800_1000|2067840_1000|1550880_1000|1033920_1000</v>
-      </c>
-      <c r="G39" t="s">
-        <v>80</v>
-      </c>
-      <c r="H39">
-        <f>ROUND(L35/(E35*H38/100/H35),0)</f>
-        <v>2067840</v>
-      </c>
-      <c r="I39" t="s">
-        <v>71</v>
-      </c>
-      <c r="J39" t="s">
-        <v>81</v>
-      </c>
-      <c r="K39" s="12" t="s">
-        <v>82</v>
-      </c>
-      <c r="L39" s="12">
-        <v>0.25</v>
-      </c>
-      <c r="M39" t="s">
-        <v>83</v>
-      </c>
-      <c r="N39">
-        <f>ROUND(P39*(1+2*L39),0)</f>
-        <v>3101760</v>
-      </c>
-      <c r="O39">
-        <f>ROUND(P39*(1+1*L39),0)</f>
-        <v>2584800</v>
-      </c>
-      <c r="P39">
-        <f>H39</f>
-        <v>2067840</v>
-      </c>
-      <c r="Q39">
-        <f>ROUND(P39*(1-1*L39),0)</f>
-        <v>1550880</v>
-      </c>
-      <c r="R39">
-        <f>ROUND(P39*(1-2*L39),0)</f>
-        <v>1033920</v>
-      </c>
-      <c r="S39" t="str">
-        <f>_xlfn.TEXTJOIN("_",TRUE,N39,1000)</f>
-        <v>3101760_1000</v>
-      </c>
-      <c r="T39" t="str">
-        <f>_xlfn.TEXTJOIN("_",TRUE,O39,1000)</f>
-        <v>2584800_1000</v>
-      </c>
-      <c r="U39" t="str">
-        <f>_xlfn.TEXTJOIN("_",TRUE,P39,1000)</f>
-        <v>2067840_1000</v>
-      </c>
-      <c r="V39" t="str">
-        <f>_xlfn.TEXTJOIN("_",TRUE,Q39,1000)</f>
-        <v>1550880_1000</v>
-      </c>
-      <c r="W39" t="str">
-        <f>_xlfn.TEXTJOIN("_",TRUE,R39,1000)</f>
-        <v>1033920_1000</v>
+        <v>73</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
-  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/gm/resources/sample/global.xlsx
+++ b/gm/resources/sample/global.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\java\gamedoc\游戏配置表\common\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCF864D1-CE52-4CEC-9A1B-F1C30F91D0D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="globalConfig" sheetId="1" r:id="rId1"/>
@@ -26,8 +32,42 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Administrator</author>
+  </authors>
+  <commentList>
+    <comment ref="E35" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+总量 ÷ 平均中奖金额 = 中奖次数
+1000000000 ÷ 718000 = 1392.7577
+初始天数30天</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="85">
   <si>
     <t>sid</t>
   </si>
@@ -233,6 +273,18 @@
     <t>官方派奖转盘奖池金币数量</t>
   </si>
   <si>
+    <t>从OfficialAwards表中取平均中奖金额</t>
+  </si>
+  <si>
+    <t>活动时间</t>
+  </si>
+  <si>
+    <t>天</t>
+  </si>
+  <si>
+    <t>毫秒</t>
+  </si>
+  <si>
     <t>官方派奖：有效下注转换积分比例 ：有效下注 = X积分</t>
   </si>
   <si>
@@ -249,19 +301,35 @@
   </si>
   <si>
     <t>10_90</t>
+  </si>
+  <si>
+    <t>机器人奖池比例</t>
+  </si>
+  <si>
+    <t>官方派奖：机器人中奖间隔（毫秒_权重|毫秒_权重）</t>
+  </si>
+  <si>
+    <t>平均中奖间隔</t>
+  </si>
+  <si>
+    <t>共5档</t>
+  </si>
+  <si>
+    <t>每档偏移</t>
+  </si>
+  <si>
+    <t>每档时间</t>
+  </si>
+  <si>
+    <t>3101760_1000|2584800_1000|2067840_1000|1550880_1000|1033920_1000</t>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="22">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -283,345 +351,40 @@
       <charset val="134"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <b/>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
+      <sz val="9"/>
       <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
+      <family val="3"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="10">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -644,253 +407,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -904,16 +425,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -921,68 +436,26 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" quotePrefix="1">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" quotePrefix="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1240,24 +713,26 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:G38"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="6"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:W39"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="65.375" customWidth="1"/>
-    <col min="3" max="3" width="22" customWidth="1"/>
+    <col min="3" max="3" width="37.625" customWidth="1"/>
     <col min="4" max="4" width="9.375" customWidth="1"/>
     <col min="5" max="5" width="11.5" customWidth="1"/>
     <col min="6" max="6" width="9.625" customWidth="1"/>
     <col min="7" max="7" width="23.375" customWidth="1"/>
+    <col min="10" max="10" width="11.5"/>
+    <col min="12" max="12" width="11.5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1278,7 +753,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
         <v>6</v>
       </c>
@@ -1297,8 +772,8 @@
       </c>
       <c r="G2" s="2"/>
     </row>
-    <row r="3" spans="1:7">
-      <c r="A3" s="5" t="s">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A3" s="1" t="s">
         <v>10</v>
       </c>
       <c r="B3" s="2"/>
@@ -1316,13 +791,13 @@
       </c>
       <c r="G3" s="2"/>
     </row>
-    <row r="4" spans="1:7">
-      <c r="A4" s="6"/>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A4" s="5"/>
       <c r="B4" s="4"/>
       <c r="C4" s="4"/>
       <c r="G4" s="4"/>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>1</v>
       </c>
@@ -1336,7 +811,7 @@
       <c r="F5" s="4"/>
       <c r="G5" s="4"/>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>2</v>
       </c>
@@ -1352,7 +827,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>3</v>
       </c>
@@ -1368,7 +843,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>4</v>
       </c>
@@ -1385,7 +860,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>5</v>
       </c>
@@ -1399,92 +874,92 @@
         <v>22</v>
       </c>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>6</v>
       </c>
       <c r="B10" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="C10" s="12" t="s">
+      <c r="C10" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="D10" s="7"/>
+      <c r="D10" s="6"/>
       <c r="E10" s="4"/>
       <c r="F10" s="4"/>
       <c r="G10" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="11" spans="1:7">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>7</v>
       </c>
       <c r="B11" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="C11" s="13" t="s">
+      <c r="C11" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="D11" s="8"/>
+      <c r="D11" s="4"/>
       <c r="E11" s="4"/>
       <c r="F11" s="4"/>
       <c r="G11" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="12" spans="1:7">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>8</v>
       </c>
       <c r="B12" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C12" s="13" t="s">
+      <c r="C12" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="D12" s="8"/>
+      <c r="D12" s="4"/>
       <c r="E12" s="4"/>
       <c r="F12" s="4"/>
       <c r="G12" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="13" spans="1:7">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>9</v>
       </c>
       <c r="B13" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="C13" s="13" t="s">
+      <c r="C13" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="D13" s="8"/>
+      <c r="D13" s="4"/>
       <c r="E13" s="4"/>
       <c r="F13" s="4"/>
       <c r="G13" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="14" spans="1:7">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>10</v>
       </c>
       <c r="B14" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="C14" s="13" t="s">
+      <c r="C14" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="D14" s="8"/>
+      <c r="D14" s="4"/>
       <c r="E14" s="4"/>
       <c r="F14" s="4"/>
       <c r="G14" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="15" spans="1:4">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>11</v>
       </c>
@@ -1496,7 +971,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="16" spans="1:7">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>12</v>
       </c>
@@ -1510,7 +985,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="17" spans="1:4">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>13</v>
       </c>
@@ -1521,32 +996,32 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:7">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>14</v>
       </c>
       <c r="B18" t="s">
         <v>38</v>
       </c>
-      <c r="C18" s="9" t="s">
+      <c r="C18" s="7" t="s">
         <v>39</v>
       </c>
       <c r="G18" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="19" spans="1:4">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>15</v>
       </c>
-      <c r="B19" s="10" t="s">
+      <c r="B19" s="8" t="s">
         <v>41</v>
       </c>
       <c r="D19">
         <v>5</v>
       </c>
     </row>
-    <row r="20" spans="1:4">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>16</v>
       </c>
@@ -1557,7 +1032,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="21" spans="1:3">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>17</v>
       </c>
@@ -1568,7 +1043,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="22" spans="1:4">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>18</v>
       </c>
@@ -1580,7 +1055,7 @@
         <v>604800</v>
       </c>
     </row>
-    <row r="23" spans="1:3">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>19</v>
       </c>
@@ -1591,7 +1066,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="24" spans="1:4">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>20</v>
       </c>
@@ -1602,7 +1077,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="25" spans="1:7">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A25">
         <v>21</v>
       </c>
@@ -1616,7 +1091,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="26" spans="1:7">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A26">
         <v>22</v>
       </c>
@@ -1630,7 +1105,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="27" spans="1:4">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A27">
         <v>23</v>
       </c>
@@ -1641,7 +1116,7 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="28" spans="1:4">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A28">
         <v>24</v>
       </c>
@@ -1652,7 +1127,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="29" customFormat="1" spans="1:3">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A29">
         <v>25</v>
       </c>
@@ -1663,19 +1138,19 @@
         <v>58</v>
       </c>
     </row>
-    <row r="30" spans="1:4">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A30">
         <v>26</v>
       </c>
       <c r="B30" t="s">
         <v>59</v>
       </c>
-      <c r="C30" s="11"/>
+      <c r="C30" s="9"/>
       <c r="D30">
         <v>500</v>
       </c>
     </row>
-    <row r="31" spans="1:7">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A31">
         <v>27</v>
       </c>
@@ -1689,7 +1164,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="32" spans="1:3">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A32">
         <v>28</v>
       </c>
@@ -1700,7 +1175,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="33" spans="1:4">
+    <row r="33" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A33">
         <v>29</v>
       </c>
@@ -1711,7 +1186,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="34" customFormat="1" spans="1:3">
+    <row r="34" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A34">
         <v>30</v>
       </c>
@@ -1722,7 +1197,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="35" customFormat="1" spans="1:5">
+    <row r="35" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A35">
         <v>31</v>
       </c>
@@ -1732,43 +1207,146 @@
       <c r="E35">
         <v>1000000000</v>
       </c>
-    </row>
-    <row r="36" spans="1:3">
+      <c r="G35" t="s">
+        <v>68</v>
+      </c>
+      <c r="H35">
+        <v>718000</v>
+      </c>
+      <c r="I35" t="s">
+        <v>69</v>
+      </c>
+      <c r="J35">
+        <v>30</v>
+      </c>
+      <c r="K35" t="s">
+        <v>70</v>
+      </c>
+      <c r="L35">
+        <f>J35*24*60*60*1000</f>
+        <v>2592000000</v>
+      </c>
+      <c r="M35" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="36" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A36">
         <v>32</v>
       </c>
       <c r="B36" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="C36" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="37" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A37">
         <v>33</v>
       </c>
       <c r="B37" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="C37" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="38" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A38">
         <v>34</v>
       </c>
       <c r="B38" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="C38" t="s">
-        <v>73</v>
+        <v>77</v>
+      </c>
+      <c r="G38" t="s">
+        <v>78</v>
+      </c>
+      <c r="H38">
+        <f>VALUE(MID(C38,FIND("_",C38)+1,4))</f>
+        <v>90</v>
+      </c>
+    </row>
+    <row r="39" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A39">
+        <v>35</v>
+      </c>
+      <c r="B39" t="s">
+        <v>79</v>
+      </c>
+      <c r="C39" s="13" t="s">
+        <v>84</v>
+      </c>
+      <c r="G39" t="s">
+        <v>80</v>
+      </c>
+      <c r="H39">
+        <f>ROUND(L35/(E35*H38/100/H35),0)</f>
+        <v>2067840</v>
+      </c>
+      <c r="I39" t="s">
+        <v>71</v>
+      </c>
+      <c r="J39" t="s">
+        <v>81</v>
+      </c>
+      <c r="K39" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="L39" s="10">
+        <v>0.25</v>
+      </c>
+      <c r="M39" t="s">
+        <v>83</v>
+      </c>
+      <c r="N39">
+        <f>ROUND(P39*(1+2*L39),0)</f>
+        <v>3101760</v>
+      </c>
+      <c r="O39">
+        <f>ROUND(P39*(1+1*L39),0)</f>
+        <v>2584800</v>
+      </c>
+      <c r="P39">
+        <f>H39</f>
+        <v>2067840</v>
+      </c>
+      <c r="Q39">
+        <f>ROUND(P39*(1-1*L39),0)</f>
+        <v>1550880</v>
+      </c>
+      <c r="R39">
+        <f>ROUND(P39*(1-2*L39),0)</f>
+        <v>1033920</v>
+      </c>
+      <c r="S39" t="str">
+        <f>_xlfn.TEXTJOIN("_",TRUE,N39,1000)</f>
+        <v>3101760_1000</v>
+      </c>
+      <c r="T39" t="str">
+        <f>_xlfn.TEXTJOIN("_",TRUE,O39,1000)</f>
+        <v>2584800_1000</v>
+      </c>
+      <c r="U39" t="str">
+        <f>_xlfn.TEXTJOIN("_",TRUE,P39,1000)</f>
+        <v>2067840_1000</v>
+      </c>
+      <c r="V39" t="str">
+        <f>_xlfn.TEXTJOIN("_",TRUE,Q39,1000)</f>
+        <v>1550880_1000</v>
+      </c>
+      <c r="W39" t="str">
+        <f>_xlfn.TEXTJOIN("_",TRUE,R39,1000)</f>
+        <v>1033920_1000</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/gm/resources/sample/global.xlsx
+++ b/gm/resources/sample/global.xlsx
@@ -26,8 +26,42 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Administrator</author>
+  </authors>
+  <commentList>
+    <comment ref="E35" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+总量 ÷ 平均中奖金额 = 中奖次数
+1000000000 ÷ 718000 = 1392.7577
+初始天数30天</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="87">
   <si>
     <t>sid</t>
   </si>
@@ -233,6 +267,18 @@
     <t>官方派奖转盘奖池金币数量</t>
   </si>
   <si>
+    <t>从OfficialAwards表中取平均中奖金额</t>
+  </si>
+  <si>
+    <t>活动时间</t>
+  </si>
+  <si>
+    <t>天</t>
+  </si>
+  <si>
+    <t>毫秒</t>
+  </si>
+  <si>
     <t>官方派奖：有效下注转换积分比例 ：有效下注 = X积分</t>
   </si>
   <si>
@@ -249,6 +295,33 @@
   </si>
   <si>
     <t>10_90</t>
+  </si>
+  <si>
+    <t>机器人奖池比例</t>
+  </si>
+  <si>
+    <t>官方派奖：机器人中奖间隔（毫秒_权重|毫秒_权重）</t>
+  </si>
+  <si>
+    <t>平均中奖间隔</t>
+  </si>
+  <si>
+    <t>共5档</t>
+  </si>
+  <si>
+    <t>每档偏移</t>
+  </si>
+  <si>
+    <t>每档时间</t>
+  </si>
+  <si>
+    <t>积分大奖： 参与转盘每次消耗积分数</t>
+  </si>
+  <si>
+    <t>积分大奖：时段排行榜上榜的最低积分要求</t>
+  </si>
+  <si>
+    <t>积分大奖：月总排行榜上榜的最低积分要求</t>
   </si>
 </sst>
 </file>
@@ -261,7 +334,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -425,6 +498,17 @@
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="33">
@@ -890,7 +974,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -921,6 +1005,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" quotePrefix="1">
       <alignment vertical="center"/>
     </xf>
@@ -1246,15 +1331,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G38"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="6"/>
+  <dimension ref="A1:W42"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="2" max="2" width="65.375" customWidth="1"/>
-    <col min="3" max="3" width="22" customWidth="1"/>
+    <col min="3" max="3" width="37.625" customWidth="1"/>
     <col min="4" max="4" width="9.375" customWidth="1"/>
     <col min="5" max="5" width="11.5" customWidth="1"/>
     <col min="6" max="6" width="9.625" customWidth="1"/>
     <col min="7" max="7" width="23.375" customWidth="1"/>
+    <col min="10" max="10" width="11.5"/>
+    <col min="12" max="12" width="11.5"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
@@ -1406,7 +1493,7 @@
       <c r="B10" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="C10" s="12" t="s">
+      <c r="C10" s="13" t="s">
         <v>24</v>
       </c>
       <c r="D10" s="7"/>
@@ -1423,7 +1510,7 @@
       <c r="B11" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="C11" s="13" t="s">
+      <c r="C11" s="14" t="s">
         <v>27</v>
       </c>
       <c r="D11" s="8"/>
@@ -1440,7 +1527,7 @@
       <c r="B12" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C12" s="13" t="s">
+      <c r="C12" s="14" t="s">
         <v>29</v>
       </c>
       <c r="D12" s="8"/>
@@ -1457,7 +1544,7 @@
       <c r="B13" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="C13" s="13" t="s">
+      <c r="C13" s="14" t="s">
         <v>31</v>
       </c>
       <c r="D13" s="8"/>
@@ -1474,7 +1561,7 @@
       <c r="B14" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="C14" s="13" t="s">
+      <c r="C14" s="14" t="s">
         <v>33</v>
       </c>
       <c r="D14" s="8"/>
@@ -1722,7 +1809,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="35" customFormat="1" spans="1:5">
+    <row r="35" customFormat="1" spans="1:13">
       <c r="A35">
         <v>31</v>
       </c>
@@ -1731,6 +1818,28 @@
       </c>
       <c r="E35">
         <v>1000000000</v>
+      </c>
+      <c r="G35" t="s">
+        <v>68</v>
+      </c>
+      <c r="H35">
+        <v>718000</v>
+      </c>
+      <c r="I35" t="s">
+        <v>69</v>
+      </c>
+      <c r="J35">
+        <v>30</v>
+      </c>
+      <c r="K35" t="s">
+        <v>70</v>
+      </c>
+      <c r="L35">
+        <f>J35*24*60*60*1000</f>
+        <v>2592000000</v>
+      </c>
+      <c r="M35" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="36" spans="1:3">
@@ -1738,10 +1847,10 @@
         <v>32</v>
       </c>
       <c r="B36" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="C36" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
     </row>
     <row r="37" spans="1:3">
@@ -1749,26 +1858,141 @@
         <v>33</v>
       </c>
       <c r="B37" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="C37" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8">
       <c r="A38">
         <v>34</v>
       </c>
       <c r="B38" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="C38" t="s">
-        <v>73</v>
+        <v>77</v>
+      </c>
+      <c r="G38" t="s">
+        <v>78</v>
+      </c>
+      <c r="H38">
+        <f>VALUE(MID(C38,FIND("_",C38)+1,4))</f>
+        <v>90</v>
+      </c>
+    </row>
+    <row r="39" spans="1:23">
+      <c r="A39">
+        <v>35</v>
+      </c>
+      <c r="B39" t="s">
+        <v>79</v>
+      </c>
+      <c r="C39" t="str">
+        <f>_xlfn.TEXTJOIN("|",TRUE,S39:W39)</f>
+        <v>3101760_1000|2584800_1000|2067840_1000|1550880_1000|1033920_1000</v>
+      </c>
+      <c r="G39" t="s">
+        <v>80</v>
+      </c>
+      <c r="H39">
+        <f>ROUND(L35/(E35*H38/100/H35),0)</f>
+        <v>2067840</v>
+      </c>
+      <c r="I39" t="s">
+        <v>71</v>
+      </c>
+      <c r="J39" t="s">
+        <v>81</v>
+      </c>
+      <c r="K39" s="12" t="s">
+        <v>82</v>
+      </c>
+      <c r="L39" s="12">
+        <v>0.25</v>
+      </c>
+      <c r="M39" t="s">
+        <v>83</v>
+      </c>
+      <c r="N39">
+        <f>ROUND(P39*(1+2*L39),0)</f>
+        <v>3101760</v>
+      </c>
+      <c r="O39">
+        <f>ROUND(P39*(1+1*L39),0)</f>
+        <v>2584800</v>
+      </c>
+      <c r="P39">
+        <f>H39</f>
+        <v>2067840</v>
+      </c>
+      <c r="Q39">
+        <f>ROUND(P39*(1-1*L39),0)</f>
+        <v>1550880</v>
+      </c>
+      <c r="R39">
+        <f>ROUND(P39*(1-2*L39),0)</f>
+        <v>1033920</v>
+      </c>
+      <c r="S39" t="str">
+        <f>_xlfn.TEXTJOIN("_",TRUE,N39,1000)</f>
+        <v>3101760_1000</v>
+      </c>
+      <c r="T39" t="str">
+        <f>_xlfn.TEXTJOIN("_",TRUE,O39,1000)</f>
+        <v>2584800_1000</v>
+      </c>
+      <c r="U39" t="str">
+        <f>_xlfn.TEXTJOIN("_",TRUE,P39,1000)</f>
+        <v>2067840_1000</v>
+      </c>
+      <c r="V39" t="str">
+        <f>_xlfn.TEXTJOIN("_",TRUE,Q39,1000)</f>
+        <v>1550880_1000</v>
+      </c>
+      <c r="W39" t="str">
+        <f>_xlfn.TEXTJOIN("_",TRUE,R39,1000)</f>
+        <v>1033920_1000</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4">
+      <c r="A40">
+        <v>36</v>
+      </c>
+      <c r="B40" t="s">
+        <v>84</v>
+      </c>
+      <c r="D40">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4">
+      <c r="A41">
+        <v>37</v>
+      </c>
+      <c r="B41" t="s">
+        <v>85</v>
+      </c>
+      <c r="D41">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4">
+      <c r="A42">
+        <v>38</v>
+      </c>
+      <c r="B42" t="s">
+        <v>86</v>
+      </c>
+      <c r="D42">
+        <v>2000</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/gm/resources/sample/global.xlsx
+++ b/gm/resources/sample/global.xlsx
@@ -291,7 +291,7 @@
     <t>10_1</t>
   </si>
   <si>
-    <t>官方派奖：真人和机器人奖池比例(百分比)</t>
+    <t>官方派奖：真人和机器人奖池比例(百分比)  废弃</t>
   </si>
   <si>
     <t>10_90</t>
@@ -315,13 +315,13 @@
     <t>每档时间</t>
   </si>
   <si>
-    <t>积分大奖： 参与转盘每次消耗积分数</t>
-  </si>
-  <si>
-    <t>积分大奖：时段排行榜上榜的最低积分要求</t>
-  </si>
-  <si>
-    <t>积分大奖：月总排行榜上榜的最低积分要求</t>
+    <t>积分大奖： 转盘每次消耗积分数</t>
+  </si>
+  <si>
+    <t>积分大奖：时段榜-上榜的最低积分要求(上午榜、下午榜共用)</t>
+  </si>
+  <si>
+    <t>积分大奖：月总榜-上榜的最低积分要求</t>
   </si>
 </sst>
 </file>
@@ -334,10 +334,17 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0" tint="-0.25"/>
       <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -511,12 +518,24 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -844,76 +863,70 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -922,10 +935,10 @@
     <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -934,10 +947,10 @@
     <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -946,10 +959,10 @@
     <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -958,10 +971,10 @@
     <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -970,19 +983,26 @@
     <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1001,10 +1021,15 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" quotePrefix="1">
       <alignment vertical="center"/>
@@ -1345,51 +1370,51 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2" t="s">
+      <c r="B1" s="3"/>
+      <c r="C1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="3" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2" t="s">
+      <c r="B2" s="3"/>
+      <c r="C2" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="5" t="s">
         <v>6</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="G2" s="2"/>
+      <c r="G2" s="3"/>
     </row>
     <row r="3" spans="1:7">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="2"/>
-      <c r="C3" s="2" t="s">
+      <c r="B3" s="3"/>
+      <c r="C3" s="3" t="s">
         <v>11</v>
       </c>
       <c r="D3" t="s">
@@ -1401,41 +1426,41 @@
       <c r="F3" t="s">
         <v>14</v>
       </c>
-      <c r="G3" s="2"/>
+      <c r="G3" s="3"/>
     </row>
     <row r="4" spans="1:7">
-      <c r="A4" s="6"/>
-      <c r="B4" s="4"/>
-      <c r="C4" s="4"/>
-      <c r="G4" s="4"/>
+      <c r="A4" s="7"/>
+      <c r="B4" s="5"/>
+      <c r="C4" s="5"/>
+      <c r="G4" s="5"/>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
         <v>1</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="D5" s="4">
+      <c r="D5" s="5">
         <v>200</v>
       </c>
-      <c r="E5" s="4"/>
-      <c r="F5" s="4"/>
-      <c r="G5" s="4"/>
+      <c r="E5" s="5"/>
+      <c r="F5" s="5"/>
+      <c r="G5" s="5"/>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
         <v>2</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="D6" s="4">
+      <c r="D6" s="5">
         <v>10000</v>
       </c>
-      <c r="E6" s="4"/>
-      <c r="F6" s="4"/>
-      <c r="G6" s="4" t="s">
+      <c r="E6" s="5"/>
+      <c r="F6" s="5"/>
+      <c r="G6" s="5" t="s">
         <v>17</v>
       </c>
     </row>
@@ -1443,15 +1468,15 @@
       <c r="A7">
         <v>3</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="D7" s="4">
+      <c r="D7" s="5">
         <v>10000</v>
       </c>
-      <c r="E7" s="4"/>
-      <c r="F7" s="4"/>
-      <c r="G7" s="4" t="s">
+      <c r="E7" s="5"/>
+      <c r="F7" s="5"/>
+      <c r="G7" s="5" t="s">
         <v>17</v>
       </c>
     </row>
@@ -1459,16 +1484,16 @@
       <c r="A8">
         <v>4</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="C8" s="4">
+      <c r="C8" s="5">
         <v>100</v>
       </c>
-      <c r="D8" s="4"/>
-      <c r="E8" s="4"/>
-      <c r="F8" s="4"/>
-      <c r="G8" s="4" t="s">
+      <c r="D8" s="5"/>
+      <c r="E8" s="5"/>
+      <c r="F8" s="5"/>
+      <c r="G8" s="5" t="s">
         <v>20</v>
       </c>
     </row>
@@ -1490,15 +1515,15 @@
       <c r="A10">
         <v>6</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="B10" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="C10" s="13" t="s">
+      <c r="C10" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="D10" s="7"/>
-      <c r="E10" s="4"/>
-      <c r="F10" s="4"/>
+      <c r="D10" s="8"/>
+      <c r="E10" s="5"/>
+      <c r="F10" s="5"/>
       <c r="G10" t="s">
         <v>25</v>
       </c>
@@ -1507,15 +1532,15 @@
       <c r="A11">
         <v>7</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="B11" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="C11" s="14" t="s">
+      <c r="C11" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="D11" s="8"/>
-      <c r="E11" s="4"/>
-      <c r="F11" s="4"/>
+      <c r="D11" s="9"/>
+      <c r="E11" s="5"/>
+      <c r="F11" s="5"/>
       <c r="G11" t="s">
         <v>25</v>
       </c>
@@ -1524,15 +1549,15 @@
       <c r="A12">
         <v>8</v>
       </c>
-      <c r="B12" s="4" t="s">
+      <c r="B12" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="C12" s="14" t="s">
+      <c r="C12" s="20" t="s">
         <v>29</v>
       </c>
-      <c r="D12" s="8"/>
-      <c r="E12" s="4"/>
-      <c r="F12" s="4"/>
+      <c r="D12" s="9"/>
+      <c r="E12" s="5"/>
+      <c r="F12" s="5"/>
       <c r="G12" t="s">
         <v>25</v>
       </c>
@@ -1541,15 +1566,15 @@
       <c r="A13">
         <v>9</v>
       </c>
-      <c r="B13" s="4" t="s">
+      <c r="B13" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="C13" s="14" t="s">
+      <c r="C13" s="20" t="s">
         <v>31</v>
       </c>
-      <c r="D13" s="8"/>
-      <c r="E13" s="4"/>
-      <c r="F13" s="4"/>
+      <c r="D13" s="9"/>
+      <c r="E13" s="5"/>
+      <c r="F13" s="5"/>
       <c r="G13" t="s">
         <v>25</v>
       </c>
@@ -1558,15 +1583,15 @@
       <c r="A14">
         <v>10</v>
       </c>
-      <c r="B14" s="4" t="s">
+      <c r="B14" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="C14" s="14" t="s">
+      <c r="C14" s="20" t="s">
         <v>33</v>
       </c>
-      <c r="D14" s="8"/>
-      <c r="E14" s="4"/>
-      <c r="F14" s="4"/>
+      <c r="D14" s="9"/>
+      <c r="E14" s="5"/>
+      <c r="F14" s="5"/>
       <c r="G14" t="s">
         <v>25</v>
       </c>
@@ -1615,7 +1640,7 @@
       <c r="B18" t="s">
         <v>38</v>
       </c>
-      <c r="C18" s="9" t="s">
+      <c r="C18" s="10" t="s">
         <v>39</v>
       </c>
       <c r="G18" t="s">
@@ -1626,7 +1651,7 @@
       <c r="A19">
         <v>15</v>
       </c>
-      <c r="B19" s="10" t="s">
+      <c r="B19" s="11" t="s">
         <v>41</v>
       </c>
       <c r="D19">
@@ -1757,7 +1782,7 @@
       <c r="B30" t="s">
         <v>59</v>
       </c>
-      <c r="C30" s="11"/>
+      <c r="C30" s="12"/>
       <c r="D30">
         <v>500</v>
       </c>
@@ -1799,10 +1824,10 @@
       </c>
     </row>
     <row r="34" customFormat="1" spans="1:3">
-      <c r="A34">
+      <c r="A34" s="13">
         <v>30</v>
       </c>
-      <c r="B34" t="s">
+      <c r="B34" s="13" t="s">
         <v>65</v>
       </c>
       <c r="C34" t="s">
@@ -1810,10 +1835,10 @@
       </c>
     </row>
     <row r="35" customFormat="1" spans="1:13">
-      <c r="A35">
+      <c r="A35" s="13">
         <v>31</v>
       </c>
-      <c r="B35" t="s">
+      <c r="B35" s="13" t="s">
         <v>67</v>
       </c>
       <c r="E35">
@@ -1843,10 +1868,10 @@
       </c>
     </row>
     <row r="36" spans="1:3">
-      <c r="A36">
+      <c r="A36" s="13">
         <v>32</v>
       </c>
-      <c r="B36" t="s">
+      <c r="B36" s="13" t="s">
         <v>72</v>
       </c>
       <c r="C36" t="s">
@@ -1854,39 +1879,39 @@
       </c>
     </row>
     <row r="37" spans="1:3">
-      <c r="A37">
+      <c r="A37" s="13">
         <v>33</v>
       </c>
-      <c r="B37" t="s">
+      <c r="B37" s="13" t="s">
         <v>74</v>
       </c>
       <c r="C37" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="38" spans="1:8">
-      <c r="A38">
+    <row r="38" s="1" customFormat="1" spans="1:8">
+      <c r="A38" s="14">
         <v>34</v>
       </c>
-      <c r="B38" t="s">
+      <c r="B38" s="15" t="s">
         <v>76</v>
       </c>
-      <c r="C38" t="s">
+      <c r="C38" s="16" t="s">
         <v>77</v>
       </c>
-      <c r="G38" t="s">
+      <c r="G38" s="16" t="s">
         <v>78</v>
       </c>
-      <c r="H38">
+      <c r="H38" s="1">
         <f>VALUE(MID(C38,FIND("_",C38)+1,4))</f>
         <v>90</v>
       </c>
     </row>
     <row r="39" spans="1:23">
-      <c r="A39">
+      <c r="A39" s="13">
         <v>35</v>
       </c>
-      <c r="B39" t="s">
+      <c r="B39" s="13" t="s">
         <v>79</v>
       </c>
       <c r="C39" t="str">
@@ -1906,10 +1931,10 @@
       <c r="J39" t="s">
         <v>81</v>
       </c>
-      <c r="K39" s="12" t="s">
+      <c r="K39" s="18" t="s">
         <v>82</v>
       </c>
-      <c r="L39" s="12">
+      <c r="L39" s="18">
         <v>0.25</v>
       </c>
       <c r="M39" t="s">
@@ -1957,10 +1982,10 @@
       </c>
     </row>
     <row r="40" spans="1:4">
-      <c r="A40">
-        <v>36</v>
-      </c>
-      <c r="B40" t="s">
+      <c r="A40" s="17">
+        <v>40</v>
+      </c>
+      <c r="B40" s="17" t="s">
         <v>84</v>
       </c>
       <c r="D40">
@@ -1968,10 +1993,10 @@
       </c>
     </row>
     <row r="41" spans="1:4">
-      <c r="A41">
-        <v>37</v>
-      </c>
-      <c r="B41" t="s">
+      <c r="A41" s="17">
+        <v>41</v>
+      </c>
+      <c r="B41" s="17" t="s">
         <v>85</v>
       </c>
       <c r="D41">
@@ -1979,10 +2004,10 @@
       </c>
     </row>
     <row r="42" spans="1:4">
-      <c r="A42">
-        <v>38</v>
-      </c>
-      <c r="B42" t="s">
+      <c r="A42" s="17">
+        <v>42</v>
+      </c>
+      <c r="B42" s="17" t="s">
         <v>86</v>
       </c>
       <c r="D42">

--- a/gm/resources/sample/global.xlsx
+++ b/gm/resources/sample/global.xlsx
@@ -264,7 +264,7 @@
     <t>1000_3000_5000</t>
   </si>
   <si>
-    <t>官方派奖转盘奖池金币数量</t>
+    <t>官方派奖转盘奖池金币数量（废弃，在活动配置表中配置）</t>
   </si>
   <si>
     <t>从OfficialAwards表中取平均中奖金额</t>
@@ -291,7 +291,7 @@
     <t>10_1</t>
   </si>
   <si>
-    <t>官方派奖：真人和机器人奖池比例(百分比)</t>
+    <t>官方派奖：真人和机器人奖池比例(百分比)  （废弃，功能不存在）</t>
   </si>
   <si>
     <t>10_90</t>
@@ -315,13 +315,13 @@
     <t>每档时间</t>
   </si>
   <si>
-    <t>积分大奖： 参与转盘每次消耗积分数</t>
-  </si>
-  <si>
-    <t>积分大奖：时段排行榜上榜的最低积分要求</t>
-  </si>
-  <si>
-    <t>积分大奖：月总排行榜上榜的最低积分要求</t>
+    <t>积分大奖： 转盘每次消耗积分数</t>
+  </si>
+  <si>
+    <t>积分大奖：时段榜-上榜的最低积分要求(上午榜、下午榜共用)</t>
+  </si>
+  <si>
+    <t>积分大奖：月总榜-上榜的最低积分要求</t>
   </si>
 </sst>
 </file>
@@ -334,10 +334,17 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0" tint="-0.25"/>
       <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -511,12 +518,24 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -844,76 +863,70 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -922,10 +935,10 @@
     <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -934,10 +947,10 @@
     <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -946,10 +959,10 @@
     <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -958,10 +971,10 @@
     <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -970,19 +983,27 @@
     <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1001,10 +1022,14 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" quotePrefix="1">
       <alignment vertical="center"/>
@@ -1345,51 +1370,51 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2" t="s">
+      <c r="B1" s="4"/>
+      <c r="C1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="4" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2" t="s">
+      <c r="B2" s="4"/>
+      <c r="C2" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="6" t="s">
         <v>6</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="G2" s="2"/>
+      <c r="G2" s="4"/>
     </row>
     <row r="3" spans="1:7">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="2"/>
-      <c r="C3" s="2" t="s">
+      <c r="B3" s="4"/>
+      <c r="C3" s="4" t="s">
         <v>11</v>
       </c>
       <c r="D3" t="s">
@@ -1401,41 +1426,41 @@
       <c r="F3" t="s">
         <v>14</v>
       </c>
-      <c r="G3" s="2"/>
+      <c r="G3" s="4"/>
     </row>
     <row r="4" spans="1:7">
-      <c r="A4" s="6"/>
-      <c r="B4" s="4"/>
-      <c r="C4" s="4"/>
-      <c r="G4" s="4"/>
+      <c r="A4" s="8"/>
+      <c r="B4" s="6"/>
+      <c r="C4" s="6"/>
+      <c r="G4" s="6"/>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
         <v>1</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="D5" s="4">
+      <c r="D5" s="6">
         <v>200</v>
       </c>
-      <c r="E5" s="4"/>
-      <c r="F5" s="4"/>
-      <c r="G5" s="4"/>
+      <c r="E5" s="6"/>
+      <c r="F5" s="6"/>
+      <c r="G5" s="6"/>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
         <v>2</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="D6" s="4">
+      <c r="D6" s="6">
         <v>10000</v>
       </c>
-      <c r="E6" s="4"/>
-      <c r="F6" s="4"/>
-      <c r="G6" s="4" t="s">
+      <c r="E6" s="6"/>
+      <c r="F6" s="6"/>
+      <c r="G6" s="6" t="s">
         <v>17</v>
       </c>
     </row>
@@ -1443,15 +1468,15 @@
       <c r="A7">
         <v>3</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="D7" s="4">
+      <c r="D7" s="6">
         <v>10000</v>
       </c>
-      <c r="E7" s="4"/>
-      <c r="F7" s="4"/>
-      <c r="G7" s="4" t="s">
+      <c r="E7" s="6"/>
+      <c r="F7" s="6"/>
+      <c r="G7" s="6" t="s">
         <v>17</v>
       </c>
     </row>
@@ -1459,16 +1484,16 @@
       <c r="A8">
         <v>4</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="C8" s="4">
+      <c r="C8" s="6">
         <v>100</v>
       </c>
-      <c r="D8" s="4"/>
-      <c r="E8" s="4"/>
-      <c r="F8" s="4"/>
-      <c r="G8" s="4" t="s">
+      <c r="D8" s="6"/>
+      <c r="E8" s="6"/>
+      <c r="F8" s="6"/>
+      <c r="G8" s="6" t="s">
         <v>20</v>
       </c>
     </row>
@@ -1490,15 +1515,15 @@
       <c r="A10">
         <v>6</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="B10" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="C10" s="13" t="s">
+      <c r="C10" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="D10" s="7"/>
-      <c r="E10" s="4"/>
-      <c r="F10" s="4"/>
+      <c r="D10" s="9"/>
+      <c r="E10" s="6"/>
+      <c r="F10" s="6"/>
       <c r="G10" t="s">
         <v>25</v>
       </c>
@@ -1507,15 +1532,15 @@
       <c r="A11">
         <v>7</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="B11" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="C11" s="14" t="s">
+      <c r="C11" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="D11" s="8"/>
-      <c r="E11" s="4"/>
-      <c r="F11" s="4"/>
+      <c r="D11" s="10"/>
+      <c r="E11" s="6"/>
+      <c r="F11" s="6"/>
       <c r="G11" t="s">
         <v>25</v>
       </c>
@@ -1524,15 +1549,15 @@
       <c r="A12">
         <v>8</v>
       </c>
-      <c r="B12" s="4" t="s">
+      <c r="B12" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="C12" s="14" t="s">
+      <c r="C12" s="20" t="s">
         <v>29</v>
       </c>
-      <c r="D12" s="8"/>
-      <c r="E12" s="4"/>
-      <c r="F12" s="4"/>
+      <c r="D12" s="10"/>
+      <c r="E12" s="6"/>
+      <c r="F12" s="6"/>
       <c r="G12" t="s">
         <v>25</v>
       </c>
@@ -1541,15 +1566,15 @@
       <c r="A13">
         <v>9</v>
       </c>
-      <c r="B13" s="4" t="s">
+      <c r="B13" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="C13" s="14" t="s">
+      <c r="C13" s="20" t="s">
         <v>31</v>
       </c>
-      <c r="D13" s="8"/>
-      <c r="E13" s="4"/>
-      <c r="F13" s="4"/>
+      <c r="D13" s="10"/>
+      <c r="E13" s="6"/>
+      <c r="F13" s="6"/>
       <c r="G13" t="s">
         <v>25</v>
       </c>
@@ -1558,15 +1583,15 @@
       <c r="A14">
         <v>10</v>
       </c>
-      <c r="B14" s="4" t="s">
+      <c r="B14" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="C14" s="14" t="s">
+      <c r="C14" s="20" t="s">
         <v>33</v>
       </c>
-      <c r="D14" s="8"/>
-      <c r="E14" s="4"/>
-      <c r="F14" s="4"/>
+      <c r="D14" s="10"/>
+      <c r="E14" s="6"/>
+      <c r="F14" s="6"/>
       <c r="G14" t="s">
         <v>25</v>
       </c>
@@ -1615,7 +1640,7 @@
       <c r="B18" t="s">
         <v>38</v>
       </c>
-      <c r="C18" s="9" t="s">
+      <c r="C18" s="11" t="s">
         <v>39</v>
       </c>
       <c r="G18" t="s">
@@ -1626,7 +1651,7 @@
       <c r="A19">
         <v>15</v>
       </c>
-      <c r="B19" s="10" t="s">
+      <c r="B19" s="12" t="s">
         <v>41</v>
       </c>
       <c r="D19">
@@ -1757,7 +1782,7 @@
       <c r="B30" t="s">
         <v>59</v>
       </c>
-      <c r="C30" s="11"/>
+      <c r="C30" s="13"/>
       <c r="D30">
         <v>500</v>
       </c>
@@ -1799,54 +1824,54 @@
       </c>
     </row>
     <row r="34" customFormat="1" spans="1:3">
-      <c r="A34">
+      <c r="A34" s="14">
         <v>30</v>
       </c>
-      <c r="B34" t="s">
+      <c r="B34" s="14" t="s">
         <v>65</v>
       </c>
       <c r="C34" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="35" customFormat="1" spans="1:13">
-      <c r="A35">
+    <row r="35" s="1" customFormat="1" spans="1:13">
+      <c r="A35" s="15">
         <v>31</v>
       </c>
-      <c r="B35" t="s">
+      <c r="B35" s="16" t="s">
         <v>67</v>
       </c>
-      <c r="E35">
+      <c r="E35" s="1">
         <v>1000000000</v>
       </c>
-      <c r="G35" t="s">
+      <c r="G35" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="H35">
+      <c r="H35" s="1">
         <v>718000</v>
       </c>
-      <c r="I35" t="s">
+      <c r="I35" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="J35">
+      <c r="J35" s="1">
         <v>30</v>
       </c>
-      <c r="K35" t="s">
+      <c r="K35" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="L35">
+      <c r="L35" s="1">
         <f>J35*24*60*60*1000</f>
         <v>2592000000</v>
       </c>
-      <c r="M35" t="s">
+      <c r="M35" s="2" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="36" spans="1:3">
-      <c r="A36">
+      <c r="A36" s="14">
         <v>32</v>
       </c>
-      <c r="B36" t="s">
+      <c r="B36" s="14" t="s">
         <v>72</v>
       </c>
       <c r="C36" t="s">
@@ -1854,39 +1879,39 @@
       </c>
     </row>
     <row r="37" spans="1:3">
-      <c r="A37">
+      <c r="A37" s="14">
         <v>33</v>
       </c>
-      <c r="B37" t="s">
+      <c r="B37" s="14" t="s">
         <v>74</v>
       </c>
       <c r="C37" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="38" spans="1:8">
-      <c r="A38">
+    <row r="38" s="2" customFormat="1" spans="1:8">
+      <c r="A38" s="16">
         <v>34</v>
       </c>
-      <c r="B38" t="s">
+      <c r="B38" s="16" t="s">
         <v>76</v>
       </c>
-      <c r="C38" t="s">
+      <c r="C38" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="G38" t="s">
+      <c r="G38" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="H38">
+      <c r="H38" s="2">
         <f>VALUE(MID(C38,FIND("_",C38)+1,4))</f>
         <v>90</v>
       </c>
     </row>
     <row r="39" spans="1:23">
-      <c r="A39">
+      <c r="A39" s="14">
         <v>35</v>
       </c>
-      <c r="B39" t="s">
+      <c r="B39" s="14" t="s">
         <v>79</v>
       </c>
       <c r="C39" t="str">
@@ -1906,10 +1931,10 @@
       <c r="J39" t="s">
         <v>81</v>
       </c>
-      <c r="K39" s="12" t="s">
+      <c r="K39" s="18" t="s">
         <v>82</v>
       </c>
-      <c r="L39" s="12">
+      <c r="L39" s="18">
         <v>0.25</v>
       </c>
       <c r="M39" t="s">
@@ -1957,10 +1982,10 @@
       </c>
     </row>
     <row r="40" spans="1:4">
-      <c r="A40">
-        <v>36</v>
-      </c>
-      <c r="B40" t="s">
+      <c r="A40" s="17">
+        <v>40</v>
+      </c>
+      <c r="B40" s="17" t="s">
         <v>84</v>
       </c>
       <c r="D40">
@@ -1968,10 +1993,10 @@
       </c>
     </row>
     <row r="41" spans="1:4">
-      <c r="A41">
-        <v>37</v>
-      </c>
-      <c r="B41" t="s">
+      <c r="A41" s="17">
+        <v>41</v>
+      </c>
+      <c r="B41" s="17" t="s">
         <v>85</v>
       </c>
       <c r="D41">
@@ -1979,10 +2004,10 @@
       </c>
     </row>
     <row r="42" spans="1:4">
-      <c r="A42">
-        <v>38</v>
-      </c>
-      <c r="B42" t="s">
+      <c r="A42" s="17">
+        <v>42</v>
+      </c>
+      <c r="B42" s="17" t="s">
         <v>86</v>
       </c>
       <c r="D42">

--- a/gm/resources/sample/global.xlsx
+++ b/gm/resources/sample/global.xlsx
@@ -264,7 +264,7 @@
     <t>1000_3000_5000</t>
   </si>
   <si>
-    <t>官方派奖转盘奖池金币数量</t>
+    <t>官方派奖转盘奖池金币数量（废弃，在活动配置表中配置）</t>
   </si>
   <si>
     <t>从OfficialAwards表中取平均中奖金额</t>
@@ -291,7 +291,7 @@
     <t>10_1</t>
   </si>
   <si>
-    <t>官方派奖：真人和机器人奖池比例(百分比)  废弃</t>
+    <t>官方派奖：真人和机器人奖池比例(百分比)  （废弃，功能不存在）</t>
   </si>
   <si>
     <t>10_90</t>
@@ -996,6 +996,7 @@
   <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1028,7 +1029,6 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" quotePrefix="1">
@@ -1370,51 +1370,51 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3" t="s">
+      <c r="B1" s="4"/>
+      <c r="C1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="4" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3" t="s">
+      <c r="B2" s="4"/>
+      <c r="C2" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="6" t="s">
         <v>6</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="F2" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="G2" s="3"/>
+      <c r="G2" s="4"/>
     </row>
     <row r="3" spans="1:7">
-      <c r="A3" s="6" t="s">
+      <c r="A3" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="3"/>
-      <c r="C3" s="3" t="s">
+      <c r="B3" s="4"/>
+      <c r="C3" s="4" t="s">
         <v>11</v>
       </c>
       <c r="D3" t="s">
@@ -1426,41 +1426,41 @@
       <c r="F3" t="s">
         <v>14</v>
       </c>
-      <c r="G3" s="3"/>
+      <c r="G3" s="4"/>
     </row>
     <row r="4" spans="1:7">
-      <c r="A4" s="7"/>
-      <c r="B4" s="5"/>
-      <c r="C4" s="5"/>
-      <c r="G4" s="5"/>
+      <c r="A4" s="8"/>
+      <c r="B4" s="6"/>
+      <c r="C4" s="6"/>
+      <c r="G4" s="6"/>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
         <v>1</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="D5" s="5">
+      <c r="D5" s="6">
         <v>200</v>
       </c>
-      <c r="E5" s="5"/>
-      <c r="F5" s="5"/>
-      <c r="G5" s="5"/>
+      <c r="E5" s="6"/>
+      <c r="F5" s="6"/>
+      <c r="G5" s="6"/>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
         <v>2</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="D6" s="5">
+      <c r="D6" s="6">
         <v>10000</v>
       </c>
-      <c r="E6" s="5"/>
-      <c r="F6" s="5"/>
-      <c r="G6" s="5" t="s">
+      <c r="E6" s="6"/>
+      <c r="F6" s="6"/>
+      <c r="G6" s="6" t="s">
         <v>17</v>
       </c>
     </row>
@@ -1468,15 +1468,15 @@
       <c r="A7">
         <v>3</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="D7" s="5">
+      <c r="D7" s="6">
         <v>10000</v>
       </c>
-      <c r="E7" s="5"/>
-      <c r="F7" s="5"/>
-      <c r="G7" s="5" t="s">
+      <c r="E7" s="6"/>
+      <c r="F7" s="6"/>
+      <c r="G7" s="6" t="s">
         <v>17</v>
       </c>
     </row>
@@ -1484,16 +1484,16 @@
       <c r="A8">
         <v>4</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="C8" s="5">
+      <c r="C8" s="6">
         <v>100</v>
       </c>
-      <c r="D8" s="5"/>
-      <c r="E8" s="5"/>
-      <c r="F8" s="5"/>
-      <c r="G8" s="5" t="s">
+      <c r="D8" s="6"/>
+      <c r="E8" s="6"/>
+      <c r="F8" s="6"/>
+      <c r="G8" s="6" t="s">
         <v>20</v>
       </c>
     </row>
@@ -1515,15 +1515,15 @@
       <c r="A10">
         <v>6</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="6" t="s">
         <v>23</v>
       </c>
       <c r="C10" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="D10" s="8"/>
-      <c r="E10" s="5"/>
-      <c r="F10" s="5"/>
+      <c r="D10" s="9"/>
+      <c r="E10" s="6"/>
+      <c r="F10" s="6"/>
       <c r="G10" t="s">
         <v>25</v>
       </c>
@@ -1532,15 +1532,15 @@
       <c r="A11">
         <v>7</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="6" t="s">
         <v>26</v>
       </c>
       <c r="C11" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="D11" s="9"/>
-      <c r="E11" s="5"/>
-      <c r="F11" s="5"/>
+      <c r="D11" s="10"/>
+      <c r="E11" s="6"/>
+      <c r="F11" s="6"/>
       <c r="G11" t="s">
         <v>25</v>
       </c>
@@ -1549,15 +1549,15 @@
       <c r="A12">
         <v>8</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B12" s="6" t="s">
         <v>28</v>
       </c>
       <c r="C12" s="20" t="s">
         <v>29</v>
       </c>
-      <c r="D12" s="9"/>
-      <c r="E12" s="5"/>
-      <c r="F12" s="5"/>
+      <c r="D12" s="10"/>
+      <c r="E12" s="6"/>
+      <c r="F12" s="6"/>
       <c r="G12" t="s">
         <v>25</v>
       </c>
@@ -1566,15 +1566,15 @@
       <c r="A13">
         <v>9</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B13" s="6" t="s">
         <v>30</v>
       </c>
       <c r="C13" s="20" t="s">
         <v>31</v>
       </c>
-      <c r="D13" s="9"/>
-      <c r="E13" s="5"/>
-      <c r="F13" s="5"/>
+      <c r="D13" s="10"/>
+      <c r="E13" s="6"/>
+      <c r="F13" s="6"/>
       <c r="G13" t="s">
         <v>25</v>
       </c>
@@ -1583,15 +1583,15 @@
       <c r="A14">
         <v>10</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="B14" s="6" t="s">
         <v>32</v>
       </c>
       <c r="C14" s="20" t="s">
         <v>33</v>
       </c>
-      <c r="D14" s="9"/>
-      <c r="E14" s="5"/>
-      <c r="F14" s="5"/>
+      <c r="D14" s="10"/>
+      <c r="E14" s="6"/>
+      <c r="F14" s="6"/>
       <c r="G14" t="s">
         <v>25</v>
       </c>
@@ -1640,7 +1640,7 @@
       <c r="B18" t="s">
         <v>38</v>
       </c>
-      <c r="C18" s="10" t="s">
+      <c r="C18" s="11" t="s">
         <v>39</v>
       </c>
       <c r="G18" t="s">
@@ -1651,7 +1651,7 @@
       <c r="A19">
         <v>15</v>
       </c>
-      <c r="B19" s="11" t="s">
+      <c r="B19" s="12" t="s">
         <v>41</v>
       </c>
       <c r="D19">
@@ -1782,7 +1782,7 @@
       <c r="B30" t="s">
         <v>59</v>
       </c>
-      <c r="C30" s="12"/>
+      <c r="C30" s="13"/>
       <c r="D30">
         <v>500</v>
       </c>
@@ -1824,54 +1824,54 @@
       </c>
     </row>
     <row r="34" customFormat="1" spans="1:3">
-      <c r="A34" s="13">
+      <c r="A34" s="14">
         <v>30</v>
       </c>
-      <c r="B34" s="13" t="s">
+      <c r="B34" s="14" t="s">
         <v>65</v>
       </c>
       <c r="C34" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="35" customFormat="1" spans="1:13">
-      <c r="A35" s="13">
+    <row r="35" s="1" customFormat="1" spans="1:13">
+      <c r="A35" s="15">
         <v>31</v>
       </c>
-      <c r="B35" s="13" t="s">
+      <c r="B35" s="16" t="s">
         <v>67</v>
       </c>
-      <c r="E35">
+      <c r="E35" s="1">
         <v>1000000000</v>
       </c>
-      <c r="G35" t="s">
+      <c r="G35" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="H35">
+      <c r="H35" s="1">
         <v>718000</v>
       </c>
-      <c r="I35" t="s">
+      <c r="I35" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="J35">
+      <c r="J35" s="1">
         <v>30</v>
       </c>
-      <c r="K35" t="s">
+      <c r="K35" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="L35">
+      <c r="L35" s="1">
         <f>J35*24*60*60*1000</f>
         <v>2592000000</v>
       </c>
-      <c r="M35" t="s">
+      <c r="M35" s="2" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="36" spans="1:3">
-      <c r="A36" s="13">
+      <c r="A36" s="14">
         <v>32</v>
       </c>
-      <c r="B36" s="13" t="s">
+      <c r="B36" s="14" t="s">
         <v>72</v>
       </c>
       <c r="C36" t="s">
@@ -1879,39 +1879,39 @@
       </c>
     </row>
     <row r="37" spans="1:3">
-      <c r="A37" s="13">
+      <c r="A37" s="14">
         <v>33</v>
       </c>
-      <c r="B37" s="13" t="s">
+      <c r="B37" s="14" t="s">
         <v>74</v>
       </c>
       <c r="C37" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="38" s="1" customFormat="1" spans="1:8">
-      <c r="A38" s="14">
+    <row r="38" s="2" customFormat="1" spans="1:8">
+      <c r="A38" s="16">
         <v>34</v>
       </c>
-      <c r="B38" s="15" t="s">
+      <c r="B38" s="16" t="s">
         <v>76</v>
       </c>
-      <c r="C38" s="16" t="s">
+      <c r="C38" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="G38" s="16" t="s">
+      <c r="G38" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="H38" s="1">
+      <c r="H38" s="2">
         <f>VALUE(MID(C38,FIND("_",C38)+1,4))</f>
         <v>90</v>
       </c>
     </row>
     <row r="39" spans="1:23">
-      <c r="A39" s="13">
+      <c r="A39" s="14">
         <v>35</v>
       </c>
-      <c r="B39" s="13" t="s">
+      <c r="B39" s="14" t="s">
         <v>79</v>
       </c>
       <c r="C39" t="str">

--- a/gm/resources/sample/global.xlsx
+++ b/gm/resources/sample/global.xlsx
@@ -993,9 +993,8 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1027,7 +1026,6 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1370,51 +1368,51 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4" t="s">
+      <c r="B1" s="3"/>
+      <c r="C1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="3" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="4"/>
-      <c r="C2" s="4" t="s">
+      <c r="B2" s="3"/>
+      <c r="C2" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" s="5" t="s">
         <v>6</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="F2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="G2" s="4"/>
+      <c r="G2" s="3"/>
     </row>
     <row r="3" spans="1:7">
-      <c r="A3" s="7" t="s">
+      <c r="A3" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="4"/>
-      <c r="C3" s="4" t="s">
+      <c r="B3" s="3"/>
+      <c r="C3" s="3" t="s">
         <v>11</v>
       </c>
       <c r="D3" t="s">
@@ -1426,41 +1424,41 @@
       <c r="F3" t="s">
         <v>14</v>
       </c>
-      <c r="G3" s="4"/>
+      <c r="G3" s="3"/>
     </row>
     <row r="4" spans="1:7">
-      <c r="A4" s="8"/>
-      <c r="B4" s="6"/>
-      <c r="C4" s="6"/>
-      <c r="G4" s="6"/>
+      <c r="A4" s="7"/>
+      <c r="B4" s="5"/>
+      <c r="C4" s="5"/>
+      <c r="G4" s="5"/>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
         <v>1</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="D5" s="6">
+      <c r="D5" s="5">
         <v>200</v>
       </c>
-      <c r="E5" s="6"/>
-      <c r="F5" s="6"/>
-      <c r="G5" s="6"/>
+      <c r="E5" s="5"/>
+      <c r="F5" s="5"/>
+      <c r="G5" s="5"/>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
         <v>2</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="D6" s="6">
+      <c r="D6" s="5">
         <v>10000</v>
       </c>
-      <c r="E6" s="6"/>
-      <c r="F6" s="6"/>
-      <c r="G6" s="6" t="s">
+      <c r="E6" s="5"/>
+      <c r="F6" s="5"/>
+      <c r="G6" s="5" t="s">
         <v>17</v>
       </c>
     </row>
@@ -1468,15 +1466,15 @@
       <c r="A7">
         <v>3</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="D7" s="6">
+      <c r="D7" s="5">
         <v>10000</v>
       </c>
-      <c r="E7" s="6"/>
-      <c r="F7" s="6"/>
-      <c r="G7" s="6" t="s">
+      <c r="E7" s="5"/>
+      <c r="F7" s="5"/>
+      <c r="G7" s="5" t="s">
         <v>17</v>
       </c>
     </row>
@@ -1484,16 +1482,16 @@
       <c r="A8">
         <v>4</v>
       </c>
-      <c r="B8" s="6" t="s">
+      <c r="B8" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="C8" s="6">
+      <c r="C8" s="5">
         <v>100</v>
       </c>
-      <c r="D8" s="6"/>
-      <c r="E8" s="6"/>
-      <c r="F8" s="6"/>
-      <c r="G8" s="6" t="s">
+      <c r="D8" s="5"/>
+      <c r="E8" s="5"/>
+      <c r="F8" s="5"/>
+      <c r="G8" s="5" t="s">
         <v>20</v>
       </c>
     </row>
@@ -1515,15 +1513,15 @@
       <c r="A10">
         <v>6</v>
       </c>
-      <c r="B10" s="6" t="s">
+      <c r="B10" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="C10" s="19" t="s">
+      <c r="C10" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="D10" s="9"/>
-      <c r="E10" s="6"/>
-      <c r="F10" s="6"/>
+      <c r="D10" s="8"/>
+      <c r="E10" s="5"/>
+      <c r="F10" s="5"/>
       <c r="G10" t="s">
         <v>25</v>
       </c>
@@ -1532,15 +1530,15 @@
       <c r="A11">
         <v>7</v>
       </c>
-      <c r="B11" s="6" t="s">
+      <c r="B11" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="C11" s="20" t="s">
+      <c r="C11" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="D11" s="10"/>
-      <c r="E11" s="6"/>
-      <c r="F11" s="6"/>
+      <c r="D11" s="9"/>
+      <c r="E11" s="5"/>
+      <c r="F11" s="5"/>
       <c r="G11" t="s">
         <v>25</v>
       </c>
@@ -1549,15 +1547,15 @@
       <c r="A12">
         <v>8</v>
       </c>
-      <c r="B12" s="6" t="s">
+      <c r="B12" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="C12" s="20" t="s">
+      <c r="C12" s="18" t="s">
         <v>29</v>
       </c>
-      <c r="D12" s="10"/>
-      <c r="E12" s="6"/>
-      <c r="F12" s="6"/>
+      <c r="D12" s="9"/>
+      <c r="E12" s="5"/>
+      <c r="F12" s="5"/>
       <c r="G12" t="s">
         <v>25</v>
       </c>
@@ -1566,15 +1564,15 @@
       <c r="A13">
         <v>9</v>
       </c>
-      <c r="B13" s="6" t="s">
+      <c r="B13" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="C13" s="20" t="s">
+      <c r="C13" s="18" t="s">
         <v>31</v>
       </c>
-      <c r="D13" s="10"/>
-      <c r="E13" s="6"/>
-      <c r="F13" s="6"/>
+      <c r="D13" s="9"/>
+      <c r="E13" s="5"/>
+      <c r="F13" s="5"/>
       <c r="G13" t="s">
         <v>25</v>
       </c>
@@ -1583,15 +1581,15 @@
       <c r="A14">
         <v>10</v>
       </c>
-      <c r="B14" s="6" t="s">
+      <c r="B14" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="C14" s="20" t="s">
+      <c r="C14" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="D14" s="10"/>
-      <c r="E14" s="6"/>
-      <c r="F14" s="6"/>
+      <c r="D14" s="9"/>
+      <c r="E14" s="5"/>
+      <c r="F14" s="5"/>
       <c r="G14" t="s">
         <v>25</v>
       </c>
@@ -1640,7 +1638,7 @@
       <c r="B18" t="s">
         <v>38</v>
       </c>
-      <c r="C18" s="11" t="s">
+      <c r="C18" s="10" t="s">
         <v>39</v>
       </c>
       <c r="G18" t="s">
@@ -1651,7 +1649,7 @@
       <c r="A19">
         <v>15</v>
       </c>
-      <c r="B19" s="12" t="s">
+      <c r="B19" s="11" t="s">
         <v>41</v>
       </c>
       <c r="D19">
@@ -1782,9 +1780,9 @@
       <c r="B30" t="s">
         <v>59</v>
       </c>
-      <c r="C30" s="13"/>
+      <c r="C30" s="12"/>
       <c r="D30">
-        <v>500</v>
+        <v>100</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1824,10 +1822,10 @@
       </c>
     </row>
     <row r="34" customFormat="1" spans="1:3">
-      <c r="A34" s="14">
+      <c r="A34" s="13">
         <v>30</v>
       </c>
-      <c r="B34" s="14" t="s">
+      <c r="B34" s="13" t="s">
         <v>65</v>
       </c>
       <c r="C34" t="s">
@@ -1835,43 +1833,43 @@
       </c>
     </row>
     <row r="35" s="1" customFormat="1" spans="1:13">
-      <c r="A35" s="15">
+      <c r="A35" s="14">
         <v>31</v>
       </c>
-      <c r="B35" s="16" t="s">
+      <c r="B35" s="14" t="s">
         <v>67</v>
       </c>
       <c r="E35" s="1">
         <v>1000000000</v>
       </c>
-      <c r="G35" s="2" t="s">
+      <c r="G35" s="1" t="s">
         <v>68</v>
       </c>
       <c r="H35" s="1">
         <v>718000</v>
       </c>
-      <c r="I35" s="2" t="s">
+      <c r="I35" s="1" t="s">
         <v>69</v>
       </c>
       <c r="J35" s="1">
         <v>30</v>
       </c>
-      <c r="K35" s="2" t="s">
+      <c r="K35" s="1" t="s">
         <v>70</v>
       </c>
       <c r="L35" s="1">
         <f>J35*24*60*60*1000</f>
         <v>2592000000</v>
       </c>
-      <c r="M35" s="2" t="s">
+      <c r="M35" s="1" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="36" spans="1:3">
-      <c r="A36" s="14">
+      <c r="A36" s="13">
         <v>32</v>
       </c>
-      <c r="B36" s="14" t="s">
+      <c r="B36" s="13" t="s">
         <v>72</v>
       </c>
       <c r="C36" t="s">
@@ -1879,39 +1877,39 @@
       </c>
     </row>
     <row r="37" spans="1:3">
-      <c r="A37" s="14">
+      <c r="A37" s="13">
         <v>33</v>
       </c>
-      <c r="B37" s="14" t="s">
+      <c r="B37" s="13" t="s">
         <v>74</v>
       </c>
       <c r="C37" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="38" s="2" customFormat="1" spans="1:8">
-      <c r="A38" s="16">
+    <row r="38" s="1" customFormat="1" spans="1:8">
+      <c r="A38" s="14">
         <v>34</v>
       </c>
-      <c r="B38" s="16" t="s">
+      <c r="B38" s="14" t="s">
         <v>76</v>
       </c>
-      <c r="C38" s="2" t="s">
+      <c r="C38" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="G38" s="2" t="s">
+      <c r="G38" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="H38" s="2">
+      <c r="H38" s="1">
         <f>VALUE(MID(C38,FIND("_",C38)+1,4))</f>
         <v>90</v>
       </c>
     </row>
     <row r="39" spans="1:23">
-      <c r="A39" s="14">
+      <c r="A39" s="13">
         <v>35</v>
       </c>
-      <c r="B39" s="14" t="s">
+      <c r="B39" s="13" t="s">
         <v>79</v>
       </c>
       <c r="C39" t="str">
@@ -1931,10 +1929,10 @@
       <c r="J39" t="s">
         <v>81</v>
       </c>
-      <c r="K39" s="18" t="s">
+      <c r="K39" s="16" t="s">
         <v>82</v>
       </c>
-      <c r="L39" s="18">
+      <c r="L39" s="16">
         <v>0.25</v>
       </c>
       <c r="M39" t="s">
@@ -1982,10 +1980,10 @@
       </c>
     </row>
     <row r="40" spans="1:4">
-      <c r="A40" s="17">
+      <c r="A40" s="15">
         <v>40</v>
       </c>
-      <c r="B40" s="17" t="s">
+      <c r="B40" s="15" t="s">
         <v>84</v>
       </c>
       <c r="D40">
@@ -1993,10 +1991,10 @@
       </c>
     </row>
     <row r="41" spans="1:4">
-      <c r="A41" s="17">
+      <c r="A41" s="15">
         <v>41</v>
       </c>
-      <c r="B41" s="17" t="s">
+      <c r="B41" s="15" t="s">
         <v>85</v>
       </c>
       <c r="D41">
@@ -2004,10 +2002,10 @@
       </c>
     </row>
     <row r="42" spans="1:4">
-      <c r="A42" s="17">
+      <c r="A42" s="15">
         <v>42</v>
       </c>
-      <c r="B42" s="17" t="s">
+      <c r="B42" s="15" t="s">
         <v>86</v>
       </c>
       <c r="D42">

--- a/gm/resources/sample/global.xlsx
+++ b/gm/resources/sample/global.xlsx
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="88">
   <si>
     <t>sid</t>
   </si>
@@ -322,6 +322,9 @@
   </si>
   <si>
     <t>积分大奖：月总榜-上榜的最低积分要求</t>
+  </si>
+  <si>
+    <t>积分大奖：每日转盘默认次数上限</t>
   </si>
 </sst>
 </file>
@@ -1354,7 +1357,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:W42"/>
+  <dimension ref="A1:W43"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="2" max="2" width="65.375" customWidth="1"/>
@@ -2012,6 +2015,17 @@
         <v>2000</v>
       </c>
     </row>
+    <row r="43" spans="1:4">
+      <c r="A43" s="15">
+        <v>43</v>
+      </c>
+      <c r="B43" s="15" t="s">
+        <v>87</v>
+      </c>
+      <c r="D43">
+        <v>10</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/gm/resources/sample/global.xlsx
+++ b/gm/resources/sample/global.xlsx
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="91">
   <si>
     <t>sid</t>
   </si>
@@ -325,6 +325,15 @@
   </si>
   <si>
     <t>积分大奖：每日转盘默认次数上限</t>
+  </si>
+  <si>
+    <t>积分大奖：充值多少金额给一次转盘次数</t>
+  </si>
+  <si>
+    <t>积分大奖：积分保底奖励</t>
+  </si>
+  <si>
+    <t>1000_1990000_200000|2000_1990000_500000|5000_1990000_1000000|8000_1990000_1500000|10000_1990000_2000000</t>
   </si>
 </sst>
 </file>
@@ -1357,7 +1366,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:W43"/>
+  <dimension ref="A1:W45"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="2" max="2" width="65.375" customWidth="1"/>
@@ -2026,6 +2035,29 @@
         <v>10</v>
       </c>
     </row>
+    <row r="44" spans="1:4">
+      <c r="A44" s="15">
+        <v>44</v>
+      </c>
+      <c r="B44" t="s">
+        <v>88</v>
+      </c>
+      <c r="C44"/>
+      <c r="D44">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3">
+      <c r="A45" s="15">
+        <v>45</v>
+      </c>
+      <c r="B45" t="s">
+        <v>89</v>
+      </c>
+      <c r="C45" t="s">
+        <v>90</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/gm/resources/sample/global.xlsx
+++ b/gm/resources/sample/global.xlsx
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="93">
   <si>
     <t>sid</t>
   </si>
@@ -330,10 +330,16 @@
     <t>积分大奖：充值多少金额给一次转盘次数</t>
   </si>
   <si>
-    <t>积分大奖：积分保底奖励</t>
+    <t>积分大奖：积分保底奖励（积分数量_奖励道具ID_奖励道具数量）</t>
   </si>
   <si>
     <t>1000_1990000_200000|2000_1990000_500000|5000_1990000_1000000|8000_1990000_1500000|10000_1990000_2000000</t>
+  </si>
+  <si>
+    <t>VIP充值：充值金额与经验转换比例(充值金额_获得vip经验，最低支持0.01_1)</t>
+  </si>
+  <si>
+    <t>1000_1</t>
   </si>
 </sst>
 </file>
@@ -1366,7 +1372,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:W45"/>
+  <dimension ref="A1:W46"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="2" max="2" width="65.375" customWidth="1"/>
@@ -2042,7 +2048,6 @@
       <c r="B44" t="s">
         <v>88</v>
       </c>
-      <c r="C44"/>
       <c r="D44">
         <v>1000</v>
       </c>
@@ -2056,6 +2061,17 @@
       </c>
       <c r="C45" t="s">
         <v>90</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3">
+      <c r="A46">
+        <v>46</v>
+      </c>
+      <c r="B46" t="s">
+        <v>91</v>
+      </c>
+      <c r="C46" t="s">
+        <v>92</v>
       </c>
     </row>
   </sheetData>

--- a/gm/resources/sample/global.xlsx
+++ b/gm/resources/sample/global.xlsx
@@ -56,12 +56,34 @@
         </r>
       </text>
     </comment>
+    <comment ref="D47" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+配置 dropConfig.xlsx 中的 id 值</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="94">
   <si>
     <t>sid</t>
   </si>
@@ -340,6 +362,9 @@
   </si>
   <si>
     <t>1000_1</t>
+  </si>
+  <si>
+    <t>掉落1001-1999【我的赌场】</t>
   </si>
 </sst>
 </file>
@@ -362,22 +387,20 @@
     </font>
     <font>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="0" tint="-0.25"/>
-      <name val="等线"/>
+      <name val="微软雅黑"/>
       <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
       <color theme="1"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
+      <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1011,46 +1034,50 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" quotePrefix="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" quotePrefix="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" quotePrefix="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" quotePrefix="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1372,706 +1399,724 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:W46"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
+  <dimension ref="A1:W47"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
-    <col min="2" max="2" width="65.375" customWidth="1"/>
-    <col min="3" max="3" width="37.625" customWidth="1"/>
-    <col min="4" max="4" width="9.375" customWidth="1"/>
-    <col min="5" max="5" width="11.5" customWidth="1"/>
-    <col min="6" max="6" width="9.625" customWidth="1"/>
-    <col min="7" max="7" width="23.375" customWidth="1"/>
-    <col min="10" max="10" width="11.5"/>
-    <col min="12" max="12" width="11.5"/>
+    <col min="1" max="1" width="9" style="1"/>
+    <col min="2" max="2" width="65.375" style="1" customWidth="1"/>
+    <col min="3" max="3" width="37.625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="9.375" style="1" customWidth="1"/>
+    <col min="5" max="5" width="11.5" style="1" customWidth="1"/>
+    <col min="6" max="6" width="9.625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="23.375" style="1" customWidth="1"/>
+    <col min="8" max="8" width="9.25" style="1"/>
+    <col min="9" max="9" width="9" style="1"/>
+    <col min="10" max="10" width="11.5" style="1"/>
+    <col min="11" max="11" width="9" style="1"/>
+    <col min="12" max="12" width="12.875" style="1"/>
+    <col min="13" max="13" width="9" style="1"/>
+    <col min="14" max="18" width="9.25" style="1"/>
+    <col min="19" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3" t="s">
+      <c r="B1" s="4"/>
+      <c r="C1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="5" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3" t="s">
+      <c r="B2" s="4"/>
+      <c r="C2" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="F2" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="G2" s="3"/>
+      <c r="G2" s="4"/>
     </row>
     <row r="3" spans="1:7">
-      <c r="A3" s="6" t="s">
+      <c r="A3" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="3"/>
-      <c r="C3" s="3" t="s">
+      <c r="B3" s="4"/>
+      <c r="C3" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E3" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="F3" t="s">
+      <c r="F3" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="G3" s="3"/>
+      <c r="G3" s="4"/>
     </row>
     <row r="4" spans="1:7">
-      <c r="A4" s="7"/>
-      <c r="B4" s="5"/>
-      <c r="C4" s="5"/>
-      <c r="G4" s="5"/>
+      <c r="A4" s="9"/>
+      <c r="B4" s="10"/>
+      <c r="C4" s="10"/>
+      <c r="G4" s="10"/>
     </row>
     <row r="5" spans="1:7">
-      <c r="A5">
+      <c r="A5" s="1">
         <v>1</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="D5" s="5">
+      <c r="D5" s="10">
         <v>200</v>
       </c>
-      <c r="E5" s="5"/>
-      <c r="F5" s="5"/>
-      <c r="G5" s="5"/>
+      <c r="E5" s="10"/>
+      <c r="F5" s="10"/>
+      <c r="G5" s="10"/>
     </row>
     <row r="6" spans="1:7">
-      <c r="A6">
+      <c r="A6" s="1">
         <v>2</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="D6" s="5">
+      <c r="D6" s="10">
         <v>10000</v>
       </c>
-      <c r="E6" s="5"/>
-      <c r="F6" s="5"/>
-      <c r="G6" s="5" t="s">
+      <c r="E6" s="10"/>
+      <c r="F6" s="10"/>
+      <c r="G6" s="7" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="7" spans="1:7">
-      <c r="A7">
+      <c r="A7" s="1">
         <v>3</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="D7" s="5">
+      <c r="D7" s="10">
         <v>10000</v>
       </c>
-      <c r="E7" s="5"/>
-      <c r="F7" s="5"/>
-      <c r="G7" s="5" t="s">
+      <c r="E7" s="10"/>
+      <c r="F7" s="10"/>
+      <c r="G7" s="7" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="8" spans="1:7">
-      <c r="A8">
+      <c r="A8" s="1">
         <v>4</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="C8" s="5">
+      <c r="C8" s="10">
         <v>100</v>
       </c>
-      <c r="D8" s="5"/>
-      <c r="E8" s="5"/>
-      <c r="F8" s="5"/>
-      <c r="G8" s="5" t="s">
+      <c r="D8" s="10"/>
+      <c r="E8" s="10"/>
+      <c r="F8" s="10"/>
+      <c r="G8" s="7" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="9" spans="1:7">
-      <c r="A9">
+      <c r="A9" s="1">
         <v>5</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="C9">
+      <c r="C9" s="1">
         <v>4</v>
       </c>
-      <c r="G9" t="s">
+      <c r="G9" s="8" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="10" spans="1:7">
-      <c r="A10">
+      <c r="A10" s="1">
         <v>6</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="C10" s="17" t="s">
+      <c r="C10" s="21" t="s">
         <v>24</v>
       </c>
-      <c r="D10" s="8"/>
-      <c r="E10" s="5"/>
-      <c r="F10" s="5"/>
-      <c r="G10" t="s">
+      <c r="D10" s="11"/>
+      <c r="E10" s="10"/>
+      <c r="F10" s="10"/>
+      <c r="G10" s="8" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="11" spans="1:7">
-      <c r="A11">
+      <c r="A11" s="1">
         <v>7</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="C11" s="18" t="s">
+      <c r="C11" s="22" t="s">
         <v>27</v>
       </c>
-      <c r="D11" s="9"/>
-      <c r="E11" s="5"/>
-      <c r="F11" s="5"/>
-      <c r="G11" t="s">
+      <c r="D11" s="7"/>
+      <c r="E11" s="10"/>
+      <c r="F11" s="10"/>
+      <c r="G11" s="8" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="12" spans="1:7">
-      <c r="A12">
+      <c r="A12" s="1">
         <v>8</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B12" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="C12" s="18" t="s">
+      <c r="C12" s="22" t="s">
         <v>29</v>
       </c>
-      <c r="D12" s="9"/>
-      <c r="E12" s="5"/>
-      <c r="F12" s="5"/>
-      <c r="G12" t="s">
+      <c r="D12" s="7"/>
+      <c r="E12" s="10"/>
+      <c r="F12" s="10"/>
+      <c r="G12" s="8" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="13" spans="1:7">
-      <c r="A13">
+      <c r="A13" s="1">
         <v>9</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B13" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="C13" s="18" t="s">
+      <c r="C13" s="22" t="s">
         <v>31</v>
       </c>
-      <c r="D13" s="9"/>
-      <c r="E13" s="5"/>
-      <c r="F13" s="5"/>
-      <c r="G13" t="s">
+      <c r="D13" s="7"/>
+      <c r="E13" s="10"/>
+      <c r="F13" s="10"/>
+      <c r="G13" s="8" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="14" spans="1:7">
-      <c r="A14">
+      <c r="A14" s="1">
         <v>10</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="B14" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="C14" s="18" t="s">
+      <c r="C14" s="22" t="s">
         <v>33</v>
       </c>
-      <c r="D14" s="9"/>
-      <c r="E14" s="5"/>
-      <c r="F14" s="5"/>
-      <c r="G14" t="s">
+      <c r="D14" s="7"/>
+      <c r="E14" s="10"/>
+      <c r="F14" s="10"/>
+      <c r="G14" s="8" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="15" spans="1:4">
-      <c r="A15">
+      <c r="A15" s="1">
         <v>11</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B15" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="D15">
+      <c r="D15" s="1">
         <f>2*3*5*3</f>
         <v>90</v>
       </c>
     </row>
     <row r="16" spans="1:7">
-      <c r="A16">
+      <c r="A16" s="1">
         <v>12</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B16" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="D16">
+      <c r="D16" s="1">
         <v>100</v>
       </c>
-      <c r="G16" t="s">
+      <c r="G16" s="8" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="17" spans="1:4">
-      <c r="A17">
+      <c r="A17" s="1">
         <v>13</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B17" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="D17">
+      <c r="D17" s="1">
         <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:7">
-      <c r="A18">
+      <c r="A18" s="1">
         <v>14</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B18" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="C18" s="10" t="s">
+      <c r="C18" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="G18" t="s">
+      <c r="G18" s="8" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="19" spans="1:4">
-      <c r="A19">
+      <c r="A19" s="1">
         <v>15</v>
       </c>
-      <c r="B19" s="11" t="s">
+      <c r="B19" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="D19">
+      <c r="D19" s="1">
         <v>5</v>
       </c>
     </row>
     <row r="20" spans="1:4">
-      <c r="A20">
+      <c r="A20" s="1">
         <v>16</v>
       </c>
-      <c r="B20" t="s">
+      <c r="B20" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="D20">
+      <c r="D20" s="1">
         <v>10</v>
       </c>
     </row>
     <row r="21" spans="1:3">
-      <c r="A21">
+      <c r="A21" s="1">
         <v>17</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B21" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="C21" t="s">
+      <c r="C21" s="8" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="22" spans="1:4">
-      <c r="A22">
+      <c r="A22" s="1">
         <v>18</v>
       </c>
-      <c r="B22" t="s">
+      <c r="B22" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="D22">
+      <c r="D22" s="1">
         <f>7*24*60*60</f>
         <v>604800</v>
       </c>
     </row>
     <row r="23" spans="1:3">
-      <c r="A23">
+      <c r="A23" s="1">
         <v>19</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B23" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="C23" t="s">
+      <c r="C23" s="8" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="24" spans="1:4">
-      <c r="A24">
+      <c r="A24" s="1">
         <v>20</v>
       </c>
-      <c r="B24" t="s">
+      <c r="B24" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="D24">
+      <c r="D24" s="1">
         <v>10</v>
       </c>
     </row>
     <row r="25" spans="1:7">
-      <c r="A25">
+      <c r="A25" s="1">
         <v>21</v>
       </c>
-      <c r="B25" t="s">
+      <c r="B25" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="C25" t="s">
+      <c r="C25" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="G25" t="s">
+      <c r="G25" s="8" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="26" spans="1:7">
-      <c r="A26">
+      <c r="A26" s="1">
         <v>22</v>
       </c>
-      <c r="B26" t="s">
+      <c r="B26" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="C26" t="s">
+      <c r="C26" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="G26" t="s">
+      <c r="G26" s="8" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="27" spans="1:4">
-      <c r="A27">
+      <c r="A27" s="1">
         <v>23</v>
       </c>
-      <c r="B27" t="s">
+      <c r="B27" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="D27">
+      <c r="D27" s="1">
         <v>10000</v>
       </c>
     </row>
     <row r="28" spans="1:4">
-      <c r="A28">
+      <c r="A28" s="1">
         <v>24</v>
       </c>
-      <c r="B28" t="s">
+      <c r="B28" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="D28">
+      <c r="D28" s="1">
         <v>100</v>
       </c>
     </row>
-    <row r="29" customFormat="1" spans="1:3">
-      <c r="A29">
+    <row r="29" s="1" customFormat="1" spans="1:3">
+      <c r="A29" s="1">
         <v>25</v>
       </c>
-      <c r="B29" t="s">
+      <c r="B29" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="C29" t="s">
+      <c r="C29" s="8" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="30" spans="1:4">
-      <c r="A30">
+      <c r="A30" s="1">
         <v>26</v>
       </c>
-      <c r="B30" t="s">
+      <c r="B30" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="C30" s="12"/>
-      <c r="D30">
+      <c r="C30" s="13"/>
+      <c r="D30" s="1">
         <v>100</v>
       </c>
     </row>
     <row r="31" spans="1:7">
-      <c r="A31">
+      <c r="A31" s="1">
         <v>27</v>
       </c>
-      <c r="B31" t="s">
+      <c r="B31" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="D31">
+      <c r="D31" s="1">
         <v>9900</v>
       </c>
-      <c r="G31" t="s">
+      <c r="G31" s="8" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="32" spans="1:3">
-      <c r="A32">
+      <c r="A32" s="1">
         <v>28</v>
       </c>
-      <c r="B32" t="s">
+      <c r="B32" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="C32" t="s">
+      <c r="C32" s="8" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="33" spans="1:4">
-      <c r="A33">
+      <c r="A33" s="1">
         <v>29</v>
       </c>
-      <c r="B33" t="s">
+      <c r="B33" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="D33">
+      <c r="D33" s="1">
         <v>6</v>
       </c>
     </row>
-    <row r="34" customFormat="1" spans="1:3">
-      <c r="A34" s="13">
+    <row r="34" s="1" customFormat="1" spans="1:3">
+      <c r="A34" s="14">
         <v>30</v>
       </c>
-      <c r="B34" s="13" t="s">
+      <c r="B34" s="15" t="s">
         <v>65</v>
       </c>
-      <c r="C34" t="s">
+      <c r="C34" s="8" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="35" s="1" customFormat="1" spans="1:13">
-      <c r="A35" s="14">
+    <row r="35" s="2" customFormat="1" spans="1:13">
+      <c r="A35" s="16">
         <v>31</v>
       </c>
-      <c r="B35" s="14" t="s">
+      <c r="B35" s="16" t="s">
         <v>67</v>
       </c>
-      <c r="E35" s="1">
+      <c r="E35" s="2">
         <v>1000000000</v>
       </c>
-      <c r="G35" s="1" t="s">
+      <c r="G35" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="H35" s="1">
+      <c r="H35" s="2">
         <v>718000</v>
       </c>
-      <c r="I35" s="1" t="s">
+      <c r="I35" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="J35" s="1">
+      <c r="J35" s="2">
         <v>30</v>
       </c>
-      <c r="K35" s="1" t="s">
+      <c r="K35" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="L35" s="1">
+      <c r="L35" s="2">
         <f>J35*24*60*60*1000</f>
         <v>2592000000</v>
       </c>
-      <c r="M35" s="1" t="s">
+      <c r="M35" s="2" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="36" spans="1:3">
-      <c r="A36" s="13">
+      <c r="A36" s="14">
         <v>32</v>
       </c>
-      <c r="B36" s="13" t="s">
+      <c r="B36" s="15" t="s">
         <v>72</v>
       </c>
-      <c r="C36" t="s">
+      <c r="C36" s="8" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="37" spans="1:3">
-      <c r="A37" s="13">
+      <c r="A37" s="14">
         <v>33</v>
       </c>
-      <c r="B37" s="13" t="s">
+      <c r="B37" s="15" t="s">
         <v>74</v>
       </c>
-      <c r="C37" t="s">
+      <c r="C37" s="8" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="38" s="1" customFormat="1" spans="1:8">
-      <c r="A38" s="14">
+    <row r="38" s="2" customFormat="1" spans="1:8">
+      <c r="A38" s="16">
         <v>34</v>
       </c>
-      <c r="B38" s="14" t="s">
+      <c r="B38" s="16" t="s">
         <v>76</v>
       </c>
-      <c r="C38" s="1" t="s">
+      <c r="C38" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="G38" s="1" t="s">
+      <c r="G38" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="H38" s="1">
+      <c r="H38" s="2">
         <f>VALUE(MID(C38,FIND("_",C38)+1,4))</f>
         <v>90</v>
       </c>
     </row>
     <row r="39" spans="1:23">
-      <c r="A39" s="13">
+      <c r="A39" s="14">
         <v>35</v>
       </c>
-      <c r="B39" s="13" t="s">
+      <c r="B39" s="15" t="s">
         <v>79</v>
       </c>
-      <c r="C39" t="str">
+      <c r="C39" s="8" t="str">
         <f>_xlfn.TEXTJOIN("|",TRUE,S39:W39)</f>
         <v>3101760_1000|2584800_1000|2067840_1000|1550880_1000|1033920_1000</v>
       </c>
-      <c r="G39" t="s">
+      <c r="G39" s="8" t="s">
         <v>80</v>
       </c>
-      <c r="H39">
+      <c r="H39" s="1">
         <f>ROUND(L35/(E35*H38/100/H35),0)</f>
         <v>2067840</v>
       </c>
-      <c r="I39" t="s">
+      <c r="I39" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="J39" t="s">
+      <c r="J39" s="8" t="s">
         <v>81</v>
       </c>
-      <c r="K39" s="16" t="s">
+      <c r="K39" s="19" t="s">
         <v>82</v>
       </c>
-      <c r="L39" s="16">
+      <c r="L39" s="20">
         <v>0.25</v>
       </c>
-      <c r="M39" t="s">
+      <c r="M39" s="8" t="s">
         <v>83</v>
       </c>
-      <c r="N39">
+      <c r="N39" s="1">
         <f>ROUND(P39*(1+2*L39),0)</f>
         <v>3101760</v>
       </c>
-      <c r="O39">
+      <c r="O39" s="1">
         <f>ROUND(P39*(1+1*L39),0)</f>
         <v>2584800</v>
       </c>
-      <c r="P39">
+      <c r="P39" s="1">
         <f>H39</f>
         <v>2067840</v>
       </c>
-      <c r="Q39">
+      <c r="Q39" s="1">
         <f>ROUND(P39*(1-1*L39),0)</f>
         <v>1550880</v>
       </c>
-      <c r="R39">
+      <c r="R39" s="1">
         <f>ROUND(P39*(1-2*L39),0)</f>
         <v>1033920</v>
       </c>
-      <c r="S39" t="str">
+      <c r="S39" s="8" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,N39,1000)</f>
         <v>3101760_1000</v>
       </c>
-      <c r="T39" t="str">
+      <c r="T39" s="8" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,O39,1000)</f>
         <v>2584800_1000</v>
       </c>
-      <c r="U39" t="str">
+      <c r="U39" s="8" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,P39,1000)</f>
         <v>2067840_1000</v>
       </c>
-      <c r="V39" t="str">
+      <c r="V39" s="8" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,Q39,1000)</f>
         <v>1550880_1000</v>
       </c>
-      <c r="W39" t="str">
+      <c r="W39" s="8" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,R39,1000)</f>
         <v>1033920_1000</v>
       </c>
     </row>
     <row r="40" spans="1:4">
-      <c r="A40" s="15">
+      <c r="A40" s="17">
         <v>40</v>
       </c>
-      <c r="B40" s="15" t="s">
+      <c r="B40" s="18" t="s">
         <v>84</v>
       </c>
-      <c r="D40">
+      <c r="D40" s="1">
         <v>50</v>
       </c>
     </row>
     <row r="41" spans="1:4">
-      <c r="A41" s="15">
+      <c r="A41" s="17">
         <v>41</v>
       </c>
-      <c r="B41" s="15" t="s">
+      <c r="B41" s="18" t="s">
         <v>85</v>
       </c>
-      <c r="D41">
+      <c r="D41" s="1">
         <v>200</v>
       </c>
     </row>
     <row r="42" spans="1:4">
-      <c r="A42" s="15">
+      <c r="A42" s="17">
         <v>42</v>
       </c>
-      <c r="B42" s="15" t="s">
+      <c r="B42" s="18" t="s">
         <v>86</v>
       </c>
-      <c r="D42">
+      <c r="D42" s="1">
         <v>2000</v>
       </c>
     </row>
     <row r="43" spans="1:4">
-      <c r="A43" s="15">
+      <c r="A43" s="17">
         <v>43</v>
       </c>
-      <c r="B43" s="15" t="s">
+      <c r="B43" s="18" t="s">
         <v>87</v>
       </c>
-      <c r="D43">
+      <c r="D43" s="1">
         <v>10</v>
       </c>
     </row>
     <row r="44" spans="1:4">
-      <c r="A44" s="15">
+      <c r="A44" s="17">
         <v>44</v>
       </c>
-      <c r="B44" t="s">
+      <c r="B44" s="8" t="s">
         <v>88</v>
       </c>
-      <c r="D44">
+      <c r="D44" s="1">
         <v>1000</v>
       </c>
     </row>
     <row r="45" spans="1:3">
-      <c r="A45" s="15">
+      <c r="A45" s="17">
         <v>45</v>
       </c>
-      <c r="B45" t="s">
+      <c r="B45" s="8" t="s">
         <v>89</v>
       </c>
-      <c r="C45" t="s">
+      <c r="C45" s="8" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="46" spans="1:3">
-      <c r="A46">
+      <c r="A46" s="1">
         <v>46</v>
       </c>
-      <c r="B46" t="s">
+      <c r="B46" s="8" t="s">
         <v>91</v>
       </c>
-      <c r="C46" t="s">
+      <c r="C46" s="8" t="s">
         <v>92</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4">
+      <c r="A47" s="1">
+        <v>1001</v>
+      </c>
+      <c r="B47" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="D47" s="1">
+        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/gm/resources/sample/global.xlsx
+++ b/gm/resources/sample/global.xlsx
@@ -56,7 +56,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D47" authorId="0">
+    <comment ref="D48" authorId="0">
       <text>
         <r>
           <rPr>
@@ -83,7 +83,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="95">
   <si>
     <t>sid</t>
   </si>
@@ -362,6 +362,9 @@
   </si>
   <si>
     <t>1000_1</t>
+  </si>
+  <si>
+    <t>积分大奖：实物奖励兑换码过期时间（天）</t>
   </si>
   <si>
     <t>掉落1001-1999【我的赌场】</t>
@@ -1034,7 +1037,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1044,21 +1047,14 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1068,11 +1064,8 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" quotePrefix="1">
       <alignment vertical="center"/>
@@ -1399,7 +1392,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:W47"/>
+  <dimension ref="A1:W48"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
@@ -1424,37 +1417,37 @@
         <v>0</v>
       </c>
       <c r="B1" s="4"/>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="G1" s="4" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="5" t="s">
         <v>6</v>
       </c>
       <c r="B2" s="4"/>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="7" t="s">
+      <c r="D2" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="E2" s="8" t="s">
+      <c r="E2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="F2" s="4" t="s">
         <v>9</v>
       </c>
       <c r="G2" s="4"/>
@@ -1464,53 +1457,53 @@
         <v>10</v>
       </c>
       <c r="B3" s="4"/>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="8" t="s">
+      <c r="D3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="8" t="s">
+      <c r="E3" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="F3" s="8" t="s">
+      <c r="F3" s="1" t="s">
         <v>14</v>
       </c>
       <c r="G3" s="4"/>
     </row>
     <row r="4" spans="1:7">
-      <c r="A4" s="9"/>
-      <c r="B4" s="10"/>
-      <c r="C4" s="10"/>
-      <c r="G4" s="10"/>
+      <c r="A4" s="7"/>
+      <c r="B4" s="6"/>
+      <c r="C4" s="6"/>
+      <c r="G4" s="6"/>
     </row>
     <row r="5" spans="1:7">
       <c r="A5" s="1">
         <v>1</v>
       </c>
-      <c r="B5" s="7" t="s">
+      <c r="B5" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="D5" s="10">
+      <c r="D5" s="6">
         <v>200</v>
       </c>
-      <c r="E5" s="10"/>
-      <c r="F5" s="10"/>
-      <c r="G5" s="10"/>
+      <c r="E5" s="6"/>
+      <c r="F5" s="6"/>
+      <c r="G5" s="6"/>
     </row>
     <row r="6" spans="1:7">
       <c r="A6" s="1">
         <v>2</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="B6" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="D6" s="10">
+      <c r="D6" s="6">
         <v>10000</v>
       </c>
-      <c r="E6" s="10"/>
-      <c r="F6" s="10"/>
-      <c r="G6" s="7" t="s">
+      <c r="E6" s="6"/>
+      <c r="F6" s="6"/>
+      <c r="G6" s="6" t="s">
         <v>17</v>
       </c>
     </row>
@@ -1518,15 +1511,15 @@
       <c r="A7" s="1">
         <v>3</v>
       </c>
-      <c r="B7" s="7" t="s">
+      <c r="B7" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="D7" s="10">
+      <c r="D7" s="6">
         <v>10000</v>
       </c>
-      <c r="E7" s="10"/>
-      <c r="F7" s="10"/>
-      <c r="G7" s="7" t="s">
+      <c r="E7" s="6"/>
+      <c r="F7" s="6"/>
+      <c r="G7" s="6" t="s">
         <v>17</v>
       </c>
     </row>
@@ -1534,16 +1527,16 @@
       <c r="A8" s="1">
         <v>4</v>
       </c>
-      <c r="B8" s="7" t="s">
+      <c r="B8" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="C8" s="10">
+      <c r="C8" s="6">
         <v>100</v>
       </c>
-      <c r="D8" s="10"/>
-      <c r="E8" s="10"/>
-      <c r="F8" s="10"/>
-      <c r="G8" s="7" t="s">
+      <c r="D8" s="6"/>
+      <c r="E8" s="6"/>
+      <c r="F8" s="6"/>
+      <c r="G8" s="6" t="s">
         <v>20</v>
       </c>
     </row>
@@ -1551,13 +1544,13 @@
       <c r="A9" s="1">
         <v>5</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="1" t="s">
         <v>21</v>
       </c>
       <c r="C9" s="1">
         <v>4</v>
       </c>
-      <c r="G9" s="8" t="s">
+      <c r="G9" s="1" t="s">
         <v>22</v>
       </c>
     </row>
@@ -1565,16 +1558,16 @@
       <c r="A10" s="1">
         <v>6</v>
       </c>
-      <c r="B10" s="7" t="s">
+      <c r="B10" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="C10" s="21" t="s">
+      <c r="C10" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="D10" s="11"/>
-      <c r="E10" s="10"/>
-      <c r="F10" s="10"/>
-      <c r="G10" s="8" t="s">
+      <c r="D10" s="8"/>
+      <c r="E10" s="6"/>
+      <c r="F10" s="6"/>
+      <c r="G10" s="1" t="s">
         <v>25</v>
       </c>
     </row>
@@ -1582,16 +1575,16 @@
       <c r="A11" s="1">
         <v>7</v>
       </c>
-      <c r="B11" s="7" t="s">
+      <c r="B11" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="C11" s="22" t="s">
+      <c r="C11" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="D11" s="7"/>
-      <c r="E11" s="10"/>
-      <c r="F11" s="10"/>
-      <c r="G11" s="8" t="s">
+      <c r="D11" s="6"/>
+      <c r="E11" s="6"/>
+      <c r="F11" s="6"/>
+      <c r="G11" s="1" t="s">
         <v>25</v>
       </c>
     </row>
@@ -1599,16 +1592,16 @@
       <c r="A12" s="1">
         <v>8</v>
       </c>
-      <c r="B12" s="7" t="s">
+      <c r="B12" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="C12" s="22" t="s">
+      <c r="C12" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="D12" s="7"/>
-      <c r="E12" s="10"/>
-      <c r="F12" s="10"/>
-      <c r="G12" s="8" t="s">
+      <c r="D12" s="6"/>
+      <c r="E12" s="6"/>
+      <c r="F12" s="6"/>
+      <c r="G12" s="1" t="s">
         <v>25</v>
       </c>
     </row>
@@ -1616,16 +1609,16 @@
       <c r="A13" s="1">
         <v>9</v>
       </c>
-      <c r="B13" s="7" t="s">
+      <c r="B13" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="C13" s="22" t="s">
+      <c r="C13" s="16" t="s">
         <v>31</v>
       </c>
-      <c r="D13" s="7"/>
-      <c r="E13" s="10"/>
-      <c r="F13" s="10"/>
-      <c r="G13" s="8" t="s">
+      <c r="D13" s="6"/>
+      <c r="E13" s="6"/>
+      <c r="F13" s="6"/>
+      <c r="G13" s="1" t="s">
         <v>25</v>
       </c>
     </row>
@@ -1633,16 +1626,16 @@
       <c r="A14" s="1">
         <v>10</v>
       </c>
-      <c r="B14" s="7" t="s">
+      <c r="B14" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="C14" s="22" t="s">
+      <c r="C14" s="16" t="s">
         <v>33</v>
       </c>
-      <c r="D14" s="7"/>
-      <c r="E14" s="10"/>
-      <c r="F14" s="10"/>
-      <c r="G14" s="8" t="s">
+      <c r="D14" s="6"/>
+      <c r="E14" s="6"/>
+      <c r="F14" s="6"/>
+      <c r="G14" s="1" t="s">
         <v>25</v>
       </c>
     </row>
@@ -1650,7 +1643,7 @@
       <c r="A15" s="1">
         <v>11</v>
       </c>
-      <c r="B15" s="8" t="s">
+      <c r="B15" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D15" s="1">
@@ -1662,13 +1655,13 @@
       <c r="A16" s="1">
         <v>12</v>
       </c>
-      <c r="B16" s="8" t="s">
+      <c r="B16" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D16" s="1">
         <v>100</v>
       </c>
-      <c r="G16" s="8" t="s">
+      <c r="G16" s="1" t="s">
         <v>36</v>
       </c>
     </row>
@@ -1676,7 +1669,7 @@
       <c r="A17" s="1">
         <v>13</v>
       </c>
-      <c r="B17" s="8" t="s">
+      <c r="B17" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D17" s="1">
@@ -1687,13 +1680,13 @@
       <c r="A18" s="1">
         <v>14</v>
       </c>
-      <c r="B18" s="8" t="s">
+      <c r="B18" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C18" s="12" t="s">
+      <c r="C18" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="G18" s="8" t="s">
+      <c r="G18" s="1" t="s">
         <v>40</v>
       </c>
     </row>
@@ -1701,7 +1694,7 @@
       <c r="A19" s="1">
         <v>15</v>
       </c>
-      <c r="B19" s="8" t="s">
+      <c r="B19" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D19" s="1">
@@ -1712,7 +1705,7 @@
       <c r="A20" s="1">
         <v>16</v>
       </c>
-      <c r="B20" s="8" t="s">
+      <c r="B20" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D20" s="1">
@@ -1723,10 +1716,10 @@
       <c r="A21" s="1">
         <v>17</v>
       </c>
-      <c r="B21" s="8" t="s">
+      <c r="B21" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="C21" s="8" t="s">
+      <c r="C21" s="1" t="s">
         <v>44</v>
       </c>
     </row>
@@ -1734,7 +1727,7 @@
       <c r="A22" s="1">
         <v>18</v>
       </c>
-      <c r="B22" s="8" t="s">
+      <c r="B22" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D22" s="1">
@@ -1746,10 +1739,10 @@
       <c r="A23" s="1">
         <v>19</v>
       </c>
-      <c r="B23" s="8" t="s">
+      <c r="B23" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="C23" s="8" t="s">
+      <c r="C23" s="1" t="s">
         <v>47</v>
       </c>
     </row>
@@ -1757,7 +1750,7 @@
       <c r="A24" s="1">
         <v>20</v>
       </c>
-      <c r="B24" s="8" t="s">
+      <c r="B24" s="1" t="s">
         <v>48</v>
       </c>
       <c r="D24" s="1">
@@ -1768,13 +1761,13 @@
       <c r="A25" s="1">
         <v>21</v>
       </c>
-      <c r="B25" s="8" t="s">
+      <c r="B25" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="C25" s="8" t="s">
+      <c r="C25" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="G25" s="8" t="s">
+      <c r="G25" s="1" t="s">
         <v>51</v>
       </c>
     </row>
@@ -1782,13 +1775,13 @@
       <c r="A26" s="1">
         <v>22</v>
       </c>
-      <c r="B26" s="8" t="s">
+      <c r="B26" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="C26" s="8" t="s">
+      <c r="C26" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="G26" s="8" t="s">
+      <c r="G26" s="1" t="s">
         <v>54</v>
       </c>
     </row>
@@ -1796,7 +1789,7 @@
       <c r="A27" s="1">
         <v>23</v>
       </c>
-      <c r="B27" s="8" t="s">
+      <c r="B27" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D27" s="1">
@@ -1807,7 +1800,7 @@
       <c r="A28" s="1">
         <v>24</v>
       </c>
-      <c r="B28" s="8" t="s">
+      <c r="B28" s="1" t="s">
         <v>56</v>
       </c>
       <c r="D28" s="1">
@@ -1818,10 +1811,10 @@
       <c r="A29" s="1">
         <v>25</v>
       </c>
-      <c r="B29" s="8" t="s">
+      <c r="B29" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="C29" s="8" t="s">
+      <c r="C29" s="1" t="s">
         <v>58</v>
       </c>
     </row>
@@ -1829,10 +1822,10 @@
       <c r="A30" s="1">
         <v>26</v>
       </c>
-      <c r="B30" s="8" t="s">
+      <c r="B30" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="C30" s="13"/>
+      <c r="C30" s="10"/>
       <c r="D30" s="1">
         <v>100</v>
       </c>
@@ -1841,13 +1834,13 @@
       <c r="A31" s="1">
         <v>27</v>
       </c>
-      <c r="B31" s="8" t="s">
+      <c r="B31" s="1" t="s">
         <v>60</v>
       </c>
       <c r="D31" s="1">
         <v>9900</v>
       </c>
-      <c r="G31" s="8" t="s">
+      <c r="G31" s="1" t="s">
         <v>61</v>
       </c>
     </row>
@@ -1855,10 +1848,10 @@
       <c r="A32" s="1">
         <v>28</v>
       </c>
-      <c r="B32" s="8" t="s">
+      <c r="B32" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="C32" s="8" t="s">
+      <c r="C32" s="1" t="s">
         <v>63</v>
       </c>
     </row>
@@ -1866,7 +1859,7 @@
       <c r="A33" s="1">
         <v>29</v>
       </c>
-      <c r="B33" s="8" t="s">
+      <c r="B33" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D33" s="1">
@@ -1874,21 +1867,21 @@
       </c>
     </row>
     <row r="34" s="1" customFormat="1" spans="1:3">
-      <c r="A34" s="14">
+      <c r="A34" s="11">
         <v>30</v>
       </c>
-      <c r="B34" s="15" t="s">
+      <c r="B34" s="11" t="s">
         <v>65</v>
       </c>
-      <c r="C34" s="8" t="s">
+      <c r="C34" s="1" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="35" s="2" customFormat="1" spans="1:13">
-      <c r="A35" s="16">
+      <c r="A35" s="12">
         <v>31</v>
       </c>
-      <c r="B35" s="16" t="s">
+      <c r="B35" s="12" t="s">
         <v>67</v>
       </c>
       <c r="E35" s="2">
@@ -1918,32 +1911,32 @@
       </c>
     </row>
     <row r="36" spans="1:3">
-      <c r="A36" s="14">
+      <c r="A36" s="11">
         <v>32</v>
       </c>
-      <c r="B36" s="15" t="s">
+      <c r="B36" s="11" t="s">
         <v>72</v>
       </c>
-      <c r="C36" s="8" t="s">
+      <c r="C36" s="1" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="37" spans="1:3">
-      <c r="A37" s="14">
+      <c r="A37" s="11">
         <v>33</v>
       </c>
-      <c r="B37" s="15" t="s">
+      <c r="B37" s="11" t="s">
         <v>74</v>
       </c>
-      <c r="C37" s="8" t="s">
+      <c r="C37" s="1" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="38" s="2" customFormat="1" spans="1:8">
-      <c r="A38" s="16">
+      <c r="A38" s="12">
         <v>34</v>
       </c>
-      <c r="B38" s="16" t="s">
+      <c r="B38" s="12" t="s">
         <v>76</v>
       </c>
       <c r="C38" s="2" t="s">
@@ -1958,36 +1951,36 @@
       </c>
     </row>
     <row r="39" spans="1:23">
-      <c r="A39" s="14">
+      <c r="A39" s="11">
         <v>35</v>
       </c>
-      <c r="B39" s="15" t="s">
+      <c r="B39" s="11" t="s">
         <v>79</v>
       </c>
-      <c r="C39" s="8" t="str">
+      <c r="C39" s="1" t="str">
         <f>_xlfn.TEXTJOIN("|",TRUE,S39:W39)</f>
         <v>3101760_1000|2584800_1000|2067840_1000|1550880_1000|1033920_1000</v>
       </c>
-      <c r="G39" s="8" t="s">
+      <c r="G39" s="1" t="s">
         <v>80</v>
       </c>
       <c r="H39" s="1">
         <f>ROUND(L35/(E35*H38/100/H35),0)</f>
         <v>2067840</v>
       </c>
-      <c r="I39" s="8" t="s">
+      <c r="I39" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="J39" s="8" t="s">
+      <c r="J39" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="K39" s="19" t="s">
+      <c r="K39" s="14" t="s">
         <v>82</v>
       </c>
-      <c r="L39" s="20">
+      <c r="L39" s="14">
         <v>0.25</v>
       </c>
-      <c r="M39" s="8" t="s">
+      <c r="M39" s="1" t="s">
         <v>83</v>
       </c>
       <c r="N39" s="1">
@@ -2010,32 +2003,32 @@
         <f>ROUND(P39*(1-2*L39),0)</f>
         <v>1033920</v>
       </c>
-      <c r="S39" s="8" t="str">
+      <c r="S39" s="1" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,N39,1000)</f>
         <v>3101760_1000</v>
       </c>
-      <c r="T39" s="8" t="str">
+      <c r="T39" s="1" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,O39,1000)</f>
         <v>2584800_1000</v>
       </c>
-      <c r="U39" s="8" t="str">
+      <c r="U39" s="1" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,P39,1000)</f>
         <v>2067840_1000</v>
       </c>
-      <c r="V39" s="8" t="str">
+      <c r="V39" s="1" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,Q39,1000)</f>
         <v>1550880_1000</v>
       </c>
-      <c r="W39" s="8" t="str">
+      <c r="W39" s="1" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,R39,1000)</f>
         <v>1033920_1000</v>
       </c>
     </row>
     <row r="40" spans="1:4">
-      <c r="A40" s="17">
+      <c r="A40" s="13">
         <v>40</v>
       </c>
-      <c r="B40" s="18" t="s">
+      <c r="B40" s="13" t="s">
         <v>84</v>
       </c>
       <c r="D40" s="1">
@@ -2043,10 +2036,10 @@
       </c>
     </row>
     <row r="41" spans="1:4">
-      <c r="A41" s="17">
+      <c r="A41" s="13">
         <v>41</v>
       </c>
-      <c r="B41" s="18" t="s">
+      <c r="B41" s="13" t="s">
         <v>85</v>
       </c>
       <c r="D41" s="1">
@@ -2054,10 +2047,10 @@
       </c>
     </row>
     <row r="42" spans="1:4">
-      <c r="A42" s="17">
+      <c r="A42" s="13">
         <v>42</v>
       </c>
-      <c r="B42" s="18" t="s">
+      <c r="B42" s="13" t="s">
         <v>86</v>
       </c>
       <c r="D42" s="1">
@@ -2065,10 +2058,10 @@
       </c>
     </row>
     <row r="43" spans="1:4">
-      <c r="A43" s="17">
+      <c r="A43" s="13">
         <v>43</v>
       </c>
-      <c r="B43" s="18" t="s">
+      <c r="B43" s="13" t="s">
         <v>87</v>
       </c>
       <c r="D43" s="1">
@@ -2076,10 +2069,10 @@
       </c>
     </row>
     <row r="44" spans="1:4">
-      <c r="A44" s="17">
+      <c r="A44" s="13">
         <v>44</v>
       </c>
-      <c r="B44" s="8" t="s">
+      <c r="B44" s="1" t="s">
         <v>88</v>
       </c>
       <c r="D44" s="1">
@@ -2087,13 +2080,13 @@
       </c>
     </row>
     <row r="45" spans="1:3">
-      <c r="A45" s="17">
+      <c r="A45" s="13">
         <v>45</v>
       </c>
-      <c r="B45" s="8" t="s">
+      <c r="B45" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="C45" s="8" t="s">
+      <c r="C45" s="1" t="s">
         <v>90</v>
       </c>
     </row>
@@ -2101,21 +2094,32 @@
       <c r="A46" s="1">
         <v>46</v>
       </c>
-      <c r="B46" s="8" t="s">
+      <c r="B46" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="C46" s="8" t="s">
+      <c r="C46" s="1" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="47" spans="1:4">
       <c r="A47" s="1">
+        <v>47</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="D47" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4">
+      <c r="A48" s="1">
         <v>1001</v>
       </c>
-      <c r="B47" s="8" t="s">
-        <v>93</v>
-      </c>
-      <c r="D47" s="1">
+      <c r="B48" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="D48" s="1">
         <v>4</v>
       </c>
     </row>

--- a/gm/resources/sample/global.xlsx
+++ b/gm/resources/sample/global.xlsx
@@ -1485,7 +1485,7 @@
         <v>15</v>
       </c>
       <c r="D5" s="6">
-        <v>200</v>
+        <v>999</v>
       </c>
       <c r="E5" s="6"/>
       <c r="F5" s="6"/>

--- a/gm/resources/sample/global.xlsx
+++ b/gm/resources/sample/global.xlsx
@@ -283,7 +283,7 @@
     <t>官方派奖每个转盘需求积分：初、中、高</t>
   </si>
   <si>
-    <t>1000_3000_5000</t>
+    <t>10_200_5000</t>
   </si>
   <si>
     <t>官方派奖转盘奖池金币数量（废弃，在活动配置表中配置）</t>
@@ -310,7 +310,7 @@
     <t>官方派奖：充值转换积分比例 ：充值金额 = X积分</t>
   </si>
   <si>
-    <t>10_1</t>
+    <t>1_1</t>
   </si>
   <si>
     <t>官方派奖：真人和机器人奖池比例(百分比)  （废弃，功能不存在）</t>
@@ -1911,13 +1911,13 @@
       </c>
     </row>
     <row r="36" spans="1:3">
-      <c r="A36" s="11">
+      <c r="A36" s="12">
         <v>32</v>
       </c>
-      <c r="B36" s="11" t="s">
+      <c r="B36" s="12" t="s">
         <v>72</v>
       </c>
-      <c r="C36" s="1" t="s">
+      <c r="C36" s="2" t="s">
         <v>73</v>
       </c>
     </row>

--- a/gm/resources/sample/global.xlsx
+++ b/gm/resources/sample/global.xlsx
@@ -283,7 +283,7 @@
     <t>官方派奖每个转盘需求积分：初、中、高</t>
   </si>
   <si>
-    <t>1000_3000_5000</t>
+    <t>10_200_5000</t>
   </si>
   <si>
     <t>官方派奖转盘奖池金币数量（废弃，在活动配置表中配置）</t>
@@ -310,7 +310,7 @@
     <t>官方派奖：充值转换积分比例 ：充值金额 = X积分</t>
   </si>
   <si>
-    <t>10_1</t>
+    <t>1_1</t>
   </si>
   <si>
     <t>官方派奖：真人和机器人奖池比例(百分比)  （废弃，功能不存在）</t>
@@ -346,7 +346,7 @@
     <t>积分大奖：月总榜-上榜的最低积分要求</t>
   </si>
   <si>
-    <t>积分大奖：每日转盘默认次数上限</t>
+    <t>积分大奖：每日转盘默认初始次数上限</t>
   </si>
   <si>
     <t>积分大奖：充值多少金额给一次转盘次数</t>
@@ -1911,13 +1911,13 @@
       </c>
     </row>
     <row r="36" spans="1:3">
-      <c r="A36" s="11">
+      <c r="A36" s="12">
         <v>32</v>
       </c>
-      <c r="B36" s="11" t="s">
+      <c r="B36" s="12" t="s">
         <v>72</v>
       </c>
-      <c r="C36" s="1" t="s">
+      <c r="C36" s="2" t="s">
         <v>73</v>
       </c>
     </row>
@@ -2065,7 +2065,7 @@
         <v>87</v>
       </c>
       <c r="D43" s="1">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="44" spans="1:4">

--- a/gm/resources/sample/global.xlsx
+++ b/gm/resources/sample/global.xlsx
@@ -56,7 +56,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D48" authorId="0">
+    <comment ref="D49" authorId="0">
       <text>
         <r>
           <rPr>
@@ -83,7 +83,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="97">
   <si>
     <t>sid</t>
   </si>
@@ -365,6 +365,12 @@
   </si>
   <si>
     <t>积分大奖：实物奖励兑换码过期时间（天）</t>
+  </si>
+  <si>
+    <t>新手奖励</t>
+  </si>
+  <si>
+    <t>1990000_200000</t>
   </si>
   <si>
     <t>掉落1001-1999【我的赌场】</t>
@@ -1392,7 +1398,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:W48"/>
+  <dimension ref="A1:W49"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
@@ -2112,14 +2118,25 @@
         <v>3</v>
       </c>
     </row>
-    <row r="48" spans="1:4">
+    <row r="48" spans="1:3">
       <c r="A48" s="1">
-        <v>1001</v>
+        <v>50</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="D48" s="1">
+      <c r="C48" s="1" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4">
+      <c r="A49" s="1">
+        <v>1001</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="D49" s="1">
         <v>4</v>
       </c>
     </row>

--- a/gm/resources/sample/global.xlsx
+++ b/gm/resources/sample/global.xlsx
@@ -370,7 +370,7 @@
     <t>新手奖励</t>
   </si>
   <si>
-    <t>1990000_200000</t>
+    <t>1990000_99000</t>
   </si>
   <si>
     <t>掉落1001-1999【我的赌场】</t>

--- a/gm/resources/sample/global.xlsx
+++ b/gm/resources/sample/global.xlsx
@@ -202,7 +202,7 @@
     <t>默认装扮</t>
   </si>
   <si>
-    <t>1:1001:2001:3001:4001:5001:6001</t>
+    <t>1:1001:2001:4001:5001:6001</t>
   </si>
   <si>
     <t>avatar表的ID</t>

--- a/gm/resources/sample/global.xlsx
+++ b/gm/resources/sample/global.xlsx
@@ -32,6 +32,29 @@
     <author>Administrator</author>
   </authors>
   <commentList>
+    <comment ref="G18" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+默认头像：默认头像框：默认国旗：默认头衔：默认筹码：默认牌背：默认大厅背景
+不需要时填0，不要改变分割</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="E35" authorId="0">
       <text>
         <r>
@@ -202,7 +225,7 @@
     <t>默认装扮</t>
   </si>
   <si>
-    <t>1:1001:2001:4001:5001:6001</t>
+    <t>1:1001:2001:0:4001:5001:6001</t>
   </si>
   <si>
     <t>avatar表的ID</t>

--- a/gm/resources/sample/global.xlsx
+++ b/gm/resources/sample/global.xlsx
@@ -346,7 +346,7 @@
     <t>积分大奖：月总榜-上榜的最低积分要求</t>
   </si>
   <si>
-    <t>积分大奖：每日转盘默认次数上限</t>
+    <t>积分大奖：每日转盘默认初始次数上限</t>
   </si>
   <si>
     <t>积分大奖：充值多少金额给一次转盘次数</t>
@@ -2065,7 +2065,7 @@
         <v>87</v>
       </c>
       <c r="D43" s="1">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="44" spans="1:4">

--- a/gm/resources/sample/global.xlsx
+++ b/gm/resources/sample/global.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="11925"/>
   </bookViews>
   <sheets>
     <sheet name="globalConfig" sheetId="1" r:id="rId1"/>
@@ -79,34 +79,12 @@
         </r>
       </text>
     </comment>
-    <comment ref="D49" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>Administrator:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">
-配置 dropConfig.xlsx 中的 id 值</t>
-        </r>
-      </text>
-    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="97">
   <si>
     <t>sid</t>
   </si>
@@ -378,13 +356,10 @@
     <t>积分大奖：积分保底奖励（积分数量_奖励道具ID_奖励道具数量）</t>
   </si>
   <si>
-    <t>1000_1990000_200000|2000_1990000_500000|5000_1990000_1000000|8000_1990000_1500000|10000_1990000_2000000</t>
-  </si>
-  <si>
-    <t>VIP充值：充值金额与经验转换比例(充值金额_获得vip经验，最低支持0.01_1)</t>
-  </si>
-  <si>
-    <t>1000_1</t>
+    <t>360_1990000_1400000|960_1990001_2800000|1800_1990002_5600000|2400_1990003_14000000|3000_1990004_35000000|3600_1990005_105000000</t>
+  </si>
+  <si>
+    <t>VIP充值：充值金额与经验转换比例(充值金额_获得vip经验，最低支持0.01_1，美元)</t>
   </si>
   <si>
     <t>积分大奖：实物奖励兑换码过期时间（天）</t>
@@ -393,10 +368,48 @@
     <t>新手奖励</t>
   </si>
   <si>
-    <t>1990000_99000</t>
-  </si>
-  <si>
-    <t>掉落1001-1999【我的赌场】</t>
+    <t>1990000_700000</t>
+  </si>
+  <si>
+    <t>手机短信区号</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>‌</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>84</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>‌</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>_91_351</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -409,7 +422,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="25">
+  <fonts count="26">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -433,6 +446,12 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
       <charset val="134"/>
     </font>
     <font>
@@ -936,137 +955,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1094,8 +1113,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" quotePrefix="1">
       <alignment vertical="center"/>
     </xf>
@@ -1590,7 +1610,7 @@
       <c r="B10" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="C10" s="15" t="s">
+      <c r="C10" s="16" t="s">
         <v>24</v>
       </c>
       <c r="D10" s="8"/>
@@ -1607,7 +1627,7 @@
       <c r="B11" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="C11" s="16" t="s">
+      <c r="C11" s="17" t="s">
         <v>27</v>
       </c>
       <c r="D11" s="6"/>
@@ -1624,7 +1644,7 @@
       <c r="B12" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="C12" s="16" t="s">
+      <c r="C12" s="17" t="s">
         <v>29</v>
       </c>
       <c r="D12" s="6"/>
@@ -1641,7 +1661,7 @@
       <c r="B13" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="C13" s="16" t="s">
+      <c r="C13" s="17" t="s">
         <v>31</v>
       </c>
       <c r="D13" s="6"/>
@@ -1658,7 +1678,7 @@
       <c r="B14" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="C14" s="16" t="s">
+      <c r="C14" s="17" t="s">
         <v>33</v>
       </c>
       <c r="D14" s="6"/>
@@ -1668,7 +1688,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="15" spans="1:4">
+    <row r="15" spans="1:7">
       <c r="A15" s="1">
         <v>11</v>
       </c>
@@ -1694,7 +1714,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="17" spans="1:4">
+    <row r="17" spans="1:7">
       <c r="A17" s="1">
         <v>13</v>
       </c>
@@ -1719,7 +1739,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="19" spans="1:4">
+    <row r="19" spans="1:7">
       <c r="A19" s="1">
         <v>15</v>
       </c>
@@ -1730,7 +1750,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="20" spans="1:4">
+    <row r="20" spans="1:7">
       <c r="A20" s="1">
         <v>16</v>
       </c>
@@ -1741,7 +1761,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="21" spans="1:3">
+    <row r="21" spans="1:7">
       <c r="A21" s="1">
         <v>17</v>
       </c>
@@ -1752,7 +1772,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="22" spans="1:4">
+    <row r="22" spans="1:7">
       <c r="A22" s="1">
         <v>18</v>
       </c>
@@ -1764,7 +1784,7 @@
         <v>604800</v>
       </c>
     </row>
-    <row r="23" spans="1:3">
+    <row r="23" spans="1:7">
       <c r="A23" s="1">
         <v>19</v>
       </c>
@@ -1775,7 +1795,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="24" spans="1:4">
+    <row r="24" spans="1:7">
       <c r="A24" s="1">
         <v>20</v>
       </c>
@@ -1814,7 +1834,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="27" spans="1:4">
+    <row r="27" spans="1:7">
       <c r="A27" s="1">
         <v>23</v>
       </c>
@@ -1825,7 +1845,7 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="28" spans="1:4">
+    <row r="28" spans="1:7">
       <c r="A28" s="1">
         <v>24</v>
       </c>
@@ -1836,7 +1856,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="29" s="1" customFormat="1" spans="1:3">
+    <row r="29" s="1" customFormat="1" spans="1:7">
       <c r="A29" s="1">
         <v>25</v>
       </c>
@@ -1847,7 +1867,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="30" spans="1:4">
+    <row r="30" spans="1:7">
       <c r="A30" s="1">
         <v>26</v>
       </c>
@@ -1873,7 +1893,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="32" spans="1:3">
+    <row r="32" spans="1:7">
       <c r="A32" s="1">
         <v>28</v>
       </c>
@@ -1884,7 +1904,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="33" spans="1:4">
+    <row r="33" spans="1:23">
       <c r="A33" s="1">
         <v>29</v>
       </c>
@@ -1895,7 +1915,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="34" s="1" customFormat="1" spans="1:3">
+    <row r="34" s="1" customFormat="1" spans="1:23">
       <c r="A34" s="11">
         <v>30</v>
       </c>
@@ -1906,7 +1926,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="35" s="2" customFormat="1" spans="1:13">
+    <row r="35" s="2" customFormat="1" spans="1:23">
       <c r="A35" s="12">
         <v>31</v>
       </c>
@@ -1939,7 +1959,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="36" spans="1:3">
+    <row r="36" spans="1:23">
       <c r="A36" s="12">
         <v>32</v>
       </c>
@@ -1950,7 +1970,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="37" spans="1:3">
+    <row r="37" spans="1:23">
       <c r="A37" s="11">
         <v>33</v>
       </c>
@@ -1961,7 +1981,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="38" s="2" customFormat="1" spans="1:8">
+    <row r="38" s="2" customFormat="1" spans="1:23">
       <c r="A38" s="12">
         <v>34</v>
       </c>
@@ -2003,10 +2023,10 @@
       <c r="J39" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="K39" s="14" t="s">
+      <c r="K39" s="13" t="s">
         <v>82</v>
       </c>
-      <c r="L39" s="14">
+      <c r="L39" s="13">
         <v>0.25</v>
       </c>
       <c r="M39" s="1" t="s">
@@ -2053,63 +2073,63 @@
         <v>1033920_1000</v>
       </c>
     </row>
-    <row r="40" spans="1:4">
-      <c r="A40" s="13">
+    <row r="40" spans="1:23">
+      <c r="A40" s="14">
         <v>40</v>
       </c>
-      <c r="B40" s="13" t="s">
+      <c r="B40" s="14" t="s">
         <v>84</v>
       </c>
       <c r="D40" s="1">
         <v>50</v>
       </c>
     </row>
-    <row r="41" spans="1:4">
-      <c r="A41" s="13">
+    <row r="41" spans="1:23">
+      <c r="A41" s="14">
         <v>41</v>
       </c>
-      <c r="B41" s="13" t="s">
+      <c r="B41" s="14" t="s">
         <v>85</v>
       </c>
       <c r="D41" s="1">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4">
-      <c r="A42" s="13">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="42" spans="1:23">
+      <c r="A42" s="14">
         <v>42</v>
       </c>
-      <c r="B42" s="13" t="s">
+      <c r="B42" s="14" t="s">
         <v>86</v>
       </c>
       <c r="D42" s="1">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4">
-      <c r="A43" s="13">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="43" spans="1:23">
+      <c r="A43" s="14">
         <v>43</v>
       </c>
-      <c r="B43" s="13" t="s">
+      <c r="B43" s="14" t="s">
         <v>87</v>
       </c>
       <c r="D43" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:4">
-      <c r="A44" s="13">
+    <row r="44" spans="1:23">
+      <c r="A44" s="14">
         <v>44</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>88</v>
       </c>
       <c r="D44" s="1">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3">
-      <c r="A45" s="13">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="45" spans="1:23">
+      <c r="A45" s="14">
         <v>45</v>
       </c>
       <c r="B45" s="1" t="s">
@@ -2119,7 +2139,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="46" spans="1:3">
+    <row r="46" spans="1:23">
       <c r="A46" s="1">
         <v>46</v>
       </c>
@@ -2127,40 +2147,40 @@
         <v>91</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="47" spans="1:23">
       <c r="A47" s="1">
         <v>47</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D47" s="1">
         <v>3</v>
       </c>
     </row>
-    <row r="48" spans="1:3">
+    <row r="48" spans="1:23">
       <c r="A48" s="1">
         <v>50</v>
       </c>
       <c r="B48" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="C48" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="C48" s="1" t="s">
+    </row>
+    <row r="49" spans="1:3">
+      <c r="A49" s="1">
+        <v>51</v>
+      </c>
+      <c r="B49" s="1" t="s">
         <v>95</v>
       </c>
-    </row>
-    <row r="49" spans="1:4">
-      <c r="A49" s="1">
-        <v>1001</v>
-      </c>
-      <c r="B49" s="1" t="s">
+      <c r="C49" s="15" t="s">
         <v>96</v>
-      </c>
-      <c r="D49" s="1">
-        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/gm/resources/sample/global.xlsx
+++ b/gm/resources/sample/global.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="11925"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="globalConfig" sheetId="1" r:id="rId1"/>
@@ -79,12 +79,34 @@
         </r>
       </text>
     </comment>
+    <comment ref="C37" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+修改此比例后，需要在多语言表中(67016)修正描述数值</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="99">
   <si>
     <t>sid</t>
   </si>
@@ -281,7 +303,7 @@
     <t>幸运夺宝(一元购)能配置商品数量上限</t>
   </si>
   <si>
-    <t>官方派奖每个转盘需求积分：初、中、高</t>
+    <t>官方派奖每个转盘需求积分：初、中、高(字段废弃，配置移到ActivityConfig.xlsx)</t>
   </si>
   <si>
     <t>10_200_5000</t>
@@ -302,7 +324,7 @@
     <t>毫秒</t>
   </si>
   <si>
-    <t>官方派奖：有效下注转换积分比例 ：有效下注 = X积分</t>
+    <t>官方派奖：有效下注转换积分比例 ：有效下注 = X积分(字段废弃)</t>
   </si>
   <si>
     <t>100000_1</t>
@@ -356,7 +378,7 @@
     <t>积分大奖：积分保底奖励（积分数量_奖励道具ID_奖励道具数量）</t>
   </si>
   <si>
-    <t>360_1990000_1400000|960_1990001_2800000|1800_1990002_5600000|2400_1990003_14000000|3000_1990004_35000000|3600_1990005_105000000</t>
+    <t>360_1990000_1400000|960_1990000_2800000|1800_1990000_5600000|2400_1990000_14000000|3000_1990000_35000000|3600_1990000_105000000</t>
   </si>
   <si>
     <t>VIP充值：充值金额与经验转换比例(充值金额_获得vip经验，最低支持0.01_1，美元)</t>
@@ -410,6 +432,12 @@
       </rPr>
       <t>_91_351</t>
     </r>
+  </si>
+  <si>
+    <t>VIP充值返利给金币时的金币数量，金币数量 = 返利金额 * 此值</t>
+  </si>
+  <si>
+    <t>推广分享给金币时的金币数量，金币数量 = 返利金额 * 此值</t>
   </si>
 </sst>
 </file>
@@ -1111,8 +1139,8 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1441,7 +1469,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:W49"/>
+  <dimension ref="A1:W51"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
@@ -1915,22 +1943,22 @@
         <v>6</v>
       </c>
     </row>
-    <row r="34" s="1" customFormat="1" spans="1:23">
+    <row r="34" s="2" customFormat="1" spans="1:23">
       <c r="A34" s="11">
         <v>30</v>
       </c>
       <c r="B34" s="11" t="s">
         <v>65</v>
       </c>
-      <c r="C34" s="1" t="s">
+      <c r="C34" s="2" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="35" s="2" customFormat="1" spans="1:23">
-      <c r="A35" s="12">
+      <c r="A35" s="11">
         <v>31</v>
       </c>
-      <c r="B35" s="12" t="s">
+      <c r="B35" s="11" t="s">
         <v>67</v>
       </c>
       <c r="E35" s="2">
@@ -1960,10 +1988,10 @@
       </c>
     </row>
     <row r="36" spans="1:23">
-      <c r="A36" s="12">
+      <c r="A36" s="11">
         <v>32</v>
       </c>
-      <c r="B36" s="12" t="s">
+      <c r="B36" s="11" t="s">
         <v>72</v>
       </c>
       <c r="C36" s="2" t="s">
@@ -1971,10 +1999,10 @@
       </c>
     </row>
     <row r="37" spans="1:23">
-      <c r="A37" s="11">
+      <c r="A37" s="12">
         <v>33</v>
       </c>
-      <c r="B37" s="11" t="s">
+      <c r="B37" s="12" t="s">
         <v>74</v>
       </c>
       <c r="C37" s="1" t="s">
@@ -1982,10 +2010,10 @@
       </c>
     </row>
     <row r="38" s="2" customFormat="1" spans="1:23">
-      <c r="A38" s="12">
+      <c r="A38" s="11">
         <v>34</v>
       </c>
-      <c r="B38" s="12" t="s">
+      <c r="B38" s="11" t="s">
         <v>76</v>
       </c>
       <c r="C38" s="2" t="s">
@@ -2000,10 +2028,10 @@
       </c>
     </row>
     <row r="39" spans="1:23">
-      <c r="A39" s="11">
+      <c r="A39" s="12">
         <v>35</v>
       </c>
-      <c r="B39" s="11" t="s">
+      <c r="B39" s="12" t="s">
         <v>79</v>
       </c>
       <c r="C39" s="1" t="str">
@@ -2172,7 +2200,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="49" spans="1:3">
+    <row r="49" spans="1:4">
       <c r="A49" s="1">
         <v>51</v>
       </c>
@@ -2181,6 +2209,28 @@
       </c>
       <c r="C49" s="15" t="s">
         <v>96</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4">
+      <c r="A50" s="1">
+        <v>52</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="D50" s="1">
+        <v>700000</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4">
+      <c r="A51" s="1">
+        <v>53</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="D51" s="1">
+        <v>700000</v>
       </c>
     </row>
   </sheetData>

--- a/gm/resources/sample/global.xlsx
+++ b/gm/resources/sample/global.xlsx
@@ -55,7 +55,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E35" authorId="0">
+    <comment ref="E36" authorId="0">
       <text>
         <r>
           <rPr>
@@ -79,7 +79,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C37" authorId="0">
+    <comment ref="C38" authorId="0">
       <text>
         <r>
           <rPr>
@@ -106,7 +106,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="101">
   <si>
     <t>sid</t>
   </si>
@@ -300,7 +300,10 @@
     <t>1022502_1</t>
   </si>
   <si>
-    <t>幸运夺宝(一元购)能配置商品数量上限</t>
+    <t>幸运夺宝能配置商品数量上限</t>
+  </si>
+  <si>
+    <t>幸运夺宝开奖时间(秒)</t>
   </si>
   <si>
     <t>官方派奖每个转盘需求积分：初、中、高(字段废弃，配置移到ActivityConfig.xlsx)</t>
@@ -439,6 +442,9 @@
   <si>
     <t>推广分享给金币时的金币数量，金币数量 = 返利金额 * 此值</t>
   </si>
+  <si>
+    <t>VIP充值返利给钻石时的钻石数量，钻石数量 = 返利金额 * 此值</t>
+  </si>
 </sst>
 </file>
 
@@ -627,12 +633,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1469,7 +1475,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:W51"/>
+  <dimension ref="A1:W53"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
@@ -1940,181 +1946,182 @@
         <v>64</v>
       </c>
       <c r="D33" s="1">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="34" s="2" customFormat="1" spans="1:23">
-      <c r="A34" s="11">
-        <v>30</v>
-      </c>
-      <c r="B34" s="11" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="34" customFormat="1" spans="1:23">
+      <c r="A34" s="1">
+        <v>55</v>
+      </c>
+      <c r="B34" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="C34" s="2" t="s">
-        <v>66</v>
+      <c r="C34" s="1"/>
+      <c r="D34" s="1">
+        <v>60</v>
       </c>
     </row>
     <row r="35" s="2" customFormat="1" spans="1:23">
       <c r="A35" s="11">
+        <v>30</v>
+      </c>
+      <c r="B35" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="36" s="2" customFormat="1" spans="1:23">
+      <c r="A36" s="11">
         <v>31</v>
       </c>
-      <c r="B35" s="11" t="s">
-        <v>67</v>
-      </c>
-      <c r="E35" s="2">
+      <c r="B36" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="E36" s="2">
         <v>1000000000</v>
       </c>
-      <c r="G35" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="H35" s="2">
+      <c r="G36" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="H36" s="2">
         <v>718000</v>
       </c>
-      <c r="I35" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="J35" s="2">
+      <c r="I36" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="J36" s="2">
         <v>30</v>
       </c>
-      <c r="K35" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="L35" s="2">
-        <f>J35*24*60*60*1000</f>
+      <c r="K36" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="L36" s="2">
+        <f>J36*24*60*60*1000</f>
         <v>2592000000</v>
       </c>
-      <c r="M35" s="2" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="36" spans="1:23">
-      <c r="A36" s="11">
+      <c r="M36" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="37" spans="1:23">
+      <c r="A37" s="11">
         <v>32</v>
       </c>
-      <c r="B36" s="11" t="s">
+      <c r="B37" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="38" spans="1:23">
+      <c r="A38" s="12">
+        <v>33</v>
+      </c>
+      <c r="B38" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="39" s="2" customFormat="1" spans="1:23">
+      <c r="A39" s="11">
+        <v>34</v>
+      </c>
+      <c r="B39" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="G39" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="H39" s="2">
+        <f>VALUE(MID(C39,FIND("_",C39)+1,4))</f>
+        <v>90</v>
+      </c>
+    </row>
+    <row r="40" spans="1:23">
+      <c r="A40" s="12">
+        <v>35</v>
+      </c>
+      <c r="B40" s="12" t="s">
+        <v>80</v>
+      </c>
+      <c r="C40" s="1" t="str">
+        <f>_xlfn.TEXTJOIN("|",TRUE,S40:W40)</f>
+        <v>3101760_1000|2584800_1000|2067840_1000|1550880_1000|1033920_1000</v>
+      </c>
+      <c r="G40" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="H40" s="1">
+        <f>ROUND(L36/(E36*H39/100/H36),0)</f>
+        <v>2067840</v>
+      </c>
+      <c r="I40" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="C36" s="2" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="37" spans="1:23">
-      <c r="A37" s="12">
-        <v>33</v>
-      </c>
-      <c r="B37" s="12" t="s">
-        <v>74</v>
-      </c>
-      <c r="C37" s="1" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="38" s="2" customFormat="1" spans="1:23">
-      <c r="A38" s="11">
-        <v>34</v>
-      </c>
-      <c r="B38" s="11" t="s">
-        <v>76</v>
-      </c>
-      <c r="C38" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="G38" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="H38" s="2">
-        <f>VALUE(MID(C38,FIND("_",C38)+1,4))</f>
-        <v>90</v>
-      </c>
-    </row>
-    <row r="39" spans="1:23">
-      <c r="A39" s="12">
-        <v>35</v>
-      </c>
-      <c r="B39" s="12" t="s">
-        <v>79</v>
-      </c>
-      <c r="C39" s="1" t="str">
-        <f>_xlfn.TEXTJOIN("|",TRUE,S39:W39)</f>
-        <v>3101760_1000|2584800_1000|2067840_1000|1550880_1000|1033920_1000</v>
-      </c>
-      <c r="G39" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="H39" s="1">
-        <f>ROUND(L35/(E35*H38/100/H35),0)</f>
+      <c r="J40" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="K40" s="13" t="s">
+        <v>83</v>
+      </c>
+      <c r="L40" s="13">
+        <v>0.25</v>
+      </c>
+      <c r="M40" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="N40" s="1">
+        <f>ROUND(P40*(1+2*L40),0)</f>
+        <v>3101760</v>
+      </c>
+      <c r="O40" s="1">
+        <f>ROUND(P40*(1+1*L40),0)</f>
+        <v>2584800</v>
+      </c>
+      <c r="P40" s="1">
+        <f>H40</f>
         <v>2067840</v>
       </c>
-      <c r="I39" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="J39" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="K39" s="13" t="s">
-        <v>82</v>
-      </c>
-      <c r="L39" s="13">
-        <v>0.25</v>
-      </c>
-      <c r="M39" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="N39" s="1">
-        <f>ROUND(P39*(1+2*L39),0)</f>
-        <v>3101760</v>
-      </c>
-      <c r="O39" s="1">
-        <f>ROUND(P39*(1+1*L39),0)</f>
-        <v>2584800</v>
-      </c>
-      <c r="P39" s="1">
-        <f>H39</f>
-        <v>2067840</v>
-      </c>
-      <c r="Q39" s="1">
-        <f>ROUND(P39*(1-1*L39),0)</f>
+      <c r="Q40" s="1">
+        <f>ROUND(P40*(1-1*L40),0)</f>
         <v>1550880</v>
       </c>
-      <c r="R39" s="1">
-        <f>ROUND(P39*(1-2*L39),0)</f>
+      <c r="R40" s="1">
+        <f>ROUND(P40*(1-2*L40),0)</f>
         <v>1033920</v>
       </c>
-      <c r="S39" s="1" t="str">
-        <f>_xlfn.TEXTJOIN("_",TRUE,N39,1000)</f>
+      <c r="S40" s="1" t="str">
+        <f>_xlfn.TEXTJOIN("_",TRUE,N40,1000)</f>
         <v>3101760_1000</v>
       </c>
-      <c r="T39" s="1" t="str">
-        <f>_xlfn.TEXTJOIN("_",TRUE,O39,1000)</f>
+      <c r="T40" s="1" t="str">
+        <f>_xlfn.TEXTJOIN("_",TRUE,O40,1000)</f>
         <v>2584800_1000</v>
       </c>
-      <c r="U39" s="1" t="str">
-        <f>_xlfn.TEXTJOIN("_",TRUE,P39,1000)</f>
+      <c r="U40" s="1" t="str">
+        <f>_xlfn.TEXTJOIN("_",TRUE,P40,1000)</f>
         <v>2067840_1000</v>
       </c>
-      <c r="V39" s="1" t="str">
-        <f>_xlfn.TEXTJOIN("_",TRUE,Q39,1000)</f>
+      <c r="V40" s="1" t="str">
+        <f>_xlfn.TEXTJOIN("_",TRUE,Q40,1000)</f>
         <v>1550880_1000</v>
       </c>
-      <c r="W39" s="1" t="str">
-        <f>_xlfn.TEXTJOIN("_",TRUE,R39,1000)</f>
+      <c r="W40" s="1" t="str">
+        <f>_xlfn.TEXTJOIN("_",TRUE,R40,1000)</f>
         <v>1033920_1000</v>
-      </c>
-    </row>
-    <row r="40" spans="1:23">
-      <c r="A40" s="14">
-        <v>40</v>
-      </c>
-      <c r="B40" s="14" t="s">
-        <v>84</v>
-      </c>
-      <c r="D40" s="1">
-        <v>50</v>
       </c>
     </row>
     <row r="41" spans="1:23">
       <c r="A41" s="14">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B41" s="14" t="s">
         <v>85</v>
@@ -2125,112 +2132,134 @@
     </row>
     <row r="42" spans="1:23">
       <c r="A42" s="14">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B42" s="14" t="s">
         <v>86</v>
       </c>
       <c r="D42" s="1">
-        <v>500</v>
+        <v>50</v>
       </c>
     </row>
     <row r="43" spans="1:23">
       <c r="A43" s="14">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B43" s="14" t="s">
         <v>87</v>
       </c>
       <c r="D43" s="1">
-        <v>1</v>
+        <v>500</v>
       </c>
     </row>
     <row r="44" spans="1:23">
       <c r="A44" s="14">
-        <v>44</v>
-      </c>
-      <c r="B44" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B44" s="14" t="s">
         <v>88</v>
       </c>
       <c r="D44" s="1">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="45" spans="1:23">
       <c r="A45" s="14">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="C45" s="1" t="s">
+      <c r="D45" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="46" spans="1:23">
+      <c r="A46" s="14">
+        <v>45</v>
+      </c>
+      <c r="B46" s="1" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="46" spans="1:23">
-      <c r="A46" s="1">
-        <v>46</v>
-      </c>
-      <c r="B46" s="1" t="s">
+      <c r="C46" s="1" t="s">
         <v>91</v>
-      </c>
-      <c r="C46" s="1" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="47" spans="1:23">
       <c r="A47" s="1">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="D47" s="1">
-        <v>3</v>
+      <c r="C47" s="1" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="48" spans="1:23">
       <c r="A48" s="1">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="C48" s="1" t="s">
-        <v>94</v>
+      <c r="D48" s="1">
+        <v>3</v>
       </c>
     </row>
     <row r="49" spans="1:4">
       <c r="A49" s="1">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B49" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="C49" s="1" t="s">
         <v>95</v>
-      </c>
-      <c r="C49" s="15" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="50" spans="1:4">
       <c r="A50" s="1">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B50" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="C50" s="15" t="s">
         <v>97</v>
-      </c>
-      <c r="D50" s="1">
-        <v>700000</v>
       </c>
     </row>
     <row r="51" spans="1:4">
       <c r="A51" s="1">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>98</v>
       </c>
       <c r="D51" s="1">
         <v>700000</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4">
+      <c r="A52" s="1">
+        <v>53</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="D52" s="1">
+        <v>700000</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4">
+      <c r="A53" s="1">
+        <v>54</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="D53" s="1">
+        <v>700</v>
       </c>
     </row>
   </sheetData>

--- a/gm/resources/sample/global.xlsx
+++ b/gm/resources/sample/global.xlsx
@@ -101,6 +101,28 @@
         </r>
       </text>
     </comment>
+    <comment ref="B50" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+废弃</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
@@ -396,45 +418,10 @@
     <t>1990000_700000</t>
   </si>
   <si>
-    <t>手机短信区号</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <charset val="134"/>
-      </rPr>
-      <t>‌</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="微软雅黑"/>
-        <charset val="134"/>
-      </rPr>
-      <t>84</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <charset val="134"/>
-      </rPr>
-      <t>‌</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="微软雅黑"/>
-        <charset val="134"/>
-      </rPr>
-      <t>_91_351</t>
-    </r>
+    <t>手机短信区号（印度、巴基斯坦、菲律宾、巴西、尼日利亚）废弃</t>
+  </si>
+  <si>
+    <t>‌91_92_63_55_234</t>
   </si>
   <si>
     <t>VIP充值返利给金币时的金币数量，金币数量 = 返利金额 * 此值</t>
@@ -484,7 +471,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color theme="0" tint="-0.25"/>
       <name val="Times New Roman"/>
       <charset val="134"/>
     </font>
@@ -633,12 +620,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -2218,11 +2205,11 @@
         <v>95</v>
       </c>
     </row>
-    <row r="50" spans="1:4">
-      <c r="A50" s="1">
+    <row r="50" s="2" customFormat="1" spans="1:4">
+      <c r="A50" s="2">
         <v>51</v>
       </c>
-      <c r="B50" s="1" t="s">
+      <c r="B50" s="2" t="s">
         <v>96</v>
       </c>
       <c r="C50" s="15" t="s">

--- a/gm/resources/sample/global.xlsx
+++ b/gm/resources/sample/global.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="11925"/>
   </bookViews>
   <sheets>
     <sheet name="globalConfig" sheetId="1" r:id="rId1"/>
@@ -1908,7 +1908,7 @@
         <v>60</v>
       </c>
       <c r="D31" s="1">
-        <v>9900</v>
+        <v>10000</v>
       </c>
       <c r="G31" s="1" t="s">
         <v>61</v>

--- a/gm/resources/sample/global.xlsx
+++ b/gm/resources/sample/global.xlsx
@@ -128,7 +128,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="102">
   <si>
     <t>sid</t>
   </si>
@@ -407,6 +407,9 @@
   </si>
   <si>
     <t>VIP充值：充值金额与经验转换比例(充值金额_获得vip经验，最低支持0.01_1，美元)</t>
+  </si>
+  <si>
+    <t>0.01_20000</t>
   </si>
   <si>
     <t>积分大奖：实物奖励兑换码过期时间（天）</t>
@@ -620,12 +623,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -2180,7 +2183,7 @@
         <v>92</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>76</v>
+        <v>93</v>
       </c>
     </row>
     <row r="48" spans="1:23">
@@ -2188,7 +2191,7 @@
         <v>47</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D48" s="1">
         <v>3</v>
@@ -2199,10 +2202,10 @@
         <v>50</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="50" s="2" customFormat="1" spans="1:4">
@@ -2210,10 +2213,10 @@
         <v>51</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C50" s="15" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2221,7 +2224,7 @@
         <v>52</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D51" s="1">
         <v>700000</v>
@@ -2232,7 +2235,7 @@
         <v>53</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D52" s="1">
         <v>700000</v>
@@ -2243,7 +2246,7 @@
         <v>54</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D53" s="1">
         <v>700</v>

--- a/gm/resources/sample/global.xlsx
+++ b/gm/resources/sample/global.xlsx
@@ -32,6 +32,28 @@
     <author>Administrator</author>
   </authors>
   <commentList>
+    <comment ref="D16" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+赢家抽3%，再次基础上再抽3333/10000返给房主</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="G18" authorId="0">
       <text>
         <r>
@@ -623,12 +645,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1732,7 +1754,7 @@
         <v>35</v>
       </c>
       <c r="D16" s="1">
-        <v>100</v>
+        <v>3333</v>
       </c>
       <c r="G16" s="1" t="s">
         <v>36</v>

--- a/gm/resources/sample/global.xlsx
+++ b/gm/resources/sample/global.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="11925"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="globalConfig" sheetId="1" r:id="rId1"/>
@@ -377,10 +377,10 @@
     <t>100000_1</t>
   </si>
   <si>
-    <t>官方派奖：充值转换积分比例 ：充值金额 = X积分</t>
-  </si>
-  <si>
-    <t>1_1</t>
+    <t>官方派奖：充值转换积分比例 ：充值金额（1 美元 = 100 积分 )</t>
+  </si>
+  <si>
+    <t>1_100</t>
   </si>
   <si>
     <t>官方派奖：真人和机器人奖池比例(百分比)  （废弃，功能不存在）</t>
@@ -645,12 +645,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>

--- a/gm/resources/sample/global.xlsx
+++ b/gm/resources/sample/global.xlsx
@@ -145,6 +145,74 @@
         </r>
       </text>
     </comment>
+    <comment ref="D51" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+值为0表示不返利</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D52" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+值为0表示不返利
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D53" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+值为0表示不返利
+</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
@@ -645,12 +713,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -2271,7 +2339,7 @@
         <v>101</v>
       </c>
       <c r="D53" s="1">
-        <v>700</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/gm/resources/sample/global.xlsx
+++ b/gm/resources/sample/global.xlsx
@@ -213,12 +213,34 @@
         </r>
       </text>
     </comment>
+    <comment ref="C54" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+配置几月几号领取，就在当天可领取奖励</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="106">
   <si>
     <t>sid</t>
   </si>
@@ -524,6 +546,18 @@
   </si>
   <si>
     <t>VIP充值返利给钻石时的钻石数量，钻石数量 = 返利金额 * 此值</t>
+  </si>
+  <si>
+    <t>VIP季度奖励领取时间(月份1日期1_月份2日期2_月份3日期3_月份4日期4)</t>
+  </si>
+  <si>
+    <t>0331_0630_0930_1231</t>
+  </si>
+  <si>
+    <t>推广分享链接及宣传图</t>
+  </si>
+  <si>
+    <t>itemicon_1990000.png_https://1plhi02.jpz4yb3q.com/chatwindow.aspx?siteId=65002831&amp;planId=c245fbe6-4ec5-46d6-8542-657f871cc0b3</t>
   </si>
 </sst>
 </file>
@@ -713,12 +747,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1555,7 +1589,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:W53"/>
+  <dimension ref="A1:W55"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
@@ -2342,6 +2376,28 @@
         <v>0</v>
       </c>
     </row>
+    <row r="54" spans="1:4">
+      <c r="A54" s="1">
+        <v>56</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4">
+      <c r="A55" s="1">
+        <v>60</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>105</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/gm/resources/sample/global.xlsx
+++ b/gm/resources/sample/global.xlsx
@@ -240,7 +240,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="108">
   <si>
     <t>sid</t>
   </si>
@@ -558,6 +558,12 @@
   </si>
   <si>
     <t>itemicon_1990000.png_https://1plhi02.jpz4yb3q.com/chatwindow.aspx?siteId=65002831&amp;planId=c245fbe6-4ec5-46d6-8542-657f871cc0b3</t>
+  </si>
+  <si>
+    <t>隐私政策链接</t>
+  </si>
+  <si>
+    <t>http://chat.kinghush.com/privacy.html</t>
   </si>
 </sst>
 </file>
@@ -747,12 +753,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1233,7 +1239,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1264,6 +1270,7 @@
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="6" applyAlignment="1"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" quotePrefix="1">
       <alignment vertical="center"/>
     </xf>
@@ -1589,7 +1596,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:W55"/>
+  <dimension ref="A1:W56"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
@@ -1758,7 +1765,7 @@
       <c r="B10" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="C10" s="16" t="s">
+      <c r="C10" s="17" t="s">
         <v>24</v>
       </c>
       <c r="D10" s="8"/>
@@ -1775,7 +1782,7 @@
       <c r="B11" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="C11" s="17" t="s">
+      <c r="C11" s="18" t="s">
         <v>27</v>
       </c>
       <c r="D11" s="6"/>
@@ -1792,7 +1799,7 @@
       <c r="B12" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="C12" s="17" t="s">
+      <c r="C12" s="18" t="s">
         <v>29</v>
       </c>
       <c r="D12" s="6"/>
@@ -1809,7 +1816,7 @@
       <c r="B13" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="C13" s="17" t="s">
+      <c r="C13" s="18" t="s">
         <v>31</v>
       </c>
       <c r="D13" s="6"/>
@@ -1826,7 +1833,7 @@
       <c r="B14" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="C14" s="17" t="s">
+      <c r="C14" s="18" t="s">
         <v>33</v>
       </c>
       <c r="D14" s="6"/>
@@ -2396,6 +2403,17 @@
       </c>
       <c r="C55" s="1" t="s">
         <v>105</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4">
+      <c r="A56" s="1">
+        <v>61</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C56" s="16" t="s">
+        <v>107</v>
       </c>
     </row>
   </sheetData>

--- a/gm/resources/sample/global.xlsx
+++ b/gm/resources/sample/global.xlsx
@@ -557,7 +557,7 @@
     <t>推广分享链接及宣传图</t>
   </si>
   <si>
-    <t>itemicon_1990000.png_https://1plhi02.jpz4yb3q.com/chatwindow.aspx?siteId=65002831&amp;planId=c245fbe6-4ec5-46d6-8542-657f871cc0b3</t>
+    <t>https://aws-s3-jjg-asset-bucket.s3.ap-southeast-1.amazonaws.com/tanchuang_res/english/tc_sc_1.png</t>
   </si>
   <si>
     <t>隐私政策链接</t>
@@ -576,7 +576,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="26">
+  <fonts count="27">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -606,6 +606,12 @@
       <sz val="11"/>
       <color theme="0" tint="-0.25"/>
       <name val="Times New Roman"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
+      <color rgb="FF006CE0"/>
+      <name val="Arial"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1109,137 +1115,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1270,7 +1276,8 @@
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="6" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="6" applyAlignment="1"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" quotePrefix="1">
       <alignment vertical="center"/>
     </xf>
@@ -1765,7 +1772,7 @@
       <c r="B10" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="C10" s="17" t="s">
+      <c r="C10" s="18" t="s">
         <v>24</v>
       </c>
       <c r="D10" s="8"/>
@@ -1782,7 +1789,7 @@
       <c r="B11" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="C11" s="18" t="s">
+      <c r="C11" s="19" t="s">
         <v>27</v>
       </c>
       <c r="D11" s="6"/>
@@ -1799,7 +1806,7 @@
       <c r="B12" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="C12" s="18" t="s">
+      <c r="C12" s="19" t="s">
         <v>29</v>
       </c>
       <c r="D12" s="6"/>
@@ -1816,7 +1823,7 @@
       <c r="B13" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="C13" s="18" t="s">
+      <c r="C13" s="19" t="s">
         <v>31</v>
       </c>
       <c r="D13" s="6"/>
@@ -1833,7 +1840,7 @@
       <c r="B14" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="C14" s="18" t="s">
+      <c r="C14" s="19" t="s">
         <v>33</v>
       </c>
       <c r="D14" s="6"/>
@@ -2401,7 +2408,7 @@
       <c r="B55" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="C55" s="1" t="s">
+      <c r="C55" s="16" t="s">
         <v>105</v>
       </c>
     </row>
@@ -2412,11 +2419,14 @@
       <c r="B56" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="C56" s="16" t="s">
+      <c r="C56" s="17" t="s">
         <v>107</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="C55" r:id="rId3" display="https://aws-s3-jjg-asset-bucket.s3.ap-southeast-1.amazonaws.com/tanchuang_res/english/tc_sc_1.png" tooltip="https://aws-s3-jjg-asset-bucket.s3.ap-southeast-1.amazonaws.com/tanchuang_res/english/tc_sc_1.png"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>

--- a/gm/resources/sample/global.xlsx
+++ b/gm/resources/sample/global.xlsx
@@ -240,7 +240,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="112">
   <si>
     <t>sid</t>
   </si>
@@ -515,7 +515,7 @@
     <t>积分大奖：积分保底奖励（积分数量_奖励道具ID_奖励道具数量）</t>
   </si>
   <si>
-    <t>360_1990000_1400000|960_1990000_2800000|1800_1990000_5600000|2400_1990000_14000000|3000_1990000_35000000|3600_1990000_105000000</t>
+    <t>100_1990000_700000|400_1990000_2800000|800_1990000_5600000|1100_1990000_7700000|1600_1990000_11200000|2500_1990000_17500000</t>
   </si>
   <si>
     <t>VIP充值：充值金额与经验转换比例(充值金额_获得vip经验，最低支持0.01_1，美元)</t>
@@ -564,6 +564,18 @@
   </si>
   <si>
     <t>http://chat.kinghush.com/privacy.html</t>
+  </si>
+  <si>
+    <t>推广分享：分享1人得固定奖励</t>
+  </si>
+  <si>
+    <t>1990000_200000</t>
+  </si>
+  <si>
+    <t>推广分享：二维码图片配置(该资源放在资源服务器实时下载显示的)</t>
+  </si>
+  <si>
+    <t>QR_Code001.png</t>
   </si>
 </sst>
 </file>
@@ -1603,7 +1615,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:W56"/>
+  <dimension ref="A1:W58"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
@@ -2423,6 +2435,28 @@
         <v>107</v>
       </c>
     </row>
+    <row r="57" spans="1:4">
+      <c r="A57" s="1">
+        <v>62</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4">
+      <c r="A58" s="1">
+        <v>63</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>111</v>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="C55" r:id="rId3" display="https://aws-s3-jjg-asset-bucket.s3.ap-southeast-1.amazonaws.com/tanchuang_res/english/tc_sc_1.png" tooltip="https://aws-s3-jjg-asset-bucket.s3.ap-southeast-1.amazonaws.com/tanchuang_res/english/tc_sc_1.png"/>

--- a/gm/resources/sample/global.xlsx
+++ b/gm/resources/sample/global.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="11925"/>
   </bookViews>
   <sheets>
     <sheet name="globalConfig" sheetId="1" r:id="rId1"/>
@@ -240,7 +240,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="115">
   <si>
     <t>sid</t>
   </si>
@@ -569,13 +569,22 @@
     <t>推广分享：分享1人得固定奖励</t>
   </si>
   <si>
-    <t>1990000_200000</t>
+    <t>1990000_630000</t>
   </si>
   <si>
     <t>推广分享：二维码图片配置(该资源放在资源服务器实时下载显示的)</t>
   </si>
   <si>
     <t>QR_Code001.png</t>
+  </si>
+  <si>
+    <t>财富轮盘：昨日输的金币兑换为积分的比例（昨日所输金币_获得积分）</t>
+  </si>
+  <si>
+    <t>1000000_1</t>
+  </si>
+  <si>
+    <t>财富轮盘：每次抽奖所消耗的积分</t>
   </si>
 </sst>
 </file>
@@ -1615,7 +1624,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:W58"/>
+  <dimension ref="A1:W60"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
@@ -2457,6 +2466,28 @@
         <v>111</v>
       </c>
     </row>
+    <row r="59" spans="1:4">
+      <c r="A59" s="1">
+        <v>70</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4">
+      <c r="A60" s="1">
+        <v>71</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="D60" s="1">
+        <v>10</v>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="C55" r:id="rId3" display="https://aws-s3-jjg-asset-bucket.s3.ap-southeast-1.amazonaws.com/tanchuang_res/english/tc_sc_1.png" tooltip="https://aws-s3-jjg-asset-bucket.s3.ap-southeast-1.amazonaws.com/tanchuang_res/english/tc_sc_1.png"/>

--- a/gm/resources/sample/global.xlsx
+++ b/gm/resources/sample/global.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="11925"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="globalConfig" sheetId="1" r:id="rId1"/>
@@ -240,7 +240,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="117">
   <si>
     <t>sid</t>
   </si>
@@ -575,7 +575,7 @@
     <t>推广分享：二维码图片配置(该资源放在资源服务器实时下载显示的)</t>
   </si>
   <si>
-    <t>QR_Code001.png</t>
+    <t>ShareQRCode/QR_Code001.png</t>
   </si>
   <si>
     <t>财富轮盘：昨日输的金币兑换为积分的比例（昨日所输金币_获得积分）</t>
@@ -585,6 +585,12 @@
   </si>
   <si>
     <t>财富轮盘：每次抽奖所消耗的积分</t>
+  </si>
+  <si>
+    <t>推广分享：周榜上榜条件设置(收益数量)</t>
+  </si>
+  <si>
+    <t>1990000_10000</t>
   </si>
 </sst>
 </file>
@@ -631,7 +637,7 @@
     </font>
     <font>
       <sz val="10.5"/>
-      <color rgb="FF006CE0"/>
+      <color theme="0" tint="-0.25"/>
       <name val="Arial"/>
       <charset val="134"/>
     </font>
@@ -780,12 +786,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1624,7 +1630,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:W60"/>
+  <dimension ref="A1:W61"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
@@ -2422,11 +2428,11 @@
         <v>103</v>
       </c>
     </row>
-    <row r="55" spans="1:4">
-      <c r="A55" s="1">
+    <row r="55" s="2" customFormat="1" spans="1:4">
+      <c r="A55" s="2">
         <v>60</v>
       </c>
-      <c r="B55" s="1" t="s">
+      <c r="B55" s="2" t="s">
         <v>104</v>
       </c>
       <c r="C55" s="16" t="s">
@@ -2486,6 +2492,17 @@
       </c>
       <c r="D60" s="1">
         <v>10</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4">
+      <c r="A61" s="1">
+        <v>72</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>116</v>
       </c>
     </row>
   </sheetData>

--- a/gm/resources/sample/global.xlsx
+++ b/gm/resources/sample/global.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="11925"/>
   </bookViews>
   <sheets>
     <sheet name="globalConfig" sheetId="1" r:id="rId1"/>
@@ -578,6 +578,12 @@
     <t>ShareQRCode/QR_Code001.png</t>
   </si>
   <si>
+    <t>推广分享：周榜上榜条件设置(收益数量)</t>
+  </si>
+  <si>
+    <t>1990000_10000</t>
+  </si>
+  <si>
     <t>财富轮盘：昨日输的金币兑换为积分的比例（昨日所输金币_获得积分）</t>
   </si>
   <si>
@@ -585,12 +591,6 @@
   </si>
   <si>
     <t>财富轮盘：每次抽奖所消耗的积分</t>
-  </si>
-  <si>
-    <t>推广分享：周榜上榜条件设置(收益数量)</t>
-  </si>
-  <si>
-    <t>1990000_10000</t>
   </si>
 </sst>
 </file>
@@ -786,12 +786,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -2474,7 +2474,7 @@
     </row>
     <row r="59" spans="1:4">
       <c r="A59" s="1">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="B59" s="1" t="s">
         <v>112</v>
@@ -2485,24 +2485,24 @@
     </row>
     <row r="60" spans="1:4">
       <c r="A60" s="1">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B60" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="D60" s="1">
-        <v>10</v>
+      <c r="C60" s="1" t="s">
+        <v>115</v>
       </c>
     </row>
     <row r="61" spans="1:4">
       <c r="A61" s="1">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="C61" s="1" t="s">
         <v>116</v>
+      </c>
+      <c r="D61" s="1">
+        <v>10</v>
       </c>
     </row>
   </sheetData>

--- a/gm/resources/sample/global.xlsx
+++ b/gm/resources/sample/global.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="11925"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="globalConfig" sheetId="1" r:id="rId1"/>
@@ -240,7 +240,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="118">
   <si>
     <t>sid</t>
   </si>
@@ -591,6 +591,9 @@
   </si>
   <si>
     <t>财富轮盘：每次抽奖所消耗的积分</t>
+  </si>
+  <si>
+    <t>买一送七：限购时间，单位秒，活动开始后到此倒计时结束之间才能付费参与活动</t>
   </si>
 </sst>
 </file>
@@ -1272,7 +1275,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1305,6 +1308,11 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="6" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" quotePrefix="1">
       <alignment vertical="center"/>
     </xf>
@@ -1630,11 +1638,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:W61"/>
+  <dimension ref="A1:W62"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
-    <col min="2" max="2" width="65.375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="69" style="1" customWidth="1"/>
     <col min="3" max="3" width="37.625" style="1" customWidth="1"/>
     <col min="4" max="4" width="9.375" style="1" customWidth="1"/>
     <col min="5" max="5" width="11.5" style="1" customWidth="1"/>
@@ -1799,7 +1807,7 @@
       <c r="B10" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="C10" s="18" t="s">
+      <c r="C10" s="21" t="s">
         <v>24</v>
       </c>
       <c r="D10" s="8"/>
@@ -1816,7 +1824,7 @@
       <c r="B11" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="C11" s="19" t="s">
+      <c r="C11" s="22" t="s">
         <v>27</v>
       </c>
       <c r="D11" s="6"/>
@@ -1833,7 +1841,7 @@
       <c r="B12" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="C12" s="19" t="s">
+      <c r="C12" s="22" t="s">
         <v>29</v>
       </c>
       <c r="D12" s="6"/>
@@ -1850,7 +1858,7 @@
       <c r="B13" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="C13" s="19" t="s">
+      <c r="C13" s="22" t="s">
         <v>31</v>
       </c>
       <c r="D13" s="6"/>
@@ -1867,7 +1875,7 @@
       <c r="B14" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="C14" s="19" t="s">
+      <c r="C14" s="22" t="s">
         <v>33</v>
       </c>
       <c r="D14" s="6"/>
@@ -2362,7 +2370,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="49" spans="1:4">
+    <row r="49" spans="1:20">
       <c r="A49" s="1">
         <v>50</v>
       </c>
@@ -2373,7 +2381,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="50" s="2" customFormat="1" spans="1:4">
+    <row r="50" s="2" customFormat="1" spans="1:20">
       <c r="A50" s="2">
         <v>51</v>
       </c>
@@ -2384,7 +2392,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="51" spans="1:4">
+    <row r="51" spans="1:20">
       <c r="A51" s="1">
         <v>52</v>
       </c>
@@ -2395,7 +2403,7 @@
         <v>700000</v>
       </c>
     </row>
-    <row r="52" spans="1:4">
+    <row r="52" spans="1:20">
       <c r="A52" s="1">
         <v>53</v>
       </c>
@@ -2406,7 +2414,7 @@
         <v>700000</v>
       </c>
     </row>
-    <row r="53" spans="1:4">
+    <row r="53" spans="1:20">
       <c r="A53" s="1">
         <v>54</v>
       </c>
@@ -2417,7 +2425,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:4">
+    <row r="54" spans="1:20">
       <c r="A54" s="1">
         <v>56</v>
       </c>
@@ -2428,7 +2436,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="55" s="2" customFormat="1" spans="1:4">
+    <row r="55" s="2" customFormat="1" spans="1:20">
       <c r="A55" s="2">
         <v>60</v>
       </c>
@@ -2439,7 +2447,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="56" spans="1:4">
+    <row r="56" spans="1:20">
       <c r="A56" s="1">
         <v>61</v>
       </c>
@@ -2450,7 +2458,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="57" spans="1:4">
+    <row r="57" spans="1:20">
       <c r="A57" s="1">
         <v>62</v>
       </c>
@@ -2461,7 +2469,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="58" spans="1:4">
+    <row r="58" spans="1:20">
       <c r="A58" s="1">
         <v>63</v>
       </c>
@@ -2472,7 +2480,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="59" spans="1:4">
+    <row r="59" spans="1:20">
       <c r="A59" s="1">
         <v>64</v>
       </c>
@@ -2483,7 +2491,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="60" spans="1:4">
+    <row r="60" spans="1:20">
       <c r="A60" s="1">
         <v>70</v>
       </c>
@@ -2494,7 +2502,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="61" spans="1:4">
+    <row r="61" spans="1:20">
       <c r="A61" s="1">
         <v>71</v>
       </c>
@@ -2504,6 +2512,34 @@
       <c r="D61" s="1">
         <v>10</v>
       </c>
+    </row>
+    <row r="62" spans="1:20">
+      <c r="A62" s="18">
+        <v>80</v>
+      </c>
+      <c r="B62" s="19" t="s">
+        <v>117</v>
+      </c>
+      <c r="C62" s="18"/>
+      <c r="D62" s="18">
+        <v>259200</v>
+      </c>
+      <c r="E62" s="20"/>
+      <c r="F62" s="20"/>
+      <c r="G62" s="20"/>
+      <c r="H62" s="20"/>
+      <c r="I62" s="20"/>
+      <c r="J62" s="20"/>
+      <c r="K62" s="20"/>
+      <c r="L62" s="20"/>
+      <c r="M62" s="20"/>
+      <c r="N62" s="20"/>
+      <c r="O62" s="20"/>
+      <c r="P62" s="20"/>
+      <c r="Q62" s="20"/>
+      <c r="R62" s="20"/>
+      <c r="S62" s="20"/>
+      <c r="T62" s="20"/>
     </row>
   </sheetData>
   <hyperlinks>

--- a/gm/resources/sample/global.xlsx
+++ b/gm/resources/sample/global.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="globalConfig" sheetId="1" r:id="rId1"/>
@@ -600,11 +600,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
+  <numFmts count="5">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="0_ "/>
   </numFmts>
   <fonts count="27">
     <font>
@@ -1275,7 +1276,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1303,16 +1304,13 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="6" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" quotePrefix="1">
       <alignment vertical="center"/>
     </xf>
@@ -1648,7 +1646,7 @@
     <col min="5" max="5" width="11.5" style="1" customWidth="1"/>
     <col min="6" max="6" width="9.625" style="1" customWidth="1"/>
     <col min="7" max="7" width="23.375" style="1" customWidth="1"/>
-    <col min="8" max="8" width="9.25" style="1"/>
+    <col min="8" max="8" width="12.75" style="1"/>
     <col min="9" max="9" width="9" style="1"/>
     <col min="10" max="10" width="11.5" style="1"/>
     <col min="11" max="11" width="9" style="1"/>
@@ -1807,7 +1805,7 @@
       <c r="B10" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="C10" s="21" t="s">
+      <c r="C10" s="20" t="s">
         <v>24</v>
       </c>
       <c r="D10" s="8"/>
@@ -1824,7 +1822,7 @@
       <c r="B11" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="C11" s="22" t="s">
+      <c r="C11" s="21" t="s">
         <v>27</v>
       </c>
       <c r="D11" s="6"/>
@@ -1841,7 +1839,7 @@
       <c r="B12" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="C12" s="22" t="s">
+      <c r="C12" s="21" t="s">
         <v>29</v>
       </c>
       <c r="D12" s="6"/>
@@ -1858,7 +1856,7 @@
       <c r="B13" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="C13" s="22" t="s">
+      <c r="C13" s="21" t="s">
         <v>31</v>
       </c>
       <c r="D13" s="6"/>
@@ -1875,7 +1873,7 @@
       <c r="B14" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="C14" s="22" t="s">
+      <c r="C14" s="21" t="s">
         <v>33</v>
       </c>
       <c r="D14" s="6"/>
@@ -2143,26 +2141,26 @@
         <v>68</v>
       </c>
       <c r="E36" s="2">
-        <v>1000000000</v>
+        <v>20989402.5988449</v>
       </c>
       <c r="G36" s="2" t="s">
         <v>69</v>
       </c>
       <c r="H36" s="2">
-        <v>718000</v>
+        <v>1049470.12994225</v>
       </c>
       <c r="I36" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J36" s="2">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="K36" s="2" t="s">
         <v>71</v>
       </c>
       <c r="L36" s="2">
         <f>J36*24*60*60*1000</f>
-        <v>2592000000</v>
+        <v>86400000</v>
       </c>
       <c r="M36" s="2" t="s">
         <v>72</v>
@@ -2204,8 +2202,11 @@
         <v>79</v>
       </c>
       <c r="H39" s="2">
-        <f>VALUE(MID(C39,FIND("_",C39)+1,4))</f>
-        <v>90</v>
+        <v>30</v>
+      </c>
+      <c r="J39" s="2">
+        <f>H40/1000/60/60</f>
+        <v>4</v>
       </c>
     </row>
     <row r="40" spans="1:23">
@@ -2217,14 +2218,14 @@
       </c>
       <c r="C40" s="1" t="str">
         <f>_xlfn.TEXTJOIN("|",TRUE,S40:W40)</f>
-        <v>3101760_1000|2584800_1000|2067840_1000|1550880_1000|1033920_1000</v>
+        <v>21600000_1000|18000000_1000|14400000_1000|10800000_1000|7200000_1000</v>
       </c>
       <c r="G40" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="H40" s="1">
+      <c r="H40" s="13">
         <f>ROUND(L36/(E36*H39/100/H36),0)</f>
-        <v>2067840</v>
+        <v>14400000</v>
       </c>
       <c r="I40" s="1" t="s">
         <v>72</v>
@@ -2232,10 +2233,10 @@
       <c r="J40" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="K40" s="13" t="s">
+      <c r="K40" s="14" t="s">
         <v>83</v>
       </c>
-      <c r="L40" s="13">
+      <c r="L40" s="14">
         <v>0.25</v>
       </c>
       <c r="M40" s="1" t="s">
@@ -2243,50 +2244,50 @@
       </c>
       <c r="N40" s="1">
         <f>ROUND(P40*(1+2*L40),0)</f>
-        <v>3101760</v>
+        <v>21600000</v>
       </c>
       <c r="O40" s="1">
         <f>ROUND(P40*(1+1*L40),0)</f>
-        <v>2584800</v>
+        <v>18000000</v>
       </c>
       <c r="P40" s="1">
         <f>H40</f>
-        <v>2067840</v>
+        <v>14400000</v>
       </c>
       <c r="Q40" s="1">
         <f>ROUND(P40*(1-1*L40),0)</f>
-        <v>1550880</v>
+        <v>10800000</v>
       </c>
       <c r="R40" s="1">
         <f>ROUND(P40*(1-2*L40),0)</f>
-        <v>1033920</v>
+        <v>7200000</v>
       </c>
       <c r="S40" s="1" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,N40,1000)</f>
-        <v>3101760_1000</v>
+        <v>21600000_1000</v>
       </c>
       <c r="T40" s="1" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,O40,1000)</f>
-        <v>2584800_1000</v>
+        <v>18000000_1000</v>
       </c>
       <c r="U40" s="1" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,P40,1000)</f>
-        <v>2067840_1000</v>
+        <v>14400000_1000</v>
       </c>
       <c r="V40" s="1" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,Q40,1000)</f>
-        <v>1550880_1000</v>
+        <v>10800000_1000</v>
       </c>
       <c r="W40" s="1" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,R40,1000)</f>
-        <v>1033920_1000</v>
+        <v>7200000_1000</v>
       </c>
     </row>
     <row r="41" spans="1:23">
-      <c r="A41" s="14">
+      <c r="A41" s="15">
         <v>40</v>
       </c>
-      <c r="B41" s="14" t="s">
+      <c r="B41" s="15" t="s">
         <v>85</v>
       </c>
       <c r="D41" s="1">
@@ -2294,10 +2295,10 @@
       </c>
     </row>
     <row r="42" spans="1:23">
-      <c r="A42" s="14">
+      <c r="A42" s="15">
         <v>41</v>
       </c>
-      <c r="B42" s="14" t="s">
+      <c r="B42" s="15" t="s">
         <v>86</v>
       </c>
       <c r="D42" s="1">
@@ -2305,10 +2306,10 @@
       </c>
     </row>
     <row r="43" spans="1:23">
-      <c r="A43" s="14">
+      <c r="A43" s="15">
         <v>42</v>
       </c>
-      <c r="B43" s="14" t="s">
+      <c r="B43" s="15" t="s">
         <v>87</v>
       </c>
       <c r="D43" s="1">
@@ -2316,10 +2317,10 @@
       </c>
     </row>
     <row r="44" spans="1:23">
-      <c r="A44" s="14">
+      <c r="A44" s="15">
         <v>43</v>
       </c>
-      <c r="B44" s="14" t="s">
+      <c r="B44" s="15" t="s">
         <v>88</v>
       </c>
       <c r="D44" s="1">
@@ -2327,7 +2328,7 @@
       </c>
     </row>
     <row r="45" spans="1:23">
-      <c r="A45" s="14">
+      <c r="A45" s="15">
         <v>44</v>
       </c>
       <c r="B45" s="1" t="s">
@@ -2338,7 +2339,7 @@
       </c>
     </row>
     <row r="46" spans="1:23">
-      <c r="A46" s="14">
+      <c r="A46" s="15">
         <v>45</v>
       </c>
       <c r="B46" s="1" t="s">
@@ -2388,7 +2389,7 @@
       <c r="B50" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="C50" s="15" t="s">
+      <c r="C50" s="16" t="s">
         <v>98</v>
       </c>
     </row>
@@ -2443,7 +2444,7 @@
       <c r="B55" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="C55" s="16" t="s">
+      <c r="C55" s="17" t="s">
         <v>105</v>
       </c>
     </row>
@@ -2454,7 +2455,7 @@
       <c r="B56" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="C56" s="17" t="s">
+      <c r="C56" s="18" t="s">
         <v>107</v>
       </c>
     </row>
@@ -2514,32 +2515,32 @@
       </c>
     </row>
     <row r="62" spans="1:20">
-      <c r="A62" s="18">
+      <c r="A62" s="19">
         <v>80</v>
       </c>
       <c r="B62" s="19" t="s">
         <v>117</v>
       </c>
-      <c r="C62" s="18"/>
-      <c r="D62" s="18">
+      <c r="C62" s="19"/>
+      <c r="D62" s="19">
         <v>259200</v>
       </c>
-      <c r="E62" s="20"/>
-      <c r="F62" s="20"/>
-      <c r="G62" s="20"/>
-      <c r="H62" s="20"/>
-      <c r="I62" s="20"/>
-      <c r="J62" s="20"/>
-      <c r="K62" s="20"/>
-      <c r="L62" s="20"/>
-      <c r="M62" s="20"/>
-      <c r="N62" s="20"/>
-      <c r="O62" s="20"/>
-      <c r="P62" s="20"/>
-      <c r="Q62" s="20"/>
-      <c r="R62" s="20"/>
-      <c r="S62" s="20"/>
-      <c r="T62" s="20"/>
+      <c r="E62" s="5"/>
+      <c r="F62" s="5"/>
+      <c r="G62" s="5"/>
+      <c r="H62" s="5"/>
+      <c r="I62" s="5"/>
+      <c r="J62" s="5"/>
+      <c r="K62" s="5"/>
+      <c r="L62" s="5"/>
+      <c r="M62" s="5"/>
+      <c r="N62" s="5"/>
+      <c r="O62" s="5"/>
+      <c r="P62" s="5"/>
+      <c r="Q62" s="5"/>
+      <c r="R62" s="5"/>
+      <c r="S62" s="5"/>
+      <c r="T62" s="5"/>
     </row>
   </sheetData>
   <hyperlinks>

--- a/gm/resources/sample/global.xlsx
+++ b/gm/resources/sample/global.xlsx
@@ -77,7 +77,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E36" authorId="0">
+    <comment ref="E35" authorId="0">
       <text>
         <r>
           <rPr>
@@ -101,7 +101,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C38" authorId="0">
+    <comment ref="C37" authorId="0">
       <text>
         <r>
           <rPr>
@@ -213,7 +213,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C54" authorId="0">
+    <comment ref="C55" authorId="0">
       <text>
         <r>
           <rPr>
@@ -235,12 +235,43 @@
         </r>
       </text>
     </comment>
+    <comment ref="C64" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">Administrator:
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>游戏大类_有效的游戏ID范围|……
+【游戏大类】
+1:slot类型游戏
+2:押注类游戏
+3:对战类游戏
+【有效的游戏ID】
+Warehouse表中的gameID
+-1:此类型的所有游戏
+100100：金矿大亨
+……</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="125">
   <si>
     <t>sid</t>
   </si>
@@ -437,117 +468,123 @@
     <t>幸运夺宝能配置商品数量上限</t>
   </si>
   <si>
+    <t>官方派奖每个转盘需求积分：初、中、高(字段废弃，配置移到ActivityConfig.xlsx)</t>
+  </si>
+  <si>
+    <t>10_200_5000</t>
+  </si>
+  <si>
+    <t>官方派奖转盘奖池金币数量（废弃，在活动配置表中配置）</t>
+  </si>
+  <si>
+    <t>从OfficialAwards表中取平均中奖金额</t>
+  </si>
+  <si>
+    <t>活动时间</t>
+  </si>
+  <si>
+    <t>天</t>
+  </si>
+  <si>
+    <t>毫秒</t>
+  </si>
+  <si>
+    <t>官方派奖：有效下注转换积分比例 ：有效下注 = X积分(字段废弃)</t>
+  </si>
+  <si>
+    <t>100000_1</t>
+  </si>
+  <si>
+    <t>官方派奖：充值转换积分比例 ：充值金额（1 美元 = 100 积分 )</t>
+  </si>
+  <si>
+    <t>1_100</t>
+  </si>
+  <si>
+    <t>官方派奖：真人和机器人奖池比例(百分比)  （废弃，功能不存在）</t>
+  </si>
+  <si>
+    <t>10_90</t>
+  </si>
+  <si>
+    <t>机器人奖池比例</t>
+  </si>
+  <si>
+    <t>官方派奖：机器人中奖间隔（毫秒_权重|毫秒_权重）</t>
+  </si>
+  <si>
+    <t>平均中奖间隔</t>
+  </si>
+  <si>
+    <t>共5档</t>
+  </si>
+  <si>
+    <t>每档偏移</t>
+  </si>
+  <si>
+    <t>每档时间</t>
+  </si>
+  <si>
+    <t>积分大奖： 转盘每次消耗积分数</t>
+  </si>
+  <si>
+    <t>积分大奖：时段榜-上榜的最低积分要求(上午榜、下午榜共用)</t>
+  </si>
+  <si>
+    <t>积分大奖：月总榜-上榜的最低积分要求</t>
+  </si>
+  <si>
+    <t>积分大奖：每日转盘默认初始次数上限</t>
+  </si>
+  <si>
+    <t>积分大奖：充值多少金额给一次转盘次数</t>
+  </si>
+  <si>
+    <t>积分大奖：积分保底奖励（积分数量_奖励道具ID_奖励道具数量）</t>
+  </si>
+  <si>
+    <t>100_1990000_700000|400_1990000_2800000|800_1990000_5600000|1100_1990000_7700000|1600_1990000_11200000|2500_1990000_17500000</t>
+  </si>
+  <si>
+    <t>VIP充值：充值金额与经验转换比例(充值金额_获得vip经验，最低支持0.01_1，美元)</t>
+  </si>
+  <si>
+    <t>0.01_20000</t>
+  </si>
+  <si>
+    <t>积分大奖：实物奖励兑换码过期时间（天）</t>
+  </si>
+  <si>
+    <t>积分大奖：占用榜单的机器人条件，活动开始X分钟后出现_VIP等级_玩家等级</t>
+  </si>
+  <si>
+    <t>20_5_600</t>
+  </si>
+  <si>
+    <t>新手奖励</t>
+  </si>
+  <si>
+    <t>1990000_700000</t>
+  </si>
+  <si>
+    <t>手机短信区号（印度、巴基斯坦、菲律宾、巴西、尼日利亚）废弃</t>
+  </si>
+  <si>
+    <t>‌91_92_63_55_234</t>
+  </si>
+  <si>
+    <t>VIP充值返利给金币时的金币数量，金币数量 = 返利金额 * 此值</t>
+  </si>
+  <si>
+    <t>推广分享给金币时的金币数量，金币数量 = 返利金额 * 此值</t>
+  </si>
+  <si>
+    <t>VIP充值返利给钻石时的钻石数量，钻石数量 = 返利金额 * 此值</t>
+  </si>
+  <si>
     <t>幸运夺宝开奖时间(秒)</t>
   </si>
   <si>
-    <t>官方派奖每个转盘需求积分：初、中、高(字段废弃，配置移到ActivityConfig.xlsx)</t>
-  </si>
-  <si>
-    <t>10_200_5000</t>
-  </si>
-  <si>
-    <t>官方派奖转盘奖池金币数量（废弃，在活动配置表中配置）</t>
-  </si>
-  <si>
-    <t>从OfficialAwards表中取平均中奖金额</t>
-  </si>
-  <si>
-    <t>活动时间</t>
-  </si>
-  <si>
-    <t>天</t>
-  </si>
-  <si>
-    <t>毫秒</t>
-  </si>
-  <si>
-    <t>官方派奖：有效下注转换积分比例 ：有效下注 = X积分(字段废弃)</t>
-  </si>
-  <si>
-    <t>100000_1</t>
-  </si>
-  <si>
-    <t>官方派奖：充值转换积分比例 ：充值金额（1 美元 = 100 积分 )</t>
-  </si>
-  <si>
-    <t>1_100</t>
-  </si>
-  <si>
-    <t>官方派奖：真人和机器人奖池比例(百分比)  （废弃，功能不存在）</t>
-  </si>
-  <si>
-    <t>10_90</t>
-  </si>
-  <si>
-    <t>机器人奖池比例</t>
-  </si>
-  <si>
-    <t>官方派奖：机器人中奖间隔（毫秒_权重|毫秒_权重）</t>
-  </si>
-  <si>
-    <t>平均中奖间隔</t>
-  </si>
-  <si>
-    <t>共5档</t>
-  </si>
-  <si>
-    <t>每档偏移</t>
-  </si>
-  <si>
-    <t>每档时间</t>
-  </si>
-  <si>
-    <t>积分大奖： 转盘每次消耗积分数</t>
-  </si>
-  <si>
-    <t>积分大奖：时段榜-上榜的最低积分要求(上午榜、下午榜共用)</t>
-  </si>
-  <si>
-    <t>积分大奖：月总榜-上榜的最低积分要求</t>
-  </si>
-  <si>
-    <t>积分大奖：每日转盘默认初始次数上限</t>
-  </si>
-  <si>
-    <t>积分大奖：充值多少金额给一次转盘次数</t>
-  </si>
-  <si>
-    <t>积分大奖：积分保底奖励（积分数量_奖励道具ID_奖励道具数量）</t>
-  </si>
-  <si>
-    <t>100_1990000_700000|400_1990000_2800000|800_1990000_5600000|1100_1990000_7700000|1600_1990000_11200000|2500_1990000_17500000</t>
-  </si>
-  <si>
-    <t>VIP充值：充值金额与经验转换比例(充值金额_获得vip经验，最低支持0.01_1，美元)</t>
-  </si>
-  <si>
-    <t>0.01_20000</t>
-  </si>
-  <si>
-    <t>积分大奖：实物奖励兑换码过期时间（天）</t>
-  </si>
-  <si>
-    <t>新手奖励</t>
-  </si>
-  <si>
-    <t>1990000_700000</t>
-  </si>
-  <si>
-    <t>手机短信区号（印度、巴基斯坦、菲律宾、巴西、尼日利亚）废弃</t>
-  </si>
-  <si>
-    <t>‌91_92_63_55_234</t>
-  </si>
-  <si>
-    <t>VIP充值返利给金币时的金币数量，金币数量 = 返利金额 * 此值</t>
-  </si>
-  <si>
-    <t>推广分享给金币时的金币数量，金币数量 = 返利金额 * 此值</t>
-  </si>
-  <si>
-    <t>VIP充值返利给钻石时的钻石数量，钻石数量 = 返利金额 * 此值</t>
-  </si>
-  <si>
     <t>VIP季度奖励领取时间(月份1日期1_月份2日期2_月份3日期3_月份4日期4)</t>
   </si>
   <si>
@@ -584,6 +621,12 @@
     <t>1990000_10000</t>
   </si>
   <si>
+    <t>推广分享：有效用户达标条件</t>
+  </si>
+  <si>
+    <t>12007_100000|11002_10000_0</t>
+  </si>
+  <si>
     <t>财富轮盘：昨日输的金币兑换为积分的比例（昨日所输金币_获得积分）</t>
   </si>
   <si>
@@ -593,7 +636,16 @@
     <t>财富轮盘：每次抽奖所消耗的积分</t>
   </si>
   <si>
+    <t>财富轮盘：指定游戏内的打码才可以转为积分，填游戏范围</t>
+  </si>
+  <si>
+    <t>1_-1|2_-1|3_-1</t>
+  </si>
+  <si>
     <t>买一送七：限购时间，单位秒，活动开始后到此倒计时结束之间才能付费参与活动</t>
+  </si>
+  <si>
+    <t>摇钱树奖池保底：当摇钱树奖池金额低于此值时，始终不中奖</t>
   </si>
 </sst>
 </file>
@@ -1636,7 +1688,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:W62"/>
+  <dimension ref="A1:W66"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
@@ -1652,7 +1704,8 @@
     <col min="11" max="11" width="9" style="1"/>
     <col min="12" max="12" width="12.875" style="1"/>
     <col min="13" max="13" width="9" style="1"/>
-    <col min="14" max="18" width="9.25" style="1"/>
+    <col min="14" max="17" width="10.375" style="1"/>
+    <col min="18" max="18" width="9.25" style="1"/>
     <col min="19" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -2110,182 +2163,181 @@
         <v>10</v>
       </c>
     </row>
-    <row r="34" customFormat="1" spans="1:23">
-      <c r="A34" s="1">
-        <v>55</v>
-      </c>
-      <c r="B34" s="1" t="s">
+    <row r="34" s="2" customFormat="1" spans="1:23">
+      <c r="A34" s="11">
+        <v>30</v>
+      </c>
+      <c r="B34" s="11" t="s">
         <v>65</v>
       </c>
-      <c r="C34" s="1"/>
-      <c r="D34" s="1">
-        <v>60</v>
+      <c r="C34" s="2" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="35" s="2" customFormat="1" spans="1:23">
       <c r="A35" s="11">
+        <v>31</v>
+      </c>
+      <c r="B35" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="E35" s="2">
+        <v>20989402.5988449</v>
+      </c>
+      <c r="G35" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="H35" s="2">
+        <v>1049470.12994225</v>
+      </c>
+      <c r="I35" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="J35" s="2">
+        <v>1</v>
+      </c>
+      <c r="K35" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="L35" s="2">
+        <f>J35*24*60*60*1000</f>
+        <v>86400000</v>
+      </c>
+      <c r="M35" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="36" spans="1:23">
+      <c r="A36" s="11">
+        <v>32</v>
+      </c>
+      <c r="B36" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="37" spans="1:23">
+      <c r="A37" s="12">
+        <v>33</v>
+      </c>
+      <c r="B37" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="38" s="2" customFormat="1" spans="1:23">
+      <c r="A38" s="11">
+        <v>34</v>
+      </c>
+      <c r="B38" s="11" t="s">
+        <v>76</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G38" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="H38" s="2">
         <v>30</v>
       </c>
-      <c r="B35" s="11" t="s">
-        <v>66</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="36" s="2" customFormat="1" spans="1:23">
-      <c r="A36" s="11">
-        <v>31</v>
-      </c>
-      <c r="B36" s="11" t="s">
-        <v>68</v>
-      </c>
-      <c r="E36" s="2">
-        <v>20989402.5988449</v>
-      </c>
-      <c r="G36" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="H36" s="2">
-        <v>1049470.12994225</v>
-      </c>
-      <c r="I36" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="J36" s="2">
-        <v>1</v>
-      </c>
-      <c r="K36" s="2" t="s">
+      <c r="J38" s="2">
+        <f>H39/1000/60/60</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="39" spans="1:23">
+      <c r="A39" s="12">
+        <v>35</v>
+      </c>
+      <c r="B39" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="C39" s="1" t="str">
+        <f>_xlfn.TEXTJOIN("|",TRUE,S39:W39)</f>
+        <v>21600000_1000|18000000_1000|14400000_1000|10800000_1000|7200000_1000</v>
+      </c>
+      <c r="G39" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="H39" s="13">
+        <f>ROUND(L35/(E35*H38/100/H35),0)</f>
+        <v>14400000</v>
+      </c>
+      <c r="I39" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="L36" s="2">
-        <f>J36*24*60*60*1000</f>
-        <v>86400000</v>
-      </c>
-      <c r="M36" s="2" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="37" spans="1:23">
-      <c r="A37" s="11">
-        <v>32</v>
-      </c>
-      <c r="B37" s="11" t="s">
-        <v>73</v>
-      </c>
-      <c r="C37" s="2" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="38" spans="1:23">
-      <c r="A38" s="12">
-        <v>33</v>
-      </c>
-      <c r="B38" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="C38" s="1" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="39" s="2" customFormat="1" spans="1:23">
-      <c r="A39" s="11">
-        <v>34</v>
-      </c>
-      <c r="B39" s="11" t="s">
-        <v>77</v>
-      </c>
-      <c r="C39" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="G39" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="H39" s="2">
-        <v>30</v>
-      </c>
-      <c r="J39" s="2">
-        <f>H40/1000/60/60</f>
-        <v>4</v>
+      <c r="J39" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="K39" s="14" t="s">
+        <v>82</v>
+      </c>
+      <c r="L39" s="14">
+        <v>0.25</v>
+      </c>
+      <c r="M39" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="N39" s="1">
+        <f>ROUND(P39*(1+2*L39),0)</f>
+        <v>21600000</v>
+      </c>
+      <c r="O39" s="1">
+        <f>ROUND(P39*(1+1*L39),0)</f>
+        <v>18000000</v>
+      </c>
+      <c r="P39" s="1">
+        <f>H39</f>
+        <v>14400000</v>
+      </c>
+      <c r="Q39" s="1">
+        <f>ROUND(P39*(1-1*L39),0)</f>
+        <v>10800000</v>
+      </c>
+      <c r="R39" s="1">
+        <f>ROUND(P39*(1-2*L39),0)</f>
+        <v>7200000</v>
+      </c>
+      <c r="S39" s="1" t="str">
+        <f>_xlfn.TEXTJOIN("_",TRUE,N39,1000)</f>
+        <v>21600000_1000</v>
+      </c>
+      <c r="T39" s="1" t="str">
+        <f>_xlfn.TEXTJOIN("_",TRUE,O39,1000)</f>
+        <v>18000000_1000</v>
+      </c>
+      <c r="U39" s="1" t="str">
+        <f>_xlfn.TEXTJOIN("_",TRUE,P39,1000)</f>
+        <v>14400000_1000</v>
+      </c>
+      <c r="V39" s="1" t="str">
+        <f>_xlfn.TEXTJOIN("_",TRUE,Q39,1000)</f>
+        <v>10800000_1000</v>
+      </c>
+      <c r="W39" s="1" t="str">
+        <f>_xlfn.TEXTJOIN("_",TRUE,R39,1000)</f>
+        <v>7200000_1000</v>
       </c>
     </row>
     <row r="40" spans="1:23">
-      <c r="A40" s="12">
-        <v>35</v>
-      </c>
-      <c r="B40" s="12" t="s">
-        <v>80</v>
-      </c>
-      <c r="C40" s="1" t="str">
-        <f>_xlfn.TEXTJOIN("|",TRUE,S40:W40)</f>
-        <v>21600000_1000|18000000_1000|14400000_1000|10800000_1000|7200000_1000</v>
-      </c>
-      <c r="G40" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="H40" s="13">
-        <f>ROUND(L36/(E36*H39/100/H36),0)</f>
-        <v>14400000</v>
-      </c>
-      <c r="I40" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="J40" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="K40" s="14" t="s">
-        <v>83</v>
-      </c>
-      <c r="L40" s="14">
-        <v>0.25</v>
-      </c>
-      <c r="M40" s="1" t="s">
+      <c r="A40" s="15">
+        <v>40</v>
+      </c>
+      <c r="B40" s="15" t="s">
         <v>84</v>
       </c>
-      <c r="N40" s="1">
-        <f>ROUND(P40*(1+2*L40),0)</f>
-        <v>21600000</v>
-      </c>
-      <c r="O40" s="1">
-        <f>ROUND(P40*(1+1*L40),0)</f>
-        <v>18000000</v>
-      </c>
-      <c r="P40" s="1">
-        <f>H40</f>
-        <v>14400000</v>
-      </c>
-      <c r="Q40" s="1">
-        <f>ROUND(P40*(1-1*L40),0)</f>
-        <v>10800000</v>
-      </c>
-      <c r="R40" s="1">
-        <f>ROUND(P40*(1-2*L40),0)</f>
-        <v>7200000</v>
-      </c>
-      <c r="S40" s="1" t="str">
-        <f>_xlfn.TEXTJOIN("_",TRUE,N40,1000)</f>
-        <v>21600000_1000</v>
-      </c>
-      <c r="T40" s="1" t="str">
-        <f>_xlfn.TEXTJOIN("_",TRUE,O40,1000)</f>
-        <v>18000000_1000</v>
-      </c>
-      <c r="U40" s="1" t="str">
-        <f>_xlfn.TEXTJOIN("_",TRUE,P40,1000)</f>
-        <v>14400000_1000</v>
-      </c>
-      <c r="V40" s="1" t="str">
-        <f>_xlfn.TEXTJOIN("_",TRUE,Q40,1000)</f>
-        <v>10800000_1000</v>
-      </c>
-      <c r="W40" s="1" t="str">
-        <f>_xlfn.TEXTJOIN("_",TRUE,R40,1000)</f>
-        <v>7200000_1000</v>
+      <c r="D40" s="1">
+        <v>50</v>
       </c>
     </row>
     <row r="41" spans="1:23">
       <c r="A41" s="15">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B41" s="15" t="s">
         <v>85</v>
@@ -2296,183 +2348,184 @@
     </row>
     <row r="42" spans="1:23">
       <c r="A42" s="15">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B42" s="15" t="s">
         <v>86</v>
       </c>
       <c r="D42" s="1">
-        <v>50</v>
+        <v>500</v>
       </c>
     </row>
     <row r="43" spans="1:23">
       <c r="A43" s="15">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B43" s="15" t="s">
         <v>87</v>
       </c>
       <c r="D43" s="1">
-        <v>500</v>
+        <v>1</v>
       </c>
     </row>
     <row r="44" spans="1:23">
       <c r="A44" s="15">
-        <v>43</v>
-      </c>
-      <c r="B44" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="B44" s="1" t="s">
         <v>88</v>
       </c>
       <c r="D44" s="1">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="45" spans="1:23">
       <c r="A45" s="15">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D45" s="1">
-        <v>10</v>
+      <c r="C45" s="1" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="46" spans="1:23">
-      <c r="A46" s="15">
-        <v>45</v>
+      <c r="A46" s="1">
+        <v>46</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="47" spans="1:23">
       <c r="A47" s="1">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="C47" s="1" t="s">
         <v>93</v>
+      </c>
+      <c r="D47" s="1">
+        <v>3</v>
       </c>
     </row>
     <row r="48" spans="1:23">
       <c r="A48" s="1">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="D48" s="1">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="49" spans="1:20">
+      <c r="C48" s="1" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4">
       <c r="A49" s="1">
         <v>50</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="50" s="2" customFormat="1" spans="1:20">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="50" s="2" customFormat="1" spans="1:4">
       <c r="A50" s="2">
         <v>51</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C50" s="16" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="51" spans="1:20">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4">
       <c r="A51" s="1">
         <v>52</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D51" s="1">
         <v>700000</v>
       </c>
     </row>
-    <row r="52" spans="1:20">
+    <row r="52" spans="1:4">
       <c r="A52" s="1">
         <v>53</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D52" s="1">
         <v>700000</v>
       </c>
     </row>
-    <row r="53" spans="1:20">
+    <row r="53" spans="1:4">
       <c r="A53" s="1">
         <v>54</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D53" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:20">
+    <row r="54" customFormat="1" spans="1:4">
       <c r="A54" s="1">
+        <v>55</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="C54" s="1"/>
+      <c r="D54" s="1">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4">
+      <c r="A55" s="1">
         <v>56</v>
       </c>
-      <c r="B54" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="C54" s="1" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="55" s="2" customFormat="1" spans="1:20">
-      <c r="A55" s="2">
+      <c r="B55" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="56" s="2" customFormat="1" spans="1:4">
+      <c r="A56" s="2">
         <v>60</v>
       </c>
-      <c r="B55" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="C55" s="17" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="56" spans="1:20">
-      <c r="A56" s="1">
+      <c r="B56" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="C56" s="17" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4">
+      <c r="A57" s="1">
         <v>61</v>
-      </c>
-      <c r="B56" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="C56" s="18" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="57" spans="1:20">
-      <c r="A57" s="1">
-        <v>62</v>
       </c>
       <c r="B57" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="C57" s="1" t="s">
+      <c r="C57" s="18" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="58" spans="1:20">
+    <row r="58" spans="1:4">
       <c r="A58" s="1">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B58" s="1" t="s">
         <v>110</v>
@@ -2481,9 +2534,9 @@
         <v>111</v>
       </c>
     </row>
-    <row r="59" spans="1:20">
+    <row r="59" spans="1:4">
       <c r="A59" s="1">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B59" s="1" t="s">
         <v>112</v>
@@ -2492,9 +2545,9 @@
         <v>113</v>
       </c>
     </row>
-    <row r="60" spans="1:20">
+    <row r="60" spans="1:4">
       <c r="A60" s="1">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="B60" s="1" t="s">
         <v>114</v>
@@ -2503,48 +2556,92 @@
         <v>115</v>
       </c>
     </row>
-    <row r="61" spans="1:20">
+    <row r="61" spans="1:4">
       <c r="A61" s="1">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="B61" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="D61" s="1">
+      <c r="C61" s="1" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4">
+      <c r="A62" s="1">
+        <v>70</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4">
+      <c r="A63" s="1">
+        <v>71</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="D63" s="1">
         <v>10</v>
       </c>
     </row>
-    <row r="62" spans="1:20">
-      <c r="A62" s="19">
+    <row r="64" spans="1:4">
+      <c r="A64" s="1">
+        <v>72</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="65" spans="1:20">
+      <c r="A65" s="19">
         <v>80</v>
       </c>
-      <c r="B62" s="19" t="s">
-        <v>117</v>
-      </c>
-      <c r="C62" s="19"/>
-      <c r="D62" s="19">
+      <c r="B65" s="19" t="s">
+        <v>123</v>
+      </c>
+      <c r="C65" s="19"/>
+      <c r="D65" s="19">
         <v>259200</v>
       </c>
-      <c r="E62" s="5"/>
-      <c r="F62" s="5"/>
-      <c r="G62" s="5"/>
-      <c r="H62" s="5"/>
-      <c r="I62" s="5"/>
-      <c r="J62" s="5"/>
-      <c r="K62" s="5"/>
-      <c r="L62" s="5"/>
-      <c r="M62" s="5"/>
-      <c r="N62" s="5"/>
-      <c r="O62" s="5"/>
-      <c r="P62" s="5"/>
-      <c r="Q62" s="5"/>
-      <c r="R62" s="5"/>
-      <c r="S62" s="5"/>
-      <c r="T62" s="5"/>
+      <c r="E65" s="5"/>
+      <c r="F65" s="5"/>
+      <c r="G65" s="5"/>
+      <c r="H65" s="5"/>
+      <c r="I65" s="5"/>
+      <c r="J65" s="5"/>
+      <c r="K65" s="5"/>
+      <c r="L65" s="5"/>
+      <c r="M65" s="5"/>
+      <c r="N65" s="5"/>
+      <c r="O65" s="5"/>
+      <c r="P65" s="5"/>
+      <c r="Q65" s="5"/>
+      <c r="R65" s="5"/>
+      <c r="S65" s="5"/>
+      <c r="T65" s="5"/>
+    </row>
+    <row r="66" spans="1:20">
+      <c r="A66" s="1">
+        <v>90</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="D66" s="1">
+        <v>10000</v>
+      </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="C55" r:id="rId3" display="https://aws-s3-jjg-asset-bucket.s3.ap-southeast-1.amazonaws.com/tanchuang_res/english/tc_sc_1.png" tooltip="https://aws-s3-jjg-asset-bucket.s3.ap-southeast-1.amazonaws.com/tanchuang_res/english/tc_sc_1.png"/>
+    <hyperlink ref="C56" r:id="rId3" display="https://aws-s3-jjg-asset-bucket.s3.ap-southeast-1.amazonaws.com/tanchuang_res/english/tc_sc_1.png" tooltip="https://aws-s3-jjg-asset-bucket.s3.ap-southeast-1.amazonaws.com/tanchuang_res/english/tc_sc_1.png"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/gm/resources/sample/global.xlsx
+++ b/gm/resources/sample/global.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="11925"/>
   </bookViews>
   <sheets>
     <sheet name="globalConfig" sheetId="1" r:id="rId1"/>
@@ -621,7 +621,18 @@
     <t>1990000_10000</t>
   </si>
   <si>
-    <t>推广分享：有效用户达标条件</t>
+    <r>
+      <t>推广分享：有效用户达标条件</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>【第一个位置填有效下注条件|第二个填充值条件】</t>
+    </r>
   </si>
   <si>
     <t>12007_100000|11002_10000_0</t>
@@ -659,7 +670,7 @@
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="0_ "/>
   </numFmts>
-  <fonts count="27">
+  <fonts count="28">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -840,6 +851,12 @@
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
     </font>
     <font>
       <b/>

--- a/gm/resources/sample/global.xlsx
+++ b/gm/resources/sample/global.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="11925"/>
   </bookViews>
   <sheets>
     <sheet name="globalConfig" sheetId="1" r:id="rId1"/>
@@ -271,7 +271,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="124">
   <si>
     <t>sid</t>
   </si>
@@ -555,10 +555,7 @@
     <t>积分大奖：实物奖励兑换码过期时间（天）</t>
   </si>
   <si>
-    <t>积分大奖：占用榜单的机器人条件，活动开始X分钟后出现_VIP等级_玩家等级</t>
-  </si>
-  <si>
-    <t>20_5_600</t>
+    <t>积分大奖：占用榜单的机器人条件，活动开始X分钟后出现</t>
   </si>
   <si>
     <t>新手奖励</t>
@@ -2419,8 +2416,8 @@
       <c r="B48" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="C48" s="1" t="s">
-        <v>95</v>
+      <c r="C48" s="1">
+        <v>20</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2428,10 +2425,10 @@
         <v>50</v>
       </c>
       <c r="B49" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C49" s="1" t="s">
         <v>96</v>
-      </c>
-      <c r="C49" s="1" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="50" s="2" customFormat="1" spans="1:4">
@@ -2439,10 +2436,10 @@
         <v>51</v>
       </c>
       <c r="B50" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="C50" s="16" t="s">
         <v>98</v>
-      </c>
-      <c r="C50" s="16" t="s">
-        <v>99</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2450,7 +2447,7 @@
         <v>52</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D51" s="1">
         <v>700000</v>
@@ -2461,7 +2458,7 @@
         <v>53</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D52" s="1">
         <v>700000</v>
@@ -2472,7 +2469,7 @@
         <v>54</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D53" s="1">
         <v>0</v>
@@ -2483,7 +2480,7 @@
         <v>55</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C54" s="1"/>
       <c r="D54" s="1">
@@ -2495,10 +2492,10 @@
         <v>56</v>
       </c>
       <c r="B55" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="C55" s="1" t="s">
         <v>104</v>
-      </c>
-      <c r="C55" s="1" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="56" s="2" customFormat="1" spans="1:4">
@@ -2506,10 +2503,10 @@
         <v>60</v>
       </c>
       <c r="B56" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="C56" s="17" t="s">
         <v>106</v>
-      </c>
-      <c r="C56" s="17" t="s">
-        <v>107</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2517,10 +2514,10 @@
         <v>61</v>
       </c>
       <c r="B57" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="C57" s="18" t="s">
         <v>108</v>
-      </c>
-      <c r="C57" s="18" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2528,10 +2525,10 @@
         <v>62</v>
       </c>
       <c r="B58" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="C58" s="1" t="s">
         <v>110</v>
-      </c>
-      <c r="C58" s="1" t="s">
-        <v>111</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2539,10 +2536,10 @@
         <v>63</v>
       </c>
       <c r="B59" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="C59" s="1" t="s">
         <v>112</v>
-      </c>
-      <c r="C59" s="1" t="s">
-        <v>113</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2550,10 +2547,10 @@
         <v>64</v>
       </c>
       <c r="B60" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="C60" s="1" t="s">
         <v>114</v>
-      </c>
-      <c r="C60" s="1" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2561,10 +2558,10 @@
         <v>65</v>
       </c>
       <c r="B61" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="C61" s="1" t="s">
         <v>116</v>
-      </c>
-      <c r="C61" s="1" t="s">
-        <v>117</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2572,10 +2569,10 @@
         <v>70</v>
       </c>
       <c r="B62" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="C62" s="1" t="s">
         <v>118</v>
-      </c>
-      <c r="C62" s="1" t="s">
-        <v>119</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2583,7 +2580,7 @@
         <v>71</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D63" s="1">
         <v>10</v>
@@ -2594,10 +2591,10 @@
         <v>72</v>
       </c>
       <c r="B64" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="C64" s="1" t="s">
         <v>121</v>
-      </c>
-      <c r="C64" s="1" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="65" spans="1:20">
@@ -2605,7 +2602,7 @@
         <v>80</v>
       </c>
       <c r="B65" s="19" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C65" s="19"/>
       <c r="D65" s="19">
@@ -2633,7 +2630,7 @@
         <v>90</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D66" s="1">
         <v>10000</v>

--- a/gm/resources/sample/global.xlsx
+++ b/gm/resources/sample/global.xlsx
@@ -123,7 +123,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B50" authorId="0">
+    <comment ref="B51" authorId="0">
       <text>
         <r>
           <rPr>
@@ -145,7 +145,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D51" authorId="0">
+    <comment ref="D52" authorId="0">
       <text>
         <r>
           <rPr>
@@ -164,29 +164,6 @@
           </rPr>
           <t xml:space="preserve">
 值为0表示不返利</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="D52" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>Administrator:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">
-值为0表示不返利
-</t>
         </r>
       </text>
     </comment>
@@ -213,7 +190,30 @@
         </r>
       </text>
     </comment>
-    <comment ref="C55" authorId="0">
+    <comment ref="D54" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+值为0表示不返利
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C56" authorId="0">
       <text>
         <r>
           <rPr>
@@ -235,7 +235,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C64" authorId="0">
+    <comment ref="C65" authorId="0">
       <text>
         <r>
           <rPr>
@@ -271,7 +271,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="129">
   <si>
     <t>sid</t>
   </si>
@@ -528,7 +528,7 @@
     <t>积分大奖： 转盘每次消耗积分数</t>
   </si>
   <si>
-    <t>积分大奖：时段榜-上榜的最低积分要求(上午榜、下午榜共用)</t>
+    <t>积分大奖：上榜的最低积分要求(日榜、周榜)</t>
   </si>
   <si>
     <t>积分大奖：月总榜-上榜的最低积分要求</t>
@@ -549,13 +549,22 @@
     <t>VIP充值：充值金额与经验转换比例(充值金额_获得vip经验，最低支持0.01_1，美元)</t>
   </si>
   <si>
-    <t>0.01_20000</t>
+    <t>1_1</t>
   </si>
   <si>
     <t>积分大奖：实物奖励兑换码过期时间（天）</t>
   </si>
   <si>
-    <t>积分大奖：占用榜单的机器人条件，活动开始X分钟后出现</t>
+    <t>积分大奖：占用榜单的机器人条件，触发的倒计时，单位秒【倒计时下限_倒计时上限_最小增长积分_前X名用机器人占榜】</t>
+  </si>
+  <si>
+    <t>1800_3600_1000_300</t>
+  </si>
+  <si>
+    <t>积分大奖: 【日榜排行榜显示人数_周榜排行榜显示人数_月榜排行榜显示人数】</t>
+  </si>
+  <si>
+    <t>300_300_300</t>
   </si>
   <si>
     <t>新手奖励</t>
@@ -618,10 +627,10 @@
     <t>1990000_10000</t>
   </si>
   <si>
-    <t>推广分享：有效用户达标条件</t>
-  </si>
-  <si>
-    <t>12007_100000|11002_10000_0</t>
+    <t>推广分享：有效用户达标条件（有效下注累计_数值|累计充值_数值）</t>
+  </si>
+  <si>
+    <t>12007_10000|11002_100_0</t>
   </si>
   <si>
     <t>财富轮盘：昨日输的金币兑换为积分的比例（昨日所输金币_获得积分）</t>
@@ -636,13 +645,19 @@
     <t>财富轮盘：指定游戏内的打码才可以转为积分，填游戏范围</t>
   </si>
   <si>
-    <t>1_-1|2_-1|3_-1</t>
+    <t>1_101200_101400|2_200100_200300|3_300100</t>
   </si>
   <si>
     <t>买一送七：限购时间，单位秒，活动开始后到此倒计时结束之间才能付费参与活动</t>
   </si>
   <si>
     <t>摇钱树奖池保底：当摇钱树奖池金额低于此值时，始终不中奖</t>
+  </si>
+  <si>
+    <t>货币文本符号，服务器发个前端</t>
+  </si>
+  <si>
+    <t>$</t>
   </si>
 </sst>
 </file>
@@ -1685,12 +1700,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:W66"/>
+  <dimension ref="A1:W68"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
-    <col min="2" max="2" width="69" style="1" customWidth="1"/>
-    <col min="3" max="3" width="37.625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="100.25" style="1" customWidth="1"/>
+    <col min="3" max="3" width="44.25" style="1" customWidth="1"/>
     <col min="4" max="4" width="9.375" style="1" customWidth="1"/>
     <col min="5" max="5" width="11.5" style="1" customWidth="1"/>
     <col min="6" max="6" width="9.625" style="1" customWidth="1"/>
@@ -2339,8 +2354,8 @@
       <c r="B41" s="15" t="s">
         <v>85</v>
       </c>
-      <c r="D41" s="1">
-        <v>50</v>
+      <c r="C41" s="1">
+        <v>200</v>
       </c>
     </row>
     <row r="42" spans="1:23">
@@ -2416,49 +2431,49 @@
       <c r="B48" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="C48" s="1">
-        <v>20</v>
+      <c r="C48" s="1" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="49" spans="1:4">
       <c r="A49" s="1">
+        <v>49</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4">
+      <c r="A50" s="1">
         <v>50</v>
       </c>
-      <c r="B49" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="C49" s="1" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="50" s="2" customFormat="1" spans="1:4">
-      <c r="A50" s="2">
+      <c r="B50" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="51" s="2" customFormat="1" spans="1:4">
+      <c r="A51" s="2">
         <v>51</v>
       </c>
-      <c r="B50" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="C50" s="16" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="51" spans="1:4">
-      <c r="A51" s="1">
-        <v>52</v>
-      </c>
-      <c r="B51" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="D51" s="1">
-        <v>700000</v>
+      <c r="B51" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="C51" s="16" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="52" spans="1:4">
       <c r="A52" s="1">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D52" s="1">
         <v>700000</v>
@@ -2466,179 +2481,201 @@
     </row>
     <row r="53" spans="1:4">
       <c r="A53" s="1">
+        <v>53</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="D53" s="1">
+        <v>700000</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4">
+      <c r="A54" s="1">
         <v>54</v>
       </c>
-      <c r="B53" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="D53" s="1">
+      <c r="B54" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="D54" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="54" customFormat="1" spans="1:4">
-      <c r="A54" s="1">
+    <row r="55" customFormat="1" spans="1:4">
+      <c r="A55" s="1">
         <v>55</v>
       </c>
-      <c r="B54" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="C54" s="1"/>
-      <c r="D54" s="1">
+      <c r="B55" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="C55" s="1"/>
+      <c r="D55" s="1">
         <v>60</v>
       </c>
     </row>
-    <row r="55" spans="1:4">
-      <c r="A55" s="1">
+    <row r="56" spans="1:4">
+      <c r="A56" s="1">
         <v>56</v>
       </c>
-      <c r="B55" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="C55" s="1" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="56" s="2" customFormat="1" spans="1:4">
-      <c r="A56" s="2">
+      <c r="B56" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="57" s="2" customFormat="1" spans="1:4">
+      <c r="A57" s="2">
         <v>60</v>
       </c>
-      <c r="B56" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="C56" s="17" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="57" spans="1:4">
-      <c r="A57" s="1">
-        <v>61</v>
-      </c>
-      <c r="B57" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="C57" s="18" t="s">
+      <c r="B57" s="2" t="s">
         <v>108</v>
+      </c>
+      <c r="C57" s="17" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="58" spans="1:4">
       <c r="A58" s="1">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="C58" s="1" t="s">
         <v>110</v>
+      </c>
+      <c r="C58" s="18" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="59" spans="1:4">
       <c r="A59" s="1">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="60" spans="1:4">
       <c r="A60" s="1">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="61" spans="1:4">
       <c r="A61" s="1">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="62" spans="1:4">
       <c r="A62" s="1">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="63" spans="1:4">
       <c r="A63" s="1">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="D63" s="1">
-        <v>10</v>
+        <v>120</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="64" spans="1:4">
       <c r="A64" s="1">
+        <v>71</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="D64" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="65" spans="1:20">
+      <c r="A65" s="1">
         <v>72</v>
       </c>
-      <c r="B64" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="C64" s="1" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="65" spans="1:20">
-      <c r="A65" s="19">
+      <c r="B65" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="C65" s="1" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="66" spans="1:20">
+      <c r="A66" s="19">
         <v>80</v>
       </c>
-      <c r="B65" s="19" t="s">
-        <v>122</v>
-      </c>
-      <c r="C65" s="19"/>
-      <c r="D65" s="19">
+      <c r="B66" s="19" t="s">
+        <v>125</v>
+      </c>
+      <c r="C66" s="19"/>
+      <c r="D66" s="19">
         <v>259200</v>
       </c>
-      <c r="E65" s="5"/>
-      <c r="F65" s="5"/>
-      <c r="G65" s="5"/>
-      <c r="H65" s="5"/>
-      <c r="I65" s="5"/>
-      <c r="J65" s="5"/>
-      <c r="K65" s="5"/>
-      <c r="L65" s="5"/>
-      <c r="M65" s="5"/>
-      <c r="N65" s="5"/>
-      <c r="O65" s="5"/>
-      <c r="P65" s="5"/>
-      <c r="Q65" s="5"/>
-      <c r="R65" s="5"/>
-      <c r="S65" s="5"/>
-      <c r="T65" s="5"/>
-    </row>
-    <row r="66" spans="1:20">
-      <c r="A66" s="1">
+      <c r="E66" s="5"/>
+      <c r="F66" s="5"/>
+      <c r="G66" s="5"/>
+      <c r="H66" s="5"/>
+      <c r="I66" s="5"/>
+      <c r="J66" s="5"/>
+      <c r="K66" s="5"/>
+      <c r="L66" s="5"/>
+      <c r="M66" s="5"/>
+      <c r="N66" s="5"/>
+      <c r="O66" s="5"/>
+      <c r="P66" s="5"/>
+      <c r="Q66" s="5"/>
+      <c r="R66" s="5"/>
+      <c r="S66" s="5"/>
+      <c r="T66" s="5"/>
+    </row>
+    <row r="67" spans="1:20">
+      <c r="A67" s="1">
         <v>90</v>
       </c>
-      <c r="B66" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="D66" s="1">
+      <c r="B67" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="D67" s="1">
         <v>10000</v>
+      </c>
+    </row>
+    <row r="68" spans="1:20">
+      <c r="A68" s="1">
+        <v>100</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="C68" s="1" t="s">
+        <v>128</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="C56" r:id="rId3" display="https://aws-s3-jjg-asset-bucket.s3.ap-southeast-1.amazonaws.com/tanchuang_res/english/tc_sc_1.png" tooltip="https://aws-s3-jjg-asset-bucket.s3.ap-southeast-1.amazonaws.com/tanchuang_res/english/tc_sc_1.png"/>
+    <hyperlink ref="C57" r:id="rId3" display="https://aws-s3-jjg-asset-bucket.s3.ap-southeast-1.amazonaws.com/tanchuang_res/english/tc_sc_1.png" tooltip="https://aws-s3-jjg-asset-bucket.s3.ap-southeast-1.amazonaws.com/tanchuang_res/english/tc_sc_1.png"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/gm/resources/sample/global.xlsx
+++ b/gm/resources/sample/global.xlsx
@@ -327,7 +327,7 @@
     <t>万分比</t>
   </si>
   <si>
-    <t>基础流水倍率</t>
+    <t>基础流水倍率（打码量）</t>
   </si>
   <si>
     <t>商店价格显示转换</t>
@@ -423,7 +423,7 @@
     <t>摇钱树活动增长金额</t>
   </si>
   <si>
-    <t>0_3_200_500|3_12_50_150|12_18_100_300|18_24_200_500</t>
+    <t>0_12_100_250|12_24_100_250</t>
   </si>
   <si>
     <t>开始时间/时_结束时间/时（左闭右开）_每次增长值_每次增长下限|</t>
@@ -498,7 +498,7 @@
     <t>官方派奖：充值转换积分比例 ：充值金额（1 美元 = 100 积分 )</t>
   </si>
   <si>
-    <t>1_100</t>
+    <t>29000_1</t>
   </si>
   <si>
     <t>官方派奖：真人和机器人奖池比例(百分比)  （废弃，功能不存在）</t>
@@ -543,13 +543,13 @@
     <t>积分大奖：积分保底奖励（积分数量_奖励道具ID_奖励道具数量）</t>
   </si>
   <si>
-    <t>100_1990000_700000|400_1990000_2800000|800_1990000_5600000|1100_1990000_7700000|1600_1990000_11200000|2500_1990000_17500000</t>
+    <t>100_1990000_14000|400_1990000_57000|800_1990000_115000|1100_1990000_159000|1600_1990000_231000|2500_1990000_362000</t>
   </si>
   <si>
     <t>VIP充值：充值金额与经验转换比例(充值金额_获得vip经验，最低支持0.01_1，美元)</t>
   </si>
   <si>
-    <t>1_1</t>
+    <t>1_10</t>
   </si>
   <si>
     <t>积分大奖：实物奖励兑换码过期时间（天）</t>
@@ -570,7 +570,7 @@
     <t>新手奖励</t>
   </si>
   <si>
-    <t>1990000_700000</t>
+    <t>1990000_100</t>
   </si>
   <si>
     <t>手机短信区号（印度、巴基斯坦、菲律宾、巴西、尼日利亚）废弃</t>
@@ -612,7 +612,7 @@
     <t>推广分享：分享1人得固定奖励</t>
   </si>
   <si>
-    <t>1990000_630000</t>
+    <t>1990000_22040</t>
   </si>
   <si>
     <t>推广分享：二维码图片配置(该资源放在资源服务器实时下载显示的)</t>
@@ -624,7 +624,7 @@
     <t>推广分享：周榜上榜条件设置(收益数量)</t>
   </si>
   <si>
-    <t>1990000_10000</t>
+    <t>1990000_43500</t>
   </si>
   <si>
     <t>推广分享：有效用户达标条件（有效下注累计_数值|累计充值_数值）</t>
@@ -645,7 +645,7 @@
     <t>财富轮盘：指定游戏内的打码才可以转为积分，填游戏范围</t>
   </si>
   <si>
-    <t>1_101200_101400|2_200100_200300|3_300100</t>
+    <t>1_101200_101400|2_200101_200100_200300|3_300100</t>
   </si>
   <si>
     <t>买一送七：限购时间，单位秒，活动开始后到此倒计时结束之间才能付费参与活动</t>
@@ -671,7 +671,7 @@
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="0_ "/>
   </numFmts>
-  <fonts count="27">
+  <fonts count="29">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -694,6 +694,19 @@
     <font>
       <sz val="10"/>
       <color theme="1"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
@@ -1210,137 +1223,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1359,21 +1372,26 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="20" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="6" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="6" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" quotePrefix="1">
       <alignment vertical="center"/>
@@ -1704,8 +1722,8 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
-    <col min="2" max="2" width="100.25" style="1" customWidth="1"/>
-    <col min="3" max="3" width="44.25" style="1" customWidth="1"/>
+    <col min="2" max="2" width="40.2916666666667" style="1" customWidth="1"/>
+    <col min="3" max="3" width="16.4666666666667" style="1" customWidth="1"/>
     <col min="4" max="4" width="9.375" style="1" customWidth="1"/>
     <col min="5" max="5" width="11.5" style="1" customWidth="1"/>
     <col min="6" max="6" width="9.625" style="1" customWidth="1"/>
@@ -1807,8 +1825,8 @@
       <c r="B6" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="D6" s="6">
-        <v>10000</v>
+      <c r="D6" s="8">
+        <v>30000</v>
       </c>
       <c r="E6" s="6"/>
       <c r="F6" s="6"/>
@@ -1870,10 +1888,10 @@
       <c r="B10" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="C10" s="20" t="s">
+      <c r="C10" s="23" t="s">
         <v>24</v>
       </c>
-      <c r="D10" s="8"/>
+      <c r="D10" s="9"/>
       <c r="E10" s="6"/>
       <c r="F10" s="6"/>
       <c r="G10" s="1" t="s">
@@ -1887,7 +1905,7 @@
       <c r="B11" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="C11" s="21" t="s">
+      <c r="C11" s="24" t="s">
         <v>27</v>
       </c>
       <c r="D11" s="6"/>
@@ -1904,7 +1922,7 @@
       <c r="B12" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="C12" s="21" t="s">
+      <c r="C12" s="24" t="s">
         <v>29</v>
       </c>
       <c r="D12" s="6"/>
@@ -1921,7 +1939,7 @@
       <c r="B13" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="C13" s="21" t="s">
+      <c r="C13" s="24" t="s">
         <v>31</v>
       </c>
       <c r="D13" s="6"/>
@@ -1938,7 +1956,7 @@
       <c r="B14" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="C14" s="21" t="s">
+      <c r="C14" s="24" t="s">
         <v>33</v>
       </c>
       <c r="D14" s="6"/>
@@ -1992,7 +2010,7 @@
       <c r="B18" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C18" s="9" t="s">
+      <c r="C18" s="10" t="s">
         <v>39</v>
       </c>
       <c r="G18" s="1" t="s">
@@ -2073,7 +2091,7 @@
       <c r="B25" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="C25" s="1" t="s">
+      <c r="C25" s="11" t="s">
         <v>50</v>
       </c>
       <c r="G25" s="1" t="s">
@@ -2134,7 +2152,7 @@
       <c r="B30" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="C30" s="10"/>
+      <c r="C30" s="12"/>
       <c r="D30" s="1">
         <v>100</v>
       </c>
@@ -2176,10 +2194,10 @@
       </c>
     </row>
     <row r="34" s="2" customFormat="1" spans="1:23">
-      <c r="A34" s="11">
+      <c r="A34" s="13">
         <v>30</v>
       </c>
-      <c r="B34" s="11" t="s">
+      <c r="B34" s="13" t="s">
         <v>65</v>
       </c>
       <c r="C34" s="2" t="s">
@@ -2187,20 +2205,20 @@
       </c>
     </row>
     <row r="35" s="2" customFormat="1" spans="1:23">
-      <c r="A35" s="11">
+      <c r="A35" s="13">
         <v>31</v>
       </c>
-      <c r="B35" s="11" t="s">
+      <c r="B35" s="13" t="s">
         <v>67</v>
       </c>
-      <c r="E35" s="2">
-        <v>20989402.5988449</v>
+      <c r="E35" s="14">
+        <v>114109.053811181</v>
       </c>
       <c r="G35" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="H35" s="2">
-        <v>1049470.12994225</v>
+      <c r="H35" s="14">
+        <v>5705.45269055904</v>
       </c>
       <c r="I35" s="2" t="s">
         <v>69</v>
@@ -2220,10 +2238,10 @@
       </c>
     </row>
     <row r="36" spans="1:23">
-      <c r="A36" s="11">
+      <c r="A36" s="13">
         <v>32</v>
       </c>
-      <c r="B36" s="11" t="s">
+      <c r="B36" s="13" t="s">
         <v>72</v>
       </c>
       <c r="C36" s="2" t="s">
@@ -2231,21 +2249,21 @@
       </c>
     </row>
     <row r="37" spans="1:23">
-      <c r="A37" s="12">
+      <c r="A37" s="15">
         <v>33</v>
       </c>
-      <c r="B37" s="12" t="s">
+      <c r="B37" s="15" t="s">
         <v>74</v>
       </c>
-      <c r="C37" s="1" t="s">
+      <c r="C37" s="14" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="38" s="2" customFormat="1" spans="1:23">
-      <c r="A38" s="11">
+      <c r="A38" s="13">
         <v>34</v>
       </c>
-      <c r="B38" s="11" t="s">
+      <c r="B38" s="13" t="s">
         <v>76</v>
       </c>
       <c r="C38" s="2" t="s">
@@ -2254,31 +2272,27 @@
       <c r="G38" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="H38" s="2">
-        <v>30</v>
-      </c>
-      <c r="J38" s="2">
-        <f>H39/1000/60/60</f>
-        <v>4</v>
+      <c r="H38" s="14">
+        <v>60</v>
       </c>
     </row>
     <row r="39" spans="1:23">
-      <c r="A39" s="12">
+      <c r="A39" s="15">
         <v>35</v>
       </c>
-      <c r="B39" s="12" t="s">
+      <c r="B39" s="15" t="s">
         <v>79</v>
       </c>
       <c r="C39" s="1" t="str">
         <f>_xlfn.TEXTJOIN("|",TRUE,S39:W39)</f>
-        <v>21600000_1000|18000000_1000|14400000_1000|10800000_1000|7200000_1000</v>
+        <v>10800000_1000|9000000_1000|7200000_1000|5400000_1000|3600000_1000</v>
       </c>
       <c r="G39" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="H39" s="13">
+      <c r="H39" s="16">
         <f>ROUND(L35/(E35*H38/100/H35),0)</f>
-        <v>14400000</v>
+        <v>7200000</v>
       </c>
       <c r="I39" s="1" t="s">
         <v>71</v>
@@ -2286,10 +2300,10 @@
       <c r="J39" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="K39" s="14" t="s">
+      <c r="K39" s="17" t="s">
         <v>82</v>
       </c>
-      <c r="L39" s="14">
+      <c r="L39" s="17">
         <v>0.25</v>
       </c>
       <c r="M39" s="1" t="s">
@@ -2297,108 +2311,109 @@
       </c>
       <c r="N39" s="1">
         <f>ROUND(P39*(1+2*L39),0)</f>
-        <v>21600000</v>
+        <v>10800000</v>
       </c>
       <c r="O39" s="1">
         <f>ROUND(P39*(1+1*L39),0)</f>
-        <v>18000000</v>
+        <v>9000000</v>
       </c>
       <c r="P39" s="1">
         <f>H39</f>
-        <v>14400000</v>
+        <v>7200000</v>
       </c>
       <c r="Q39" s="1">
         <f>ROUND(P39*(1-1*L39),0)</f>
-        <v>10800000</v>
+        <v>5400000</v>
       </c>
       <c r="R39" s="1">
         <f>ROUND(P39*(1-2*L39),0)</f>
-        <v>7200000</v>
+        <v>3600000</v>
       </c>
       <c r="S39" s="1" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,N39,1000)</f>
-        <v>21600000_1000</v>
+        <v>10800000_1000</v>
       </c>
       <c r="T39" s="1" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,O39,1000)</f>
-        <v>18000000_1000</v>
+        <v>9000000_1000</v>
       </c>
       <c r="U39" s="1" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,P39,1000)</f>
-        <v>14400000_1000</v>
+        <v>7200000_1000</v>
       </c>
       <c r="V39" s="1" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,Q39,1000)</f>
-        <v>10800000_1000</v>
+        <v>5400000_1000</v>
       </c>
       <c r="W39" s="1" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,R39,1000)</f>
-        <v>7200000_1000</v>
+        <v>3600000_1000</v>
       </c>
     </row>
     <row r="40" spans="1:23">
-      <c r="A40" s="15">
+      <c r="A40" s="18">
         <v>40</v>
       </c>
-      <c r="B40" s="15" t="s">
+      <c r="B40" s="18" t="s">
         <v>84</v>
       </c>
-      <c r="D40" s="1">
+      <c r="D40" s="14">
         <v>50</v>
       </c>
     </row>
     <row r="41" spans="1:23">
-      <c r="A41" s="15">
+      <c r="A41" s="18">
         <v>41</v>
       </c>
-      <c r="B41" s="15" t="s">
+      <c r="B41" s="18" t="s">
         <v>85</v>
       </c>
-      <c r="C41" s="1">
+      <c r="C41" s="1"/>
+      <c r="D41" s="14">
         <v>200</v>
       </c>
     </row>
     <row r="42" spans="1:23">
-      <c r="A42" s="15">
+      <c r="A42" s="18">
         <v>42</v>
       </c>
-      <c r="B42" s="15" t="s">
+      <c r="B42" s="18" t="s">
         <v>86</v>
       </c>
-      <c r="D42" s="1">
+      <c r="D42" s="14">
         <v>500</v>
       </c>
     </row>
     <row r="43" spans="1:23">
-      <c r="A43" s="15">
+      <c r="A43" s="18">
         <v>43</v>
       </c>
-      <c r="B43" s="15" t="s">
+      <c r="B43" s="18" t="s">
         <v>87</v>
       </c>
-      <c r="D43" s="1">
+      <c r="D43" s="14">
         <v>1</v>
       </c>
     </row>
     <row r="44" spans="1:23">
-      <c r="A44" s="15">
+      <c r="A44" s="18">
         <v>44</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="D44" s="1">
-        <v>10</v>
+      <c r="D44" s="14">
+        <v>290000</v>
       </c>
     </row>
     <row r="45" spans="1:23">
-      <c r="A45" s="15">
+      <c r="A45" s="18">
         <v>45</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="C45" s="1" t="s">
+      <c r="C45" s="14" t="s">
         <v>90</v>
       </c>
     </row>
@@ -2409,7 +2424,7 @@
       <c r="B46" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="C46" s="1" t="s">
+      <c r="C46" s="14" t="s">
         <v>92</v>
       </c>
     </row>
@@ -2453,8 +2468,12 @@
       <c r="B50" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="C50" s="1" t="s">
+      <c r="C50" s="14" t="s">
         <v>99</v>
+      </c>
+      <c r="D50" s="1">
+        <f>100/29000*7</f>
+        <v>0.0241379310344828</v>
       </c>
     </row>
     <row r="51" s="2" customFormat="1" spans="1:4">
@@ -2464,7 +2483,7 @@
       <c r="B51" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="C51" s="16" t="s">
+      <c r="C51" s="19" t="s">
         <v>101</v>
       </c>
     </row>
@@ -2475,8 +2494,8 @@
       <c r="B52" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="D52" s="1">
-        <v>700000</v>
+      <c r="D52" s="11">
+        <v>29000</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2486,8 +2505,8 @@
       <c r="B53" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="D53" s="1">
-        <v>700000</v>
+      <c r="D53" s="11">
+        <v>29000</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2531,7 +2550,7 @@
       <c r="B57" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="C57" s="17" t="s">
+      <c r="C57" s="20" t="s">
         <v>109</v>
       </c>
     </row>
@@ -2542,7 +2561,7 @@
       <c r="B58" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="C58" s="18" t="s">
+      <c r="C58" s="21" t="s">
         <v>111</v>
       </c>
     </row>
@@ -2553,7 +2572,7 @@
       <c r="B59" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="C59" s="1" t="s">
+      <c r="C59" s="11" t="s">
         <v>113</v>
       </c>
     </row>
@@ -2575,7 +2594,7 @@
       <c r="B61" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="C61" s="1" t="s">
+      <c r="C61" s="14" t="s">
         <v>117</v>
       </c>
     </row>
@@ -2624,14 +2643,14 @@
       </c>
     </row>
     <row r="66" spans="1:20">
-      <c r="A66" s="19">
+      <c r="A66" s="22">
         <v>80</v>
       </c>
-      <c r="B66" s="19" t="s">
+      <c r="B66" s="22" t="s">
         <v>125</v>
       </c>
-      <c r="C66" s="19"/>
-      <c r="D66" s="19">
+      <c r="C66" s="22"/>
+      <c r="D66" s="22">
         <v>259200</v>
       </c>
       <c r="E66" s="5"/>
@@ -2659,7 +2678,7 @@
         <v>126</v>
       </c>
       <c r="D67" s="1">
-        <v>10000</v>
+        <v>1000000</v>
       </c>
     </row>
     <row r="68" spans="1:20">

--- a/gm/resources/sample/global.xlsx
+++ b/gm/resources/sample/global.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="11925"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="globalConfig" sheetId="1" r:id="rId1"/>
@@ -120,6 +120,28 @@
           </rPr>
           <t xml:space="preserve">
 修改此比例后，需要在多语言表中(67016)修正描述数值</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B48" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+机器人积分增长最大值 = 参数 * 总排名（300） / 100</t>
         </r>
       </text>
     </comment>
@@ -543,13 +565,13 @@
     <t>积分大奖：积分保底奖励（积分数量_奖励道具ID_奖励道具数量）</t>
   </si>
   <si>
-    <t>100_1990000_14000|400_1990000_57000|800_1990000_115000|1100_1990000_159000|1600_1990000_231000|2500_1990000_362000</t>
+    <t>300_1990000_2170|600_1990000_4300|1200_1990000_8600|2400_1990000_17300|3600_1990000_26000|4800_1990000_34000</t>
   </si>
   <si>
     <t>VIP充值：充值金额与经验转换比例(充值金额_获得vip经验，最低支持0.01_1，美元)</t>
   </si>
   <si>
-    <t>1_10</t>
+    <t>1_2</t>
   </si>
   <si>
     <t>积分大奖：实物奖励兑换码过期时间（天）</t>
@@ -558,7 +580,7 @@
     <t>积分大奖：占用榜单的机器人条件，触发的倒计时，单位秒【倒计时下限_倒计时上限_最小增长积分_前X名用机器人占榜】</t>
   </si>
   <si>
-    <t>1800_3600_1000_300</t>
+    <t>1800_3600_2000_300</t>
   </si>
   <si>
     <t>积分大奖: 【日榜排行榜显示人数_周榜排行榜显示人数_月榜排行榜显示人数】</t>
@@ -645,7 +667,7 @@
     <t>财富轮盘：指定游戏内的打码才可以转为积分，填游戏范围</t>
   </si>
   <si>
-    <t>1_101200_101400|2_200101_200100_200300|3_300100</t>
+    <t>1_-1|2_201000|3_300400</t>
   </si>
   <si>
     <t>买一送七：限购时间，单位秒，活动开始后到此倒计时结束之间才能付费参与活动</t>
@@ -2368,7 +2390,6 @@
       <c r="B41" s="18" t="s">
         <v>85</v>
       </c>
-      <c r="C41" s="1"/>
       <c r="D41" s="14">
         <v>200</v>
       </c>
@@ -2381,7 +2402,7 @@
         <v>86</v>
       </c>
       <c r="D42" s="14">
-        <v>500</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="43" spans="1:23">
@@ -2638,7 +2659,7 @@
       <c r="B65" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="C65" s="1" t="s">
+      <c r="C65" s="14" t="s">
         <v>124</v>
       </c>
     </row>

--- a/gm/resources/sample/global.xlsx
+++ b/gm/resources/sample/global.xlsx
@@ -145,6 +145,28 @@
         </r>
       </text>
     </comment>
+    <comment ref="C50" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+值为空，表示不开启该活动</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="B51" authorId="0">
       <text>
         <r>
@@ -276,6 +298,7 @@
             <charset val="134"/>
           </rPr>
           <t>游戏大类_有效的游戏ID范围|……
+1_-1|2_201000_200100|3_300400
 【游戏大类】
 1:slot类型游戏
 2:押注类游戏
@@ -293,7 +316,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="128">
   <si>
     <t>sid</t>
   </si>
@@ -592,9 +615,6 @@
     <t>新手奖励</t>
   </si>
   <si>
-    <t>1990000_100</t>
-  </si>
-  <si>
     <t>手机短信区号（印度、巴基斯坦、菲律宾、巴西、尼日利亚）废弃</t>
   </si>
   <si>
@@ -658,7 +678,7 @@
     <t>财富轮盘：昨日输的金币兑换为积分的比例（昨日所输金币_获得积分）</t>
   </si>
   <si>
-    <t>1000000_1</t>
+    <t>2000_1</t>
   </si>
   <si>
     <t>财富轮盘：每次抽奖所消耗的积分</t>
@@ -667,7 +687,7 @@
     <t>财富轮盘：指定游戏内的打码才可以转为积分，填游戏范围</t>
   </si>
   <si>
-    <t>1_-1|2_201000|3_300400</t>
+    <t>1_-1</t>
   </si>
   <si>
     <t>买一送七：限购时间，单位秒，活动开始后到此倒计时结束之间才能付费参与活动</t>
@@ -1375,7 +1395,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1414,6 +1434,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="6" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" quotePrefix="1">
       <alignment vertical="center"/>
@@ -1744,9 +1765,8 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
-    <col min="2" max="2" width="40.2916666666667" style="1" customWidth="1"/>
-    <col min="3" max="3" width="16.4666666666667" style="1" customWidth="1"/>
-    <col min="4" max="4" width="9.375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="55.8833333333333" style="1" customWidth="1"/>
+    <col min="3" max="4" width="28.3833333333333" style="1" customWidth="1"/>
     <col min="5" max="5" width="11.5" style="1" customWidth="1"/>
     <col min="6" max="6" width="9.625" style="1" customWidth="1"/>
     <col min="7" max="7" width="23.375" style="1" customWidth="1"/>
@@ -1910,7 +1930,7 @@
       <c r="B10" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="C10" s="23" t="s">
+      <c r="C10" s="24" t="s">
         <v>24</v>
       </c>
       <c r="D10" s="9"/>
@@ -1927,7 +1947,7 @@
       <c r="B11" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="C11" s="24" t="s">
+      <c r="C11" s="25" t="s">
         <v>27</v>
       </c>
       <c r="D11" s="6"/>
@@ -1944,7 +1964,7 @@
       <c r="B12" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="C12" s="24" t="s">
+      <c r="C12" s="25" t="s">
         <v>29</v>
       </c>
       <c r="D12" s="6"/>
@@ -1961,7 +1981,7 @@
       <c r="B13" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="C13" s="24" t="s">
+      <c r="C13" s="25" t="s">
         <v>31</v>
       </c>
       <c r="D13" s="6"/>
@@ -1978,7 +1998,7 @@
       <c r="B14" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="C14" s="24" t="s">
+      <c r="C14" s="25" t="s">
         <v>33</v>
       </c>
       <c r="D14" s="6"/>
@@ -2489,23 +2509,17 @@
       <c r="B50" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="C50" s="14" t="s">
-        <v>99</v>
-      </c>
-      <c r="D50" s="1">
-        <f>100/29000*7</f>
-        <v>0.0241379310344828</v>
-      </c>
+      <c r="C50" s="14"/>
     </row>
     <row r="51" s="2" customFormat="1" spans="1:4">
       <c r="A51" s="2">
         <v>51</v>
       </c>
       <c r="B51" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="C51" s="19" t="s">
         <v>100</v>
-      </c>
-      <c r="C51" s="19" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2513,7 +2527,7 @@
         <v>52</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D52" s="11">
         <v>29000</v>
@@ -2524,7 +2538,7 @@
         <v>53</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D53" s="11">
         <v>29000</v>
@@ -2535,7 +2549,7 @@
         <v>54</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D54" s="1">
         <v>0</v>
@@ -2546,7 +2560,7 @@
         <v>55</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C55" s="1"/>
       <c r="D55" s="1">
@@ -2558,10 +2572,10 @@
         <v>56</v>
       </c>
       <c r="B56" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="C56" s="1" t="s">
         <v>106</v>
-      </c>
-      <c r="C56" s="1" t="s">
-        <v>107</v>
       </c>
     </row>
     <row r="57" s="2" customFormat="1" spans="1:4">
@@ -2569,10 +2583,10 @@
         <v>60</v>
       </c>
       <c r="B57" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="C57" s="20" t="s">
         <v>108</v>
-      </c>
-      <c r="C57" s="20" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2580,10 +2594,10 @@
         <v>61</v>
       </c>
       <c r="B58" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="C58" s="21" t="s">
         <v>110</v>
-      </c>
-      <c r="C58" s="21" t="s">
-        <v>111</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2591,10 +2605,10 @@
         <v>62</v>
       </c>
       <c r="B59" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="C59" s="11" t="s">
         <v>112</v>
-      </c>
-      <c r="C59" s="11" t="s">
-        <v>113</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2602,10 +2616,10 @@
         <v>63</v>
       </c>
       <c r="B60" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="C60" s="1" t="s">
         <v>114</v>
-      </c>
-      <c r="C60" s="1" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2613,10 +2627,10 @@
         <v>64</v>
       </c>
       <c r="B61" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="C61" s="14" t="s">
         <v>116</v>
-      </c>
-      <c r="C61" s="14" t="s">
-        <v>117</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2624,10 +2638,10 @@
         <v>65</v>
       </c>
       <c r="B62" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="C62" s="14" t="s">
         <v>118</v>
-      </c>
-      <c r="C62" s="1" t="s">
-        <v>119</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2635,21 +2649,23 @@
         <v>70</v>
       </c>
       <c r="B63" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="C63" s="22" t="s">
         <v>120</v>
       </c>
-      <c r="C63" s="1" t="s">
-        <v>121</v>
-      </c>
+      <c r="D63" s="22"/>
     </row>
     <row r="64" spans="1:4">
       <c r="A64" s="1">
         <v>71</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="D64" s="1">
-        <v>10</v>
+        <v>121</v>
+      </c>
+      <c r="C64" s="22"/>
+      <c r="D64" s="22">
+        <v>10000</v>
       </c>
     </row>
     <row r="65" spans="1:20">
@@ -2657,21 +2673,21 @@
         <v>72</v>
       </c>
       <c r="B65" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="C65" s="14" t="s">
         <v>123</v>
       </c>
-      <c r="C65" s="14" t="s">
+    </row>
+    <row r="66" spans="1:20">
+      <c r="A66" s="23">
+        <v>80</v>
+      </c>
+      <c r="B66" s="23" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="66" spans="1:20">
-      <c r="A66" s="22">
-        <v>80</v>
-      </c>
-      <c r="B66" s="22" t="s">
-        <v>125</v>
-      </c>
-      <c r="C66" s="22"/>
-      <c r="D66" s="22">
+      <c r="C66" s="23"/>
+      <c r="D66" s="23">
         <v>259200</v>
       </c>
       <c r="E66" s="5"/>
@@ -2696,7 +2712,7 @@
         <v>90</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D67" s="1">
         <v>1000000</v>
@@ -2707,10 +2723,10 @@
         <v>100</v>
       </c>
       <c r="B68" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="C68" s="1" t="s">
         <v>127</v>
-      </c>
-      <c r="C68" s="1" t="s">
-        <v>128</v>
       </c>
     </row>
   </sheetData>

--- a/gm/resources/sample/global.xlsx
+++ b/gm/resources/sample/global.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="11925"/>
   </bookViews>
   <sheets>
     <sheet name="globalConfig" sheetId="1" r:id="rId1"/>
@@ -540,7 +540,7 @@
     <t>100000_1</t>
   </si>
   <si>
-    <t>官方派奖：充值转换积分比例 ：充值金额（1 美元 = 100 积分 )</t>
+    <t>官方派奖：充值转换积分比例 ：充值金额（29000越南盾 = 1 积分 )</t>
   </si>
   <si>
     <t>29000_1</t>
@@ -909,12 +909,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1765,7 +1765,7 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
-    <col min="2" max="2" width="55.8833333333333" style="1" customWidth="1"/>
+    <col min="2" max="2" width="74.4083333333333" style="1" customWidth="1"/>
     <col min="3" max="4" width="28.3833333333333" style="1" customWidth="1"/>
     <col min="5" max="5" width="11.5" style="1" customWidth="1"/>
     <col min="6" max="6" width="9.625" style="1" customWidth="1"/>

--- a/gm/resources/sample/global.xlsx
+++ b/gm/resources/sample/global.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="11925"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="globalConfig" sheetId="1" r:id="rId1"/>
@@ -603,7 +603,7 @@
     <t>积分大奖：占用榜单的机器人条件，触发的倒计时，单位秒【倒计时下限_倒计时上限_最小增长积分_前X名用机器人占榜】</t>
   </si>
   <si>
-    <t>1800_3600_2000_300</t>
+    <t>1800_3600_100_300</t>
   </si>
   <si>
     <t>积分大奖: 【日榜排行榜显示人数_周榜排行榜显示人数_月榜排行榜显示人数】</t>
@@ -699,7 +699,7 @@
     <t>货币文本符号，服务器发个前端</t>
   </si>
   <si>
-    <t>$</t>
+    <t>₫</t>
   </si>
 </sst>
 </file>
@@ -909,12 +909,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>

--- a/gm/resources/sample/global.xlsx
+++ b/gm/resources/sample/global.xlsx
@@ -123,7 +123,51 @@
         </r>
       </text>
     </comment>
-    <comment ref="B50" authorId="0">
+    <comment ref="B48" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+机器人积分增长最大值 = 参数 * 总排名（300） / 100</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C50" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+值为空，表示不开启该活动</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B51" authorId="0">
       <text>
         <r>
           <rPr>
@@ -145,7 +189,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D51" authorId="0">
+    <comment ref="D52" authorId="0">
       <text>
         <r>
           <rPr>
@@ -164,29 +208,6 @@
           </rPr>
           <t xml:space="preserve">
 值为0表示不返利</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="D52" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>Administrator:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">
-值为0表示不返利
-</t>
         </r>
       </text>
     </comment>
@@ -213,7 +234,30 @@
         </r>
       </text>
     </comment>
-    <comment ref="C55" authorId="0">
+    <comment ref="D54" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+值为0表示不返利
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C56" authorId="0">
       <text>
         <r>
           <rPr>
@@ -235,7 +279,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C64" authorId="0">
+    <comment ref="C65" authorId="0">
       <text>
         <r>
           <rPr>
@@ -254,6 +298,7 @@
             <charset val="134"/>
           </rPr>
           <t>游戏大类_有效的游戏ID范围|……
+1_-1|2_201000_200100|3_300400
 【游戏大类】
 1:slot类型游戏
 2:押注类游戏
@@ -271,7 +316,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="128">
   <si>
     <t>sid</t>
   </si>
@@ -327,7 +372,7 @@
     <t>万分比</t>
   </si>
   <si>
-    <t>基础流水倍率</t>
+    <t>基础流水倍率（打码量）</t>
   </si>
   <si>
     <t>商店价格显示转换</t>
@@ -390,7 +435,7 @@
     <t>默认装扮</t>
   </si>
   <si>
-    <t>1:1001:2001:0:4001:5001:6001</t>
+    <t>1:1001:2023:0:4001:5001:6001</t>
   </si>
   <si>
     <t>avatar表的ID</t>
@@ -423,7 +468,7 @@
     <t>摇钱树活动增长金额</t>
   </si>
   <si>
-    <t>0_3_200_500|3_12_50_150|12_18_100_300|18_24_200_500</t>
+    <t>0_12_100_250|12_24_100_250</t>
   </si>
   <si>
     <t>开始时间/时_结束时间/时（左闭右开）_每次增长值_每次增长下限|</t>
@@ -495,10 +540,10 @@
     <t>100000_1</t>
   </si>
   <si>
-    <t>官方派奖：充值转换积分比例 ：充值金额（1 美元 = 100 积分 )</t>
-  </si>
-  <si>
-    <t>1_100</t>
+    <t>官方派奖：充值转换积分比例 ：充值金额（29000越南盾 = 1 积分 )</t>
+  </si>
+  <si>
+    <t>29000_1</t>
   </si>
   <si>
     <t>官方派奖：真人和机器人奖池比例(百分比)  （废弃，功能不存在）</t>
@@ -528,7 +573,7 @@
     <t>积分大奖： 转盘每次消耗积分数</t>
   </si>
   <si>
-    <t>积分大奖：时段榜-上榜的最低积分要求(上午榜、下午榜共用)</t>
+    <t>积分大奖：上榜的最低积分要求(日榜、周榜)</t>
   </si>
   <si>
     <t>积分大奖：月总榜-上榜的最低积分要求</t>
@@ -543,30 +588,33 @@
     <t>积分大奖：积分保底奖励（积分数量_奖励道具ID_奖励道具数量）</t>
   </si>
   <si>
-    <t>100_1990000_700000|400_1990000_2800000|800_1990000_5600000|1100_1990000_7700000|1600_1990000_11200000|2500_1990000_17500000</t>
+    <t>300_1990000_2170|600_1990000_4300|1200_1990000_8600|2400_1990000_17300|3600_1990000_26000|4800_1990000_34000</t>
   </si>
   <si>
     <t>VIP充值：充值金额与经验转换比例(充值金额_获得vip经验，最低支持0.01_1，美元)</t>
   </si>
   <si>
-    <t>0.01_20000</t>
+    <t>1_2</t>
   </si>
   <si>
     <t>积分大奖：实物奖励兑换码过期时间（天）</t>
   </si>
   <si>
-    <t>积分大奖：占用榜单的机器人条件，活动开始X分钟后出现_VIP等级_玩家等级</t>
-  </si>
-  <si>
-    <t>20_5_600</t>
+    <t>积分大奖：占用榜单的机器人条件，触发的倒计时，单位秒【倒计时下限_倒计时上限_最小增长积分_前X名用机器人占榜】</t>
+  </si>
+  <si>
+    <t>1800_3600_100_300</t>
+  </si>
+  <si>
+    <t>积分大奖: 【日榜排行榜显示人数_周榜排行榜显示人数_月榜排行榜显示人数】</t>
+  </si>
+  <si>
+    <t>300_300_300</t>
   </si>
   <si>
     <t>新手奖励</t>
   </si>
   <si>
-    <t>1990000_700000</t>
-  </si>
-  <si>
     <t>手机短信区号（印度、巴基斯坦、菲律宾、巴西、尼日利亚）废弃</t>
   </si>
   <si>
@@ -606,7 +654,7 @@
     <t>推广分享：分享1人得固定奖励</t>
   </si>
   <si>
-    <t>1990000_630000</t>
+    <t>1990000_22040</t>
   </si>
   <si>
     <t>推广分享：二维码图片配置(该资源放在资源服务器实时下载显示的)</t>
@@ -618,30 +666,19 @@
     <t>推广分享：周榜上榜条件设置(收益数量)</t>
   </si>
   <si>
-    <t>1990000_10000</t>
-  </si>
-  <si>
-    <r>
-      <t>推广分享：有效用户达标条件</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="微软雅黑"/>
-        <charset val="134"/>
-      </rPr>
-      <t>【第一个位置填有效下注条件|第二个填充值条件】</t>
-    </r>
-  </si>
-  <si>
-    <t>12007_100000|11002_10000_0</t>
+    <t>1990000_43500</t>
+  </si>
+  <si>
+    <t>推广分享：有效用户达标条件（有效下注累计_数值|累计充值_数值）</t>
+  </si>
+  <si>
+    <t>12007_10000|11002_100_0</t>
   </si>
   <si>
     <t>财富轮盘：昨日输的金币兑换为积分的比例（昨日所输金币_获得积分）</t>
   </si>
   <si>
-    <t>1000000_1</t>
+    <t>2000_1</t>
   </si>
   <si>
     <t>财富轮盘：每次抽奖所消耗的积分</t>
@@ -650,13 +687,19 @@
     <t>财富轮盘：指定游戏内的打码才可以转为积分，填游戏范围</t>
   </si>
   <si>
-    <t>1_-1|2_-1|3_-1</t>
+    <t>1_-1</t>
   </si>
   <si>
     <t>买一送七：限购时间，单位秒，活动开始后到此倒计时结束之间才能付费参与活动</t>
   </si>
   <si>
     <t>摇钱树奖池保底：当摇钱树奖池金额低于此值时，始终不中奖</t>
+  </si>
+  <si>
+    <t>货币文本符号，服务器发个前端放在货币数值前面</t>
+  </si>
+  <si>
+    <t>VND</t>
   </si>
 </sst>
 </file>
@@ -670,7 +713,7 @@
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="0_ "/>
   </numFmts>
-  <fonts count="28">
+  <fonts count="29">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -693,6 +736,19 @@
     <font>
       <sz val="10"/>
       <color theme="1"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
@@ -851,12 +907,6 @@
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="微软雅黑"/>
-      <charset val="134"/>
     </font>
     <font>
       <b/>
@@ -1215,137 +1265,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1364,21 +1414,27 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="20" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="6" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="6" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" quotePrefix="1">
       <alignment vertical="center"/>
@@ -1705,13 +1761,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:W66"/>
+  <dimension ref="A1:W68"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
-    <col min="2" max="2" width="69" style="1" customWidth="1"/>
-    <col min="3" max="3" width="37.625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="9.375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="74.4083333333333" style="1" customWidth="1"/>
+    <col min="3" max="4" width="28.3833333333333" style="1" customWidth="1"/>
     <col min="5" max="5" width="11.5" style="1" customWidth="1"/>
     <col min="6" max="6" width="9.625" style="1" customWidth="1"/>
     <col min="7" max="7" width="23.375" style="1" customWidth="1"/>
@@ -1812,8 +1867,8 @@
       <c r="B6" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="D6" s="6">
-        <v>10000</v>
+      <c r="D6" s="8">
+        <v>30000</v>
       </c>
       <c r="E6" s="6"/>
       <c r="F6" s="6"/>
@@ -1875,10 +1930,10 @@
       <c r="B10" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="C10" s="20" t="s">
+      <c r="C10" s="24" t="s">
         <v>24</v>
       </c>
-      <c r="D10" s="8"/>
+      <c r="D10" s="9"/>
       <c r="E10" s="6"/>
       <c r="F10" s="6"/>
       <c r="G10" s="1" t="s">
@@ -1892,7 +1947,7 @@
       <c r="B11" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="C11" s="21" t="s">
+      <c r="C11" s="25" t="s">
         <v>27</v>
       </c>
       <c r="D11" s="6"/>
@@ -1909,7 +1964,7 @@
       <c r="B12" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="C12" s="21" t="s">
+      <c r="C12" s="25" t="s">
         <v>29</v>
       </c>
       <c r="D12" s="6"/>
@@ -1926,7 +1981,7 @@
       <c r="B13" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="C13" s="21" t="s">
+      <c r="C13" s="25" t="s">
         <v>31</v>
       </c>
       <c r="D13" s="6"/>
@@ -1943,7 +1998,7 @@
       <c r="B14" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="C14" s="21" t="s">
+      <c r="C14" s="25" t="s">
         <v>33</v>
       </c>
       <c r="D14" s="6"/>
@@ -1997,7 +2052,7 @@
       <c r="B18" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C18" s="9" t="s">
+      <c r="C18" s="10" t="s">
         <v>39</v>
       </c>
       <c r="G18" s="1" t="s">
@@ -2078,7 +2133,7 @@
       <c r="B25" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="C25" s="1" t="s">
+      <c r="C25" s="11" t="s">
         <v>50</v>
       </c>
       <c r="G25" s="1" t="s">
@@ -2139,7 +2194,7 @@
       <c r="B30" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="C30" s="10"/>
+      <c r="C30" s="12"/>
       <c r="D30" s="1">
         <v>100</v>
       </c>
@@ -2181,10 +2236,10 @@
       </c>
     </row>
     <row r="34" s="2" customFormat="1" spans="1:23">
-      <c r="A34" s="11">
+      <c r="A34" s="13">
         <v>30</v>
       </c>
-      <c r="B34" s="11" t="s">
+      <c r="B34" s="13" t="s">
         <v>65</v>
       </c>
       <c r="C34" s="2" t="s">
@@ -2192,20 +2247,20 @@
       </c>
     </row>
     <row r="35" s="2" customFormat="1" spans="1:23">
-      <c r="A35" s="11">
+      <c r="A35" s="13">
         <v>31</v>
       </c>
-      <c r="B35" s="11" t="s">
+      <c r="B35" s="13" t="s">
         <v>67</v>
       </c>
-      <c r="E35" s="2">
-        <v>20989402.5988449</v>
+      <c r="E35" s="14">
+        <v>114109.053811181</v>
       </c>
       <c r="G35" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="H35" s="2">
-        <v>1049470.12994225</v>
+      <c r="H35" s="14">
+        <v>5705.45269055904</v>
       </c>
       <c r="I35" s="2" t="s">
         <v>69</v>
@@ -2225,10 +2280,10 @@
       </c>
     </row>
     <row r="36" spans="1:23">
-      <c r="A36" s="11">
+      <c r="A36" s="13">
         <v>32</v>
       </c>
-      <c r="B36" s="11" t="s">
+      <c r="B36" s="13" t="s">
         <v>72</v>
       </c>
       <c r="C36" s="2" t="s">
@@ -2236,21 +2291,21 @@
       </c>
     </row>
     <row r="37" spans="1:23">
-      <c r="A37" s="12">
+      <c r="A37" s="15">
         <v>33</v>
       </c>
-      <c r="B37" s="12" t="s">
+      <c r="B37" s="15" t="s">
         <v>74</v>
       </c>
-      <c r="C37" s="1" t="s">
+      <c r="C37" s="14" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="38" s="2" customFormat="1" spans="1:23">
-      <c r="A38" s="11">
+      <c r="A38" s="13">
         <v>34</v>
       </c>
-      <c r="B38" s="11" t="s">
+      <c r="B38" s="13" t="s">
         <v>76</v>
       </c>
       <c r="C38" s="2" t="s">
@@ -2259,31 +2314,27 @@
       <c r="G38" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="H38" s="2">
-        <v>30</v>
-      </c>
-      <c r="J38" s="2">
-        <f>H39/1000/60/60</f>
-        <v>4</v>
+      <c r="H38" s="14">
+        <v>60</v>
       </c>
     </row>
     <row r="39" spans="1:23">
-      <c r="A39" s="12">
+      <c r="A39" s="15">
         <v>35</v>
       </c>
-      <c r="B39" s="12" t="s">
+      <c r="B39" s="15" t="s">
         <v>79</v>
       </c>
       <c r="C39" s="1" t="str">
         <f>_xlfn.TEXTJOIN("|",TRUE,S39:W39)</f>
-        <v>21600000_1000|18000000_1000|14400000_1000|10800000_1000|7200000_1000</v>
+        <v>10800000_1000|9000000_1000|7200000_1000|5400000_1000|3600000_1000</v>
       </c>
       <c r="G39" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="H39" s="13">
+      <c r="H39" s="16">
         <f>ROUND(L35/(E35*H38/100/H35),0)</f>
-        <v>14400000</v>
+        <v>7200000</v>
       </c>
       <c r="I39" s="1" t="s">
         <v>71</v>
@@ -2291,10 +2342,10 @@
       <c r="J39" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="K39" s="14" t="s">
+      <c r="K39" s="17" t="s">
         <v>82</v>
       </c>
-      <c r="L39" s="14">
+      <c r="L39" s="17">
         <v>0.25</v>
       </c>
       <c r="M39" s="1" t="s">
@@ -2302,108 +2353,108 @@
       </c>
       <c r="N39" s="1">
         <f>ROUND(P39*(1+2*L39),0)</f>
-        <v>21600000</v>
+        <v>10800000</v>
       </c>
       <c r="O39" s="1">
         <f>ROUND(P39*(1+1*L39),0)</f>
-        <v>18000000</v>
+        <v>9000000</v>
       </c>
       <c r="P39" s="1">
         <f>H39</f>
-        <v>14400000</v>
+        <v>7200000</v>
       </c>
       <c r="Q39" s="1">
         <f>ROUND(P39*(1-1*L39),0)</f>
-        <v>10800000</v>
+        <v>5400000</v>
       </c>
       <c r="R39" s="1">
         <f>ROUND(P39*(1-2*L39),0)</f>
-        <v>7200000</v>
+        <v>3600000</v>
       </c>
       <c r="S39" s="1" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,N39,1000)</f>
-        <v>21600000_1000</v>
+        <v>10800000_1000</v>
       </c>
       <c r="T39" s="1" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,O39,1000)</f>
-        <v>18000000_1000</v>
+        <v>9000000_1000</v>
       </c>
       <c r="U39" s="1" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,P39,1000)</f>
-        <v>14400000_1000</v>
+        <v>7200000_1000</v>
       </c>
       <c r="V39" s="1" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,Q39,1000)</f>
-        <v>10800000_1000</v>
+        <v>5400000_1000</v>
       </c>
       <c r="W39" s="1" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,R39,1000)</f>
-        <v>7200000_1000</v>
+        <v>3600000_1000</v>
       </c>
     </row>
     <row r="40" spans="1:23">
-      <c r="A40" s="15">
+      <c r="A40" s="18">
         <v>40</v>
       </c>
-      <c r="B40" s="15" t="s">
+      <c r="B40" s="18" t="s">
         <v>84</v>
       </c>
-      <c r="D40" s="1">
+      <c r="D40" s="14">
         <v>50</v>
       </c>
     </row>
     <row r="41" spans="1:23">
-      <c r="A41" s="15">
+      <c r="A41" s="18">
         <v>41</v>
       </c>
-      <c r="B41" s="15" t="s">
+      <c r="B41" s="18" t="s">
         <v>85</v>
       </c>
-      <c r="D41" s="1">
-        <v>50</v>
+      <c r="D41" s="14">
+        <v>200</v>
       </c>
     </row>
     <row r="42" spans="1:23">
-      <c r="A42" s="15">
+      <c r="A42" s="18">
         <v>42</v>
       </c>
-      <c r="B42" s="15" t="s">
+      <c r="B42" s="18" t="s">
         <v>86</v>
       </c>
-      <c r="D42" s="1">
-        <v>500</v>
+      <c r="D42" s="14">
+        <v>2000</v>
       </c>
     </row>
     <row r="43" spans="1:23">
-      <c r="A43" s="15">
+      <c r="A43" s="18">
         <v>43</v>
       </c>
-      <c r="B43" s="15" t="s">
+      <c r="B43" s="18" t="s">
         <v>87</v>
       </c>
-      <c r="D43" s="1">
+      <c r="D43" s="14">
         <v>1</v>
       </c>
     </row>
     <row r="44" spans="1:23">
-      <c r="A44" s="15">
+      <c r="A44" s="18">
         <v>44</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="D44" s="1">
-        <v>10</v>
+      <c r="D44" s="14">
+        <v>290000</v>
       </c>
     </row>
     <row r="45" spans="1:23">
-      <c r="A45" s="15">
+      <c r="A45" s="18">
         <v>45</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="C45" s="1" t="s">
+      <c r="C45" s="14" t="s">
         <v>90</v>
       </c>
     </row>
@@ -2414,7 +2465,7 @@
       <c r="B46" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="C46" s="1" t="s">
+      <c r="C46" s="14" t="s">
         <v>92</v>
       </c>
     </row>
@@ -2442,7 +2493,7 @@
     </row>
     <row r="49" spans="1:4">
       <c r="A49" s="1">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>96</v>
@@ -2451,214 +2502,236 @@
         <v>97</v>
       </c>
     </row>
-    <row r="50" s="2" customFormat="1" spans="1:4">
-      <c r="A50" s="2">
+    <row r="50" spans="1:4">
+      <c r="A50" s="1">
+        <v>50</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="C50" s="14"/>
+    </row>
+    <row r="51" s="2" customFormat="1" spans="1:4">
+      <c r="A51" s="2">
         <v>51</v>
       </c>
-      <c r="B50" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="C50" s="16" t="s">
+      <c r="B51" s="2" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="51" spans="1:4">
-      <c r="A51" s="1">
-        <v>52</v>
-      </c>
-      <c r="B51" s="1" t="s">
+      <c r="C51" s="19" t="s">
         <v>100</v>
-      </c>
-      <c r="D51" s="1">
-        <v>700000</v>
       </c>
     </row>
     <row r="52" spans="1:4">
       <c r="A52" s="1">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="D52" s="1">
-        <v>700000</v>
+      <c r="D52" s="11">
+        <v>29000</v>
       </c>
     </row>
     <row r="53" spans="1:4">
       <c r="A53" s="1">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B53" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="D53" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="54" customFormat="1" spans="1:4">
+      <c r="D53" s="11">
+        <v>29000</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4">
       <c r="A54" s="1">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B54" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="C54" s="1"/>
       <c r="D54" s="1">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="55" spans="1:4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" customFormat="1" spans="1:4">
       <c r="A55" s="1">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="C55" s="1" t="s">
+      <c r="C55" s="1"/>
+      <c r="D55" s="1">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4">
+      <c r="A56" s="1">
+        <v>56</v>
+      </c>
+      <c r="B56" s="1" t="s">
         <v>105</v>
       </c>
-    </row>
-    <row r="56" s="2" customFormat="1" spans="1:4">
-      <c r="A56" s="2">
+      <c r="C56" s="1" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="57" s="2" customFormat="1" spans="1:4">
+      <c r="A57" s="2">
         <v>60</v>
       </c>
-      <c r="B56" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="C56" s="17" t="s">
+      <c r="B57" s="2" t="s">
         <v>107</v>
       </c>
-    </row>
-    <row r="57" spans="1:4">
-      <c r="A57" s="1">
-        <v>61</v>
-      </c>
-      <c r="B57" s="1" t="s">
+      <c r="C57" s="20" t="s">
         <v>108</v>
-      </c>
-      <c r="C57" s="18" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="58" spans="1:4">
       <c r="A58" s="1">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B58" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="C58" s="21" t="s">
         <v>110</v>
-      </c>
-      <c r="C58" s="1" t="s">
-        <v>111</v>
       </c>
     </row>
     <row r="59" spans="1:4">
       <c r="A59" s="1">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B59" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="C59" s="11" t="s">
         <v>112</v>
-      </c>
-      <c r="C59" s="1" t="s">
-        <v>113</v>
       </c>
     </row>
     <row r="60" spans="1:4">
       <c r="A60" s="1">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B60" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="C60" s="1" t="s">
         <v>114</v>
-      </c>
-      <c r="C60" s="1" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="61" spans="1:4">
       <c r="A61" s="1">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B61" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="C61" s="14" t="s">
         <v>116</v>
-      </c>
-      <c r="C61" s="1" t="s">
-        <v>117</v>
       </c>
     </row>
     <row r="62" spans="1:4">
       <c r="A62" s="1">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="B62" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="C62" s="14" t="s">
         <v>118</v>
-      </c>
-      <c r="C62" s="1" t="s">
-        <v>119</v>
       </c>
     </row>
     <row r="63" spans="1:4">
       <c r="A63" s="1">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B63" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="C63" s="22" t="s">
         <v>120</v>
       </c>
-      <c r="D63" s="1">
-        <v>10</v>
-      </c>
+      <c r="D63" s="22"/>
     </row>
     <row r="64" spans="1:4">
       <c r="A64" s="1">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B64" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="C64" s="1" t="s">
+      <c r="C64" s="22"/>
+      <c r="D64" s="22">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="65" spans="1:20">
+      <c r="A65" s="1">
+        <v>72</v>
+      </c>
+      <c r="B65" s="1" t="s">
         <v>122</v>
       </c>
-    </row>
-    <row r="65" spans="1:20">
-      <c r="A65" s="19">
+      <c r="C65" s="14" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="66" spans="1:20">
+      <c r="A66" s="23">
         <v>80</v>
       </c>
-      <c r="B65" s="19" t="s">
-        <v>123</v>
-      </c>
-      <c r="C65" s="19"/>
-      <c r="D65" s="19">
+      <c r="B66" s="23" t="s">
+        <v>124</v>
+      </c>
+      <c r="C66" s="23"/>
+      <c r="D66" s="23">
         <v>259200</v>
       </c>
-      <c r="E65" s="5"/>
-      <c r="F65" s="5"/>
-      <c r="G65" s="5"/>
-      <c r="H65" s="5"/>
-      <c r="I65" s="5"/>
-      <c r="J65" s="5"/>
-      <c r="K65" s="5"/>
-      <c r="L65" s="5"/>
-      <c r="M65" s="5"/>
-      <c r="N65" s="5"/>
-      <c r="O65" s="5"/>
-      <c r="P65" s="5"/>
-      <c r="Q65" s="5"/>
-      <c r="R65" s="5"/>
-      <c r="S65" s="5"/>
-      <c r="T65" s="5"/>
-    </row>
-    <row r="66" spans="1:20">
-      <c r="A66" s="1">
+      <c r="E66" s="5"/>
+      <c r="F66" s="5"/>
+      <c r="G66" s="5"/>
+      <c r="H66" s="5"/>
+      <c r="I66" s="5"/>
+      <c r="J66" s="5"/>
+      <c r="K66" s="5"/>
+      <c r="L66" s="5"/>
+      <c r="M66" s="5"/>
+      <c r="N66" s="5"/>
+      <c r="O66" s="5"/>
+      <c r="P66" s="5"/>
+      <c r="Q66" s="5"/>
+      <c r="R66" s="5"/>
+      <c r="S66" s="5"/>
+      <c r="T66" s="5"/>
+    </row>
+    <row r="67" spans="1:20">
+      <c r="A67" s="1">
         <v>90</v>
       </c>
-      <c r="B66" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="D66" s="1">
-        <v>10000</v>
+      <c r="B67" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="D67" s="1">
+        <v>1000000</v>
+      </c>
+    </row>
+    <row r="68" spans="1:20">
+      <c r="A68" s="1">
+        <v>100</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="C68" s="1" t="s">
+        <v>127</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="C56" r:id="rId3" display="https://aws-s3-jjg-asset-bucket.s3.ap-southeast-1.amazonaws.com/tanchuang_res/english/tc_sc_1.png" tooltip="https://aws-s3-jjg-asset-bucket.s3.ap-southeast-1.amazonaws.com/tanchuang_res/english/tc_sc_1.png"/>
+    <hyperlink ref="C57" r:id="rId3" display="https://aws-s3-jjg-asset-bucket.s3.ap-southeast-1.amazonaws.com/tanchuang_res/english/tc_sc_1.png" tooltip="https://aws-s3-jjg-asset-bucket.s3.ap-southeast-1.amazonaws.com/tanchuang_res/english/tc_sc_1.png"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/gm/resources/sample/global.xlsx
+++ b/gm/resources/sample/global.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="11925"/>
   </bookViews>
   <sheets>
     <sheet name="globalConfig" sheetId="1" r:id="rId1"/>
@@ -435,7 +435,7 @@
     <t>默认装扮</t>
   </si>
   <si>
-    <t>1:1001:2001:0:4001:5001:6001</t>
+    <t>1:1001:2023:0:4001:5001:6001</t>
   </si>
   <si>
     <t>avatar表的ID</t>
@@ -696,10 +696,10 @@
     <t>摇钱树奖池保底：当摇钱树奖池金额低于此值时，始终不中奖</t>
   </si>
   <si>
-    <t>货币文本符号，服务器发个前端</t>
-  </si>
-  <si>
-    <t>₫</t>
+    <t>货币文本符号，服务器发个前端放在货币数值前面</t>
+  </si>
+  <si>
+    <t>VND</t>
   </si>
 </sst>
 </file>

--- a/gm/resources/sample/global.xlsx
+++ b/gm/resources/sample/global.xlsx
@@ -603,7 +603,7 @@
     <t>积分大奖：占用榜单的机器人条件，触发的倒计时，单位秒【倒计时下限_倒计时上限_最小增长积分_前X名用机器人占榜】</t>
   </si>
   <si>
-    <t>1800_3600_100_300</t>
+    <t>1500_2100_50_300</t>
   </si>
   <si>
     <t>积分大奖: 【日榜排行榜显示人数_周榜排行榜显示人数_月榜排行榜显示人数】</t>
@@ -654,7 +654,7 @@
     <t>推广分享：分享1人得固定奖励</t>
   </si>
   <si>
-    <t>1990000_22040</t>
+    <t>1990000_100000</t>
   </si>
   <si>
     <t>推广分享：二维码图片配置(该资源放在资源服务器实时下载显示的)</t>
@@ -666,13 +666,13 @@
     <t>推广分享：周榜上榜条件设置(收益数量)</t>
   </si>
   <si>
-    <t>1990000_43500</t>
+    <t>1990000_6000000</t>
   </si>
   <si>
     <t>推广分享：有效用户达标条件（有效下注累计_数值|累计充值_数值）</t>
   </si>
   <si>
-    <t>12007_10000|11002_100_0</t>
+    <t>12007_2000000|11002_100000_0</t>
   </si>
   <si>
     <t>财富轮盘：昨日输的金币兑换为积分的比例（昨日所输金币_获得积分）</t>
@@ -1395,7 +1395,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1434,6 +1434,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="6" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" quotePrefix="1">
@@ -1930,7 +1931,7 @@
       <c r="B10" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="C10" s="24" t="s">
+      <c r="C10" s="25" t="s">
         <v>24</v>
       </c>
       <c r="D10" s="9"/>
@@ -1947,7 +1948,7 @@
       <c r="B11" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="C11" s="25" t="s">
+      <c r="C11" s="26" t="s">
         <v>27</v>
       </c>
       <c r="D11" s="6"/>
@@ -1964,7 +1965,7 @@
       <c r="B12" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="C12" s="25" t="s">
+      <c r="C12" s="26" t="s">
         <v>29</v>
       </c>
       <c r="D12" s="6"/>
@@ -1981,7 +1982,7 @@
       <c r="B13" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="C13" s="25" t="s">
+      <c r="C13" s="26" t="s">
         <v>31</v>
       </c>
       <c r="D13" s="6"/>
@@ -1998,7 +1999,7 @@
       <c r="B14" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="C14" s="25" t="s">
+      <c r="C14" s="26" t="s">
         <v>33</v>
       </c>
       <c r="D14" s="6"/>
@@ -2607,7 +2608,7 @@
       <c r="B59" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="C59" s="11" t="s">
+      <c r="C59" s="22" t="s">
         <v>112</v>
       </c>
     </row>
@@ -2651,10 +2652,10 @@
       <c r="B63" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="C63" s="22" t="s">
+      <c r="C63" s="23" t="s">
         <v>120</v>
       </c>
-      <c r="D63" s="22"/>
+      <c r="D63" s="23"/>
     </row>
     <row r="64" spans="1:4">
       <c r="A64" s="1">
@@ -2663,9 +2664,9 @@
       <c r="B64" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="C64" s="22"/>
-      <c r="D64" s="22">
-        <v>10000</v>
+      <c r="C64" s="23"/>
+      <c r="D64" s="23">
+        <v>5000</v>
       </c>
     </row>
     <row r="65" spans="1:20">
@@ -2680,14 +2681,14 @@
       </c>
     </row>
     <row r="66" spans="1:20">
-      <c r="A66" s="23">
+      <c r="A66" s="24">
         <v>80</v>
       </c>
-      <c r="B66" s="23" t="s">
+      <c r="B66" s="24" t="s">
         <v>124</v>
       </c>
-      <c r="C66" s="23"/>
-      <c r="D66" s="23">
+      <c r="C66" s="24"/>
+      <c r="D66" s="24">
         <v>259200</v>
       </c>
       <c r="E66" s="5"/>

--- a/gm/resources/sample/global.xlsx
+++ b/gm/resources/sample/global.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="11925"/>
+    <workbookView windowWidth="24045" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="globalConfig" sheetId="1" r:id="rId1"/>
@@ -540,10 +540,10 @@
     <t>100000_1</t>
   </si>
   <si>
-    <t>官方派奖：充值转换积分比例 ：充值金额（29000越南盾 = 1 积分 )</t>
-  </si>
-  <si>
-    <t>29000_1</t>
+    <t>官方派奖：充值转换积分比例 ：充值金额（290,000 越南盾 = 1 积分 )</t>
+  </si>
+  <si>
+    <t>290000_1</t>
   </si>
   <si>
     <t>官方派奖：真人和机器人奖池比例(百分比)  （废弃，功能不存在）</t>
@@ -588,13 +588,13 @@
     <t>积分大奖：积分保底奖励（积分数量_奖励道具ID_奖励道具数量）</t>
   </si>
   <si>
-    <t>300_1990000_2170|600_1990000_4300|1200_1990000_8600|2400_1990000_17300|3600_1990000_26000|4800_1990000_34000</t>
+    <t>300_1990000_2170|600_1990000_4300|1200_1990000_8600|3600_1990000_17300|10800_1990000_26000|32400_1990000_34000</t>
   </si>
   <si>
     <t>VIP充值：充值金额与经验转换比例(充值金额_获得vip经验，最低支持0.01_1，美元)</t>
   </si>
   <si>
-    <t>1_2</t>
+    <t>1_10</t>
   </si>
   <si>
     <t>积分大奖：实物奖励兑换码过期时间（天）</t>
@@ -1772,7 +1772,7 @@
     <col min="6" max="6" width="9.625" style="1" customWidth="1"/>
     <col min="7" max="7" width="23.375" style="1" customWidth="1"/>
     <col min="8" max="8" width="12.75" style="1"/>
-    <col min="9" max="9" width="9" style="1"/>
+    <col min="9" max="9" width="14.125" style="1"/>
     <col min="10" max="10" width="11.5" style="1"/>
     <col min="11" max="11" width="9" style="1"/>
     <col min="12" max="12" width="12.875" style="1"/>
@@ -2401,7 +2401,7 @@
         <v>84</v>
       </c>
       <c r="D40" s="14">
-        <v>50</v>
+        <v>88</v>
       </c>
     </row>
     <row r="41" spans="1:23">
@@ -2412,7 +2412,7 @@
         <v>85</v>
       </c>
       <c r="D41" s="14">
-        <v>200</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="42" spans="1:23">
@@ -2423,7 +2423,7 @@
         <v>86</v>
       </c>
       <c r="D42" s="14">
-        <v>2000</v>
+        <v>36000</v>
       </c>
     </row>
     <row r="43" spans="1:23">
@@ -2531,7 +2531,7 @@
         <v>101</v>
       </c>
       <c r="D52" s="11">
-        <v>29000</v>
+        <v>1</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2542,7 +2542,7 @@
         <v>102</v>
       </c>
       <c r="D53" s="11">
-        <v>29000</v>
+        <v>1</v>
       </c>
     </row>
     <row r="54" spans="1:4">

--- a/gm/resources/sample/global.xlsx
+++ b/gm/resources/sample/global.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24045" windowHeight="12375"/>
+    <workbookView windowWidth="27735" windowHeight="12270"/>
   </bookViews>
   <sheets>
     <sheet name="globalConfig" sheetId="1" r:id="rId1"/>
@@ -540,10 +540,10 @@
     <t>100000_1</t>
   </si>
   <si>
-    <t>官方派奖：充值转换积分比例 ：充值金额（290,000 越南盾 = 1 积分 )</t>
-  </si>
-  <si>
-    <t>290000_1</t>
+    <t>官方派奖：充值转换积分比例 ：充值金额（29000越南盾 = 1 积分 )</t>
+  </si>
+  <si>
+    <t>1_1</t>
   </si>
   <si>
     <t>官方派奖：真人和机器人奖池比例(百分比)  （废弃，功能不存在）</t>
@@ -588,13 +588,13 @@
     <t>积分大奖：积分保底奖励（积分数量_奖励道具ID_奖励道具数量）</t>
   </si>
   <si>
-    <t>300_1990000_2170|600_1990000_4300|1200_1990000_8600|3600_1990000_17300|10800_1990000_26000|32400_1990000_34000</t>
+    <t>300_1990000_21700|600_1990000_43000|1200_1990000_86000|2400_1990000_173000|3600_1990000_260000|4800_1990000_340000</t>
   </si>
   <si>
     <t>VIP充值：充值金额与经验转换比例(充值金额_获得vip经验，最低支持0.01_1，美元)</t>
   </si>
   <si>
-    <t>1_10</t>
+    <t>1_60000</t>
   </si>
   <si>
     <t>积分大奖：实物奖励兑换码过期时间（天）</t>
@@ -654,7 +654,7 @@
     <t>推广分享：分享1人得固定奖励</t>
   </si>
   <si>
-    <t>1990000_100000</t>
+    <t>1990000_1000000</t>
   </si>
   <si>
     <t>推广分享：二维码图片配置(该资源放在资源服务器实时下载显示的)</t>
@@ -666,7 +666,7 @@
     <t>推广分享：周榜上榜条件设置(收益数量)</t>
   </si>
   <si>
-    <t>1990000_6000000</t>
+    <t>1990000_60000000</t>
   </si>
   <si>
     <t>推广分享：有效用户达标条件（有效下注累计_数值|累计充值_数值）</t>
@@ -713,7 +713,7 @@
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="0_ "/>
   </numFmts>
-  <fonts count="29">
+  <fonts count="30">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -749,6 +749,11 @@
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
@@ -1265,137 +1270,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1433,9 +1438,10 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="6" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="6" applyAlignment="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" quotePrefix="1">
       <alignment vertical="center"/>
@@ -1772,7 +1778,7 @@
     <col min="6" max="6" width="9.625" style="1" customWidth="1"/>
     <col min="7" max="7" width="23.375" style="1" customWidth="1"/>
     <col min="8" max="8" width="12.75" style="1"/>
-    <col min="9" max="9" width="14.125" style="1"/>
+    <col min="9" max="9" width="9" style="1"/>
     <col min="10" max="10" width="11.5" style="1"/>
     <col min="11" max="11" width="9" style="1"/>
     <col min="12" max="12" width="12.875" style="1"/>
@@ -1931,7 +1937,7 @@
       <c r="B10" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="C10" s="25" t="s">
+      <c r="C10" s="26" t="s">
         <v>24</v>
       </c>
       <c r="D10" s="9"/>
@@ -1948,7 +1954,7 @@
       <c r="B11" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="C11" s="26" t="s">
+      <c r="C11" s="27" t="s">
         <v>27</v>
       </c>
       <c r="D11" s="6"/>
@@ -1965,7 +1971,7 @@
       <c r="B12" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="C12" s="26" t="s">
+      <c r="C12" s="27" t="s">
         <v>29</v>
       </c>
       <c r="D12" s="6"/>
@@ -1982,7 +1988,7 @@
       <c r="B13" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="C13" s="26" t="s">
+      <c r="C13" s="27" t="s">
         <v>31</v>
       </c>
       <c r="D13" s="6"/>
@@ -1999,7 +2005,7 @@
       <c r="B14" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="C14" s="26" t="s">
+      <c r="C14" s="27" t="s">
         <v>33</v>
       </c>
       <c r="D14" s="6"/>
@@ -2400,8 +2406,8 @@
       <c r="B40" s="18" t="s">
         <v>84</v>
       </c>
-      <c r="D40" s="14">
-        <v>88</v>
+      <c r="D40" s="19">
+        <v>50</v>
       </c>
     </row>
     <row r="41" spans="1:23">
@@ -2411,8 +2417,8 @@
       <c r="B41" s="18" t="s">
         <v>85</v>
       </c>
-      <c r="D41" s="14">
-        <v>1200</v>
+      <c r="D41" s="19">
+        <v>200</v>
       </c>
     </row>
     <row r="42" spans="1:23">
@@ -2422,8 +2428,8 @@
       <c r="B42" s="18" t="s">
         <v>86</v>
       </c>
-      <c r="D42" s="14">
-        <v>36000</v>
+      <c r="D42" s="19">
+        <v>2000</v>
       </c>
     </row>
     <row r="43" spans="1:23">
@@ -2433,7 +2439,7 @@
       <c r="B43" s="18" t="s">
         <v>87</v>
       </c>
-      <c r="D43" s="14">
+      <c r="D43" s="19">
         <v>1</v>
       </c>
     </row>
@@ -2445,7 +2451,7 @@
         <v>88</v>
       </c>
       <c r="D44" s="14">
-        <v>290000</v>
+        <v>10</v>
       </c>
     </row>
     <row r="45" spans="1:23">
@@ -2519,7 +2525,7 @@
       <c r="B51" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="C51" s="19" t="s">
+      <c r="C51" s="20" t="s">
         <v>100</v>
       </c>
     </row>
@@ -2531,7 +2537,7 @@
         <v>101</v>
       </c>
       <c r="D52" s="11">
-        <v>1</v>
+        <v>29000</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2542,7 +2548,7 @@
         <v>102</v>
       </c>
       <c r="D53" s="11">
-        <v>1</v>
+        <v>29000</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2586,7 +2592,7 @@
       <c r="B57" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="C57" s="20" t="s">
+      <c r="C57" s="21" t="s">
         <v>108</v>
       </c>
     </row>
@@ -2597,7 +2603,7 @@
       <c r="B58" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="C58" s="21" t="s">
+      <c r="C58" s="22" t="s">
         <v>110</v>
       </c>
     </row>
@@ -2608,7 +2614,7 @@
       <c r="B59" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="C59" s="22" t="s">
+      <c r="C59" s="23" t="s">
         <v>112</v>
       </c>
     </row>
@@ -2652,10 +2658,10 @@
       <c r="B63" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="C63" s="23" t="s">
+      <c r="C63" s="24" t="s">
         <v>120</v>
       </c>
-      <c r="D63" s="23"/>
+      <c r="D63" s="24"/>
     </row>
     <row r="64" spans="1:4">
       <c r="A64" s="1">
@@ -2664,8 +2670,8 @@
       <c r="B64" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="C64" s="23"/>
-      <c r="D64" s="23">
+      <c r="C64" s="24"/>
+      <c r="D64" s="24">
         <v>5000</v>
       </c>
     </row>
@@ -2676,19 +2682,20 @@
       <c r="B65" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="C65" s="14" t="s">
+      <c r="C65" s="19" t="s">
         <v>123</v>
       </c>
+      <c r="D65" s="19"/>
     </row>
     <row r="66" spans="1:20">
-      <c r="A66" s="24">
+      <c r="A66" s="25">
         <v>80</v>
       </c>
-      <c r="B66" s="24" t="s">
+      <c r="B66" s="25" t="s">
         <v>124</v>
       </c>
-      <c r="C66" s="24"/>
-      <c r="D66" s="24">
+      <c r="C66" s="25"/>
+      <c r="D66" s="25">
         <v>259200</v>
       </c>
       <c r="E66" s="5"/>

--- a/gm/resources/sample/global.xlsx
+++ b/gm/resources/sample/global.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24045" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="globalConfig" sheetId="1" r:id="rId1"/>
@@ -95,6 +95,7 @@
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
+奖池总量
 总量 ÷ 平均中奖金额 = 中奖次数
 1000000000 ÷ 718000 = 1392.7577
 初始天数30天</t>
@@ -316,7 +317,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="129">
   <si>
     <t>sid</t>
   </si>
@@ -546,16 +547,19 @@
     <t>290000_1</t>
   </si>
   <si>
-    <t>官方派奖：真人和机器人奖池比例(百分比)  （废弃，功能不存在）</t>
-  </si>
-  <si>
-    <t>10_90</t>
+    <t>官方派奖：转盘1次数_转盘2次数_转盘3次数（真人抽奖后机器人跟着的抽奖次数，填10，表示玩家抽1次，机器人抽10次）</t>
+  </si>
+  <si>
+    <t>9_1_5</t>
   </si>
   <si>
     <t>机器人奖池比例</t>
   </si>
   <si>
     <t>官方派奖：机器人中奖间隔（毫秒_权重|毫秒_权重）</t>
+  </si>
+  <si>
+    <t>3360_1000|2800_1000|2240_1000|1680_1000|1120_1000</t>
   </si>
   <si>
     <t>平均中奖间隔</t>
@@ -713,7 +717,7 @@
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="0_ "/>
   </numFmts>
-  <fonts count="29">
+  <fonts count="30">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -730,6 +734,11 @@
     <font>
       <sz val="11"/>
       <color theme="0" tint="-0.25"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
@@ -1265,147 +1274,148 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1414,28 +1424,29 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="20" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="6" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="6" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" quotePrefix="1">
       <alignment vertical="center"/>
@@ -1766,7 +1777,7 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
-    <col min="2" max="2" width="74.4083333333333" style="1" customWidth="1"/>
+    <col min="2" max="2" width="88.9666666666667" style="1" customWidth="1"/>
     <col min="3" max="4" width="28.3833333333333" style="1" customWidth="1"/>
     <col min="5" max="5" width="11.5" style="1" customWidth="1"/>
     <col min="6" max="6" width="9.625" style="1" customWidth="1"/>
@@ -1783,51 +1794,51 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4" t="s">
+      <c r="B1" s="5"/>
+      <c r="C1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="5" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="4"/>
-      <c r="C2" s="4" t="s">
+      <c r="B2" s="5"/>
+      <c r="C2" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" s="7" t="s">
         <v>6</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="F2" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="G2" s="4"/>
+      <c r="G2" s="5"/>
     </row>
     <row r="3" spans="1:7">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="4"/>
-      <c r="C3" s="4" t="s">
+      <c r="B3" s="5"/>
+      <c r="C3" s="5" t="s">
         <v>11</v>
       </c>
       <c r="D3" s="1" t="s">
@@ -1839,41 +1850,41 @@
       <c r="F3" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="G3" s="4"/>
+      <c r="G3" s="5"/>
     </row>
     <row r="4" spans="1:7">
-      <c r="A4" s="7"/>
-      <c r="B4" s="6"/>
-      <c r="C4" s="6"/>
-      <c r="G4" s="6"/>
+      <c r="A4" s="8"/>
+      <c r="B4" s="7"/>
+      <c r="C4" s="7"/>
+      <c r="G4" s="7"/>
     </row>
     <row r="5" spans="1:7">
       <c r="A5" s="1">
         <v>1</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="D5" s="6">
+      <c r="D5" s="7">
         <v>999</v>
       </c>
-      <c r="E5" s="6"/>
-      <c r="F5" s="6"/>
-      <c r="G5" s="6"/>
+      <c r="E5" s="7"/>
+      <c r="F5" s="7"/>
+      <c r="G5" s="7"/>
     </row>
     <row r="6" spans="1:7">
       <c r="A6" s="1">
         <v>2</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="D6" s="8">
+      <c r="D6" s="9">
         <v>30000</v>
       </c>
-      <c r="E6" s="6"/>
-      <c r="F6" s="6"/>
-      <c r="G6" s="6" t="s">
+      <c r="E6" s="7"/>
+      <c r="F6" s="7"/>
+      <c r="G6" s="7" t="s">
         <v>17</v>
       </c>
     </row>
@@ -1881,15 +1892,15 @@
       <c r="A7" s="1">
         <v>3</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="D7" s="6">
+      <c r="D7" s="7">
         <v>10000</v>
       </c>
-      <c r="E7" s="6"/>
-      <c r="F7" s="6"/>
-      <c r="G7" s="6" t="s">
+      <c r="E7" s="7"/>
+      <c r="F7" s="7"/>
+      <c r="G7" s="7" t="s">
         <v>17</v>
       </c>
     </row>
@@ -1897,16 +1908,16 @@
       <c r="A8" s="1">
         <v>4</v>
       </c>
-      <c r="B8" s="6" t="s">
+      <c r="B8" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="C8" s="6">
+      <c r="C8" s="7">
         <v>100</v>
       </c>
-      <c r="D8" s="6"/>
-      <c r="E8" s="6"/>
-      <c r="F8" s="6"/>
-      <c r="G8" s="6" t="s">
+      <c r="D8" s="7"/>
+      <c r="E8" s="7"/>
+      <c r="F8" s="7"/>
+      <c r="G8" s="7" t="s">
         <v>20</v>
       </c>
     </row>
@@ -1928,15 +1939,15 @@
       <c r="A10" s="1">
         <v>6</v>
       </c>
-      <c r="B10" s="6" t="s">
+      <c r="B10" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="C10" s="25" t="s">
+      <c r="C10" s="27" t="s">
         <v>24</v>
       </c>
-      <c r="D10" s="9"/>
-      <c r="E10" s="6"/>
-      <c r="F10" s="6"/>
+      <c r="D10" s="10"/>
+      <c r="E10" s="7"/>
+      <c r="F10" s="7"/>
       <c r="G10" s="1" t="s">
         <v>25</v>
       </c>
@@ -1945,15 +1956,15 @@
       <c r="A11" s="1">
         <v>7</v>
       </c>
-      <c r="B11" s="6" t="s">
+      <c r="B11" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="C11" s="26" t="s">
+      <c r="C11" s="28" t="s">
         <v>27</v>
       </c>
-      <c r="D11" s="6"/>
-      <c r="E11" s="6"/>
-      <c r="F11" s="6"/>
+      <c r="D11" s="7"/>
+      <c r="E11" s="7"/>
+      <c r="F11" s="7"/>
       <c r="G11" s="1" t="s">
         <v>25</v>
       </c>
@@ -1962,15 +1973,15 @@
       <c r="A12" s="1">
         <v>8</v>
       </c>
-      <c r="B12" s="6" t="s">
+      <c r="B12" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="C12" s="26" t="s">
+      <c r="C12" s="28" t="s">
         <v>29</v>
       </c>
-      <c r="D12" s="6"/>
-      <c r="E12" s="6"/>
-      <c r="F12" s="6"/>
+      <c r="D12" s="7"/>
+      <c r="E12" s="7"/>
+      <c r="F12" s="7"/>
       <c r="G12" s="1" t="s">
         <v>25</v>
       </c>
@@ -1979,15 +1990,15 @@
       <c r="A13" s="1">
         <v>9</v>
       </c>
-      <c r="B13" s="6" t="s">
+      <c r="B13" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="C13" s="26" t="s">
+      <c r="C13" s="28" t="s">
         <v>31</v>
       </c>
-      <c r="D13" s="6"/>
-      <c r="E13" s="6"/>
-      <c r="F13" s="6"/>
+      <c r="D13" s="7"/>
+      <c r="E13" s="7"/>
+      <c r="F13" s="7"/>
       <c r="G13" s="1" t="s">
         <v>25</v>
       </c>
@@ -1996,15 +2007,15 @@
       <c r="A14" s="1">
         <v>10</v>
       </c>
-      <c r="B14" s="6" t="s">
+      <c r="B14" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="C14" s="26" t="s">
+      <c r="C14" s="28" t="s">
         <v>33</v>
       </c>
-      <c r="D14" s="6"/>
-      <c r="E14" s="6"/>
-      <c r="F14" s="6"/>
+      <c r="D14" s="7"/>
+      <c r="E14" s="7"/>
+      <c r="F14" s="7"/>
       <c r="G14" s="1" t="s">
         <v>25</v>
       </c>
@@ -2053,7 +2064,7 @@
       <c r="B18" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C18" s="10" t="s">
+      <c r="C18" s="11" t="s">
         <v>39</v>
       </c>
       <c r="G18" s="1" t="s">
@@ -2134,7 +2145,7 @@
       <c r="B25" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="C25" s="11" t="s">
+      <c r="C25" s="12" t="s">
         <v>50</v>
       </c>
       <c r="G25" s="1" t="s">
@@ -2195,7 +2206,7 @@
       <c r="B30" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="C30" s="12"/>
+      <c r="C30" s="13"/>
       <c r="D30" s="1">
         <v>100</v>
       </c>
@@ -2237,10 +2248,10 @@
       </c>
     </row>
     <row r="34" s="2" customFormat="1" spans="1:23">
-      <c r="A34" s="13">
+      <c r="A34" s="14">
         <v>30</v>
       </c>
-      <c r="B34" s="13" t="s">
+      <c r="B34" s="14" t="s">
         <v>65</v>
       </c>
       <c r="C34" s="2" t="s">
@@ -2248,20 +2259,20 @@
       </c>
     </row>
     <row r="35" s="2" customFormat="1" spans="1:23">
-      <c r="A35" s="13">
+      <c r="A35" s="14">
         <v>31</v>
       </c>
-      <c r="B35" s="13" t="s">
+      <c r="B35" s="14" t="s">
         <v>67</v>
       </c>
-      <c r="E35" s="14">
-        <v>114109.053811181</v>
+      <c r="E35" s="15">
+        <v>372460972.440945</v>
       </c>
       <c r="G35" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="H35" s="14">
-        <v>5705.45269055904</v>
+      <c r="H35" s="15">
+        <v>8692.20472440945</v>
       </c>
       <c r="I35" s="2" t="s">
         <v>69</v>
@@ -2281,10 +2292,10 @@
       </c>
     </row>
     <row r="36" spans="1:23">
-      <c r="A36" s="13">
+      <c r="A36" s="14">
         <v>32</v>
       </c>
-      <c r="B36" s="13" t="s">
+      <c r="B36" s="14" t="s">
         <v>72</v>
       </c>
       <c r="C36" s="2" t="s">
@@ -2292,171 +2303,171 @@
       </c>
     </row>
     <row r="37" spans="1:23">
-      <c r="A37" s="15">
+      <c r="A37" s="16">
         <v>33</v>
       </c>
-      <c r="B37" s="15" t="s">
+      <c r="B37" s="16" t="s">
         <v>74</v>
       </c>
-      <c r="C37" s="14" t="s">
+      <c r="C37" s="15" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="38" s="2" customFormat="1" spans="1:23">
-      <c r="A38" s="13">
+    <row r="38" s="3" customFormat="1" spans="1:23">
+      <c r="A38" s="17">
         <v>34</v>
       </c>
-      <c r="B38" s="13" t="s">
+      <c r="B38" s="17" t="s">
         <v>76</v>
       </c>
-      <c r="C38" s="2" t="s">
+      <c r="C38" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="G38" s="2" t="s">
+      <c r="D38" s="3"/>
+      <c r="G38" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="H38" s="14">
-        <v>60</v>
+      <c r="H38" s="3">
+        <v>90</v>
       </c>
     </row>
     <row r="39" spans="1:23">
-      <c r="A39" s="15">
+      <c r="A39" s="16">
         <v>35</v>
       </c>
-      <c r="B39" s="15" t="s">
+      <c r="B39" s="16" t="s">
         <v>79</v>
       </c>
-      <c r="C39" s="1" t="str">
-        <f>_xlfn.TEXTJOIN("|",TRUE,S39:W39)</f>
-        <v>10800000_1000|9000000_1000|7200000_1000|5400000_1000|3600000_1000</v>
+      <c r="C39" s="1" t="s">
+        <v>80</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="H39" s="16">
+        <v>81</v>
+      </c>
+      <c r="H39" s="18">
         <f>ROUND(L35/(E35*H38/100/H35),0)</f>
-        <v>7200000</v>
+        <v>2240</v>
       </c>
       <c r="I39" s="1" t="s">
         <v>71</v>
       </c>
       <c r="J39" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="K39" s="17" t="s">
         <v>82</v>
       </c>
-      <c r="L39" s="17">
+      <c r="K39" s="19" t="s">
+        <v>83</v>
+      </c>
+      <c r="L39" s="19">
         <v>0.25</v>
       </c>
       <c r="M39" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="N39" s="1">
         <f>ROUND(P39*(1+2*L39),0)</f>
-        <v>10800000</v>
+        <v>3360</v>
       </c>
       <c r="O39" s="1">
         <f>ROUND(P39*(1+1*L39),0)</f>
-        <v>9000000</v>
+        <v>2800</v>
       </c>
       <c r="P39" s="1">
         <f>H39</f>
-        <v>7200000</v>
+        <v>2240</v>
       </c>
       <c r="Q39" s="1">
         <f>ROUND(P39*(1-1*L39),0)</f>
-        <v>5400000</v>
+        <v>1680</v>
       </c>
       <c r="R39" s="1">
         <f>ROUND(P39*(1-2*L39),0)</f>
-        <v>3600000</v>
+        <v>1120</v>
       </c>
       <c r="S39" s="1" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,N39,1000)</f>
-        <v>10800000_1000</v>
+        <v>3360_1000</v>
       </c>
       <c r="T39" s="1" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,O39,1000)</f>
-        <v>9000000_1000</v>
+        <v>2800_1000</v>
       </c>
       <c r="U39" s="1" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,P39,1000)</f>
-        <v>7200000_1000</v>
+        <v>2240_1000</v>
       </c>
       <c r="V39" s="1" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,Q39,1000)</f>
-        <v>5400000_1000</v>
+        <v>1680_1000</v>
       </c>
       <c r="W39" s="1" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,R39,1000)</f>
-        <v>3600000_1000</v>
+        <v>1120_1000</v>
       </c>
     </row>
     <row r="40" spans="1:23">
-      <c r="A40" s="18">
+      <c r="A40" s="20">
         <v>40</v>
       </c>
-      <c r="B40" s="18" t="s">
-        <v>84</v>
-      </c>
-      <c r="D40" s="14">
+      <c r="B40" s="20" t="s">
+        <v>85</v>
+      </c>
+      <c r="D40" s="15">
         <v>88</v>
       </c>
     </row>
     <row r="41" spans="1:23">
-      <c r="A41" s="18">
+      <c r="A41" s="20">
         <v>41</v>
       </c>
-      <c r="B41" s="18" t="s">
-        <v>85</v>
-      </c>
-      <c r="D41" s="14">
+      <c r="B41" s="20" t="s">
+        <v>86</v>
+      </c>
+      <c r="D41" s="15">
         <v>1200</v>
       </c>
     </row>
     <row r="42" spans="1:23">
-      <c r="A42" s="18">
+      <c r="A42" s="20">
         <v>42</v>
       </c>
-      <c r="B42" s="18" t="s">
-        <v>86</v>
-      </c>
-      <c r="D42" s="14">
+      <c r="B42" s="20" t="s">
+        <v>87</v>
+      </c>
+      <c r="D42" s="15">
         <v>36000</v>
       </c>
     </row>
     <row r="43" spans="1:23">
-      <c r="A43" s="18">
+      <c r="A43" s="20">
         <v>43</v>
       </c>
-      <c r="B43" s="18" t="s">
-        <v>87</v>
-      </c>
-      <c r="D43" s="14">
+      <c r="B43" s="20" t="s">
+        <v>88</v>
+      </c>
+      <c r="D43" s="15">
         <v>1</v>
       </c>
     </row>
     <row r="44" spans="1:23">
-      <c r="A44" s="18">
+      <c r="A44" s="20">
         <v>44</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="D44" s="14">
+        <v>89</v>
+      </c>
+      <c r="D44" s="15">
         <v>290000</v>
       </c>
     </row>
     <row r="45" spans="1:23">
-      <c r="A45" s="18">
+      <c r="A45" s="20">
         <v>45</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="C45" s="14" t="s">
         <v>90</v>
+      </c>
+      <c r="C45" s="15" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="46" spans="1:23">
@@ -2464,10 +2475,10 @@
         <v>46</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="C46" s="14" t="s">
         <v>92</v>
+      </c>
+      <c r="C46" s="15" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="47" spans="1:23">
@@ -2475,7 +2486,7 @@
         <v>47</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D47" s="1">
         <v>3</v>
@@ -2486,10 +2497,10 @@
         <v>48</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2497,10 +2508,10 @@
         <v>49</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2508,19 +2519,19 @@
         <v>50</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="C50" s="14"/>
+        <v>99</v>
+      </c>
+      <c r="C50" s="15"/>
     </row>
     <row r="51" s="2" customFormat="1" spans="1:4">
       <c r="A51" s="2">
         <v>51</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="C51" s="19" t="s">
         <v>100</v>
+      </c>
+      <c r="C51" s="21" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2528,9 +2539,9 @@
         <v>52</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="D52" s="11">
+        <v>102</v>
+      </c>
+      <c r="D52" s="12">
         <v>1</v>
       </c>
     </row>
@@ -2539,9 +2550,9 @@
         <v>53</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="D53" s="11">
+        <v>103</v>
+      </c>
+      <c r="D53" s="12">
         <v>1</v>
       </c>
     </row>
@@ -2550,7 +2561,7 @@
         <v>54</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D54" s="1">
         <v>0</v>
@@ -2561,7 +2572,7 @@
         <v>55</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C55" s="1"/>
       <c r="D55" s="1">
@@ -2573,10 +2584,10 @@
         <v>56</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="57" s="2" customFormat="1" spans="1:4">
@@ -2584,10 +2595,10 @@
         <v>60</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="C57" s="20" t="s">
         <v>108</v>
+      </c>
+      <c r="C57" s="22" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2595,10 +2606,10 @@
         <v>61</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="C58" s="21" t="s">
         <v>110</v>
+      </c>
+      <c r="C58" s="23" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2606,10 +2617,10 @@
         <v>62</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="C59" s="22" t="s">
         <v>112</v>
+      </c>
+      <c r="C59" s="24" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2617,10 +2628,10 @@
         <v>63</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2628,10 +2639,10 @@
         <v>64</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="C61" s="14" t="s">
         <v>116</v>
+      </c>
+      <c r="C61" s="15" t="s">
+        <v>117</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2639,10 +2650,10 @@
         <v>65</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="C62" s="14" t="s">
         <v>118</v>
+      </c>
+      <c r="C62" s="15" t="s">
+        <v>119</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2650,22 +2661,22 @@
         <v>70</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="C63" s="23" t="s">
         <v>120</v>
       </c>
-      <c r="D63" s="23"/>
+      <c r="C63" s="25" t="s">
+        <v>121</v>
+      </c>
+      <c r="D63" s="25"/>
     </row>
     <row r="64" spans="1:4">
       <c r="A64" s="1">
         <v>71</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="C64" s="23"/>
-      <c r="D64" s="23">
+        <v>122</v>
+      </c>
+      <c r="C64" s="25"/>
+      <c r="D64" s="25">
         <v>5000</v>
       </c>
     </row>
@@ -2674,46 +2685,46 @@
         <v>72</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="C65" s="14" t="s">
         <v>123</v>
       </c>
+      <c r="C65" s="15" t="s">
+        <v>124</v>
+      </c>
     </row>
     <row r="66" spans="1:20">
-      <c r="A66" s="24">
+      <c r="A66" s="26">
         <v>80</v>
       </c>
-      <c r="B66" s="24" t="s">
-        <v>124</v>
-      </c>
-      <c r="C66" s="24"/>
-      <c r="D66" s="24">
+      <c r="B66" s="26" t="s">
+        <v>125</v>
+      </c>
+      <c r="C66" s="26"/>
+      <c r="D66" s="26">
         <v>259200</v>
       </c>
-      <c r="E66" s="5"/>
-      <c r="F66" s="5"/>
-      <c r="G66" s="5"/>
-      <c r="H66" s="5"/>
-      <c r="I66" s="5"/>
-      <c r="J66" s="5"/>
-      <c r="K66" s="5"/>
-      <c r="L66" s="5"/>
-      <c r="M66" s="5"/>
-      <c r="N66" s="5"/>
-      <c r="O66" s="5"/>
-      <c r="P66" s="5"/>
-      <c r="Q66" s="5"/>
-      <c r="R66" s="5"/>
-      <c r="S66" s="5"/>
-      <c r="T66" s="5"/>
+      <c r="E66" s="6"/>
+      <c r="F66" s="6"/>
+      <c r="G66" s="6"/>
+      <c r="H66" s="6"/>
+      <c r="I66" s="6"/>
+      <c r="J66" s="6"/>
+      <c r="K66" s="6"/>
+      <c r="L66" s="6"/>
+      <c r="M66" s="6"/>
+      <c r="N66" s="6"/>
+      <c r="O66" s="6"/>
+      <c r="P66" s="6"/>
+      <c r="Q66" s="6"/>
+      <c r="R66" s="6"/>
+      <c r="S66" s="6"/>
+      <c r="T66" s="6"/>
     </row>
     <row r="67" spans="1:20">
       <c r="A67" s="1">
         <v>90</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D67" s="1">
         <v>1000000</v>
@@ -2724,10 +2735,10 @@
         <v>100</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
   </sheetData>

--- a/gm/resources/sample/global.xlsx
+++ b/gm/resources/sample/global.xlsx
@@ -317,7 +317,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="132">
   <si>
     <t>sid</t>
   </si>
@@ -544,13 +544,13 @@
     <t>官方派奖：充值转换积分比例 ：充值金额（290,000 越南盾 = 1 积分 )</t>
   </si>
   <si>
-    <t>290000_1</t>
+    <t>208000_1</t>
   </si>
   <si>
     <t>官方派奖：转盘1次数_转盘2次数_转盘3次数（真人抽奖后机器人跟着的抽奖次数，填10，表示玩家抽1次，机器人抽10次）</t>
   </si>
   <si>
-    <t>9_1_5</t>
+    <t>99_99_99</t>
   </si>
   <si>
     <t>机器人奖池比例</t>
@@ -704,6 +704,15 @@
   </si>
   <si>
     <t>VND</t>
+  </si>
+  <si>
+    <t>幸运夺宝：商品价值货币的图标</t>
+  </si>
+  <si>
+    <t>itemicon_1980000.png</t>
+  </si>
+  <si>
+    <t>幸运夺宝：抢购商品所需要的道具ID(仅在界面左上角处显示的抢购消耗道具的信息)</t>
   </si>
 </sst>
 </file>
@@ -717,7 +726,7 @@
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="0_ "/>
   </numFmts>
-  <fonts count="30">
+  <fonts count="31">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -758,6 +767,13 @@
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="2"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
@@ -1274,137 +1290,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1436,15 +1452,16 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="6" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="6" applyAlignment="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1773,7 +1790,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:W68"/>
+  <dimension ref="A1:W70"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
@@ -1942,7 +1959,7 @@
       <c r="B10" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="C10" s="27" t="s">
+      <c r="C10" s="28" t="s">
         <v>24</v>
       </c>
       <c r="D10" s="10"/>
@@ -1959,7 +1976,7 @@
       <c r="B11" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="C11" s="28" t="s">
+      <c r="C11" s="29" t="s">
         <v>27</v>
       </c>
       <c r="D11" s="7"/>
@@ -1976,7 +1993,7 @@
       <c r="B12" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="C12" s="28" t="s">
+      <c r="C12" s="29" t="s">
         <v>29</v>
       </c>
       <c r="D12" s="7"/>
@@ -1993,7 +2010,7 @@
       <c r="B13" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="C13" s="28" t="s">
+      <c r="C13" s="29" t="s">
         <v>31</v>
       </c>
       <c r="D13" s="7"/>
@@ -2010,7 +2027,7 @@
       <c r="B14" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="C14" s="28" t="s">
+      <c r="C14" s="29" t="s">
         <v>33</v>
       </c>
       <c r="D14" s="7"/>
@@ -2309,15 +2326,15 @@
       <c r="B37" s="16" t="s">
         <v>74</v>
       </c>
-      <c r="C37" s="15" t="s">
+      <c r="C37" s="17" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="38" s="3" customFormat="1" spans="1:23">
-      <c r="A38" s="17">
+      <c r="A38" s="18">
         <v>34</v>
       </c>
-      <c r="B38" s="17" t="s">
+      <c r="B38" s="18" t="s">
         <v>76</v>
       </c>
       <c r="C38" s="3" t="s">
@@ -2344,7 +2361,7 @@
       <c r="G39" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="H39" s="18">
+      <c r="H39" s="19">
         <f>ROUND(L35/(E35*H38/100/H35),0)</f>
         <v>2240</v>
       </c>
@@ -2354,10 +2371,10 @@
       <c r="J39" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="K39" s="19" t="s">
+      <c r="K39" s="20" t="s">
         <v>83</v>
       </c>
-      <c r="L39" s="19">
+      <c r="L39" s="20">
         <v>0.25</v>
       </c>
       <c r="M39" s="1" t="s">
@@ -2405,68 +2422,68 @@
       </c>
     </row>
     <row r="40" spans="1:23">
-      <c r="A40" s="20">
+      <c r="A40" s="21">
         <v>40</v>
       </c>
-      <c r="B40" s="20" t="s">
+      <c r="B40" s="21" t="s">
         <v>85</v>
       </c>
-      <c r="D40" s="15">
+      <c r="D40" s="17">
         <v>88</v>
       </c>
     </row>
     <row r="41" spans="1:23">
-      <c r="A41" s="20">
+      <c r="A41" s="21">
         <v>41</v>
       </c>
-      <c r="B41" s="20" t="s">
+      <c r="B41" s="21" t="s">
         <v>86</v>
       </c>
-      <c r="D41" s="15">
+      <c r="D41" s="17">
         <v>1200</v>
       </c>
     </row>
     <row r="42" spans="1:23">
-      <c r="A42" s="20">
+      <c r="A42" s="21">
         <v>42</v>
       </c>
-      <c r="B42" s="20" t="s">
+      <c r="B42" s="21" t="s">
         <v>87</v>
       </c>
-      <c r="D42" s="15">
+      <c r="D42" s="17">
         <v>36000</v>
       </c>
     </row>
     <row r="43" spans="1:23">
-      <c r="A43" s="20">
+      <c r="A43" s="21">
         <v>43</v>
       </c>
-      <c r="B43" s="20" t="s">
+      <c r="B43" s="21" t="s">
         <v>88</v>
       </c>
-      <c r="D43" s="15">
+      <c r="D43" s="17">
         <v>1</v>
       </c>
     </row>
     <row r="44" spans="1:23">
-      <c r="A44" s="20">
+      <c r="A44" s="21">
         <v>44</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D44" s="15">
+      <c r="D44" s="17">
         <v>290000</v>
       </c>
     </row>
     <row r="45" spans="1:23">
-      <c r="A45" s="20">
+      <c r="A45" s="21">
         <v>45</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="C45" s="15" t="s">
+      <c r="C45" s="17" t="s">
         <v>91</v>
       </c>
     </row>
@@ -2477,7 +2494,7 @@
       <c r="B46" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="C46" s="15" t="s">
+      <c r="C46" s="17" t="s">
         <v>93</v>
       </c>
     </row>
@@ -2521,7 +2538,7 @@
       <c r="B50" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="C50" s="15"/>
+      <c r="C50" s="17"/>
     </row>
     <row r="51" s="2" customFormat="1" spans="1:4">
       <c r="A51" s="2">
@@ -2530,7 +2547,7 @@
       <c r="B51" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="C51" s="21" t="s">
+      <c r="C51" s="22" t="s">
         <v>101</v>
       </c>
     </row>
@@ -2597,7 +2614,7 @@
       <c r="B57" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="C57" s="22" t="s">
+      <c r="C57" s="23" t="s">
         <v>109</v>
       </c>
     </row>
@@ -2608,7 +2625,7 @@
       <c r="B58" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="C58" s="23" t="s">
+      <c r="C58" s="24" t="s">
         <v>111</v>
       </c>
     </row>
@@ -2619,7 +2636,7 @@
       <c r="B59" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="C59" s="24" t="s">
+      <c r="C59" s="25" t="s">
         <v>113</v>
       </c>
     </row>
@@ -2641,7 +2658,7 @@
       <c r="B61" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="C61" s="15" t="s">
+      <c r="C61" s="17" t="s">
         <v>117</v>
       </c>
     </row>
@@ -2652,7 +2669,7 @@
       <c r="B62" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="C62" s="15" t="s">
+      <c r="C62" s="17" t="s">
         <v>119</v>
       </c>
     </row>
@@ -2663,10 +2680,10 @@
       <c r="B63" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="C63" s="25" t="s">
+      <c r="C63" s="26" t="s">
         <v>121</v>
       </c>
-      <c r="D63" s="25"/>
+      <c r="D63" s="26"/>
     </row>
     <row r="64" spans="1:4">
       <c r="A64" s="1">
@@ -2675,8 +2692,8 @@
       <c r="B64" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="C64" s="25"/>
-      <c r="D64" s="25">
+      <c r="C64" s="26"/>
+      <c r="D64" s="26">
         <v>5000</v>
       </c>
     </row>
@@ -2687,19 +2704,19 @@
       <c r="B65" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="C65" s="15" t="s">
+      <c r="C65" s="17" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="66" spans="1:20">
-      <c r="A66" s="26">
+      <c r="A66" s="27">
         <v>80</v>
       </c>
-      <c r="B66" s="26" t="s">
+      <c r="B66" s="27" t="s">
         <v>125</v>
       </c>
-      <c r="C66" s="26"/>
-      <c r="D66" s="26">
+      <c r="C66" s="27"/>
+      <c r="D66" s="27">
         <v>259200</v>
       </c>
       <c r="E66" s="6"/>
@@ -2741,6 +2758,28 @@
         <v>128</v>
       </c>
     </row>
+    <row r="69" spans="1:20">
+      <c r="A69" s="1">
+        <v>101</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="C69" s="1" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="70" spans="1:20">
+      <c r="A70" s="1">
+        <v>102</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="C70" s="13">
+        <v>1022503</v>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="C57" r:id="rId3" display="https://aws-s3-jjg-asset-bucket.s3.ap-southeast-1.amazonaws.com/tanchuang_res/english/tc_sc_1.png" tooltip="https://aws-s3-jjg-asset-bucket.s3.ap-southeast-1.amazonaws.com/tanchuang_res/english/tc_sc_1.png"/>

--- a/gm/resources/sample/global.xlsx
+++ b/gm/resources/sample/global.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27735" windowHeight="12270"/>
   </bookViews>
   <sheets>
     <sheet name="globalConfig" sheetId="1" r:id="rId1"/>
@@ -95,7 +95,6 @@
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
-奖池总量
 总量 ÷ 平均中奖金额 = 中奖次数
 1000000000 ÷ 718000 = 1392.7577
 初始天数30天</t>
@@ -317,7 +316,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="128">
   <si>
     <t>sid</t>
   </si>
@@ -541,16 +540,16 @@
     <t>100000_1</t>
   </si>
   <si>
-    <t>官方派奖：充值转换积分比例 ：充值金额（290,000 越南盾 = 1 积分 )</t>
-  </si>
-  <si>
-    <t>290000_1</t>
-  </si>
-  <si>
-    <t>官方派奖：转盘1次数_转盘2次数_转盘3次数（真人抽奖后机器人跟着的抽奖次数，填10，表示玩家抽1次，机器人抽10次）</t>
-  </si>
-  <si>
-    <t>9_1_5</t>
+    <t>官方派奖：充值转换积分比例 ：充值金额（29000越南盾 = 1 积分 )</t>
+  </si>
+  <si>
+    <t>1_1</t>
+  </si>
+  <si>
+    <t>官方派奖：真人和机器人奖池比例(百分比)  （废弃，功能不存在）</t>
+  </si>
+  <si>
+    <t>10_90</t>
   </si>
   <si>
     <t>机器人奖池比例</t>
@@ -559,9 +558,6 @@
     <t>官方派奖：机器人中奖间隔（毫秒_权重|毫秒_权重）</t>
   </si>
   <si>
-    <t>3360_1000|2800_1000|2240_1000|1680_1000|1120_1000</t>
-  </si>
-  <si>
     <t>平均中奖间隔</t>
   </si>
   <si>
@@ -592,13 +588,13 @@
     <t>积分大奖：积分保底奖励（积分数量_奖励道具ID_奖励道具数量）</t>
   </si>
   <si>
-    <t>300_1990000_2170|600_1990000_4300|1200_1990000_8600|3600_1990000_17300|10800_1990000_26000|32400_1990000_34000</t>
+    <t>300_1990000_21700|600_1990000_43000|1200_1990000_86000|2400_1990000_173000|3600_1990000_260000|4800_1990000_340000</t>
   </si>
   <si>
     <t>VIP充值：充值金额与经验转换比例(充值金额_获得vip经验，最低支持0.01_1，美元)</t>
   </si>
   <si>
-    <t>1_10</t>
+    <t>1_60000</t>
   </si>
   <si>
     <t>积分大奖：实物奖励兑换码过期时间（天）</t>
@@ -658,7 +654,7 @@
     <t>推广分享：分享1人得固定奖励</t>
   </si>
   <si>
-    <t>1990000_100000</t>
+    <t>1990000_1000000</t>
   </si>
   <si>
     <t>推广分享：二维码图片配置(该资源放在资源服务器实时下载显示的)</t>
@@ -670,7 +666,7 @@
     <t>推广分享：周榜上榜条件设置(收益数量)</t>
   </si>
   <si>
-    <t>1990000_6000000</t>
+    <t>1990000_60000000</t>
   </si>
   <si>
     <t>推广分享：有效用户达标条件（有效下注累计_数值|累计充值_数值）</t>
@@ -738,11 +734,6 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="11"/>
-      <name val="微软雅黑"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
@@ -758,6 +749,11 @@
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
@@ -1404,18 +1400,17 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1424,29 +1419,29 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="20" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="6" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" quotePrefix="1">
       <alignment vertical="center"/>
@@ -1777,13 +1772,13 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
-    <col min="2" max="2" width="88.9666666666667" style="1" customWidth="1"/>
+    <col min="2" max="2" width="74.4083333333333" style="1" customWidth="1"/>
     <col min="3" max="4" width="28.3833333333333" style="1" customWidth="1"/>
     <col min="5" max="5" width="11.5" style="1" customWidth="1"/>
     <col min="6" max="6" width="9.625" style="1" customWidth="1"/>
     <col min="7" max="7" width="23.375" style="1" customWidth="1"/>
     <col min="8" max="8" width="12.75" style="1"/>
-    <col min="9" max="9" width="14.125" style="1"/>
+    <col min="9" max="9" width="9" style="1"/>
     <col min="10" max="10" width="11.5" style="1"/>
     <col min="11" max="11" width="9" style="1"/>
     <col min="12" max="12" width="12.875" style="1"/>
@@ -1794,51 +1789,51 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5" t="s">
+      <c r="B1" s="4"/>
+      <c r="C1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="G1" s="4" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="5"/>
-      <c r="C2" s="5" t="s">
+      <c r="B2" s="4"/>
+      <c r="C2" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="7" t="s">
+      <c r="D2" s="6" t="s">
         <v>6</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="F2" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="G2" s="5"/>
+      <c r="G2" s="4"/>
     </row>
     <row r="3" spans="1:7">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="5"/>
-      <c r="C3" s="5" t="s">
+      <c r="B3" s="4"/>
+      <c r="C3" s="4" t="s">
         <v>11</v>
       </c>
       <c r="D3" s="1" t="s">
@@ -1850,41 +1845,41 @@
       <c r="F3" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="G3" s="5"/>
+      <c r="G3" s="4"/>
     </row>
     <row r="4" spans="1:7">
-      <c r="A4" s="8"/>
-      <c r="B4" s="7"/>
-      <c r="C4" s="7"/>
-      <c r="G4" s="7"/>
+      <c r="A4" s="7"/>
+      <c r="B4" s="6"/>
+      <c r="C4" s="6"/>
+      <c r="G4" s="6"/>
     </row>
     <row r="5" spans="1:7">
       <c r="A5" s="1">
         <v>1</v>
       </c>
-      <c r="B5" s="7" t="s">
+      <c r="B5" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="D5" s="7">
+      <c r="D5" s="6">
         <v>999</v>
       </c>
-      <c r="E5" s="7"/>
-      <c r="F5" s="7"/>
-      <c r="G5" s="7"/>
+      <c r="E5" s="6"/>
+      <c r="F5" s="6"/>
+      <c r="G5" s="6"/>
     </row>
     <row r="6" spans="1:7">
       <c r="A6" s="1">
         <v>2</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="B6" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="D6" s="9">
+      <c r="D6" s="8">
         <v>30000</v>
       </c>
-      <c r="E6" s="7"/>
-      <c r="F6" s="7"/>
-      <c r="G6" s="7" t="s">
+      <c r="E6" s="6"/>
+      <c r="F6" s="6"/>
+      <c r="G6" s="6" t="s">
         <v>17</v>
       </c>
     </row>
@@ -1892,15 +1887,15 @@
       <c r="A7" s="1">
         <v>3</v>
       </c>
-      <c r="B7" s="7" t="s">
+      <c r="B7" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="D7" s="7">
+      <c r="D7" s="6">
         <v>10000</v>
       </c>
-      <c r="E7" s="7"/>
-      <c r="F7" s="7"/>
-      <c r="G7" s="7" t="s">
+      <c r="E7" s="6"/>
+      <c r="F7" s="6"/>
+      <c r="G7" s="6" t="s">
         <v>17</v>
       </c>
     </row>
@@ -1908,16 +1903,16 @@
       <c r="A8" s="1">
         <v>4</v>
       </c>
-      <c r="B8" s="7" t="s">
+      <c r="B8" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="C8" s="7">
+      <c r="C8" s="6">
         <v>100</v>
       </c>
-      <c r="D8" s="7"/>
-      <c r="E8" s="7"/>
-      <c r="F8" s="7"/>
-      <c r="G8" s="7" t="s">
+      <c r="D8" s="6"/>
+      <c r="E8" s="6"/>
+      <c r="F8" s="6"/>
+      <c r="G8" s="6" t="s">
         <v>20</v>
       </c>
     </row>
@@ -1939,15 +1934,15 @@
       <c r="A10" s="1">
         <v>6</v>
       </c>
-      <c r="B10" s="7" t="s">
+      <c r="B10" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="C10" s="27" t="s">
+      <c r="C10" s="26" t="s">
         <v>24</v>
       </c>
-      <c r="D10" s="10"/>
-      <c r="E10" s="7"/>
-      <c r="F10" s="7"/>
+      <c r="D10" s="9"/>
+      <c r="E10" s="6"/>
+      <c r="F10" s="6"/>
       <c r="G10" s="1" t="s">
         <v>25</v>
       </c>
@@ -1956,15 +1951,15 @@
       <c r="A11" s="1">
         <v>7</v>
       </c>
-      <c r="B11" s="7" t="s">
+      <c r="B11" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="C11" s="28" t="s">
+      <c r="C11" s="27" t="s">
         <v>27</v>
       </c>
-      <c r="D11" s="7"/>
-      <c r="E11" s="7"/>
-      <c r="F11" s="7"/>
+      <c r="D11" s="6"/>
+      <c r="E11" s="6"/>
+      <c r="F11" s="6"/>
       <c r="G11" s="1" t="s">
         <v>25</v>
       </c>
@@ -1973,15 +1968,15 @@
       <c r="A12" s="1">
         <v>8</v>
       </c>
-      <c r="B12" s="7" t="s">
+      <c r="B12" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="C12" s="28" t="s">
+      <c r="C12" s="27" t="s">
         <v>29</v>
       </c>
-      <c r="D12" s="7"/>
-      <c r="E12" s="7"/>
-      <c r="F12" s="7"/>
+      <c r="D12" s="6"/>
+      <c r="E12" s="6"/>
+      <c r="F12" s="6"/>
       <c r="G12" s="1" t="s">
         <v>25</v>
       </c>
@@ -1990,15 +1985,15 @@
       <c r="A13" s="1">
         <v>9</v>
       </c>
-      <c r="B13" s="7" t="s">
+      <c r="B13" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="C13" s="28" t="s">
+      <c r="C13" s="27" t="s">
         <v>31</v>
       </c>
-      <c r="D13" s="7"/>
-      <c r="E13" s="7"/>
-      <c r="F13" s="7"/>
+      <c r="D13" s="6"/>
+      <c r="E13" s="6"/>
+      <c r="F13" s="6"/>
       <c r="G13" s="1" t="s">
         <v>25</v>
       </c>
@@ -2007,15 +2002,15 @@
       <c r="A14" s="1">
         <v>10</v>
       </c>
-      <c r="B14" s="7" t="s">
+      <c r="B14" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="C14" s="28" t="s">
+      <c r="C14" s="27" t="s">
         <v>33</v>
       </c>
-      <c r="D14" s="7"/>
-      <c r="E14" s="7"/>
-      <c r="F14" s="7"/>
+      <c r="D14" s="6"/>
+      <c r="E14" s="6"/>
+      <c r="F14" s="6"/>
       <c r="G14" s="1" t="s">
         <v>25</v>
       </c>
@@ -2064,7 +2059,7 @@
       <c r="B18" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C18" s="11" t="s">
+      <c r="C18" s="10" t="s">
         <v>39</v>
       </c>
       <c r="G18" s="1" t="s">
@@ -2145,7 +2140,7 @@
       <c r="B25" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="C25" s="12" t="s">
+      <c r="C25" s="11" t="s">
         <v>50</v>
       </c>
       <c r="G25" s="1" t="s">
@@ -2206,7 +2201,7 @@
       <c r="B30" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="C30" s="13"/>
+      <c r="C30" s="12"/>
       <c r="D30" s="1">
         <v>100</v>
       </c>
@@ -2248,10 +2243,10 @@
       </c>
     </row>
     <row r="34" s="2" customFormat="1" spans="1:23">
-      <c r="A34" s="14">
+      <c r="A34" s="13">
         <v>30</v>
       </c>
-      <c r="B34" s="14" t="s">
+      <c r="B34" s="13" t="s">
         <v>65</v>
       </c>
       <c r="C34" s="2" t="s">
@@ -2259,20 +2254,20 @@
       </c>
     </row>
     <row r="35" s="2" customFormat="1" spans="1:23">
-      <c r="A35" s="14">
+      <c r="A35" s="13">
         <v>31</v>
       </c>
-      <c r="B35" s="14" t="s">
+      <c r="B35" s="13" t="s">
         <v>67</v>
       </c>
-      <c r="E35" s="15">
-        <v>372460972.440945</v>
+      <c r="E35" s="14">
+        <v>114109.053811181</v>
       </c>
       <c r="G35" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="H35" s="15">
-        <v>8692.20472440945</v>
+      <c r="H35" s="14">
+        <v>5705.45269055904</v>
       </c>
       <c r="I35" s="2" t="s">
         <v>69</v>
@@ -2292,10 +2287,10 @@
       </c>
     </row>
     <row r="36" spans="1:23">
-      <c r="A36" s="14">
+      <c r="A36" s="13">
         <v>32</v>
       </c>
-      <c r="B36" s="14" t="s">
+      <c r="B36" s="13" t="s">
         <v>72</v>
       </c>
       <c r="C36" s="2" t="s">
@@ -2303,171 +2298,171 @@
       </c>
     </row>
     <row r="37" spans="1:23">
-      <c r="A37" s="16">
+      <c r="A37" s="15">
         <v>33</v>
       </c>
-      <c r="B37" s="16" t="s">
+      <c r="B37" s="15" t="s">
         <v>74</v>
       </c>
-      <c r="C37" s="15" t="s">
+      <c r="C37" s="14" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="38" s="3" customFormat="1" spans="1:23">
-      <c r="A38" s="17">
+    <row r="38" s="2" customFormat="1" spans="1:23">
+      <c r="A38" s="13">
         <v>34</v>
       </c>
-      <c r="B38" s="17" t="s">
+      <c r="B38" s="13" t="s">
         <v>76</v>
       </c>
-      <c r="C38" s="3" t="s">
+      <c r="C38" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="D38" s="3"/>
-      <c r="G38" s="3" t="s">
+      <c r="G38" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="H38" s="3">
-        <v>90</v>
+      <c r="H38" s="14">
+        <v>60</v>
       </c>
     </row>
     <row r="39" spans="1:23">
-      <c r="A39" s="16">
+      <c r="A39" s="15">
         <v>35</v>
       </c>
-      <c r="B39" s="16" t="s">
+      <c r="B39" s="15" t="s">
         <v>79</v>
       </c>
-      <c r="C39" s="1" t="s">
+      <c r="C39" s="1" t="str">
+        <f>_xlfn.TEXTJOIN("|",TRUE,S39:W39)</f>
+        <v>10800000_1000|9000000_1000|7200000_1000|5400000_1000|3600000_1000</v>
+      </c>
+      <c r="G39" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="G39" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="H39" s="18">
+      <c r="H39" s="16">
         <f>ROUND(L35/(E35*H38/100/H35),0)</f>
-        <v>2240</v>
+        <v>7200000</v>
       </c>
       <c r="I39" s="1" t="s">
         <v>71</v>
       </c>
       <c r="J39" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="K39" s="17" t="s">
         <v>82</v>
       </c>
-      <c r="K39" s="19" t="s">
+      <c r="L39" s="17">
+        <v>0.25</v>
+      </c>
+      <c r="M39" s="1" t="s">
         <v>83</v>
-      </c>
-      <c r="L39" s="19">
-        <v>0.25</v>
-      </c>
-      <c r="M39" s="1" t="s">
-        <v>84</v>
       </c>
       <c r="N39" s="1">
         <f>ROUND(P39*(1+2*L39),0)</f>
-        <v>3360</v>
+        <v>10800000</v>
       </c>
       <c r="O39" s="1">
         <f>ROUND(P39*(1+1*L39),0)</f>
-        <v>2800</v>
+        <v>9000000</v>
       </c>
       <c r="P39" s="1">
         <f>H39</f>
-        <v>2240</v>
+        <v>7200000</v>
       </c>
       <c r="Q39" s="1">
         <f>ROUND(P39*(1-1*L39),0)</f>
-        <v>1680</v>
+        <v>5400000</v>
       </c>
       <c r="R39" s="1">
         <f>ROUND(P39*(1-2*L39),0)</f>
-        <v>1120</v>
+        <v>3600000</v>
       </c>
       <c r="S39" s="1" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,N39,1000)</f>
-        <v>3360_1000</v>
+        <v>10800000_1000</v>
       </c>
       <c r="T39" s="1" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,O39,1000)</f>
-        <v>2800_1000</v>
+        <v>9000000_1000</v>
       </c>
       <c r="U39" s="1" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,P39,1000)</f>
-        <v>2240_1000</v>
+        <v>7200000_1000</v>
       </c>
       <c r="V39" s="1" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,Q39,1000)</f>
-        <v>1680_1000</v>
+        <v>5400000_1000</v>
       </c>
       <c r="W39" s="1" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,R39,1000)</f>
-        <v>1120_1000</v>
+        <v>3600000_1000</v>
       </c>
     </row>
     <row r="40" spans="1:23">
-      <c r="A40" s="20">
+      <c r="A40" s="18">
         <v>40</v>
       </c>
-      <c r="B40" s="20" t="s">
+      <c r="B40" s="18" t="s">
+        <v>84</v>
+      </c>
+      <c r="D40" s="19">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="41" spans="1:23">
+      <c r="A41" s="18">
+        <v>41</v>
+      </c>
+      <c r="B41" s="18" t="s">
         <v>85</v>
       </c>
-      <c r="D40" s="15">
+      <c r="D41" s="19">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="42" spans="1:23">
+      <c r="A42" s="18">
+        <v>42</v>
+      </c>
+      <c r="B42" s="18" t="s">
+        <v>86</v>
+      </c>
+      <c r="D42" s="19">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="43" spans="1:23">
+      <c r="A43" s="18">
+        <v>43</v>
+      </c>
+      <c r="B43" s="18" t="s">
+        <v>87</v>
+      </c>
+      <c r="D43" s="19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:23">
+      <c r="A44" s="18">
+        <v>44</v>
+      </c>
+      <c r="B44" s="1" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="41" spans="1:23">
-      <c r="A41" s="20">
-        <v>41</v>
-      </c>
-      <c r="B41" s="20" t="s">
-        <v>86</v>
-      </c>
-      <c r="D41" s="15">
-        <v>1200</v>
-      </c>
-    </row>
-    <row r="42" spans="1:23">
-      <c r="A42" s="20">
-        <v>42</v>
-      </c>
-      <c r="B42" s="20" t="s">
-        <v>87</v>
-      </c>
-      <c r="D42" s="15">
-        <v>36000</v>
-      </c>
-    </row>
-    <row r="43" spans="1:23">
-      <c r="A43" s="20">
-        <v>43</v>
-      </c>
-      <c r="B43" s="20" t="s">
-        <v>88</v>
-      </c>
-      <c r="D43" s="15">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="44" spans="1:23">
-      <c r="A44" s="20">
-        <v>44</v>
-      </c>
-      <c r="B44" s="1" t="s">
+      <c r="D44" s="14">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="45" spans="1:23">
+      <c r="A45" s="18">
+        <v>45</v>
+      </c>
+      <c r="B45" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D44" s="15">
-        <v>290000</v>
-      </c>
-    </row>
-    <row r="45" spans="1:23">
-      <c r="A45" s="20">
-        <v>45</v>
-      </c>
-      <c r="B45" s="1" t="s">
+      <c r="C45" s="14" t="s">
         <v>90</v>
-      </c>
-      <c r="C45" s="15" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="46" spans="1:23">
@@ -2475,10 +2470,10 @@
         <v>46</v>
       </c>
       <c r="B46" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="C46" s="14" t="s">
         <v>92</v>
-      </c>
-      <c r="C46" s="15" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="47" spans="1:23">
@@ -2486,7 +2481,7 @@
         <v>47</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D47" s="1">
         <v>3</v>
@@ -2497,10 +2492,10 @@
         <v>48</v>
       </c>
       <c r="B48" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="C48" s="1" t="s">
         <v>95</v>
-      </c>
-      <c r="C48" s="1" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2508,10 +2503,10 @@
         <v>49</v>
       </c>
       <c r="B49" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="C49" s="1" t="s">
         <v>97</v>
-      </c>
-      <c r="C49" s="1" t="s">
-        <v>98</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2519,19 +2514,19 @@
         <v>50</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="C50" s="15"/>
+        <v>98</v>
+      </c>
+      <c r="C50" s="14"/>
     </row>
     <row r="51" s="2" customFormat="1" spans="1:4">
       <c r="A51" s="2">
         <v>51</v>
       </c>
       <c r="B51" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="C51" s="20" t="s">
         <v>100</v>
-      </c>
-      <c r="C51" s="21" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2539,10 +2534,10 @@
         <v>52</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="D52" s="12">
-        <v>1</v>
+        <v>101</v>
+      </c>
+      <c r="D52" s="11">
+        <v>29000</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2550,10 +2545,10 @@
         <v>53</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="D53" s="12">
-        <v>1</v>
+        <v>102</v>
+      </c>
+      <c r="D53" s="11">
+        <v>29000</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2561,7 +2556,7 @@
         <v>54</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D54" s="1">
         <v>0</v>
@@ -2572,7 +2567,7 @@
         <v>55</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C55" s="1"/>
       <c r="D55" s="1">
@@ -2584,10 +2579,10 @@
         <v>56</v>
       </c>
       <c r="B56" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="C56" s="1" t="s">
         <v>106</v>
-      </c>
-      <c r="C56" s="1" t="s">
-        <v>107</v>
       </c>
     </row>
     <row r="57" s="2" customFormat="1" spans="1:4">
@@ -2595,10 +2590,10 @@
         <v>60</v>
       </c>
       <c r="B57" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="C57" s="21" t="s">
         <v>108</v>
-      </c>
-      <c r="C57" s="22" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2606,10 +2601,10 @@
         <v>61</v>
       </c>
       <c r="B58" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="C58" s="22" t="s">
         <v>110</v>
-      </c>
-      <c r="C58" s="23" t="s">
-        <v>111</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2617,10 +2612,10 @@
         <v>62</v>
       </c>
       <c r="B59" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="C59" s="23" t="s">
         <v>112</v>
-      </c>
-      <c r="C59" s="24" t="s">
-        <v>113</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2628,10 +2623,10 @@
         <v>63</v>
       </c>
       <c r="B60" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="C60" s="1" t="s">
         <v>114</v>
-      </c>
-      <c r="C60" s="1" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2639,10 +2634,10 @@
         <v>64</v>
       </c>
       <c r="B61" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="C61" s="14" t="s">
         <v>116</v>
-      </c>
-      <c r="C61" s="15" t="s">
-        <v>117</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2650,10 +2645,10 @@
         <v>65</v>
       </c>
       <c r="B62" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="C62" s="14" t="s">
         <v>118</v>
-      </c>
-      <c r="C62" s="15" t="s">
-        <v>119</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2661,22 +2656,22 @@
         <v>70</v>
       </c>
       <c r="B63" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="C63" s="24" t="s">
         <v>120</v>
       </c>
-      <c r="C63" s="25" t="s">
-        <v>121</v>
-      </c>
-      <c r="D63" s="25"/>
+      <c r="D63" s="24"/>
     </row>
     <row r="64" spans="1:4">
       <c r="A64" s="1">
         <v>71</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="C64" s="25"/>
-      <c r="D64" s="25">
+        <v>121</v>
+      </c>
+      <c r="C64" s="24"/>
+      <c r="D64" s="24">
         <v>5000</v>
       </c>
     </row>
@@ -2685,46 +2680,47 @@
         <v>72</v>
       </c>
       <c r="B65" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="C65" s="19" t="s">
         <v>123</v>
       </c>
-      <c r="C65" s="15" t="s">
+      <c r="D65" s="19"/>
+    </row>
+    <row r="66" spans="1:20">
+      <c r="A66" s="25">
+        <v>80</v>
+      </c>
+      <c r="B66" s="25" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="66" spans="1:20">
-      <c r="A66" s="26">
-        <v>80</v>
-      </c>
-      <c r="B66" s="26" t="s">
-        <v>125</v>
-      </c>
-      <c r="C66" s="26"/>
-      <c r="D66" s="26">
+      <c r="C66" s="25"/>
+      <c r="D66" s="25">
         <v>259200</v>
       </c>
-      <c r="E66" s="6"/>
-      <c r="F66" s="6"/>
-      <c r="G66" s="6"/>
-      <c r="H66" s="6"/>
-      <c r="I66" s="6"/>
-      <c r="J66" s="6"/>
-      <c r="K66" s="6"/>
-      <c r="L66" s="6"/>
-      <c r="M66" s="6"/>
-      <c r="N66" s="6"/>
-      <c r="O66" s="6"/>
-      <c r="P66" s="6"/>
-      <c r="Q66" s="6"/>
-      <c r="R66" s="6"/>
-      <c r="S66" s="6"/>
-      <c r="T66" s="6"/>
+      <c r="E66" s="5"/>
+      <c r="F66" s="5"/>
+      <c r="G66" s="5"/>
+      <c r="H66" s="5"/>
+      <c r="I66" s="5"/>
+      <c r="J66" s="5"/>
+      <c r="K66" s="5"/>
+      <c r="L66" s="5"/>
+      <c r="M66" s="5"/>
+      <c r="N66" s="5"/>
+      <c r="O66" s="5"/>
+      <c r="P66" s="5"/>
+      <c r="Q66" s="5"/>
+      <c r="R66" s="5"/>
+      <c r="S66" s="5"/>
+      <c r="T66" s="5"/>
     </row>
     <row r="67" spans="1:20">
       <c r="A67" s="1">
         <v>90</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D67" s="1">
         <v>1000000</v>
@@ -2735,10 +2731,10 @@
         <v>100</v>
       </c>
       <c r="B68" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="C68" s="1" t="s">
         <v>127</v>
-      </c>
-      <c r="C68" s="1" t="s">
-        <v>128</v>
       </c>
     </row>
   </sheetData>

--- a/gm/resources/sample/global.xlsx
+++ b/gm/resources/sample/global.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29426"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\gamefile\策划配置表\common\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0096D60A-50DD-4FC0-9D48-48A80A44162F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="globalConfig" sheetId="1" r:id="rId1"/>
@@ -27,12 +33,12 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Administrator</author>
   </authors>
   <commentList>
-    <comment ref="D16" authorId="0">
+    <comment ref="D16" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
       <text>
         <r>
           <rPr>
@@ -54,7 +60,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G18" authorId="0">
+    <comment ref="G18" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
       <text>
         <r>
           <rPr>
@@ -77,7 +83,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E35" authorId="0">
+    <comment ref="E35" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
       <text>
         <r>
           <rPr>
@@ -102,7 +108,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C37" authorId="0">
+    <comment ref="C37" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000004000000}">
       <text>
         <r>
           <rPr>
@@ -124,7 +130,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B48" authorId="0">
+    <comment ref="B48" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000005000000}">
       <text>
         <r>
           <rPr>
@@ -146,7 +152,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C50" authorId="0">
+    <comment ref="C50" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000006000000}">
       <text>
         <r>
           <rPr>
@@ -168,7 +174,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B51" authorId="0">
+    <comment ref="B51" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000007000000}">
       <text>
         <r>
           <rPr>
@@ -190,7 +196,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D52" authorId="0">
+    <comment ref="D52" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000008000000}">
       <text>
         <r>
           <rPr>
@@ -212,7 +218,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D53" authorId="0">
+    <comment ref="D53" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000009000000}">
       <text>
         <r>
           <rPr>
@@ -235,7 +241,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D54" authorId="0">
+    <comment ref="D54" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000A000000}">
       <text>
         <r>
           <rPr>
@@ -258,7 +264,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C56" authorId="0">
+    <comment ref="C56" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000B000000}">
       <text>
         <r>
           <rPr>
@@ -280,7 +286,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C65" authorId="0">
+    <comment ref="C65" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000C000000}">
       <text>
         <r>
           <rPr>
@@ -709,24 +715,20 @@
     <t>幸运夺宝：商品价值货币的图标</t>
   </si>
   <si>
-    <t>itemicon_1980000.png</t>
-  </si>
-  <si>
     <t>幸运夺宝：抢购商品所需要的道具ID(仅在界面左上角处显示的抢购消耗道具的信息)</t>
+  </si>
+  <si>
+    <t>icon_vnd.png</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="5">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="0_ "/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="178" formatCode="0_ "/>
   </numFmts>
-  <fonts count="31">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -742,7 +744,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0" tint="-0.25"/>
+      <color theme="0" tint="-0.249977111117893"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
@@ -779,158 +781,22 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0" tint="-0.25"/>
+      <color theme="0" tint="-0.249977111117893"/>
       <name val="Times New Roman"/>
-      <charset val="134"/>
+      <family val="1"/>
     </font>
     <font>
       <sz val="10.5"/>
-      <color theme="0" tint="-0.25"/>
+      <color theme="0" tint="-0.249977111117893"/>
       <name val="Arial"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
       <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="等线"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -944,8 +810,15 @@
       <name val="宋体"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="35">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -954,204 +827,18 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.8"/>
+        <fgColor theme="5" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -1174,249 +861,10 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1456,77 +904,32 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="178" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="6" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" quotePrefix="1">
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" quotePrefix="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+    <cellStyle name="超链接" xfId="1" builtinId="8"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1784,18 +1187,18 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:W70"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
-    <col min="2" max="2" width="88.9666666666667" style="1" customWidth="1"/>
-    <col min="3" max="4" width="28.3833333333333" style="1" customWidth="1"/>
+    <col min="2" max="2" width="89" style="1" customWidth="1"/>
+    <col min="3" max="4" width="28.375" style="1" customWidth="1"/>
     <col min="5" max="5" width="11.5" style="1" customWidth="1"/>
     <col min="6" max="6" width="9.625" style="1" customWidth="1"/>
     <col min="7" max="7" width="23.375" style="1" customWidth="1"/>
@@ -1810,7 +1213,7 @@
     <col min="19" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -1831,7 +1234,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
         <v>6</v>
       </c>
@@ -1850,7 +1253,7 @@
       </c>
       <c r="G2" s="5"/>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>10</v>
       </c>
@@ -1869,13 +1272,13 @@
       </c>
       <c r="G3" s="5"/>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="8"/>
       <c r="B4" s="7"/>
       <c r="C4" s="7"/>
       <c r="G4" s="7"/>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>1</v>
       </c>
@@ -1889,7 +1292,7 @@
       <c r="F5" s="7"/>
       <c r="G5" s="7"/>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>2</v>
       </c>
@@ -1905,7 +1308,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>3</v>
       </c>
@@ -1921,7 +1324,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>4</v>
       </c>
@@ -1938,7 +1341,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>5</v>
       </c>
@@ -1952,14 +1355,14 @@
         <v>22</v>
       </c>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>6</v>
       </c>
       <c r="B10" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="C10" s="28" t="s">
+      <c r="C10" s="26" t="s">
         <v>24</v>
       </c>
       <c r="D10" s="10"/>
@@ -1969,14 +1372,14 @@
         <v>25</v>
       </c>
     </row>
-    <row r="11" spans="1:7">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <v>7</v>
       </c>
       <c r="B11" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="C11" s="29" t="s">
+      <c r="C11" s="27" t="s">
         <v>27</v>
       </c>
       <c r="D11" s="7"/>
@@ -1986,14 +1389,14 @@
         <v>25</v>
       </c>
     </row>
-    <row r="12" spans="1:7">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <v>8</v>
       </c>
       <c r="B12" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="C12" s="29" t="s">
+      <c r="C12" s="27" t="s">
         <v>29</v>
       </c>
       <c r="D12" s="7"/>
@@ -2003,14 +1406,14 @@
         <v>25</v>
       </c>
     </row>
-    <row r="13" spans="1:7">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <v>9</v>
       </c>
       <c r="B13" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="C13" s="29" t="s">
+      <c r="C13" s="27" t="s">
         <v>31</v>
       </c>
       <c r="D13" s="7"/>
@@ -2020,14 +1423,14 @@
         <v>25</v>
       </c>
     </row>
-    <row r="14" spans="1:7">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <v>10</v>
       </c>
       <c r="B14" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="C14" s="29" t="s">
+      <c r="C14" s="27" t="s">
         <v>33</v>
       </c>
       <c r="D14" s="7"/>
@@ -2037,7 +1440,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="15" spans="1:7">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <v>11</v>
       </c>
@@ -2049,7 +1452,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="16" spans="1:7">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <v>12</v>
       </c>
@@ -2063,7 +1466,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="17" spans="1:7">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
         <v>13</v>
       </c>
@@ -2074,7 +1477,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:7">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
         <v>14</v>
       </c>
@@ -2088,7 +1491,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="19" spans="1:7">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
         <v>15</v>
       </c>
@@ -2099,7 +1502,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="20" spans="1:7">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
         <v>16</v>
       </c>
@@ -2110,7 +1513,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="21" spans="1:7">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
         <v>17</v>
       </c>
@@ -2121,7 +1524,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="22" spans="1:7">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
         <v>18</v>
       </c>
@@ -2133,7 +1536,7 @@
         <v>604800</v>
       </c>
     </row>
-    <row r="23" spans="1:7">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" s="1">
         <v>19</v>
       </c>
@@ -2144,7 +1547,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="24" spans="1:7">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" s="1">
         <v>20</v>
       </c>
@@ -2155,7 +1558,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="25" spans="1:7">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" s="1">
         <v>21</v>
       </c>
@@ -2169,7 +1572,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="26" spans="1:7">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" s="1">
         <v>22</v>
       </c>
@@ -2183,7 +1586,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="27" spans="1:7">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" s="1">
         <v>23</v>
       </c>
@@ -2194,7 +1597,7 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="28" spans="1:7">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" s="1">
         <v>24</v>
       </c>
@@ -2205,7 +1608,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="29" s="1" customFormat="1" spans="1:7">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" s="1">
         <v>25</v>
       </c>
@@ -2216,7 +1619,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="30" spans="1:7">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" s="1">
         <v>26</v>
       </c>
@@ -2228,7 +1631,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="31" spans="1:7">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" s="1">
         <v>27</v>
       </c>
@@ -2242,7 +1645,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="32" spans="1:7">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" s="1">
         <v>28</v>
       </c>
@@ -2253,7 +1656,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="33" spans="1:23">
+    <row r="33" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A33" s="1">
         <v>29</v>
       </c>
@@ -2264,7 +1667,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="34" s="2" customFormat="1" spans="1:23">
+    <row r="34" spans="1:23" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A34" s="14">
         <v>30</v>
       </c>
@@ -2275,7 +1678,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="35" s="2" customFormat="1" spans="1:23">
+    <row r="35" spans="1:23" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A35" s="14">
         <v>31</v>
       </c>
@@ -2283,13 +1686,13 @@
         <v>67</v>
       </c>
       <c r="E35" s="15">
-        <v>372460972.440945</v>
+        <v>372460972.44094503</v>
       </c>
       <c r="G35" s="2" t="s">
         <v>68</v>
       </c>
       <c r="H35" s="15">
-        <v>8692.20472440945</v>
+        <v>8692.2047244094501</v>
       </c>
       <c r="I35" s="2" t="s">
         <v>69</v>
@@ -2308,7 +1711,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="36" spans="1:23">
+    <row r="36" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A36" s="14">
         <v>32</v>
       </c>
@@ -2319,7 +1722,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="37" spans="1:23">
+    <row r="37" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A37" s="16">
         <v>33</v>
       </c>
@@ -2330,7 +1733,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="38" s="3" customFormat="1" spans="1:23">
+    <row r="38" spans="1:23" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A38" s="18">
         <v>34</v>
       </c>
@@ -2340,7 +1743,6 @@
       <c r="C38" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="D38" s="3"/>
       <c r="G38" s="3" t="s">
         <v>78</v>
       </c>
@@ -2348,7 +1750,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="39" spans="1:23">
+    <row r="39" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A39" s="16">
         <v>35</v>
       </c>
@@ -2421,7 +1823,7 @@
         <v>1120_1000</v>
       </c>
     </row>
-    <row r="40" spans="1:23">
+    <row r="40" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A40" s="21">
         <v>40</v>
       </c>
@@ -2432,7 +1834,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="41" spans="1:23">
+    <row r="41" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A41" s="21">
         <v>41</v>
       </c>
@@ -2443,7 +1845,7 @@
         <v>1200</v>
       </c>
     </row>
-    <row r="42" spans="1:23">
+    <row r="42" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A42" s="21">
         <v>42</v>
       </c>
@@ -2454,7 +1856,7 @@
         <v>36000</v>
       </c>
     </row>
-    <row r="43" spans="1:23">
+    <row r="43" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A43" s="21">
         <v>43</v>
       </c>
@@ -2465,7 +1867,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:23">
+    <row r="44" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A44" s="21">
         <v>44</v>
       </c>
@@ -2476,7 +1878,7 @@
         <v>290000</v>
       </c>
     </row>
-    <row r="45" spans="1:23">
+    <row r="45" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A45" s="21">
         <v>45</v>
       </c>
@@ -2487,7 +1889,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="46" spans="1:23">
+    <row r="46" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A46" s="1">
         <v>46</v>
       </c>
@@ -2498,7 +1900,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="47" spans="1:23">
+    <row r="47" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A47" s="1">
         <v>47</v>
       </c>
@@ -2509,7 +1911,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="48" spans="1:23">
+    <row r="48" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A48" s="1">
         <v>48</v>
       </c>
@@ -2520,7 +1922,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="49" spans="1:4">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A49" s="1">
         <v>49</v>
       </c>
@@ -2531,7 +1933,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="50" spans="1:4">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A50" s="1">
         <v>50</v>
       </c>
@@ -2540,7 +1942,7 @@
       </c>
       <c r="C50" s="17"/>
     </row>
-    <row r="51" s="2" customFormat="1" spans="1:4">
+    <row r="51" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A51" s="2">
         <v>51</v>
       </c>
@@ -2551,7 +1953,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="52" spans="1:4">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A52" s="1">
         <v>52</v>
       </c>
@@ -2562,7 +1964,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:4">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A53" s="1">
         <v>53</v>
       </c>
@@ -2573,7 +1975,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:4">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A54" s="1">
         <v>54</v>
       </c>
@@ -2584,7 +1986,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" customFormat="1" spans="1:4">
+    <row r="55" spans="1:4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A55" s="1">
         <v>55</v>
       </c>
@@ -2596,7 +1998,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="56" spans="1:4">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A56" s="1">
         <v>56</v>
       </c>
@@ -2607,7 +2009,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="57" s="2" customFormat="1" spans="1:4">
+    <row r="57" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A57" s="2">
         <v>60</v>
       </c>
@@ -2618,7 +2020,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="58" spans="1:4">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A58" s="1">
         <v>61</v>
       </c>
@@ -2629,18 +2031,18 @@
         <v>111</v>
       </c>
     </row>
-    <row r="59" spans="1:4">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A59" s="1">
         <v>62</v>
       </c>
       <c r="B59" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="C59" s="25" t="s">
+      <c r="C59" s="12" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="60" spans="1:4">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A60" s="1">
         <v>63</v>
       </c>
@@ -2651,7 +2053,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="61" spans="1:4">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A61" s="1">
         <v>64</v>
       </c>
@@ -2662,7 +2064,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="62" spans="1:4">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A62" s="1">
         <v>65</v>
       </c>
@@ -2673,31 +2075,31 @@
         <v>119</v>
       </c>
     </row>
-    <row r="63" spans="1:4">
+    <row r="63" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A63" s="1">
         <v>70</v>
       </c>
       <c r="B63" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="C63" s="26" t="s">
+      <c r="C63" s="17" t="s">
         <v>121</v>
       </c>
-      <c r="D63" s="26"/>
-    </row>
-    <row r="64" spans="1:4">
+      <c r="D63" s="17"/>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A64" s="1">
         <v>71</v>
       </c>
       <c r="B64" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="C64" s="26"/>
-      <c r="D64" s="26">
+      <c r="C64" s="17"/>
+      <c r="D64" s="17">
         <v>5000</v>
       </c>
     </row>
-    <row r="65" spans="1:20">
+    <row r="65" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A65" s="1">
         <v>72</v>
       </c>
@@ -2708,15 +2110,15 @@
         <v>124</v>
       </c>
     </row>
-    <row r="66" spans="1:20">
-      <c r="A66" s="27">
+    <row r="66" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A66" s="25">
         <v>80</v>
       </c>
-      <c r="B66" s="27" t="s">
+      <c r="B66" s="25" t="s">
         <v>125</v>
       </c>
-      <c r="C66" s="27"/>
-      <c r="D66" s="27">
+      <c r="C66" s="25"/>
+      <c r="D66" s="25">
         <v>259200</v>
       </c>
       <c r="E66" s="6"/>
@@ -2736,7 +2138,7 @@
       <c r="S66" s="6"/>
       <c r="T66" s="6"/>
     </row>
-    <row r="67" spans="1:20">
+    <row r="67" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A67" s="1">
         <v>90</v>
       </c>
@@ -2747,7 +2149,7 @@
         <v>1000000</v>
       </c>
     </row>
-    <row r="68" spans="1:20">
+    <row r="68" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A68" s="1">
         <v>100</v>
       </c>
@@ -2758,7 +2160,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="69" spans="1:20">
+    <row r="69" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A69" s="1">
         <v>101</v>
       </c>
@@ -2766,27 +2168,27 @@
         <v>129</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="70" spans="1:20">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="70" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A70" s="1">
         <v>102</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C70" s="13">
-        <v>1022503</v>
+        <v>1980000</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="13" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="C57" r:id="rId3" display="https://aws-s3-jjg-asset-bucket.s3.ap-southeast-1.amazonaws.com/tanchuang_res/english/tc_sc_1.png" tooltip="https://aws-s3-jjg-asset-bucket.s3.ap-southeast-1.amazonaws.com/tanchuang_res/english/tc_sc_1.png"/>
+    <hyperlink ref="C57" r:id="rId1" tooltip="https://aws-s3-jjg-asset-bucket.s3.ap-southeast-1.amazonaws.com/tanchuang_res/english/tc_sc_1.png" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
   <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/gm/resources/sample/global.xlsx
+++ b/gm/resources/sample/global.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29426"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\gamefile\策划配置表\common\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0096D60A-50DD-4FC0-9D48-48A80A44162F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="27735" windowHeight="12270"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="globalConfig" sheetId="1" r:id="rId1"/>
@@ -27,12 +33,12 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Administrator</author>
   </authors>
   <commentList>
-    <comment ref="D16" authorId="0">
+    <comment ref="D16" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
       <text>
         <r>
           <rPr>
@@ -54,7 +60,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G18" authorId="0">
+    <comment ref="G18" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
       <text>
         <r>
           <rPr>
@@ -77,7 +83,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E35" authorId="0">
+    <comment ref="E35" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
       <text>
         <r>
           <rPr>
@@ -95,13 +101,14 @@
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
+奖池总量
 总量 ÷ 平均中奖金额 = 中奖次数
 1000000000 ÷ 718000 = 1392.7577
 初始天数30天</t>
         </r>
       </text>
     </comment>
-    <comment ref="C37" authorId="0">
+    <comment ref="C37" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000004000000}">
       <text>
         <r>
           <rPr>
@@ -123,7 +130,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B48" authorId="0">
+    <comment ref="B48" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000005000000}">
       <text>
         <r>
           <rPr>
@@ -145,7 +152,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C50" authorId="0">
+    <comment ref="C50" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000006000000}">
       <text>
         <r>
           <rPr>
@@ -167,7 +174,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B51" authorId="0">
+    <comment ref="B51" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000007000000}">
       <text>
         <r>
           <rPr>
@@ -189,7 +196,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D52" authorId="0">
+    <comment ref="D52" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000008000000}">
       <text>
         <r>
           <rPr>
@@ -211,7 +218,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D53" authorId="0">
+    <comment ref="D53" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000009000000}">
       <text>
         <r>
           <rPr>
@@ -234,7 +241,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D54" authorId="0">
+    <comment ref="D54" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000A000000}">
       <text>
         <r>
           <rPr>
@@ -257,7 +264,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C56" authorId="0">
+    <comment ref="C56" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000B000000}">
       <text>
         <r>
           <rPr>
@@ -279,7 +286,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C65" authorId="0">
+    <comment ref="C65" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000C000000}">
       <text>
         <r>
           <rPr>
@@ -316,7 +323,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="132">
   <si>
     <t>sid</t>
   </si>
@@ -540,16 +547,16 @@
     <t>100000_1</t>
   </si>
   <si>
-    <t>官方派奖：充值转换积分比例 ：充值金额（29000越南盾 = 1 积分 )</t>
-  </si>
-  <si>
-    <t>1_1</t>
-  </si>
-  <si>
-    <t>官方派奖：真人和机器人奖池比例(百分比)  （废弃，功能不存在）</t>
-  </si>
-  <si>
-    <t>10_90</t>
+    <t>官方派奖：充值转换积分比例 ：充值金额（290,000 越南盾 = 1 积分 )</t>
+  </si>
+  <si>
+    <t>208000_1</t>
+  </si>
+  <si>
+    <t>官方派奖：转盘1次数_转盘2次数_转盘3次数（真人抽奖后机器人跟着的抽奖次数，填10，表示玩家抽1次，机器人抽10次）</t>
+  </si>
+  <si>
+    <t>99_99_99</t>
   </si>
   <si>
     <t>机器人奖池比例</t>
@@ -558,6 +565,9 @@
     <t>官方派奖：机器人中奖间隔（毫秒_权重|毫秒_权重）</t>
   </si>
   <si>
+    <t>3360_1000|2800_1000|2240_1000|1680_1000|1120_1000</t>
+  </si>
+  <si>
     <t>平均中奖间隔</t>
   </si>
   <si>
@@ -588,13 +598,13 @@
     <t>积分大奖：积分保底奖励（积分数量_奖励道具ID_奖励道具数量）</t>
   </si>
   <si>
-    <t>300_1990000_21700|600_1990000_43000|1200_1990000_86000|2400_1990000_173000|3600_1990000_260000|4800_1990000_340000</t>
+    <t>300_1990000_2170|600_1990000_4300|1200_1990000_8600|3600_1990000_17300|10800_1990000_26000|32400_1990000_34000</t>
   </si>
   <si>
     <t>VIP充值：充值金额与经验转换比例(充值金额_获得vip经验，最低支持0.01_1，美元)</t>
   </si>
   <si>
-    <t>1_60000</t>
+    <t>1_10</t>
   </si>
   <si>
     <t>积分大奖：实物奖励兑换码过期时间（天）</t>
@@ -654,7 +664,7 @@
     <t>推广分享：分享1人得固定奖励</t>
   </si>
   <si>
-    <t>1990000_1000000</t>
+    <t>1990000_100000</t>
   </si>
   <si>
     <t>推广分享：二维码图片配置(该资源放在资源服务器实时下载显示的)</t>
@@ -666,7 +676,7 @@
     <t>推广分享：周榜上榜条件设置(收益数量)</t>
   </si>
   <si>
-    <t>1990000_60000000</t>
+    <t>1990000_6000000</t>
   </si>
   <si>
     <t>推广分享：有效用户达标条件（有效下注累计_数值|累计充值_数值）</t>
@@ -700,20 +710,25 @@
   </si>
   <si>
     <t>VND</t>
+  </si>
+  <si>
+    <t>幸运夺宝：商品价值货币的图标</t>
+  </si>
+  <si>
+    <t>幸运夺宝：抢购商品所需要的道具ID(仅在界面左上角处显示的抢购消耗道具的信息)</t>
+  </si>
+  <si>
+    <t>icon_vnd.png</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="5">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="0_ "/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="178" formatCode="0_ "/>
   </numFmts>
-  <fonts count="30">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -729,7 +744,12 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0" tint="-0.25"/>
+      <color theme="0" tint="-0.249977111117893"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
@@ -753,164 +773,30 @@
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
+      <color theme="2"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0" tint="-0.25"/>
+      <color theme="0" tint="-0.249977111117893"/>
       <name val="Times New Roman"/>
-      <charset val="134"/>
+      <family val="1"/>
     </font>
     <font>
       <sz val="10.5"/>
-      <color theme="0" tint="-0.25"/>
+      <color theme="0" tint="-0.249977111117893"/>
       <name val="Arial"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
       <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="等线"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -924,8 +810,15 @@
       <name val="宋体"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="35">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -934,204 +827,18 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.8"/>
+        <fgColor theme="5" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -1154,263 +861,25 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1419,92 +888,48 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="20" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="178" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="6" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" quotePrefix="1">
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" quotePrefix="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+    <cellStyle name="超链接" xfId="1" builtinId="8"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1762,23 +1187,23 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:W68"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:W70"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
-    <col min="2" max="2" width="74.4083333333333" style="1" customWidth="1"/>
-    <col min="3" max="4" width="28.3833333333333" style="1" customWidth="1"/>
+    <col min="2" max="2" width="89" style="1" customWidth="1"/>
+    <col min="3" max="4" width="28.375" style="1" customWidth="1"/>
     <col min="5" max="5" width="11.5" style="1" customWidth="1"/>
     <col min="6" max="6" width="9.625" style="1" customWidth="1"/>
     <col min="7" max="7" width="23.375" style="1" customWidth="1"/>
     <col min="8" max="8" width="12.75" style="1"/>
-    <col min="9" max="9" width="9" style="1"/>
+    <col min="9" max="9" width="14.125" style="1"/>
     <col min="10" max="10" width="11.5" style="1"/>
     <col min="11" max="11" width="9" style="1"/>
     <col min="12" max="12" width="12.875" style="1"/>
@@ -1788,52 +1213,52 @@
     <col min="19" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4" t="s">
+      <c r="B1" s="5"/>
+      <c r="C1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="5" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
-      <c r="A2" s="5" t="s">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="4"/>
-      <c r="C2" s="4" t="s">
+      <c r="B2" s="5"/>
+      <c r="C2" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" s="7" t="s">
         <v>6</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="F2" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="G2" s="4"/>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3" s="3" t="s">
+      <c r="G2" s="5"/>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A3" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="4"/>
-      <c r="C3" s="4" t="s">
+      <c r="B3" s="5"/>
+      <c r="C3" s="5" t="s">
         <v>11</v>
       </c>
       <c r="D3" s="1" t="s">
@@ -1845,78 +1270,78 @@
       <c r="F3" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="G3" s="4"/>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4" s="7"/>
-      <c r="B4" s="6"/>
-      <c r="C4" s="6"/>
-      <c r="G4" s="6"/>
-    </row>
-    <row r="5" spans="1:7">
+      <c r="G3" s="5"/>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A4" s="8"/>
+      <c r="B4" s="7"/>
+      <c r="C4" s="7"/>
+      <c r="G4" s="7"/>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>1</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="D5" s="6">
+      <c r="D5" s="7">
         <v>999</v>
       </c>
-      <c r="E5" s="6"/>
-      <c r="F5" s="6"/>
-      <c r="G5" s="6"/>
-    </row>
-    <row r="6" spans="1:7">
+      <c r="E5" s="7"/>
+      <c r="F5" s="7"/>
+      <c r="G5" s="7"/>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>2</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="D6" s="8">
+      <c r="D6" s="9">
         <v>30000</v>
       </c>
-      <c r="E6" s="6"/>
-      <c r="F6" s="6"/>
-      <c r="G6" s="6" t="s">
+      <c r="E6" s="7"/>
+      <c r="F6" s="7"/>
+      <c r="G6" s="7" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>3</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="D7" s="6">
+      <c r="D7" s="7">
         <v>10000</v>
       </c>
-      <c r="E7" s="6"/>
-      <c r="F7" s="6"/>
-      <c r="G7" s="6" t="s">
+      <c r="E7" s="7"/>
+      <c r="F7" s="7"/>
+      <c r="G7" s="7" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>4</v>
       </c>
-      <c r="B8" s="6" t="s">
+      <c r="B8" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="C8" s="6">
+      <c r="C8" s="7">
         <v>100</v>
       </c>
-      <c r="D8" s="6"/>
-      <c r="E8" s="6"/>
-      <c r="F8" s="6"/>
-      <c r="G8" s="6" t="s">
+      <c r="D8" s="7"/>
+      <c r="E8" s="7"/>
+      <c r="F8" s="7"/>
+      <c r="G8" s="7" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>5</v>
       </c>
@@ -1930,92 +1355,92 @@
         <v>22</v>
       </c>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>6</v>
       </c>
-      <c r="B10" s="6" t="s">
+      <c r="B10" s="7" t="s">
         <v>23</v>
       </c>
       <c r="C10" s="26" t="s">
         <v>24</v>
       </c>
-      <c r="D10" s="9"/>
-      <c r="E10" s="6"/>
-      <c r="F10" s="6"/>
+      <c r="D10" s="10"/>
+      <c r="E10" s="7"/>
+      <c r="F10" s="7"/>
       <c r="G10" s="1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="11" spans="1:7">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <v>7</v>
       </c>
-      <c r="B11" s="6" t="s">
+      <c r="B11" s="7" t="s">
         <v>26</v>
       </c>
       <c r="C11" s="27" t="s">
         <v>27</v>
       </c>
-      <c r="D11" s="6"/>
-      <c r="E11" s="6"/>
-      <c r="F11" s="6"/>
+      <c r="D11" s="7"/>
+      <c r="E11" s="7"/>
+      <c r="F11" s="7"/>
       <c r="G11" s="1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="12" spans="1:7">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <v>8</v>
       </c>
-      <c r="B12" s="6" t="s">
+      <c r="B12" s="7" t="s">
         <v>28</v>
       </c>
       <c r="C12" s="27" t="s">
         <v>29</v>
       </c>
-      <c r="D12" s="6"/>
-      <c r="E12" s="6"/>
-      <c r="F12" s="6"/>
+      <c r="D12" s="7"/>
+      <c r="E12" s="7"/>
+      <c r="F12" s="7"/>
       <c r="G12" s="1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="13" spans="1:7">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <v>9</v>
       </c>
-      <c r="B13" s="6" t="s">
+      <c r="B13" s="7" t="s">
         <v>30</v>
       </c>
       <c r="C13" s="27" t="s">
         <v>31</v>
       </c>
-      <c r="D13" s="6"/>
-      <c r="E13" s="6"/>
-      <c r="F13" s="6"/>
+      <c r="D13" s="7"/>
+      <c r="E13" s="7"/>
+      <c r="F13" s="7"/>
       <c r="G13" s="1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="14" spans="1:7">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <v>10</v>
       </c>
-      <c r="B14" s="6" t="s">
+      <c r="B14" s="7" t="s">
         <v>32</v>
       </c>
       <c r="C14" s="27" t="s">
         <v>33</v>
       </c>
-      <c r="D14" s="6"/>
-      <c r="E14" s="6"/>
-      <c r="F14" s="6"/>
+      <c r="D14" s="7"/>
+      <c r="E14" s="7"/>
+      <c r="F14" s="7"/>
       <c r="G14" s="1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="15" spans="1:7">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <v>11</v>
       </c>
@@ -2027,7 +1452,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="16" spans="1:7">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <v>12</v>
       </c>
@@ -2041,7 +1466,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="17" spans="1:7">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
         <v>13</v>
       </c>
@@ -2052,21 +1477,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:7">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
         <v>14</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C18" s="10" t="s">
+      <c r="C18" s="11" t="s">
         <v>39</v>
       </c>
       <c r="G18" s="1" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="19" spans="1:7">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
         <v>15</v>
       </c>
@@ -2077,7 +1502,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="20" spans="1:7">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
         <v>16</v>
       </c>
@@ -2088,7 +1513,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="21" spans="1:7">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
         <v>17</v>
       </c>
@@ -2099,7 +1524,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="22" spans="1:7">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
         <v>18</v>
       </c>
@@ -2111,7 +1536,7 @@
         <v>604800</v>
       </c>
     </row>
-    <row r="23" spans="1:7">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" s="1">
         <v>19</v>
       </c>
@@ -2122,7 +1547,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="24" spans="1:7">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" s="1">
         <v>20</v>
       </c>
@@ -2133,21 +1558,21 @@
         <v>10</v>
       </c>
     </row>
-    <row r="25" spans="1:7">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" s="1">
         <v>21</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="C25" s="11" t="s">
+      <c r="C25" s="12" t="s">
         <v>50</v>
       </c>
       <c r="G25" s="1" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="26" spans="1:7">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" s="1">
         <v>22</v>
       </c>
@@ -2161,7 +1586,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="27" spans="1:7">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" s="1">
         <v>23</v>
       </c>
@@ -2172,7 +1597,7 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="28" spans="1:7">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" s="1">
         <v>24</v>
       </c>
@@ -2183,7 +1608,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="29" s="1" customFormat="1" spans="1:7">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" s="1">
         <v>25</v>
       </c>
@@ -2194,19 +1619,19 @@
         <v>58</v>
       </c>
     </row>
-    <row r="30" spans="1:7">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" s="1">
         <v>26</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="C30" s="12"/>
+      <c r="C30" s="13"/>
       <c r="D30" s="1">
         <v>100</v>
       </c>
     </row>
-    <row r="31" spans="1:7">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" s="1">
         <v>27</v>
       </c>
@@ -2220,7 +1645,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="32" spans="1:7">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" s="1">
         <v>28</v>
       </c>
@@ -2231,7 +1656,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="33" spans="1:23">
+    <row r="33" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A33" s="1">
         <v>29</v>
       </c>
@@ -2242,32 +1667,32 @@
         <v>10</v>
       </c>
     </row>
-    <row r="34" s="2" customFormat="1" spans="1:23">
-      <c r="A34" s="13">
+    <row r="34" spans="1:23" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="14">
         <v>30</v>
       </c>
-      <c r="B34" s="13" t="s">
+      <c r="B34" s="14" t="s">
         <v>65</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="35" s="2" customFormat="1" spans="1:23">
-      <c r="A35" s="13">
+    <row r="35" spans="1:23" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="14">
         <v>31</v>
       </c>
-      <c r="B35" s="13" t="s">
+      <c r="B35" s="14" t="s">
         <v>67</v>
       </c>
-      <c r="E35" s="14">
-        <v>114109.053811181</v>
+      <c r="E35" s="15">
+        <v>372460972.44094503</v>
       </c>
       <c r="G35" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="H35" s="14">
-        <v>5705.45269055904</v>
+      <c r="H35" s="15">
+        <v>8692.2047244094501</v>
       </c>
       <c r="I35" s="2" t="s">
         <v>69</v>
@@ -2286,464 +1711,484 @@
         <v>71</v>
       </c>
     </row>
-    <row r="36" spans="1:23">
-      <c r="A36" s="13">
+    <row r="36" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A36" s="14">
         <v>32</v>
       </c>
-      <c r="B36" s="13" t="s">
+      <c r="B36" s="14" t="s">
         <v>72</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="37" spans="1:23">
-      <c r="A37" s="15">
+    <row r="37" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A37" s="16">
         <v>33</v>
       </c>
-      <c r="B37" s="15" t="s">
+      <c r="B37" s="16" t="s">
         <v>74</v>
       </c>
-      <c r="C37" s="14" t="s">
+      <c r="C37" s="17" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="38" s="2" customFormat="1" spans="1:23">
-      <c r="A38" s="13">
+    <row r="38" spans="1:23" s="3" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="18">
         <v>34</v>
       </c>
-      <c r="B38" s="13" t="s">
+      <c r="B38" s="18" t="s">
         <v>76</v>
       </c>
-      <c r="C38" s="2" t="s">
+      <c r="C38" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="G38" s="2" t="s">
+      <c r="G38" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="H38" s="14">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="39" spans="1:23">
-      <c r="A39" s="15">
+      <c r="H38" s="3">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="39" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A39" s="16">
         <v>35</v>
       </c>
-      <c r="B39" s="15" t="s">
+      <c r="B39" s="16" t="s">
         <v>79</v>
       </c>
-      <c r="C39" s="1" t="str">
-        <f>_xlfn.TEXTJOIN("|",TRUE,S39:W39)</f>
-        <v>10800000_1000|9000000_1000|7200000_1000|5400000_1000|3600000_1000</v>
+      <c r="C39" s="1" t="s">
+        <v>80</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="H39" s="16">
+        <v>81</v>
+      </c>
+      <c r="H39" s="19">
         <f>ROUND(L35/(E35*H38/100/H35),0)</f>
-        <v>7200000</v>
+        <v>2240</v>
       </c>
       <c r="I39" s="1" t="s">
         <v>71</v>
       </c>
       <c r="J39" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="K39" s="17" t="s">
         <v>82</v>
       </c>
-      <c r="L39" s="17">
+      <c r="K39" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="L39" s="20">
         <v>0.25</v>
       </c>
       <c r="M39" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="N39" s="1">
         <f>ROUND(P39*(1+2*L39),0)</f>
-        <v>10800000</v>
+        <v>3360</v>
       </c>
       <c r="O39" s="1">
         <f>ROUND(P39*(1+1*L39),0)</f>
-        <v>9000000</v>
+        <v>2800</v>
       </c>
       <c r="P39" s="1">
         <f>H39</f>
-        <v>7200000</v>
+        <v>2240</v>
       </c>
       <c r="Q39" s="1">
         <f>ROUND(P39*(1-1*L39),0)</f>
-        <v>5400000</v>
+        <v>1680</v>
       </c>
       <c r="R39" s="1">
         <f>ROUND(P39*(1-2*L39),0)</f>
-        <v>3600000</v>
+        <v>1120</v>
       </c>
       <c r="S39" s="1" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,N39,1000)</f>
-        <v>10800000_1000</v>
+        <v>3360_1000</v>
       </c>
       <c r="T39" s="1" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,O39,1000)</f>
-        <v>9000000_1000</v>
+        <v>2800_1000</v>
       </c>
       <c r="U39" s="1" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,P39,1000)</f>
-        <v>7200000_1000</v>
+        <v>2240_1000</v>
       </c>
       <c r="V39" s="1" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,Q39,1000)</f>
-        <v>5400000_1000</v>
+        <v>1680_1000</v>
       </c>
       <c r="W39" s="1" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,R39,1000)</f>
-        <v>3600000_1000</v>
-      </c>
-    </row>
-    <row r="40" spans="1:23">
-      <c r="A40" s="18">
+        <v>1120_1000</v>
+      </c>
+    </row>
+    <row r="40" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A40" s="21">
         <v>40</v>
       </c>
-      <c r="B40" s="18" t="s">
-        <v>84</v>
-      </c>
-      <c r="D40" s="19">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="41" spans="1:23">
-      <c r="A41" s="18">
+      <c r="B40" s="21" t="s">
+        <v>85</v>
+      </c>
+      <c r="D40" s="17">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="41" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A41" s="21">
         <v>41</v>
       </c>
-      <c r="B41" s="18" t="s">
-        <v>85</v>
-      </c>
-      <c r="D41" s="19">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="42" spans="1:23">
-      <c r="A42" s="18">
+      <c r="B41" s="21" t="s">
+        <v>86</v>
+      </c>
+      <c r="D41" s="17">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="42" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A42" s="21">
         <v>42</v>
       </c>
-      <c r="B42" s="18" t="s">
-        <v>86</v>
-      </c>
-      <c r="D42" s="19">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="43" spans="1:23">
-      <c r="A43" s="18">
+      <c r="B42" s="21" t="s">
+        <v>87</v>
+      </c>
+      <c r="D42" s="17">
+        <v>36000</v>
+      </c>
+    </row>
+    <row r="43" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A43" s="21">
         <v>43</v>
       </c>
-      <c r="B43" s="18" t="s">
-        <v>87</v>
-      </c>
-      <c r="D43" s="19">
+      <c r="B43" s="21" t="s">
+        <v>88</v>
+      </c>
+      <c r="D43" s="17">
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:23">
-      <c r="A44" s="18">
+    <row r="44" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A44" s="21">
         <v>44</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="D44" s="14">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="45" spans="1:23">
-      <c r="A45" s="18">
+        <v>89</v>
+      </c>
+      <c r="D44" s="17">
+        <v>290000</v>
+      </c>
+    </row>
+    <row r="45" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A45" s="21">
         <v>45</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="C45" s="14" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="46" spans="1:23">
+      <c r="C45" s="17" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="46" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A46" s="1">
         <v>46</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="C46" s="14" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="47" spans="1:23">
+      <c r="C46" s="17" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="47" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A47" s="1">
         <v>47</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D47" s="1">
         <v>3</v>
       </c>
     </row>
-    <row r="48" spans="1:23">
+    <row r="48" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A48" s="1">
         <v>48</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A49" s="1">
         <v>49</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="50" spans="1:4">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A50" s="1">
         <v>50</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="C50" s="14"/>
-    </row>
-    <row r="51" s="2" customFormat="1" spans="1:4">
+        <v>99</v>
+      </c>
+      <c r="C50" s="17"/>
+    </row>
+    <row r="51" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A51" s="2">
         <v>51</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="C51" s="20" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="52" spans="1:4">
+      <c r="C51" s="22" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A52" s="1">
         <v>52</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="D52" s="11">
-        <v>29000</v>
-      </c>
-    </row>
-    <row r="53" spans="1:4">
+        <v>102</v>
+      </c>
+      <c r="D52" s="12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A53" s="1">
         <v>53</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="D53" s="11">
-        <v>29000</v>
-      </c>
-    </row>
-    <row r="54" spans="1:4">
+        <v>103</v>
+      </c>
+      <c r="D53" s="12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A54" s="1">
         <v>54</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D54" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="55" customFormat="1" spans="1:4">
+    <row r="55" spans="1:4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A55" s="1">
         <v>55</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C55" s="1"/>
       <c r="D55" s="1">
         <v>60</v>
       </c>
     </row>
-    <row r="56" spans="1:4">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A56" s="1">
         <v>56</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="57" s="2" customFormat="1" spans="1:4">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A57" s="2">
         <v>60</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="C57" s="21" t="s">
         <v>108</v>
       </c>
-    </row>
-    <row r="58" spans="1:4">
+      <c r="C57" s="23" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A58" s="1">
         <v>61</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="C58" s="22" t="s">
         <v>110</v>
       </c>
-    </row>
-    <row r="59" spans="1:4">
+      <c r="C58" s="24" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A59" s="1">
         <v>62</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="C59" s="23" t="s">
         <v>112</v>
       </c>
-    </row>
-    <row r="60" spans="1:4">
+      <c r="C59" s="12" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A60" s="1">
         <v>63</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="61" spans="1:4">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A61" s="1">
         <v>64</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="C61" s="14" t="s">
         <v>116</v>
       </c>
-    </row>
-    <row r="62" spans="1:4">
+      <c r="C61" s="17" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A62" s="1">
         <v>65</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="C62" s="14" t="s">
         <v>118</v>
       </c>
-    </row>
-    <row r="63" spans="1:4">
+      <c r="C62" s="17" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A63" s="1">
         <v>70</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="C63" s="24" t="s">
         <v>120</v>
       </c>
-      <c r="D63" s="24"/>
-    </row>
-    <row r="64" spans="1:4">
+      <c r="C63" s="17" t="s">
+        <v>121</v>
+      </c>
+      <c r="D63" s="17"/>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A64" s="1">
         <v>71</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="C64" s="24"/>
-      <c r="D64" s="24">
+        <v>122</v>
+      </c>
+      <c r="C64" s="17"/>
+      <c r="D64" s="17">
         <v>5000</v>
       </c>
     </row>
-    <row r="65" spans="1:20">
+    <row r="65" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A65" s="1">
         <v>72</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="C65" s="19" t="s">
         <v>123</v>
       </c>
-      <c r="D65" s="19"/>
-    </row>
-    <row r="66" spans="1:20">
+      <c r="C65" s="17" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="66" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A66" s="25">
         <v>80</v>
       </c>
       <c r="B66" s="25" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C66" s="25"/>
       <c r="D66" s="25">
         <v>259200</v>
       </c>
-      <c r="E66" s="5"/>
-      <c r="F66" s="5"/>
-      <c r="G66" s="5"/>
-      <c r="H66" s="5"/>
-      <c r="I66" s="5"/>
-      <c r="J66" s="5"/>
-      <c r="K66" s="5"/>
-      <c r="L66" s="5"/>
-      <c r="M66" s="5"/>
-      <c r="N66" s="5"/>
-      <c r="O66" s="5"/>
-      <c r="P66" s="5"/>
-      <c r="Q66" s="5"/>
-      <c r="R66" s="5"/>
-      <c r="S66" s="5"/>
-      <c r="T66" s="5"/>
-    </row>
-    <row r="67" spans="1:20">
+      <c r="E66" s="6"/>
+      <c r="F66" s="6"/>
+      <c r="G66" s="6"/>
+      <c r="H66" s="6"/>
+      <c r="I66" s="6"/>
+      <c r="J66" s="6"/>
+      <c r="K66" s="6"/>
+      <c r="L66" s="6"/>
+      <c r="M66" s="6"/>
+      <c r="N66" s="6"/>
+      <c r="O66" s="6"/>
+      <c r="P66" s="6"/>
+      <c r="Q66" s="6"/>
+      <c r="R66" s="6"/>
+      <c r="S66" s="6"/>
+      <c r="T66" s="6"/>
+    </row>
+    <row r="67" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A67" s="1">
         <v>90</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D67" s="1">
         <v>1000000</v>
       </c>
     </row>
-    <row r="68" spans="1:20">
+    <row r="68" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A68" s="1">
         <v>100</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>127</v>
+        <v>128</v>
+      </c>
+    </row>
+    <row r="69" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A69" s="1">
+        <v>101</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="C69" s="1" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="70" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A70" s="1">
+        <v>102</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="C70" s="13">
+        <v>1980000</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="13" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="C57" r:id="rId3" display="https://aws-s3-jjg-asset-bucket.s3.ap-southeast-1.amazonaws.com/tanchuang_res/english/tc_sc_1.png" tooltip="https://aws-s3-jjg-asset-bucket.s3.ap-southeast-1.amazonaws.com/tanchuang_res/english/tc_sc_1.png"/>
+    <hyperlink ref="C57" r:id="rId1" tooltip="https://aws-s3-jjg-asset-bucket.s3.ap-southeast-1.amazonaws.com/tanchuang_res/english/tc_sc_1.png" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
   <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/gm/resources/sample/global.xlsx
+++ b/gm/resources/sample/global.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29426"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\gamefile\策划配置表\common\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0096D60A-50DD-4FC0-9D48-48A80A44162F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="globalConfig" sheetId="1" r:id="rId1"/>
@@ -33,12 +27,12 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>Administrator</author>
   </authors>
   <commentList>
-    <comment ref="D16" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
+    <comment ref="D16" authorId="0">
       <text>
         <r>
           <rPr>
@@ -60,7 +54,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G18" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
+    <comment ref="G18" authorId="0">
       <text>
         <r>
           <rPr>
@@ -83,7 +77,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E35" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
+    <comment ref="E35" authorId="0">
       <text>
         <r>
           <rPr>
@@ -108,7 +102,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C37" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000004000000}">
+    <comment ref="C37" authorId="0">
       <text>
         <r>
           <rPr>
@@ -130,7 +124,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B48" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000005000000}">
+    <comment ref="B48" authorId="0">
       <text>
         <r>
           <rPr>
@@ -152,7 +146,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C50" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000006000000}">
+    <comment ref="C50" authorId="0">
       <text>
         <r>
           <rPr>
@@ -174,7 +168,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B51" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000007000000}">
+    <comment ref="B51" authorId="0">
       <text>
         <r>
           <rPr>
@@ -196,7 +190,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D52" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000008000000}">
+    <comment ref="D52" authorId="0">
       <text>
         <r>
           <rPr>
@@ -218,7 +212,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D53" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000009000000}">
+    <comment ref="D53" authorId="0">
       <text>
         <r>
           <rPr>
@@ -241,7 +235,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D54" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000A000000}">
+    <comment ref="D54" authorId="0">
       <text>
         <r>
           <rPr>
@@ -264,7 +258,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C56" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000B000000}">
+    <comment ref="C56" authorId="0">
       <text>
         <r>
           <rPr>
@@ -286,7 +280,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C65" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000C000000}">
+    <comment ref="C65" authorId="0">
       <text>
         <r>
           <rPr>
@@ -619,7 +613,7 @@
     <t>积分大奖: 【日榜排行榜显示人数_周榜排行榜显示人数_月榜排行榜显示人数】</t>
   </si>
   <si>
-    <t>300_300_300</t>
+    <t>300_50_10</t>
   </si>
   <si>
     <t>新手奖励</t>
@@ -676,7 +670,7 @@
     <t>推广分享：周榜上榜条件设置(收益数量)</t>
   </si>
   <si>
-    <t>1990000_6000000</t>
+    <t>1990000_4000000</t>
   </si>
   <si>
     <t>推广分享：有效用户达标条件（有效下注累计_数值|累计充值_数值）</t>
@@ -715,20 +709,24 @@
     <t>幸运夺宝：商品价值货币的图标</t>
   </si>
   <si>
+    <t>icon_vnd.png</t>
+  </si>
+  <si>
     <t>幸运夺宝：抢购商品所需要的道具ID(仅在界面左上角处显示的抢购消耗道具的信息)</t>
-  </si>
-  <si>
-    <t>icon_vnd.png</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="178" formatCode="0_ "/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="5">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="0_ "/>
   </numFmts>
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="31">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -738,18 +736,18 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="微软雅黑"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color theme="0" tint="-0.249977111117893"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
@@ -783,13 +781,13 @@
       <sz val="11"/>
       <color theme="0" tint="-0.249977111117893"/>
       <name val="Times New Roman"/>
-      <family val="1"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="10.5"/>
       <color theme="0" tint="-0.249977111117893"/>
       <name val="Arial"/>
-      <family val="2"/>
+      <charset val="134"/>
     </font>
     <font>
       <u/>
@@ -800,25 +798,154 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
-    <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="4">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -827,18 +954,204 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.79998168889431442"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -861,75 +1174,357 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="178" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="6" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" quotePrefix="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" quotePrefix="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="超链接" xfId="1" builtinId="8"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1187,33 +1782,33 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:W70"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
-    <col min="1" max="1" width="9" style="1"/>
-    <col min="2" max="2" width="89" style="1" customWidth="1"/>
-    <col min="3" max="4" width="28.375" style="1" customWidth="1"/>
-    <col min="5" max="5" width="11.5" style="1" customWidth="1"/>
-    <col min="6" max="6" width="9.625" style="1" customWidth="1"/>
-    <col min="7" max="7" width="23.375" style="1" customWidth="1"/>
-    <col min="8" max="8" width="12.75" style="1"/>
-    <col min="9" max="9" width="14.125" style="1"/>
-    <col min="10" max="10" width="11.5" style="1"/>
-    <col min="11" max="11" width="9" style="1"/>
-    <col min="12" max="12" width="12.875" style="1"/>
-    <col min="13" max="13" width="9" style="1"/>
-    <col min="14" max="17" width="10.375" style="1"/>
-    <col min="18" max="18" width="9.25" style="1"/>
-    <col min="19" max="16384" width="9" style="1"/>
+    <col min="1" max="1" width="9" style="3"/>
+    <col min="2" max="2" width="89" style="3" customWidth="1"/>
+    <col min="3" max="4" width="28.375" style="3" customWidth="1"/>
+    <col min="5" max="5" width="11.5" style="3" customWidth="1"/>
+    <col min="6" max="6" width="9.625" style="3" customWidth="1"/>
+    <col min="7" max="7" width="23.375" style="3" customWidth="1"/>
+    <col min="8" max="8" width="12.75" style="3"/>
+    <col min="9" max="9" width="14.125" style="3"/>
+    <col min="10" max="10" width="11.5" style="3"/>
+    <col min="11" max="11" width="9" style="3"/>
+    <col min="12" max="12" width="12.875" style="3"/>
+    <col min="13" max="13" width="9" style="3"/>
+    <col min="14" max="17" width="10.375" style="3"/>
+    <col min="18" max="18" width="9.25" style="3"/>
+    <col min="19" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -1234,7 +1829,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7">
       <c r="A2" s="6" t="s">
         <v>6</v>
       </c>
@@ -1245,7 +1840,7 @@
       <c r="D2" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" s="3" t="s">
         <v>8</v>
       </c>
       <c r="F2" s="5" t="s">
@@ -1253,7 +1848,7 @@
       </c>
       <c r="G2" s="5"/>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7">
       <c r="A3" s="4" t="s">
         <v>10</v>
       </c>
@@ -1261,25 +1856,25 @@
       <c r="C3" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="E3" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="F3" s="3" t="s">
         <v>14</v>
       </c>
       <c r="G3" s="5"/>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7">
       <c r="A4" s="8"/>
       <c r="B4" s="7"/>
       <c r="C4" s="7"/>
       <c r="G4" s="7"/>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" s="1">
+    <row r="5" spans="1:7">
+      <c r="A5" s="3">
         <v>1</v>
       </c>
       <c r="B5" s="7" t="s">
@@ -1292,8 +1887,8 @@
       <c r="F5" s="7"/>
       <c r="G5" s="7"/>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A6" s="1">
+    <row r="6" spans="1:7">
+      <c r="A6" s="3">
         <v>2</v>
       </c>
       <c r="B6" s="7" t="s">
@@ -1308,8 +1903,8 @@
         <v>17</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A7" s="1">
+    <row r="7" spans="1:7">
+      <c r="A7" s="3">
         <v>3</v>
       </c>
       <c r="B7" s="7" t="s">
@@ -1324,8 +1919,8 @@
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A8" s="1">
+    <row r="8" spans="1:7">
+      <c r="A8" s="3">
         <v>4</v>
       </c>
       <c r="B8" s="7" t="s">
@@ -1341,22 +1936,22 @@
         <v>20</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A9" s="1">
+    <row r="9" spans="1:7">
+      <c r="A9" s="3">
         <v>5</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="B9" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="C9" s="1">
+      <c r="C9" s="3">
         <v>4</v>
       </c>
-      <c r="G9" s="1" t="s">
+      <c r="G9" s="3" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A10" s="1">
+    <row r="10" spans="1:7">
+      <c r="A10" s="3">
         <v>6</v>
       </c>
       <c r="B10" s="7" t="s">
@@ -1368,12 +1963,12 @@
       <c r="D10" s="10"/>
       <c r="E10" s="7"/>
       <c r="F10" s="7"/>
-      <c r="G10" s="1" t="s">
+      <c r="G10" s="3" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A11" s="1">
+    <row r="11" spans="1:7">
+      <c r="A11" s="3">
         <v>7</v>
       </c>
       <c r="B11" s="7" t="s">
@@ -1385,12 +1980,12 @@
       <c r="D11" s="7"/>
       <c r="E11" s="7"/>
       <c r="F11" s="7"/>
-      <c r="G11" s="1" t="s">
+      <c r="G11" s="3" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A12" s="1">
+    <row r="12" spans="1:7">
+      <c r="A12" s="3">
         <v>8</v>
       </c>
       <c r="B12" s="7" t="s">
@@ -1402,12 +1997,12 @@
       <c r="D12" s="7"/>
       <c r="E12" s="7"/>
       <c r="F12" s="7"/>
-      <c r="G12" s="1" t="s">
+      <c r="G12" s="3" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A13" s="1">
+    <row r="13" spans="1:7">
+      <c r="A13" s="3">
         <v>9</v>
       </c>
       <c r="B13" s="7" t="s">
@@ -1419,12 +2014,12 @@
       <c r="D13" s="7"/>
       <c r="E13" s="7"/>
       <c r="F13" s="7"/>
-      <c r="G13" s="1" t="s">
+      <c r="G13" s="3" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A14" s="1">
+    <row r="14" spans="1:7">
+      <c r="A14" s="3">
         <v>10</v>
       </c>
       <c r="B14" s="7" t="s">
@@ -1436,249 +2031,249 @@
       <c r="D14" s="7"/>
       <c r="E14" s="7"/>
       <c r="F14" s="7"/>
-      <c r="G14" s="1" t="s">
+      <c r="G14" s="3" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A15" s="1">
+    <row r="15" spans="1:7">
+      <c r="A15" s="3">
         <v>11</v>
       </c>
-      <c r="B15" s="1" t="s">
+      <c r="B15" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="D15" s="1">
+      <c r="D15" s="3">
         <f>2*3*5*3</f>
         <v>90</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A16" s="1">
+    <row r="16" spans="1:7">
+      <c r="A16" s="3">
         <v>12</v>
       </c>
-      <c r="B16" s="1" t="s">
+      <c r="B16" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="D16" s="1">
+      <c r="D16" s="3">
         <v>3333</v>
       </c>
-      <c r="G16" s="1" t="s">
+      <c r="G16" s="3" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A17" s="1">
+    <row r="17" spans="1:7">
+      <c r="A17" s="3">
         <v>13</v>
       </c>
-      <c r="B17" s="1" t="s">
+      <c r="B17" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="D17" s="1">
+      <c r="D17" s="3">
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A18" s="1">
+    <row r="18" spans="1:7">
+      <c r="A18" s="3">
         <v>14</v>
       </c>
-      <c r="B18" s="1" t="s">
+      <c r="B18" s="3" t="s">
         <v>38</v>
       </c>
       <c r="C18" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="G18" s="1" t="s">
+      <c r="G18" s="3" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A19" s="1">
+    <row r="19" spans="1:7">
+      <c r="A19" s="3">
         <v>15</v>
       </c>
-      <c r="B19" s="1" t="s">
+      <c r="B19" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="D19" s="1">
+      <c r="D19" s="3">
         <v>5</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A20" s="1">
+    <row r="20" spans="1:7">
+      <c r="A20" s="3">
         <v>16</v>
       </c>
-      <c r="B20" s="1" t="s">
+      <c r="B20" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="D20" s="1">
+      <c r="D20" s="3">
         <v>10</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A21" s="1">
+    <row r="21" spans="1:7">
+      <c r="A21" s="3">
         <v>17</v>
       </c>
-      <c r="B21" s="1" t="s">
+      <c r="B21" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="C21" s="1" t="s">
+      <c r="C21" s="3" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A22" s="1">
+    <row r="22" spans="1:7">
+      <c r="A22" s="3">
         <v>18</v>
       </c>
-      <c r="B22" s="1" t="s">
+      <c r="B22" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="D22" s="1">
+      <c r="D22" s="3">
         <f>7*24*60*60</f>
         <v>604800</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A23" s="1">
+    <row r="23" spans="1:7">
+      <c r="A23" s="3">
         <v>19</v>
       </c>
-      <c r="B23" s="1" t="s">
+      <c r="B23" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="C23" s="1" t="s">
+      <c r="C23" s="3" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A24" s="1">
+    <row r="24" spans="1:7">
+      <c r="A24" s="3">
         <v>20</v>
       </c>
-      <c r="B24" s="1" t="s">
+      <c r="B24" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="D24" s="1">
+      <c r="D24" s="3">
         <v>10</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A25" s="1">
+    <row r="25" spans="1:7">
+      <c r="A25" s="3">
         <v>21</v>
       </c>
-      <c r="B25" s="1" t="s">
+      <c r="B25" s="3" t="s">
         <v>49</v>
       </c>
       <c r="C25" s="12" t="s">
         <v>50</v>
       </c>
-      <c r="G25" s="1" t="s">
+      <c r="G25" s="3" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A26" s="1">
+    <row r="26" spans="1:7">
+      <c r="A26" s="3">
         <v>22</v>
       </c>
-      <c r="B26" s="1" t="s">
+      <c r="B26" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="C26" s="1" t="s">
+      <c r="C26" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="G26" s="1" t="s">
+      <c r="G26" s="3" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A27" s="1">
+    <row r="27" spans="1:7">
+      <c r="A27" s="3">
         <v>23</v>
       </c>
-      <c r="B27" s="1" t="s">
+      <c r="B27" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="D27" s="1">
+      <c r="D27" s="3">
         <v>10000</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A28" s="1">
+    <row r="28" spans="1:7">
+      <c r="A28" s="3">
         <v>24</v>
       </c>
-      <c r="B28" s="1" t="s">
+      <c r="B28" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="D28" s="1">
+      <c r="D28" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A29" s="1">
+    <row r="29" spans="1:7">
+      <c r="A29" s="3">
         <v>25</v>
       </c>
-      <c r="B29" s="1" t="s">
+      <c r="B29" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="C29" s="1" t="s">
+      <c r="C29" s="3" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A30" s="1">
+    <row r="30" spans="1:7">
+      <c r="A30" s="3">
         <v>26</v>
       </c>
-      <c r="B30" s="1" t="s">
+      <c r="B30" s="3" t="s">
         <v>59</v>
       </c>
       <c r="C30" s="13"/>
-      <c r="D30" s="1">
+      <c r="D30" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A31" s="1">
+    <row r="31" spans="1:7">
+      <c r="A31" s="3">
         <v>27</v>
       </c>
-      <c r="B31" s="1" t="s">
+      <c r="B31" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="D31" s="1">
+      <c r="D31" s="3">
         <v>10000</v>
       </c>
-      <c r="G31" s="1" t="s">
+      <c r="G31" s="3" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A32" s="1">
+    <row r="32" spans="1:7">
+      <c r="A32" s="3">
         <v>28</v>
       </c>
-      <c r="B32" s="1" t="s">
+      <c r="B32" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="C32" s="1" t="s">
+      <c r="C32" s="3" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="33" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A33" s="1">
+    <row r="33" spans="1:23">
+      <c r="A33" s="3">
         <v>29</v>
       </c>
-      <c r="B33" s="1" t="s">
+      <c r="B33" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="D33" s="1">
+      <c r="D33" s="3">
         <v>10</v>
       </c>
     </row>
-    <row r="34" spans="1:23" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="34" s="1" customFormat="1" spans="1:23">
       <c r="A34" s="14">
         <v>30</v>
       </c>
       <c r="B34" s="14" t="s">
         <v>65</v>
       </c>
-      <c r="C34" s="2" t="s">
+      <c r="C34" s="1" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="35" spans="1:23" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="35" s="1" customFormat="1" spans="1:23">
       <c r="A35" s="14">
         <v>31</v>
       </c>
@@ -1686,43 +2281,43 @@
         <v>67</v>
       </c>
       <c r="E35" s="15">
-        <v>372460972.44094503</v>
-      </c>
-      <c r="G35" s="2" t="s">
+        <v>372460972.440945</v>
+      </c>
+      <c r="G35" s="1" t="s">
         <v>68</v>
       </c>
       <c r="H35" s="15">
-        <v>8692.2047244094501</v>
-      </c>
-      <c r="I35" s="2" t="s">
+        <v>8692.20472440945</v>
+      </c>
+      <c r="I35" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="J35" s="2">
+      <c r="J35" s="1">
         <v>1</v>
       </c>
-      <c r="K35" s="2" t="s">
+      <c r="K35" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="L35" s="2">
+      <c r="L35" s="1">
         <f>J35*24*60*60*1000</f>
         <v>86400000</v>
       </c>
-      <c r="M35" s="2" t="s">
+      <c r="M35" s="1" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="36" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:23">
       <c r="A36" s="14">
         <v>32</v>
       </c>
       <c r="B36" s="14" t="s">
         <v>72</v>
       </c>
-      <c r="C36" s="2" t="s">
+      <c r="C36" s="1" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="37" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:23">
       <c r="A37" s="16">
         <v>33</v>
       </c>
@@ -1733,44 +2328,44 @@
         <v>75</v>
       </c>
     </row>
-    <row r="38" spans="1:23" s="3" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="38" s="2" customFormat="1" spans="1:23">
       <c r="A38" s="18">
         <v>34</v>
       </c>
       <c r="B38" s="18" t="s">
         <v>76</v>
       </c>
-      <c r="C38" s="3" t="s">
+      <c r="C38" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="G38" s="3" t="s">
+      <c r="G38" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="H38" s="3">
+      <c r="H38" s="2">
         <v>90</v>
       </c>
     </row>
-    <row r="39" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:23">
       <c r="A39" s="16">
         <v>35</v>
       </c>
       <c r="B39" s="16" t="s">
         <v>79</v>
       </c>
-      <c r="C39" s="1" t="s">
+      <c r="C39" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="G39" s="1" t="s">
+      <c r="G39" s="3" t="s">
         <v>81</v>
       </c>
       <c r="H39" s="19">
         <f>ROUND(L35/(E35*H38/100/H35),0)</f>
         <v>2240</v>
       </c>
-      <c r="I39" s="1" t="s">
+      <c r="I39" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="J39" s="1" t="s">
+      <c r="J39" s="3" t="s">
         <v>82</v>
       </c>
       <c r="K39" s="20" t="s">
@@ -1779,51 +2374,51 @@
       <c r="L39" s="20">
         <v>0.25</v>
       </c>
-      <c r="M39" s="1" t="s">
+      <c r="M39" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="N39" s="1">
+      <c r="N39" s="3">
         <f>ROUND(P39*(1+2*L39),0)</f>
         <v>3360</v>
       </c>
-      <c r="O39" s="1">
+      <c r="O39" s="3">
         <f>ROUND(P39*(1+1*L39),0)</f>
         <v>2800</v>
       </c>
-      <c r="P39" s="1">
+      <c r="P39" s="3">
         <f>H39</f>
         <v>2240</v>
       </c>
-      <c r="Q39" s="1">
+      <c r="Q39" s="3">
         <f>ROUND(P39*(1-1*L39),0)</f>
         <v>1680</v>
       </c>
-      <c r="R39" s="1">
+      <c r="R39" s="3">
         <f>ROUND(P39*(1-2*L39),0)</f>
         <v>1120</v>
       </c>
-      <c r="S39" s="1" t="str">
+      <c r="S39" s="3" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,N39,1000)</f>
         <v>3360_1000</v>
       </c>
-      <c r="T39" s="1" t="str">
+      <c r="T39" s="3" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,O39,1000)</f>
         <v>2800_1000</v>
       </c>
-      <c r="U39" s="1" t="str">
+      <c r="U39" s="3" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,P39,1000)</f>
         <v>2240_1000</v>
       </c>
-      <c r="V39" s="1" t="str">
+      <c r="V39" s="3" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,Q39,1000)</f>
         <v>1680_1000</v>
       </c>
-      <c r="W39" s="1" t="str">
+      <c r="W39" s="3" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,R39,1000)</f>
         <v>1120_1000</v>
       </c>
     </row>
-    <row r="40" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:23">
       <c r="A40" s="21">
         <v>40</v>
       </c>
@@ -1834,7 +2429,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="41" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:23">
       <c r="A41" s="21">
         <v>41</v>
       </c>
@@ -1845,7 +2440,7 @@
         <v>1200</v>
       </c>
     </row>
-    <row r="42" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:23">
       <c r="A42" s="21">
         <v>42</v>
       </c>
@@ -1856,7 +2451,7 @@
         <v>36000</v>
       </c>
     </row>
-    <row r="43" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:23">
       <c r="A43" s="21">
         <v>43</v>
       </c>
@@ -1867,219 +2462,219 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:23">
       <c r="A44" s="21">
         <v>44</v>
       </c>
-      <c r="B44" s="1" t="s">
+      <c r="B44" s="3" t="s">
         <v>89</v>
       </c>
       <c r="D44" s="17">
         <v>290000</v>
       </c>
     </row>
-    <row r="45" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:23">
       <c r="A45" s="21">
         <v>45</v>
       </c>
-      <c r="B45" s="1" t="s">
+      <c r="B45" s="3" t="s">
         <v>90</v>
       </c>
       <c r="C45" s="17" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="46" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A46" s="1">
+    <row r="46" spans="1:23">
+      <c r="A46" s="3">
         <v>46</v>
       </c>
-      <c r="B46" s="1" t="s">
+      <c r="B46" s="3" t="s">
         <v>92</v>
       </c>
       <c r="C46" s="17" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="47" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A47" s="1">
+    <row r="47" spans="1:23">
+      <c r="A47" s="3">
         <v>47</v>
       </c>
-      <c r="B47" s="1" t="s">
+      <c r="B47" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="D47" s="1">
+      <c r="D47" s="3">
         <v>3</v>
       </c>
     </row>
-    <row r="48" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A48" s="1">
+    <row r="48" spans="1:23">
+      <c r="A48" s="3">
         <v>48</v>
       </c>
-      <c r="B48" s="1" t="s">
+      <c r="B48" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="C48" s="1" t="s">
+      <c r="C48" s="3" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A49" s="1">
+    <row r="49" spans="1:4">
+      <c r="A49" s="3">
         <v>49</v>
       </c>
-      <c r="B49" s="1" t="s">
+      <c r="B49" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="C49" s="1" t="s">
+      <c r="C49" s="3" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A50" s="1">
+    <row r="50" spans="1:4">
+      <c r="A50" s="3">
         <v>50</v>
       </c>
-      <c r="B50" s="1" t="s">
+      <c r="B50" s="3" t="s">
         <v>99</v>
       </c>
       <c r="C50" s="17"/>
     </row>
-    <row r="51" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="2">
+    <row r="51" s="1" customFormat="1" spans="1:4">
+      <c r="A51" s="1">
         <v>51</v>
       </c>
-      <c r="B51" s="2" t="s">
+      <c r="B51" s="1" t="s">
         <v>100</v>
       </c>
       <c r="C51" s="22" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A52" s="1">
+    <row r="52" spans="1:4">
+      <c r="A52" s="3">
         <v>52</v>
       </c>
-      <c r="B52" s="1" t="s">
+      <c r="B52" s="3" t="s">
         <v>102</v>
       </c>
       <c r="D52" s="12">
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A53" s="1">
+    <row r="53" spans="1:4">
+      <c r="A53" s="3">
         <v>53</v>
       </c>
-      <c r="B53" s="1" t="s">
+      <c r="B53" s="3" t="s">
         <v>103</v>
       </c>
       <c r="D53" s="12">
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A54" s="1">
+    <row r="54" spans="1:4">
+      <c r="A54" s="3">
         <v>54</v>
       </c>
-      <c r="B54" s="1" t="s">
+      <c r="B54" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="D54" s="1">
+      <c r="D54" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:4" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="1">
+    <row r="55" customFormat="1" spans="1:4">
+      <c r="A55" s="3">
         <v>55</v>
       </c>
-      <c r="B55" s="1" t="s">
+      <c r="B55" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="C55" s="1"/>
-      <c r="D55" s="1">
+      <c r="C55" s="3"/>
+      <c r="D55" s="3">
         <v>60</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A56" s="1">
+    <row r="56" spans="1:4">
+      <c r="A56" s="3">
         <v>56</v>
       </c>
-      <c r="B56" s="1" t="s">
+      <c r="B56" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="C56" s="1" t="s">
+      <c r="C56" s="3" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="57" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="2">
+    <row r="57" s="1" customFormat="1" spans="1:4">
+      <c r="A57" s="1">
         <v>60</v>
       </c>
-      <c r="B57" s="2" t="s">
+      <c r="B57" s="1" t="s">
         <v>108</v>
       </c>
       <c r="C57" s="23" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A58" s="1">
+    <row r="58" spans="1:4">
+      <c r="A58" s="3">
         <v>61</v>
       </c>
-      <c r="B58" s="1" t="s">
+      <c r="B58" s="3" t="s">
         <v>110</v>
       </c>
       <c r="C58" s="24" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A59" s="1">
+    <row r="59" spans="1:4">
+      <c r="A59" s="3">
         <v>62</v>
       </c>
-      <c r="B59" s="1" t="s">
+      <c r="B59" s="3" t="s">
         <v>112</v>
       </c>
       <c r="C59" s="12" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A60" s="1">
+    <row r="60" spans="1:4">
+      <c r="A60" s="3">
         <v>63</v>
       </c>
-      <c r="B60" s="1" t="s">
+      <c r="B60" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="C60" s="1" t="s">
+      <c r="C60" s="3" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A61" s="1">
+    <row r="61" spans="1:4">
+      <c r="A61" s="3">
         <v>64</v>
       </c>
-      <c r="B61" s="1" t="s">
+      <c r="B61" s="3" t="s">
         <v>116</v>
       </c>
       <c r="C61" s="17" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A62" s="1">
+    <row r="62" spans="1:4">
+      <c r="A62" s="3">
         <v>65</v>
       </c>
-      <c r="B62" s="1" t="s">
+      <c r="B62" s="3" t="s">
         <v>118</v>
       </c>
       <c r="C62" s="17" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A63" s="1">
+    <row r="63" spans="1:4">
+      <c r="A63" s="3">
         <v>70</v>
       </c>
-      <c r="B63" s="1" t="s">
+      <c r="B63" s="3" t="s">
         <v>120</v>
       </c>
       <c r="C63" s="17" t="s">
@@ -2087,11 +2682,11 @@
       </c>
       <c r="D63" s="17"/>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A64" s="1">
+    <row r="64" spans="1:4">
+      <c r="A64" s="3">
         <v>71</v>
       </c>
-      <c r="B64" s="1" t="s">
+      <c r="B64" s="3" t="s">
         <v>122</v>
       </c>
       <c r="C64" s="17"/>
@@ -2099,18 +2694,18 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="65" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A65" s="1">
+    <row r="65" spans="1:20">
+      <c r="A65" s="3">
         <v>72</v>
       </c>
-      <c r="B65" s="1" t="s">
+      <c r="B65" s="3" t="s">
         <v>123</v>
       </c>
       <c r="C65" s="17" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="66" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:20">
       <c r="A66" s="25">
         <v>80</v>
       </c>
@@ -2138,57 +2733,57 @@
       <c r="S66" s="6"/>
       <c r="T66" s="6"/>
     </row>
-    <row r="67" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A67" s="1">
+    <row r="67" spans="1:20">
+      <c r="A67" s="3">
         <v>90</v>
       </c>
-      <c r="B67" s="1" t="s">
+      <c r="B67" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="D67" s="1">
+      <c r="D67" s="3">
         <v>1000000</v>
       </c>
     </row>
-    <row r="68" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A68" s="1">
+    <row r="68" spans="1:20">
+      <c r="A68" s="3">
         <v>100</v>
       </c>
-      <c r="B68" s="1" t="s">
+      <c r="B68" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="C68" s="1" t="s">
+      <c r="C68" s="3" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="69" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A69" s="1">
+    <row r="69" spans="1:20">
+      <c r="A69" s="3">
         <v>101</v>
       </c>
-      <c r="B69" s="1" t="s">
+      <c r="B69" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="C69" s="1" t="s">
+      <c r="C69" s="3" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="70" spans="1:20">
+      <c r="A70" s="3">
+        <v>102</v>
+      </c>
+      <c r="B70" s="3" t="s">
         <v>131</v>
-      </c>
-    </row>
-    <row r="70" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A70" s="1">
-        <v>102</v>
-      </c>
-      <c r="B70" s="1" t="s">
-        <v>130</v>
       </c>
       <c r="C70" s="13">
         <v>1980000</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="13" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="C57" r:id="rId1" tooltip="https://aws-s3-jjg-asset-bucket.s3.ap-southeast-1.amazonaws.com/tanchuang_res/english/tc_sc_1.png" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="C57" r:id="rId3" display="https://aws-s3-jjg-asset-bucket.s3.ap-southeast-1.amazonaws.com/tanchuang_res/english/tc_sc_1.png" tooltip="https://aws-s3-jjg-asset-bucket.s3.ap-southeast-1.amazonaws.com/tanchuang_res/english/tc_sc_1.png"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
   <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/gm/resources/sample/global.xlsx
+++ b/gm/resources/sample/global.xlsx
@@ -317,7 +317,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="137">
   <si>
     <t>sid</t>
   </si>
@@ -577,7 +577,7 @@
     <t>积分大奖： 转盘每次消耗积分数</t>
   </si>
   <si>
-    <t>积分大奖：上榜的最低积分要求(日榜、周榜)</t>
+    <t>积分大奖：上榜的最低积分要求(日榜、周榜ID110 ，月榜ID42)</t>
   </si>
   <si>
     <t>积分大奖：月总榜-上榜的最低积分要求</t>
@@ -604,10 +604,19 @@
     <t>积分大奖：实物奖励兑换码过期时间（天）</t>
   </si>
   <si>
+    <t>目标积分</t>
+  </si>
+  <si>
     <t>积分大奖：占用榜单的机器人条件，触发的倒计时，单位秒【倒计时下限_倒计时上限_最小增长积分_前X名用机器人占榜】</t>
   </si>
   <si>
-    <t>1500_2100_50_300</t>
+    <t>600_1200_105_30</t>
+  </si>
+  <si>
+    <t>目标积分 / （24*60/时间间隔分）*100/(总排名/MAX(1,(当前名次*(当前名次-1)))+总排名/当前名次) =增长积分</t>
+  </si>
+  <si>
+    <t>名次</t>
   </si>
   <si>
     <t>积分大奖: 【日榜排行榜显示人数_周榜排行榜显示人数_月榜排行榜显示人数】</t>
@@ -616,6 +625,9 @@
     <t>300_50_10</t>
   </si>
   <si>
+    <t>间隔</t>
+  </si>
+  <si>
     <t>新手奖励</t>
   </si>
   <si>
@@ -713,6 +725,9 @@
   </si>
   <si>
     <t>幸运夺宝：抢购商品所需要的道具ID(仅在界面左上角处显示的抢购消耗道具的信息)</t>
+  </si>
+  <si>
+    <t>积分大奖：上榜的最低积分要求(周榜)</t>
   </si>
 </sst>
 </file>
@@ -945,7 +960,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="35">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1038,12 +1053,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -1129,12 +1138,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1362,61 +1365,61 @@
     <xf numFmtId="0" fontId="27" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="28" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="28" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1788,18 +1791,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:W70"/>
+  <dimension ref="A1:W71"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="9" style="3"/>
-    <col min="2" max="2" width="89" style="3" customWidth="1"/>
+    <col min="2" max="2" width="96.9083333333333" style="3" customWidth="1"/>
     <col min="3" max="4" width="28.375" style="3" customWidth="1"/>
     <col min="5" max="5" width="11.5" style="3" customWidth="1"/>
     <col min="6" max="6" width="9.625" style="3" customWidth="1"/>
     <col min="7" max="7" width="23.375" style="3" customWidth="1"/>
     <col min="8" max="8" width="12.75" style="3"/>
-    <col min="9" max="9" width="14.125" style="3"/>
-    <col min="10" max="10" width="11.5" style="3"/>
+    <col min="9" max="10" width="14.125" style="3"/>
     <col min="11" max="11" width="9" style="3"/>
     <col min="12" max="12" width="12.875" style="3"/>
     <col min="13" max="13" width="9" style="3"/>
@@ -2505,189 +2507,220 @@
       <c r="D47" s="3">
         <v>3</v>
       </c>
+      <c r="H47" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="I47" s="3">
+        <v>6000</v>
+      </c>
     </row>
     <row r="48" spans="1:23">
       <c r="A48" s="3">
         <v>48</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4">
+        <v>97</v>
+      </c>
+      <c r="G48" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="H48" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="I48" s="3">
+        <v>30</v>
+      </c>
+      <c r="J48" s="3">
+        <f>I47/(24*60/I49)*100/(I48/1+I48/1)</f>
+        <v>104.166666666667</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9">
       <c r="A49" s="3">
         <v>49</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="50" spans="1:4">
+        <v>101</v>
+      </c>
+      <c r="H49" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="I49" s="3">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9">
       <c r="A50" s="3">
         <v>50</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="C50" s="17"/>
-    </row>
-    <row r="51" s="1" customFormat="1" spans="1:4">
+      <c r="I50" s="3">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="51" s="1" customFormat="1" spans="1:9">
       <c r="A51" s="1">
         <v>51</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="C51" s="22" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="52" spans="1:4">
+        <v>105</v>
+      </c>
+      <c r="I51" s="1">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9">
       <c r="A52" s="3">
         <v>52</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="D52" s="12">
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:4">
+    <row r="53" spans="1:9">
       <c r="A53" s="3">
         <v>53</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="D53" s="12">
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:4">
+    <row r="54" spans="1:9">
       <c r="A54" s="3">
         <v>54</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="D54" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="55" customFormat="1" spans="1:4">
+    <row r="55" customFormat="1" spans="1:9">
       <c r="A55" s="3">
         <v>55</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="C55" s="3"/>
       <c r="D55" s="3">
         <v>60</v>
       </c>
     </row>
-    <row r="56" spans="1:4">
+    <row r="56" spans="1:9">
       <c r="A56" s="3">
         <v>56</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="57" s="1" customFormat="1" spans="1:4">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="57" s="1" customFormat="1" spans="1:9">
       <c r="A57" s="1">
         <v>60</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="C57" s="23" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="58" spans="1:4">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9">
       <c r="A58" s="3">
         <v>61</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="C58" s="24" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="59" spans="1:4">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9">
       <c r="A59" s="3">
         <v>62</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="C59" s="12" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="60" spans="1:4">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9">
       <c r="A60" s="3">
         <v>63</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="61" spans="1:4">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9">
       <c r="A61" s="3">
         <v>64</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="C61" s="17" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="62" spans="1:4">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9">
       <c r="A62" s="3">
         <v>65</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="C62" s="17" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="63" spans="1:4">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9">
       <c r="A63" s="3">
         <v>70</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="C63" s="17" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="D63" s="17"/>
     </row>
-    <row r="64" spans="1:4">
+    <row r="64" spans="1:9">
       <c r="A64" s="3">
         <v>71</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="C64" s="17"/>
       <c r="D64" s="17">
@@ -2699,10 +2732,10 @@
         <v>72</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="C65" s="17" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
     </row>
     <row r="66" spans="1:20">
@@ -2710,7 +2743,7 @@
         <v>80</v>
       </c>
       <c r="B66" s="25" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="C66" s="25"/>
       <c r="D66" s="25">
@@ -2738,7 +2771,7 @@
         <v>90</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="D67" s="3">
         <v>1000000</v>
@@ -2749,10 +2782,10 @@
         <v>100</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
     </row>
     <row r="69" spans="1:20">
@@ -2760,10 +2793,10 @@
         <v>101</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
     </row>
     <row r="70" spans="1:20">
@@ -2771,10 +2804,22 @@
         <v>102</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="C70" s="13">
         <v>1980000</v>
+      </c>
+    </row>
+    <row r="71" spans="1:20">
+      <c r="A71" s="3">
+        <v>110</v>
+      </c>
+      <c r="B71" s="21" t="s">
+        <v>136</v>
+      </c>
+      <c r="D71" s="17">
+        <f>8400</f>
+        <v>8400</v>
       </c>
     </row>
   </sheetData>

--- a/gm/resources/sample/global.xlsx
+++ b/gm/resources/sample/global.xlsx
@@ -317,7 +317,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="138">
   <si>
     <t>sid</t>
   </si>
@@ -728,6 +728,9 @@
   </si>
   <si>
     <t>积分大奖：上榜的最低积分要求(周榜)</t>
+  </si>
+  <si>
+    <t>机器人最低准入倍数放大基数：用于选择机器人的携带金额，机器人携带金额= 游戏最小准入金额× 此倍数</t>
   </si>
 </sst>
 </file>
@@ -949,12 +952,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1791,7 +1794,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:W71"/>
+  <dimension ref="A1:W72"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="9" style="3"/>
@@ -2822,6 +2825,17 @@
         <v>8400</v>
       </c>
     </row>
+    <row r="72" spans="1:20">
+      <c r="A72" s="3">
+        <v>111</v>
+      </c>
+      <c r="B72" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="D72" s="3">
+        <v>500</v>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="C57" r:id="rId3" display="https://aws-s3-jjg-asset-bucket.s3.ap-southeast-1.amazonaws.com/tanchuang_res/english/tc_sc_1.png" tooltip="https://aws-s3-jjg-asset-bucket.s3.ap-southeast-1.amazonaws.com/tanchuang_res/english/tc_sc_1.png"/>

--- a/gm/resources/sample/global.xlsx
+++ b/gm/resources/sample/global.xlsx
@@ -688,7 +688,7 @@
     <t>推广分享：有效用户达标条件（有效下注累计_数值|累计充值_数值）</t>
   </si>
   <si>
-    <t>12007_2000000|11002_100000_0</t>
+    <t>AND(totalValidBets(2000000),totalRecharge(100000,0))</t>
   </si>
   <si>
     <t>财富轮盘：昨日输的金币兑换为积分的比例（昨日所输金币_获得积分）</t>

--- a/gm/resources/sample/global.xlsx
+++ b/gm/resources/sample/global.xlsx
@@ -715,7 +715,7 @@
     <t>货币文本符号，服务器发个前端放在货币数值前面</t>
   </si>
   <si>
-    <t>VND</t>
+    <t>$</t>
   </si>
   <si>
     <t>幸运夺宝：商品价值货币的图标</t>

--- a/gm/resources/sample/global.xlsx
+++ b/gm/resources/sample/global.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="11925"/>
   </bookViews>
   <sheets>
     <sheet name="globalConfig" sheetId="1" r:id="rId1"/>
@@ -715,7 +715,7 @@
     <t>货币文本符号，服务器发个前端放在货币数值前面</t>
   </si>
   <si>
-    <t>$</t>
+    <t>VND</t>
   </si>
   <si>
     <t>幸运夺宝：商品价值货币的图标</t>
@@ -2777,7 +2777,7 @@
         <v>130</v>
       </c>
       <c r="D67" s="3">
-        <v>1000000</v>
+        <v>100000</v>
       </c>
     </row>
     <row r="68" spans="1:20">

--- a/gm/resources/sample/global.xlsx
+++ b/gm/resources/sample/global.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="11925"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="globalConfig" sheetId="1" r:id="rId1"/>
@@ -715,13 +715,13 @@
     <t>货币文本符号，服务器发个前端放在货币数值前面</t>
   </si>
   <si>
-    <t>VND</t>
+    <t>$</t>
   </si>
   <si>
     <t>幸运夺宝：商品价值货币的图标</t>
   </si>
   <si>
-    <t>icon_vnd.png</t>
+    <t>jinbi_11.png</t>
   </si>
   <si>
     <t>幸运夺宝：抢购商品所需要的道具ID(仅在界面左上角处显示的抢购消耗道具的信息)</t>
@@ -2810,7 +2810,7 @@
         <v>135</v>
       </c>
       <c r="C70" s="13">
-        <v>1980000</v>
+        <v>1022503</v>
       </c>
     </row>
     <row r="71" spans="1:20">

--- a/gm/resources/sample/global.xlsx
+++ b/gm/resources/sample/global.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="11925"/>
   </bookViews>
   <sheets>
     <sheet name="globalConfig" sheetId="1" r:id="rId1"/>
@@ -715,13 +715,13 @@
     <t>货币文本符号，服务器发个前端放在货币数值前面</t>
   </si>
   <si>
-    <t>$</t>
+    <t>VND</t>
   </si>
   <si>
     <t>幸运夺宝：商品价值货币的图标</t>
   </si>
   <si>
-    <t>jinbi_11.png</t>
+    <t>icon_vnd.png</t>
   </si>
   <si>
     <t>幸运夺宝：抢购商品所需要的道具ID(仅在界面左上角处显示的抢购消耗道具的信息)</t>
@@ -2810,7 +2810,7 @@
         <v>135</v>
       </c>
       <c r="C70" s="13">
-        <v>1022503</v>
+        <v>1980000</v>
       </c>
     </row>
     <row r="71" spans="1:20">

--- a/gm/resources/sample/global.xlsx
+++ b/gm/resources/sample/global.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="11925"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="globalConfig" sheetId="1" r:id="rId1"/>
@@ -1426,7 +1426,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1469,6 +1469,9 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="6" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" quotePrefix="1">
       <alignment vertical="center"/>
     </xf>
@@ -1962,7 +1965,7 @@
       <c r="B10" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="C10" s="26" t="s">
+      <c r="C10" s="27" t="s">
         <v>24</v>
       </c>
       <c r="D10" s="10"/>
@@ -1979,7 +1982,7 @@
       <c r="B11" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="C11" s="27" t="s">
+      <c r="C11" s="28" t="s">
         <v>27</v>
       </c>
       <c r="D11" s="7"/>
@@ -1996,7 +1999,7 @@
       <c r="B12" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="C12" s="27" t="s">
+      <c r="C12" s="28" t="s">
         <v>29</v>
       </c>
       <c r="D12" s="7"/>
@@ -2013,7 +2016,7 @@
       <c r="B13" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="C13" s="27" t="s">
+      <c r="C13" s="28" t="s">
         <v>31</v>
       </c>
       <c r="D13" s="7"/>
@@ -2030,7 +2033,7 @@
       <c r="B14" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="C14" s="27" t="s">
+      <c r="C14" s="28" t="s">
         <v>33</v>
       </c>
       <c r="D14" s="7"/>
@@ -2809,7 +2812,7 @@
       <c r="B70" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="C70" s="13">
+      <c r="D70" s="26">
         <v>1980000</v>
       </c>
     </row>

--- a/gm/resources/sample/global.xlsx
+++ b/gm/resources/sample/global.xlsx
@@ -1426,7 +1426,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1469,6 +1469,9 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="6" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" quotePrefix="1">
       <alignment vertical="center"/>
     </xf>
@@ -1962,7 +1965,7 @@
       <c r="B10" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="C10" s="26" t="s">
+      <c r="C10" s="27" t="s">
         <v>24</v>
       </c>
       <c r="D10" s="10"/>
@@ -1979,7 +1982,7 @@
       <c r="B11" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="C11" s="27" t="s">
+      <c r="C11" s="28" t="s">
         <v>27</v>
       </c>
       <c r="D11" s="7"/>
@@ -1996,7 +1999,7 @@
       <c r="B12" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="C12" s="27" t="s">
+      <c r="C12" s="28" t="s">
         <v>29</v>
       </c>
       <c r="D12" s="7"/>
@@ -2013,7 +2016,7 @@
       <c r="B13" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="C13" s="27" t="s">
+      <c r="C13" s="28" t="s">
         <v>31</v>
       </c>
       <c r="D13" s="7"/>
@@ -2030,7 +2033,7 @@
       <c r="B14" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="C14" s="27" t="s">
+      <c r="C14" s="28" t="s">
         <v>33</v>
       </c>
       <c r="D14" s="7"/>
@@ -2809,7 +2812,7 @@
       <c r="B70" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="C70" s="13">
+      <c r="D70" s="26">
         <v>1022503</v>
       </c>
     </row>

--- a/gm/resources/sample/global.xlsx
+++ b/gm/resources/sample/global.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="11925"/>
   </bookViews>
   <sheets>
     <sheet name="globalConfig" sheetId="1" r:id="rId1"/>
@@ -317,7 +317,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="139">
   <si>
     <t>sid</t>
   </si>
@@ -731,6 +731,9 @@
   </si>
   <si>
     <t>机器人最低准入倍数放大基数：用于选择机器人的携带金额，机器人携带金额= 游戏最小准入金额× 此倍数</t>
+  </si>
+  <si>
+    <t>创建房间-Slot游戏新增超时提出的倒计时，单位毫秒</t>
   </si>
 </sst>
 </file>
@@ -1797,7 +1800,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:W72"/>
+  <dimension ref="A1:W73"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="9" style="3"/>
@@ -2839,6 +2842,17 @@
         <v>500</v>
       </c>
     </row>
+    <row r="73" spans="1:20">
+      <c r="A73" s="3">
+        <v>112</v>
+      </c>
+      <c r="B73" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="D73" s="3">
+        <v>300000</v>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="C57" r:id="rId3" display="https://aws-s3-jjg-asset-bucket.s3.ap-southeast-1.amazonaws.com/tanchuang_res/english/tc_sc_1.png" tooltip="https://aws-s3-jjg-asset-bucket.s3.ap-southeast-1.amazonaws.com/tanchuang_res/english/tc_sc_1.png"/>

--- a/gm/resources/sample/global.xlsx
+++ b/gm/resources/sample/global.xlsx
@@ -164,7 +164,7 @@
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
-值为空，表示不开启该活动</t>
+为空时表示不开此活动</t>
         </r>
       </text>
     </comment>
@@ -208,7 +208,8 @@
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
-值为0表示不返利</t>
+值为0表示不返利
+</t>
         </r>
       </text>
     </comment>
@@ -317,7 +318,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="140">
   <si>
     <t>sid</t>
   </si>
@@ -469,7 +470,7 @@
     <t>摇钱树活动增长金额</t>
   </si>
   <si>
-    <t>0_12_100_250|12_24_100_250</t>
+    <t>0_12_5000_10000|12_24_5000_10000</t>
   </si>
   <si>
     <t>开始时间/时_结束时间/时（左闭右开）_每次增长值_每次增长下限|</t>
@@ -496,7 +497,7 @@
     <t>1022501_1</t>
   </si>
   <si>
-    <t>每次下注金币的万分比飞入储钱罐</t>
+    <t>储钱罐：每次下注金币的万分比飞入储钱罐</t>
   </si>
   <si>
     <t>创建房间-房间销毁时房主获得实际准备金的万分比</t>
@@ -544,13 +545,13 @@
     <t>官方派奖：充值转换积分比例 ：充值金额（290,000 越南盾 = 1 积分 )</t>
   </si>
   <si>
-    <t>208000_1</t>
+    <t>1_1</t>
   </si>
   <si>
     <t>官方派奖：转盘1次数_转盘2次数_转盘3次数（真人抽奖后机器人跟着的抽奖次数，填10，表示玩家抽1次，机器人抽10次）</t>
   </si>
   <si>
-    <t>99_99_99</t>
+    <t>1_1_1</t>
   </si>
   <si>
     <t>机器人奖池比例</t>
@@ -631,6 +632,9 @@
     <t>新手奖励</t>
   </si>
   <si>
+    <t>1990000_21400</t>
+  </si>
+  <si>
     <t>手机短信区号（印度、巴基斯坦、菲律宾、巴西、尼日利亚）废弃</t>
   </si>
   <si>
@@ -664,13 +668,13 @@
     <t>隐私政策链接</t>
   </si>
   <si>
-    <t>http://chat.kinghush.com/privacy.html</t>
+    <t>https://chat.kinghush.com/privacy.html</t>
   </si>
   <si>
     <t>推广分享：分享1人得固定奖励</t>
   </si>
   <si>
-    <t>1990000_100000</t>
+    <t>1990000_42000</t>
   </si>
   <si>
     <t>推广分享：二维码图片配置(该资源放在资源服务器实时下载显示的)</t>
@@ -682,19 +686,19 @@
     <t>推广分享：周榜上榜条件设置(收益数量)</t>
   </si>
   <si>
-    <t>1990000_4000000</t>
+    <t>1990000_750000</t>
   </si>
   <si>
     <t>推广分享：有效用户达标条件（有效下注累计_数值|累计充值_数值）</t>
   </si>
   <si>
-    <t>AND(totalValidBets(2000000),totalRecharge(100000,0))</t>
+    <t>AND(totalValidBets(4200000),totalRecharge(7,0))</t>
   </si>
   <si>
     <t>财富轮盘：昨日输的金币兑换为积分的比例（昨日所输金币_获得积分）</t>
   </si>
   <si>
-    <t>2000_1</t>
+    <t>125_1</t>
   </si>
   <si>
     <t>财富轮盘：每次抽奖所消耗的积分</t>
@@ -757,18 +761,18 @@
     </font>
     <font>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="0" tint="-0.249977111117893"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
-      <name val="微软雅黑"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
@@ -955,18 +959,18 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
-    <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
   </fonts>
-  <fills count="33">
+  <fills count="38">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -975,175 +979,205 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1305,7 +1339,7 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1329,16 +1363,16 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -1347,43 +1381,31 @@
     <xf numFmtId="0" fontId="23" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="28" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1419,66 +1441,89 @@
     <xf numFmtId="0" fontId="27" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="28" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="6" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" quotePrefix="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" quotePrefix="1">
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" quotePrefix="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" quotePrefix="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1803,1059 +1848,1062 @@
   <dimension ref="A1:W73"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
-    <col min="1" max="1" width="9" style="3"/>
-    <col min="2" max="2" width="96.9083333333333" style="3" customWidth="1"/>
-    <col min="3" max="4" width="28.375" style="3" customWidth="1"/>
-    <col min="5" max="5" width="11.5" style="3" customWidth="1"/>
-    <col min="6" max="6" width="9.625" style="3" customWidth="1"/>
-    <col min="7" max="7" width="23.375" style="3" customWidth="1"/>
-    <col min="8" max="8" width="12.75" style="3"/>
-    <col min="9" max="10" width="14.125" style="3"/>
-    <col min="11" max="11" width="9" style="3"/>
-    <col min="12" max="12" width="12.875" style="3"/>
-    <col min="13" max="13" width="9" style="3"/>
-    <col min="14" max="17" width="10.375" style="3"/>
-    <col min="18" max="18" width="9.25" style="3"/>
-    <col min="19" max="16384" width="9" style="3"/>
+    <col min="1" max="1" width="9" style="8"/>
+    <col min="2" max="2" width="96.9083333333333" style="8" customWidth="1"/>
+    <col min="3" max="4" width="28.375" style="8" customWidth="1"/>
+    <col min="5" max="5" width="11.5" style="8" customWidth="1"/>
+    <col min="6" max="6" width="9.625" style="8" customWidth="1"/>
+    <col min="7" max="7" width="23.375" style="8" customWidth="1"/>
+    <col min="8" max="8" width="12.75" style="8"/>
+    <col min="9" max="10" width="14.125" style="8"/>
+    <col min="11" max="11" width="9" style="8"/>
+    <col min="12" max="12" width="12.875" style="8"/>
+    <col min="13" max="13" width="9" style="8"/>
+    <col min="14" max="17" width="10.375" style="8"/>
+    <col min="18" max="18" width="9.25" style="8"/>
+    <col min="19" max="16384" width="9" style="8"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5" t="s">
+      <c r="B1" s="10"/>
+      <c r="C1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="G1" s="10" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="5"/>
-      <c r="C2" s="5" t="s">
+      <c r="B2" s="10"/>
+      <c r="C2" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="7" t="s">
+      <c r="D2" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="E2" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="F2" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="G2" s="5"/>
+      <c r="G2" s="10"/>
     </row>
     <row r="3" spans="1:7">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="5"/>
-      <c r="C3" s="5" t="s">
+      <c r="B3" s="10"/>
+      <c r="C3" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="F3" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="G3" s="5"/>
+      <c r="G3" s="10"/>
     </row>
     <row r="4" spans="1:7">
-      <c r="A4" s="8"/>
-      <c r="B4" s="7"/>
-      <c r="C4" s="7"/>
-      <c r="G4" s="7"/>
+      <c r="A4" s="13"/>
+      <c r="B4" s="12"/>
+      <c r="C4" s="12"/>
+      <c r="G4" s="12"/>
     </row>
     <row r="5" spans="1:7">
-      <c r="A5" s="3">
+      <c r="A5" s="8">
         <v>1</v>
       </c>
-      <c r="B5" s="7" t="s">
+      <c r="B5" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="D5" s="7">
+      <c r="D5" s="12">
         <v>999</v>
       </c>
-      <c r="E5" s="7"/>
-      <c r="F5" s="7"/>
-      <c r="G5" s="7"/>
+      <c r="E5" s="12"/>
+      <c r="F5" s="12"/>
+      <c r="G5" s="12"/>
     </row>
     <row r="6" spans="1:7">
-      <c r="A6" s="3">
+      <c r="A6" s="8">
         <v>2</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="B6" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="D6" s="9">
-        <v>30000</v>
-      </c>
-      <c r="E6" s="7"/>
-      <c r="F6" s="7"/>
-      <c r="G6" s="7" t="s">
+      <c r="D6" s="14">
+        <v>10000</v>
+      </c>
+      <c r="E6" s="12"/>
+      <c r="F6" s="12"/>
+      <c r="G6" s="12" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="7" spans="1:7">
-      <c r="A7" s="3">
+      <c r="A7" s="8">
         <v>3</v>
       </c>
-      <c r="B7" s="7" t="s">
+      <c r="B7" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="D7" s="7">
+      <c r="D7" s="12">
         <v>10000</v>
       </c>
-      <c r="E7" s="7"/>
-      <c r="F7" s="7"/>
-      <c r="G7" s="7" t="s">
+      <c r="E7" s="12"/>
+      <c r="F7" s="12"/>
+      <c r="G7" s="12" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="8" spans="1:7">
-      <c r="A8" s="3">
+      <c r="A8" s="8">
         <v>4</v>
       </c>
-      <c r="B8" s="7" t="s">
+      <c r="B8" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="C8" s="7">
+      <c r="C8" s="12">
         <v>100</v>
       </c>
-      <c r="D8" s="7"/>
-      <c r="E8" s="7"/>
-      <c r="F8" s="7"/>
-      <c r="G8" s="7" t="s">
+      <c r="D8" s="12"/>
+      <c r="E8" s="12"/>
+      <c r="F8" s="12"/>
+      <c r="G8" s="12" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="9" spans="1:7">
-      <c r="A9" s="3">
+      <c r="A9" s="8">
         <v>5</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="C9" s="3">
+      <c r="C9" s="8">
         <v>4</v>
       </c>
-      <c r="G9" s="3" t="s">
+      <c r="G9" s="8" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="10" spans="1:7">
-      <c r="A10" s="3">
+      <c r="A10" s="8">
         <v>6</v>
       </c>
-      <c r="B10" s="7" t="s">
+      <c r="B10" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="C10" s="27" t="s">
+      <c r="C10" s="38" t="s">
         <v>24</v>
       </c>
-      <c r="D10" s="10"/>
-      <c r="E10" s="7"/>
-      <c r="F10" s="7"/>
-      <c r="G10" s="3" t="s">
+      <c r="D10" s="15"/>
+      <c r="E10" s="12"/>
+      <c r="F10" s="12"/>
+      <c r="G10" s="8" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="11" spans="1:7">
-      <c r="A11" s="3">
+      <c r="A11" s="8">
         <v>7</v>
       </c>
-      <c r="B11" s="7" t="s">
+      <c r="B11" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="C11" s="28" t="s">
+      <c r="C11" s="39" t="s">
         <v>27</v>
       </c>
-      <c r="D11" s="7"/>
-      <c r="E11" s="7"/>
-      <c r="F11" s="7"/>
-      <c r="G11" s="3" t="s">
+      <c r="D11" s="12"/>
+      <c r="E11" s="12"/>
+      <c r="F11" s="12"/>
+      <c r="G11" s="8" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="12" spans="1:7">
-      <c r="A12" s="3">
+      <c r="A12" s="8">
         <v>8</v>
       </c>
-      <c r="B12" s="7" t="s">
+      <c r="B12" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="C12" s="28" t="s">
+      <c r="C12" s="39" t="s">
         <v>29</v>
       </c>
-      <c r="D12" s="7"/>
-      <c r="E12" s="7"/>
-      <c r="F12" s="7"/>
-      <c r="G12" s="3" t="s">
+      <c r="D12" s="12"/>
+      <c r="E12" s="12"/>
+      <c r="F12" s="12"/>
+      <c r="G12" s="8" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="13" spans="1:7">
-      <c r="A13" s="3">
+      <c r="A13" s="8">
         <v>9</v>
       </c>
-      <c r="B13" s="7" t="s">
+      <c r="B13" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="C13" s="28" t="s">
+      <c r="C13" s="39" t="s">
         <v>31</v>
       </c>
-      <c r="D13" s="7"/>
-      <c r="E13" s="7"/>
-      <c r="F13" s="7"/>
-      <c r="G13" s="3" t="s">
+      <c r="D13" s="12"/>
+      <c r="E13" s="12"/>
+      <c r="F13" s="12"/>
+      <c r="G13" s="8" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="14" spans="1:7">
-      <c r="A14" s="3">
+      <c r="A14" s="8">
         <v>10</v>
       </c>
-      <c r="B14" s="7" t="s">
+      <c r="B14" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="C14" s="28" t="s">
+      <c r="C14" s="39" t="s">
         <v>33</v>
       </c>
-      <c r="D14" s="7"/>
-      <c r="E14" s="7"/>
-      <c r="F14" s="7"/>
-      <c r="G14" s="3" t="s">
+      <c r="D14" s="12"/>
+      <c r="E14" s="12"/>
+      <c r="F14" s="12"/>
+      <c r="G14" s="8" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="15" spans="1:7">
-      <c r="A15" s="3">
+      <c r="A15" s="8">
         <v>11</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="B15" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="D15" s="3">
+      <c r="D15" s="8">
         <f>2*3*5*3</f>
         <v>90</v>
       </c>
     </row>
     <row r="16" spans="1:7">
-      <c r="A16" s="3">
+      <c r="A16" s="8">
         <v>12</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="B16" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="D16" s="3">
+      <c r="D16" s="8">
         <v>3333</v>
       </c>
-      <c r="G16" s="3" t="s">
+      <c r="G16" s="8" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="17" spans="1:7">
-      <c r="A17" s="3">
+      <c r="A17" s="8">
         <v>13</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="B17" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="D17" s="3">
+      <c r="D17" s="8">
         <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:7">
-      <c r="A18" s="3">
+      <c r="A18" s="8">
         <v>14</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="B18" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="C18" s="11" t="s">
+      <c r="C18" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="G18" s="3" t="s">
+      <c r="G18" s="8" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="19" spans="1:7">
-      <c r="A19" s="3">
+      <c r="A19" s="8">
         <v>15</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="B19" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="D19" s="3">
+      <c r="D19" s="8">
         <v>5</v>
       </c>
     </row>
     <row r="20" spans="1:7">
-      <c r="A20" s="3">
+      <c r="A20" s="8">
         <v>16</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="B20" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="D20" s="3">
+      <c r="D20" s="8">
         <v>10</v>
       </c>
     </row>
     <row r="21" spans="1:7">
-      <c r="A21" s="3">
+      <c r="A21" s="8">
         <v>17</v>
       </c>
-      <c r="B21" s="3" t="s">
+      <c r="B21" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="C21" s="3" t="s">
+      <c r="C21" s="8" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="22" spans="1:7">
-      <c r="A22" s="3">
+      <c r="A22" s="8">
         <v>18</v>
       </c>
-      <c r="B22" s="3" t="s">
+      <c r="B22" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="D22" s="3">
+      <c r="D22" s="8">
         <f>7*24*60*60</f>
         <v>604800</v>
       </c>
     </row>
     <row r="23" spans="1:7">
-      <c r="A23" s="3">
+      <c r="A23" s="8">
         <v>19</v>
       </c>
-      <c r="B23" s="3" t="s">
+      <c r="B23" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="C23" s="3" t="s">
+      <c r="C23" s="8" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="24" spans="1:7">
-      <c r="A24" s="3">
+      <c r="A24" s="8">
         <v>20</v>
       </c>
-      <c r="B24" s="3" t="s">
+      <c r="B24" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="D24" s="3">
+      <c r="D24" s="8">
         <v>10</v>
       </c>
     </row>
-    <row r="25" spans="1:7">
-      <c r="A25" s="3">
+    <row r="25" s="1" customFormat="1" spans="1:7">
+      <c r="A25" s="1">
         <v>21</v>
       </c>
-      <c r="B25" s="3" t="s">
+      <c r="B25" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="C25" s="12" t="s">
+      <c r="C25" s="17" t="s">
         <v>50</v>
       </c>
-      <c r="G25" s="3" t="s">
+      <c r="G25" s="1" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="26" spans="1:7">
-      <c r="A26" s="3">
+    <row r="26" s="1" customFormat="1" spans="1:7">
+      <c r="A26" s="1">
         <v>22</v>
       </c>
-      <c r="B26" s="3" t="s">
+      <c r="B26" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="C26" s="3" t="s">
+      <c r="C26" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="G26" s="3" t="s">
+      <c r="G26" s="1" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="27" spans="1:7">
-      <c r="A27" s="3">
+    <row r="27" s="1" customFormat="1" spans="1:7">
+      <c r="A27" s="1">
         <v>23</v>
       </c>
-      <c r="B27" s="3" t="s">
+      <c r="B27" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D27" s="3">
+      <c r="D27" s="1">
         <v>10000</v>
       </c>
     </row>
-    <row r="28" spans="1:7">
-      <c r="A28" s="3">
+    <row r="28" s="1" customFormat="1" spans="1:7">
+      <c r="A28" s="1">
         <v>24</v>
       </c>
-      <c r="B28" s="3" t="s">
+      <c r="B28" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="D28" s="3">
+      <c r="D28" s="1">
         <v>100</v>
       </c>
     </row>
-    <row r="29" spans="1:7">
-      <c r="A29" s="3">
+    <row r="29" s="1" customFormat="1" spans="1:7">
+      <c r="A29" s="1">
         <v>25</v>
       </c>
-      <c r="B29" s="3" t="s">
+      <c r="B29" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="C29" s="3" t="s">
+      <c r="C29" s="1" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="30" spans="1:7">
-      <c r="A30" s="3">
+      <c r="A30" s="8">
         <v>26</v>
       </c>
-      <c r="B30" s="3" t="s">
+      <c r="B30" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="C30" s="13"/>
-      <c r="D30" s="3">
+      <c r="C30" s="18"/>
+      <c r="D30" s="8">
         <v>100</v>
       </c>
     </row>
     <row r="31" spans="1:7">
-      <c r="A31" s="3">
+      <c r="A31" s="8">
         <v>27</v>
       </c>
-      <c r="B31" s="3" t="s">
+      <c r="B31" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="D31" s="3">
+      <c r="D31" s="8">
         <v>10000</v>
       </c>
-      <c r="G31" s="3" t="s">
+      <c r="G31" s="8" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="32" spans="1:7">
-      <c r="A32" s="3">
+      <c r="A32" s="8">
         <v>28</v>
       </c>
-      <c r="B32" s="3" t="s">
+      <c r="B32" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="C32" s="3" t="s">
+      <c r="C32" s="8" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="33" spans="1:23">
-      <c r="A33" s="3">
+      <c r="A33" s="8">
         <v>29</v>
       </c>
-      <c r="B33" s="3" t="s">
+      <c r="B33" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="D33" s="3">
+      <c r="D33" s="8">
         <v>10</v>
       </c>
     </row>
-    <row r="34" s="1" customFormat="1" spans="1:23">
-      <c r="A34" s="14">
+    <row r="34" s="2" customFormat="1" spans="1:23">
+      <c r="A34" s="19">
         <v>30</v>
       </c>
-      <c r="B34" s="14" t="s">
+      <c r="B34" s="19" t="s">
         <v>65</v>
       </c>
-      <c r="C34" s="1" t="s">
+      <c r="C34" s="2" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="35" s="1" customFormat="1" spans="1:23">
-      <c r="A35" s="14">
+    <row r="35" s="2" customFormat="1" spans="1:23">
+      <c r="A35" s="19">
         <v>31</v>
       </c>
-      <c r="B35" s="14" t="s">
+      <c r="B35" s="19" t="s">
         <v>67</v>
       </c>
-      <c r="E35" s="15">
+      <c r="E35" s="20">
         <v>372460972.440945</v>
       </c>
-      <c r="G35" s="1" t="s">
+      <c r="G35" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="H35" s="15">
+      <c r="H35" s="20">
         <v>8692.20472440945</v>
       </c>
-      <c r="I35" s="1" t="s">
+      <c r="I35" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="J35" s="1">
+      <c r="J35" s="2">
         <v>1</v>
       </c>
-      <c r="K35" s="1" t="s">
+      <c r="K35" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="L35" s="1">
+      <c r="L35" s="2">
         <f>J35*24*60*60*1000</f>
         <v>86400000</v>
       </c>
-      <c r="M35" s="1" t="s">
+      <c r="M35" s="2" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="36" spans="1:23">
-      <c r="A36" s="14">
+      <c r="A36" s="19">
         <v>32</v>
       </c>
-      <c r="B36" s="14" t="s">
+      <c r="B36" s="19" t="s">
         <v>72</v>
       </c>
-      <c r="C36" s="1" t="s">
+      <c r="C36" s="2" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="37" spans="1:23">
-      <c r="A37" s="16">
+      <c r="A37" s="21">
         <v>33</v>
       </c>
-      <c r="B37" s="16" t="s">
+      <c r="B37" s="21" t="s">
         <v>74</v>
       </c>
-      <c r="C37" s="17" t="s">
+      <c r="C37" s="22" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="38" s="2" customFormat="1" spans="1:23">
-      <c r="A38" s="18">
+    <row r="38" s="3" customFormat="1" spans="1:23">
+      <c r="A38" s="23">
         <v>34</v>
       </c>
-      <c r="B38" s="18" t="s">
+      <c r="B38" s="23" t="s">
         <v>76</v>
       </c>
-      <c r="C38" s="2" t="s">
+      <c r="C38" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="G38" s="2" t="s">
+      <c r="G38" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="H38" s="2">
+      <c r="H38" s="3">
         <v>90</v>
       </c>
     </row>
     <row r="39" spans="1:23">
-      <c r="A39" s="16">
+      <c r="A39" s="21">
         <v>35</v>
       </c>
-      <c r="B39" s="16" t="s">
+      <c r="B39" s="21" t="s">
         <v>79</v>
       </c>
-      <c r="C39" s="3" t="s">
+      <c r="C39" s="8" t="s">
         <v>80</v>
       </c>
-      <c r="G39" s="3" t="s">
+      <c r="G39" s="8" t="s">
         <v>81</v>
       </c>
-      <c r="H39" s="19">
+      <c r="H39" s="24">
         <f>ROUND(L35/(E35*H38/100/H35),0)</f>
         <v>2240</v>
       </c>
-      <c r="I39" s="3" t="s">
+      <c r="I39" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="J39" s="3" t="s">
+      <c r="J39" s="8" t="s">
         <v>82</v>
       </c>
-      <c r="K39" s="20" t="s">
+      <c r="K39" s="25" t="s">
         <v>83</v>
       </c>
-      <c r="L39" s="20">
+      <c r="L39" s="25">
         <v>0.25</v>
       </c>
-      <c r="M39" s="3" t="s">
+      <c r="M39" s="8" t="s">
         <v>84</v>
       </c>
-      <c r="N39" s="3">
+      <c r="N39" s="8">
         <f>ROUND(P39*(1+2*L39),0)</f>
         <v>3360</v>
       </c>
-      <c r="O39" s="3">
+      <c r="O39" s="8">
         <f>ROUND(P39*(1+1*L39),0)</f>
         <v>2800</v>
       </c>
-      <c r="P39" s="3">
+      <c r="P39" s="8">
         <f>H39</f>
         <v>2240</v>
       </c>
-      <c r="Q39" s="3">
+      <c r="Q39" s="8">
         <f>ROUND(P39*(1-1*L39),0)</f>
         <v>1680</v>
       </c>
-      <c r="R39" s="3">
+      <c r="R39" s="8">
         <f>ROUND(P39*(1-2*L39),0)</f>
         <v>1120</v>
       </c>
-      <c r="S39" s="3" t="str">
+      <c r="S39" s="8" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,N39,1000)</f>
         <v>3360_1000</v>
       </c>
-      <c r="T39" s="3" t="str">
+      <c r="T39" s="8" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,O39,1000)</f>
         <v>2800_1000</v>
       </c>
-      <c r="U39" s="3" t="str">
+      <c r="U39" s="8" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,P39,1000)</f>
         <v>2240_1000</v>
       </c>
-      <c r="V39" s="3" t="str">
+      <c r="V39" s="8" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,Q39,1000)</f>
         <v>1680_1000</v>
       </c>
-      <c r="W39" s="3" t="str">
+      <c r="W39" s="8" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,R39,1000)</f>
         <v>1120_1000</v>
       </c>
     </row>
-    <row r="40" spans="1:23">
-      <c r="A40" s="21">
+    <row r="40" s="4" customFormat="1" spans="1:23">
+      <c r="A40" s="4">
         <v>40</v>
       </c>
-      <c r="B40" s="21" t="s">
+      <c r="B40" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="D40" s="17">
+      <c r="D40" s="26">
         <v>88</v>
       </c>
     </row>
-    <row r="41" spans="1:23">
-      <c r="A41" s="21">
+    <row r="41" s="4" customFormat="1" spans="1:23">
+      <c r="A41" s="4">
         <v>41</v>
       </c>
-      <c r="B41" s="21" t="s">
+      <c r="B41" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="D41" s="17">
+      <c r="D41" s="26">
         <v>1200</v>
       </c>
     </row>
-    <row r="42" spans="1:23">
-      <c r="A42" s="21">
+    <row r="42" s="4" customFormat="1" spans="1:23">
+      <c r="A42" s="4">
         <v>42</v>
       </c>
-      <c r="B42" s="21" t="s">
+      <c r="B42" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="D42" s="17">
+      <c r="D42" s="26">
         <v>36000</v>
       </c>
     </row>
-    <row r="43" spans="1:23">
-      <c r="A43" s="21">
+    <row r="43" s="4" customFormat="1" spans="1:23">
+      <c r="A43" s="4">
         <v>43</v>
       </c>
-      <c r="B43" s="21" t="s">
+      <c r="B43" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="D43" s="17">
+      <c r="D43" s="26">
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:23">
-      <c r="A44" s="21">
+    <row r="44" s="4" customFormat="1" spans="1:23">
+      <c r="A44" s="4">
         <v>44</v>
       </c>
-      <c r="B44" s="3" t="s">
+      <c r="B44" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="D44" s="17">
-        <v>290000</v>
-      </c>
-    </row>
-    <row r="45" spans="1:23">
-      <c r="A45" s="21">
+      <c r="D44" s="26">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="45" s="4" customFormat="1" spans="1:23">
+      <c r="A45" s="4">
         <v>45</v>
       </c>
-      <c r="B45" s="3" t="s">
+      <c r="B45" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="C45" s="17" t="s">
+      <c r="C45" s="26" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="46" spans="1:23">
-      <c r="A46" s="3">
+    <row r="46" s="5" customFormat="1" spans="1:23">
+      <c r="A46" s="5">
         <v>46</v>
       </c>
-      <c r="B46" s="3" t="s">
+      <c r="B46" s="5" t="s">
         <v>92</v>
       </c>
-      <c r="C46" s="17" t="s">
+      <c r="C46" s="27" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="47" spans="1:23">
-      <c r="A47" s="3">
+    <row r="47" s="4" customFormat="1" spans="1:23">
+      <c r="A47" s="4">
         <v>47</v>
       </c>
-      <c r="B47" s="3" t="s">
+      <c r="B47" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="D47" s="3">
+      <c r="D47" s="4">
         <v>3</v>
       </c>
-      <c r="H47" s="3" t="s">
+      <c r="H47" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="I47" s="3">
+      <c r="I47" s="4">
         <v>6000</v>
       </c>
     </row>
-    <row r="48" spans="1:23">
-      <c r="A48" s="3">
+    <row r="48" s="4" customFormat="1" spans="1:23">
+      <c r="A48" s="4">
         <v>48</v>
       </c>
-      <c r="B48" s="3" t="s">
+      <c r="B48" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="C48" s="3" t="s">
+      <c r="C48" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="G48" s="3" t="s">
+      <c r="G48" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="H48" s="3" t="s">
+      <c r="H48" s="4" t="s">
         <v>99</v>
       </c>
-      <c r="I48" s="3">
+      <c r="I48" s="4">
         <v>30</v>
       </c>
-      <c r="J48" s="3">
+      <c r="J48" s="4">
         <f>I47/(24*60/I49)*100/(I48/1+I48/1)</f>
         <v>104.166666666667</v>
       </c>
     </row>
-    <row r="49" spans="1:9">
-      <c r="A49" s="3">
+    <row r="49" s="4" customFormat="1" spans="1:9">
+      <c r="A49" s="4">
         <v>49</v>
       </c>
-      <c r="B49" s="3" t="s">
+      <c r="B49" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="C49" s="3" t="s">
+      <c r="C49" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="H49" s="3" t="s">
+      <c r="H49" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="I49" s="3">
+      <c r="I49" s="4">
         <v>15</v>
       </c>
     </row>
     <row r="50" spans="1:9">
-      <c r="A50" s="3">
+      <c r="A50" s="8">
         <v>50</v>
       </c>
-      <c r="B50" s="3" t="s">
+      <c r="B50" s="8" t="s">
         <v>103</v>
       </c>
-      <c r="C50" s="17"/>
-      <c r="I50" s="3">
+      <c r="C50" s="28" t="s">
+        <v>104</v>
+      </c>
+      <c r="I50" s="8">
         <v>600</v>
       </c>
     </row>
-    <row r="51" s="1" customFormat="1" spans="1:9">
-      <c r="A51" s="1">
+    <row r="51" s="2" customFormat="1" spans="1:9">
+      <c r="A51" s="2">
         <v>51</v>
       </c>
-      <c r="B51" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="C51" s="22" t="s">
+      <c r="B51" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="I51" s="1">
+      <c r="C51" s="29" t="s">
+        <v>106</v>
+      </c>
+      <c r="I51" s="2">
         <v>1200</v>
       </c>
     </row>
-    <row r="52" spans="1:9">
-      <c r="A52" s="3">
+    <row r="52" s="5" customFormat="1" spans="1:9">
+      <c r="A52" s="5">
         <v>52</v>
       </c>
-      <c r="B52" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="D52" s="12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="53" spans="1:9">
-      <c r="A53" s="3">
+      <c r="B52" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="D52" s="30">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="53" s="6" customFormat="1" spans="1:9">
+      <c r="A53" s="6">
         <v>53</v>
       </c>
-      <c r="B53" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="D53" s="12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="54" spans="1:9">
-      <c r="A54" s="3">
+      <c r="B53" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="D53" s="31">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="54" s="5" customFormat="1" spans="1:9">
+      <c r="A54" s="5">
         <v>54</v>
       </c>
-      <c r="B54" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="D54" s="3">
+      <c r="B54" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="D54" s="5">
         <v>0</v>
       </c>
     </row>
     <row r="55" customFormat="1" spans="1:9">
-      <c r="A55" s="3">
+      <c r="A55" s="8">
         <v>55</v>
       </c>
-      <c r="B55" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="C55" s="3"/>
-      <c r="D55" s="3">
+      <c r="B55" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="C55" s="8"/>
+      <c r="D55" s="8">
         <v>60</v>
       </c>
     </row>
-    <row r="56" spans="1:9">
-      <c r="A56" s="3">
+    <row r="56" s="5" customFormat="1" spans="1:9">
+      <c r="A56" s="5">
         <v>56</v>
       </c>
-      <c r="B56" s="3" t="s">
+      <c r="B56" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="C56" s="5" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="57" s="2" customFormat="1" spans="1:9">
+      <c r="A57" s="2">
+        <v>60</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="C57" s="32" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9">
+      <c r="A58" s="8">
+        <v>61</v>
+      </c>
+      <c r="B58" s="8" t="s">
+        <v>115</v>
+      </c>
+      <c r="C58" s="33" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="59" s="6" customFormat="1" spans="1:9">
+      <c r="A59" s="6">
+        <v>62</v>
+      </c>
+      <c r="B59" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="C59" s="31" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="60" s="6" customFormat="1" spans="1:9">
+      <c r="A60" s="6">
+        <v>63</v>
+      </c>
+      <c r="B60" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="C60" s="6" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="61" s="6" customFormat="1" spans="1:9">
+      <c r="A61" s="6">
+        <v>64</v>
+      </c>
+      <c r="B61" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="C61" s="34" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="62" s="6" customFormat="1" spans="1:9">
+      <c r="A62" s="6">
+        <v>65</v>
+      </c>
+      <c r="B62" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="C62" s="34" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="63" s="7" customFormat="1" spans="1:9">
+      <c r="A63" s="7">
+        <v>70</v>
+      </c>
+      <c r="B63" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="C63" s="35" t="s">
+        <v>126</v>
+      </c>
+      <c r="D63" s="35"/>
+    </row>
+    <row r="64" s="7" customFormat="1" spans="1:9">
+      <c r="A64" s="7">
+        <v>71</v>
+      </c>
+      <c r="B64" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="C64" s="35"/>
+      <c r="D64" s="35">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="65" s="7" customFormat="1" spans="1:20">
+      <c r="A65" s="7">
+        <v>72</v>
+      </c>
+      <c r="B65" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="C65" s="35" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="66" spans="1:20">
+      <c r="A66" s="36">
+        <v>80</v>
+      </c>
+      <c r="B66" s="36" t="s">
+        <v>130</v>
+      </c>
+      <c r="C66" s="36"/>
+      <c r="D66" s="36">
+        <v>259200</v>
+      </c>
+      <c r="E66" s="11"/>
+      <c r="F66" s="11"/>
+      <c r="G66" s="11"/>
+      <c r="H66" s="11"/>
+      <c r="I66" s="11"/>
+      <c r="J66" s="11"/>
+      <c r="K66" s="11"/>
+      <c r="L66" s="11"/>
+      <c r="M66" s="11"/>
+      <c r="N66" s="11"/>
+      <c r="O66" s="11"/>
+      <c r="P66" s="11"/>
+      <c r="Q66" s="11"/>
+      <c r="R66" s="11"/>
+      <c r="S66" s="11"/>
+      <c r="T66" s="11"/>
+    </row>
+    <row r="67" s="1" customFormat="1" spans="1:20">
+      <c r="A67" s="1">
+        <v>90</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="D67" s="1">
+        <v>150000</v>
+      </c>
+    </row>
+    <row r="68" spans="1:20">
+      <c r="A68" s="8">
+        <v>100</v>
+      </c>
+      <c r="B68" s="8" t="s">
+        <v>132</v>
+      </c>
+      <c r="C68" s="8" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="69" spans="1:20">
+      <c r="A69" s="8">
+        <v>101</v>
+      </c>
+      <c r="B69" s="8" t="s">
+        <v>134</v>
+      </c>
+      <c r="C69" s="8" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="70" spans="1:20">
+      <c r="A70" s="8">
+        <v>102</v>
+      </c>
+      <c r="B70" s="8" t="s">
+        <v>136</v>
+      </c>
+      <c r="D70" s="37">
+        <v>1022503</v>
+      </c>
+    </row>
+    <row r="71" s="4" customFormat="1" spans="1:20">
+      <c r="A71" s="4">
         <v>110</v>
       </c>
-      <c r="C56" s="3" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="57" s="1" customFormat="1" spans="1:9">
-      <c r="A57" s="1">
-        <v>60</v>
-      </c>
-      <c r="B57" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="C57" s="23" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="58" spans="1:9">
-      <c r="A58" s="3">
-        <v>61</v>
-      </c>
-      <c r="B58" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="C58" s="24" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="59" spans="1:9">
-      <c r="A59" s="3">
-        <v>62</v>
-      </c>
-      <c r="B59" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="C59" s="12" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="60" spans="1:9">
-      <c r="A60" s="3">
-        <v>63</v>
-      </c>
-      <c r="B60" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="C60" s="3" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="61" spans="1:9">
-      <c r="A61" s="3">
-        <v>64</v>
-      </c>
-      <c r="B61" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="C61" s="17" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="62" spans="1:9">
-      <c r="A62" s="3">
-        <v>65</v>
-      </c>
-      <c r="B62" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="C62" s="17" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="63" spans="1:9">
-      <c r="A63" s="3">
-        <v>70</v>
-      </c>
-      <c r="B63" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="C63" s="17" t="s">
-        <v>125</v>
-      </c>
-      <c r="D63" s="17"/>
-    </row>
-    <row r="64" spans="1:9">
-      <c r="A64" s="3">
-        <v>71</v>
-      </c>
-      <c r="B64" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="C64" s="17"/>
-      <c r="D64" s="17">
-        <v>5000</v>
-      </c>
-    </row>
-    <row r="65" spans="1:20">
-      <c r="A65" s="3">
-        <v>72</v>
-      </c>
-      <c r="B65" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="C65" s="17" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="66" spans="1:20">
-      <c r="A66" s="25">
-        <v>80</v>
-      </c>
-      <c r="B66" s="25" t="s">
-        <v>129</v>
-      </c>
-      <c r="C66" s="25"/>
-      <c r="D66" s="25">
-        <v>259200</v>
-      </c>
-      <c r="E66" s="6"/>
-      <c r="F66" s="6"/>
-      <c r="G66" s="6"/>
-      <c r="H66" s="6"/>
-      <c r="I66" s="6"/>
-      <c r="J66" s="6"/>
-      <c r="K66" s="6"/>
-      <c r="L66" s="6"/>
-      <c r="M66" s="6"/>
-      <c r="N66" s="6"/>
-      <c r="O66" s="6"/>
-      <c r="P66" s="6"/>
-      <c r="Q66" s="6"/>
-      <c r="R66" s="6"/>
-      <c r="S66" s="6"/>
-      <c r="T66" s="6"/>
-    </row>
-    <row r="67" spans="1:20">
-      <c r="A67" s="3">
-        <v>90</v>
-      </c>
-      <c r="B67" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="D67" s="3">
-        <v>100000</v>
-      </c>
-    </row>
-    <row r="68" spans="1:20">
-      <c r="A68" s="3">
-        <v>100</v>
-      </c>
-      <c r="B68" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="C68" s="3" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="69" spans="1:20">
-      <c r="A69" s="3">
-        <v>101</v>
-      </c>
-      <c r="B69" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="C69" s="3" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="70" spans="1:20">
-      <c r="A70" s="3">
-        <v>102</v>
-      </c>
-      <c r="B70" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="D70" s="26">
-        <v>1022503</v>
-      </c>
-    </row>
-    <row r="71" spans="1:20">
-      <c r="A71" s="3">
-        <v>110</v>
-      </c>
-      <c r="B71" s="21" t="s">
-        <v>136</v>
-      </c>
-      <c r="D71" s="17">
+      <c r="B71" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="D71" s="26">
         <f>8400</f>
         <v>8400</v>
       </c>
     </row>
     <row r="72" spans="1:20">
-      <c r="A72" s="3">
+      <c r="A72" s="8">
         <v>111</v>
       </c>
-      <c r="B72" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="D72" s="3">
+      <c r="B72" s="8" t="s">
+        <v>138</v>
+      </c>
+      <c r="D72" s="8">
         <v>500</v>
       </c>
     </row>
     <row r="73" spans="1:20">
-      <c r="A73" s="3">
+      <c r="A73" s="8">
         <v>112</v>
       </c>
-      <c r="B73" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="D73" s="3">
+      <c r="B73" s="8" t="s">
+        <v>139</v>
+      </c>
+      <c r="D73" s="8">
         <v>300000</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="C57" r:id="rId3" display="https://aws-s3-jjg-asset-bucket.s3.ap-southeast-1.amazonaws.com/tanchuang_res/english/tc_sc_1.png" tooltip="https://aws-s3-jjg-asset-bucket.s3.ap-southeast-1.amazonaws.com/tanchuang_res/english/tc_sc_1.png"/>
+    <hyperlink ref="C58" r:id="rId4" display="https://chat.kinghush.com/privacy.html"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/gm/resources/sample/global.xlsx
+++ b/gm/resources/sample/global.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="11925"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="globalConfig" sheetId="1" r:id="rId1"/>
@@ -318,7 +318,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="142">
   <si>
     <t>sid</t>
   </si>
@@ -452,7 +452,10 @@
     <t>我的赌场清除CD价值，每X秒需要Y钻石（道具ID_道具数量_单位时间秒）</t>
   </si>
   <si>
-    <t>1980000_1_60</t>
+    <t>1980000_500_60</t>
+  </si>
+  <si>
+    <t>钻石和金币等价，30000金币等于1$，设1分钟=0.02$=0.14￥=0.02*30000=600</t>
   </si>
   <si>
     <t>默认邮件有效期（秒）</t>
@@ -461,7 +464,10 @@
     <t>我的赌场购买一键领取的消耗（道具ID_道具数量_持续时间分钟）</t>
   </si>
   <si>
-    <t>1980000_200_1440</t>
+    <t>1980000_3000_1440</t>
+  </si>
+  <si>
+    <t>钻石和金币等价，30000金币等于1$，设1分钟=0.001$=0.007￥=1*0.001*30000=30</t>
   </si>
   <si>
     <t>收藏游戏数量上限</t>
@@ -599,7 +605,7 @@
     <t>VIP充值：充值金额与经验转换比例(充值金额_获得vip经验，最低支持0.01_1，美元)</t>
   </si>
   <si>
-    <t>1_10</t>
+    <t>1_30000</t>
   </si>
   <si>
     <t>积分大奖：实物奖励兑换码过期时间（天）</t>
@@ -692,7 +698,7 @@
     <t>推广分享：有效用户达标条件（有效下注累计_数值|累计充值_数值）</t>
   </si>
   <si>
-    <t>AND(totalValidBets(4200000),totalRecharge(7,0))</t>
+    <t>AND(totalValidBets(4200000),totalRecharge(10,0))</t>
   </si>
   <si>
     <t>财富轮盘：昨日输的金币兑换为积分的比例（昨日所输金币_获得积分）</t>
@@ -959,12 +965,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -2117,7 +2123,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="17" spans="1:7">
+    <row r="17" spans="1:12">
       <c r="A17" s="8">
         <v>13</v>
       </c>
@@ -2128,7 +2134,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:7">
+    <row r="18" spans="1:12">
       <c r="A18" s="8">
         <v>14</v>
       </c>
@@ -2142,7 +2148,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="19" spans="1:7">
+    <row r="19" spans="1:12">
       <c r="A19" s="8">
         <v>15</v>
       </c>
@@ -2153,7 +2159,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="20" spans="1:7">
+    <row r="20" spans="1:12">
       <c r="A20" s="8">
         <v>16</v>
       </c>
@@ -2164,7 +2170,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="21" spans="1:7">
+    <row r="21" spans="1:12">
       <c r="A21" s="8">
         <v>17</v>
       </c>
@@ -2174,137 +2180,147 @@
       <c r="C21" s="8" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="22" spans="1:7">
+      <c r="G21" s="8" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12">
       <c r="A22" s="8">
         <v>18</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D22" s="8">
         <f>7*24*60*60</f>
         <v>604800</v>
       </c>
     </row>
-    <row r="23" spans="1:7">
+    <row r="23" spans="1:12">
       <c r="A23" s="8">
         <v>19</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7">
+        <v>48</v>
+      </c>
+      <c r="G23" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="L23" s="8">
+        <f>60*24*30</f>
+        <v>43200</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12">
       <c r="A24" s="8">
         <v>20</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D24" s="8">
         <v>10</v>
       </c>
     </row>
-    <row r="25" s="1" customFormat="1" spans="1:7">
+    <row r="25" s="1" customFormat="1" spans="1:12">
       <c r="A25" s="1">
         <v>21</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C25" s="17" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="26" s="1" customFormat="1" spans="1:7">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="26" s="1" customFormat="1" spans="1:12">
       <c r="A26" s="1">
         <v>22</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="27" s="1" customFormat="1" spans="1:7">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="27" s="1" customFormat="1" spans="1:12">
       <c r="A27" s="1">
         <v>23</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D27" s="1">
         <v>10000</v>
       </c>
     </row>
-    <row r="28" s="1" customFormat="1" spans="1:7">
+    <row r="28" s="1" customFormat="1" spans="1:12">
       <c r="A28" s="1">
         <v>24</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D28" s="1">
         <v>100</v>
       </c>
     </row>
-    <row r="29" s="1" customFormat="1" spans="1:7">
+    <row r="29" s="1" customFormat="1" spans="1:12">
       <c r="A29" s="1">
         <v>25</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12">
       <c r="A30" s="8">
         <v>26</v>
       </c>
       <c r="B30" s="8" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C30" s="18"/>
       <c r="D30" s="8">
         <v>100</v>
       </c>
     </row>
-    <row r="31" spans="1:7">
+    <row r="31" spans="1:12">
       <c r="A31" s="8">
         <v>27</v>
       </c>
       <c r="B31" s="8" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D31" s="8">
         <v>10000</v>
       </c>
       <c r="G31" s="8" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12">
       <c r="A32" s="8">
         <v>28</v>
       </c>
       <c r="B32" s="8" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C32" s="8" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="33" spans="1:23">
@@ -2312,7 +2328,7 @@
         <v>29</v>
       </c>
       <c r="B33" s="8" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D33" s="8">
         <v>10</v>
@@ -2323,10 +2339,10 @@
         <v>30</v>
       </c>
       <c r="B34" s="19" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
     <row r="35" s="2" customFormat="1" spans="1:23">
@@ -2334,32 +2350,32 @@
         <v>31</v>
       </c>
       <c r="B35" s="19" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="E35" s="20">
         <v>372460972.440945</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H35" s="20">
         <v>8692.20472440945</v>
       </c>
       <c r="I35" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="J35" s="2">
         <v>1</v>
       </c>
       <c r="K35" s="2" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="L35" s="2">
         <f>J35*24*60*60*1000</f>
         <v>86400000</v>
       </c>
       <c r="M35" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="36" spans="1:23">
@@ -2367,10 +2383,10 @@
         <v>32</v>
       </c>
       <c r="B36" s="19" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
     </row>
     <row r="37" spans="1:23">
@@ -2378,10 +2394,10 @@
         <v>33</v>
       </c>
       <c r="B37" s="21" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C37" s="22" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="38" s="3" customFormat="1" spans="1:23">
@@ -2389,13 +2405,13 @@
         <v>34</v>
       </c>
       <c r="B38" s="23" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G38" s="3" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="H38" s="3">
         <v>90</v>
@@ -2406,32 +2422,32 @@
         <v>35</v>
       </c>
       <c r="B39" s="21" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C39" s="8" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G39" s="8" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="H39" s="24">
         <f>ROUND(L35/(E35*H38/100/H35),0)</f>
         <v>2240</v>
       </c>
       <c r="I39" s="8" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="J39" s="8" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="K39" s="25" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="L39" s="25">
         <v>0.25</v>
       </c>
       <c r="M39" s="8" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="N39" s="8">
         <f>ROUND(P39*(1+2*L39),0)</f>
@@ -2479,7 +2495,7 @@
         <v>40</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D40" s="26">
         <v>88</v>
@@ -2490,7 +2506,7 @@
         <v>41</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D41" s="26">
         <v>1200</v>
@@ -2501,7 +2517,7 @@
         <v>42</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="D42" s="26">
         <v>36000</v>
@@ -2512,7 +2528,7 @@
         <v>43</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D43" s="26">
         <v>1</v>
@@ -2523,7 +2539,7 @@
         <v>44</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D44" s="26">
         <v>10</v>
@@ -2534,10 +2550,10 @@
         <v>45</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C45" s="26" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="46" s="5" customFormat="1" spans="1:23">
@@ -2545,10 +2561,10 @@
         <v>46</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C46" s="27" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
     </row>
     <row r="47" s="4" customFormat="1" spans="1:23">
@@ -2556,13 +2572,13 @@
         <v>47</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D47" s="4">
         <v>3</v>
       </c>
       <c r="H47" s="4" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="I47" s="4">
         <v>6000</v>
@@ -2573,16 +2589,16 @@
         <v>48</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="G48" s="4" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="H48" s="4" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I48" s="4">
         <v>30</v>
@@ -2597,13 +2613,13 @@
         <v>49</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="H49" s="4" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="I49" s="4">
         <v>15</v>
@@ -2614,10 +2630,10 @@
         <v>50</v>
       </c>
       <c r="B50" s="8" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C50" s="28" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="I50" s="8">
         <v>600</v>
@@ -2628,10 +2644,10 @@
         <v>51</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C51" s="29" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="I51" s="2">
         <v>1200</v>
@@ -2642,7 +2658,7 @@
         <v>52</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="D52" s="30">
         <v>30000</v>
@@ -2653,7 +2669,7 @@
         <v>53</v>
       </c>
       <c r="B53" s="6" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="D53" s="31">
         <v>30000</v>
@@ -2664,7 +2680,7 @@
         <v>54</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="D54" s="5">
         <v>0</v>
@@ -2675,7 +2691,7 @@
         <v>55</v>
       </c>
       <c r="B55" s="8" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C55" s="8"/>
       <c r="D55" s="8">
@@ -2687,10 +2703,10 @@
         <v>56</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C56" s="5" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="57" s="2" customFormat="1" spans="1:9">
@@ -2698,10 +2714,10 @@
         <v>60</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C57" s="32" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="58" spans="1:9">
@@ -2709,10 +2725,10 @@
         <v>61</v>
       </c>
       <c r="B58" s="8" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C58" s="33" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="59" s="6" customFormat="1" spans="1:9">
@@ -2720,10 +2736,10 @@
         <v>62</v>
       </c>
       <c r="B59" s="6" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C59" s="31" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="60" s="6" customFormat="1" spans="1:9">
@@ -2731,10 +2747,10 @@
         <v>63</v>
       </c>
       <c r="B60" s="6" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C60" s="6" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="61" s="6" customFormat="1" spans="1:9">
@@ -2742,10 +2758,10 @@
         <v>64</v>
       </c>
       <c r="B61" s="6" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C61" s="34" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="62" s="6" customFormat="1" spans="1:9">
@@ -2753,10 +2769,10 @@
         <v>65</v>
       </c>
       <c r="B62" s="6" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C62" s="34" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
     </row>
     <row r="63" s="7" customFormat="1" spans="1:9">
@@ -2764,10 +2780,10 @@
         <v>70</v>
       </c>
       <c r="B63" s="7" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C63" s="35" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D63" s="35"/>
     </row>
@@ -2776,7 +2792,7 @@
         <v>71</v>
       </c>
       <c r="B64" s="7" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C64" s="35"/>
       <c r="D64" s="35">
@@ -2788,10 +2804,10 @@
         <v>72</v>
       </c>
       <c r="B65" s="7" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C65" s="35" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="66" spans="1:20">
@@ -2799,7 +2815,7 @@
         <v>80</v>
       </c>
       <c r="B66" s="36" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C66" s="36"/>
       <c r="D66" s="36">
@@ -2827,7 +2843,7 @@
         <v>90</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D67" s="1">
         <v>150000</v>
@@ -2838,10 +2854,10 @@
         <v>100</v>
       </c>
       <c r="B68" s="8" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C68" s="8" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="69" spans="1:20">
@@ -2849,10 +2865,10 @@
         <v>101</v>
       </c>
       <c r="B69" s="8" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C69" s="8" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="70" spans="1:20">
@@ -2860,7 +2876,7 @@
         <v>102</v>
       </c>
       <c r="B70" s="8" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="D70" s="37">
         <v>1022503</v>
@@ -2871,7 +2887,7 @@
         <v>110</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="D71" s="26">
         <f>8400</f>
@@ -2883,7 +2899,7 @@
         <v>111</v>
       </c>
       <c r="B72" s="8" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="D72" s="8">
         <v>500</v>
@@ -2894,7 +2910,7 @@
         <v>112</v>
       </c>
       <c r="B73" s="8" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="D73" s="8">
         <v>300000</v>

--- a/gm/resources/sample/global.xlsx
+++ b/gm/resources/sample/global.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="11925"/>
   </bookViews>
   <sheets>
     <sheet name="globalConfig" sheetId="1" r:id="rId1"/>
@@ -2509,7 +2509,7 @@
         <v>88</v>
       </c>
       <c r="D41" s="26">
-        <v>1200</v>
+        <v>600</v>
       </c>
     </row>
     <row r="42" s="4" customFormat="1" spans="1:23">
@@ -2520,7 +2520,7 @@
         <v>89</v>
       </c>
       <c r="D42" s="26">
-        <v>36000</v>
+        <v>18000</v>
       </c>
     </row>
     <row r="43" s="4" customFormat="1" spans="1:23">
@@ -2890,8 +2890,7 @@
         <v>139</v>
       </c>
       <c r="D71" s="26">
-        <f>8400</f>
-        <v>8400</v>
+        <v>4200</v>
       </c>
     </row>
     <row r="72" spans="1:20">

--- a/gm/resources/sample/global.xlsx
+++ b/gm/resources/sample/global.xlsx
@@ -164,7 +164,7 @@
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
-为空时表示不开此活动</t>
+值为空，表示不开启该活动</t>
         </r>
       </text>
     </comment>
@@ -208,8 +208,7 @@
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
-值为0表示不返利
-</t>
+值为0表示不返利</t>
         </r>
       </text>
     </comment>
@@ -318,7 +317,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="139">
   <si>
     <t>sid</t>
   </si>
@@ -452,10 +451,7 @@
     <t>我的赌场清除CD价值，每X秒需要Y钻石（道具ID_道具数量_单位时间秒）</t>
   </si>
   <si>
-    <t>1980000_500_60</t>
-  </si>
-  <si>
-    <t>钻石和金币等价，30000金币等于1$，设1分钟=0.02$=0.14￥=0.02*30000=600</t>
+    <t>1980000_1_60</t>
   </si>
   <si>
     <t>默认邮件有效期（秒）</t>
@@ -464,10 +460,7 @@
     <t>我的赌场购买一键领取的消耗（道具ID_道具数量_持续时间分钟）</t>
   </si>
   <si>
-    <t>1980000_3000_1440</t>
-  </si>
-  <si>
-    <t>钻石和金币等价，30000金币等于1$，设1分钟=0.001$=0.007￥=1*0.001*30000=30</t>
+    <t>1980000_200_1440</t>
   </si>
   <si>
     <t>收藏游戏数量上限</t>
@@ -476,7 +469,7 @@
     <t>摇钱树活动增长金额</t>
   </si>
   <si>
-    <t>0_12_5000_10000|12_24_5000_10000</t>
+    <t>0_12_100_250|12_24_100_250</t>
   </si>
   <si>
     <t>开始时间/时_结束时间/时（左闭右开）_每次增长值_每次增长下限|</t>
@@ -503,7 +496,7 @@
     <t>1022501_1</t>
   </si>
   <si>
-    <t>储钱罐：每次下注金币的万分比飞入储钱罐</t>
+    <t>每次下注金币的万分比飞入储钱罐</t>
   </si>
   <si>
     <t>创建房间-房间销毁时房主获得实际准备金的万分比</t>
@@ -551,13 +544,13 @@
     <t>官方派奖：充值转换积分比例 ：充值金额（290,000 越南盾 = 1 积分 )</t>
   </si>
   <si>
-    <t>1_1</t>
+    <t>208000_1</t>
   </si>
   <si>
     <t>官方派奖：转盘1次数_转盘2次数_转盘3次数（真人抽奖后机器人跟着的抽奖次数，填10，表示玩家抽1次，机器人抽10次）</t>
   </si>
   <si>
-    <t>1_1_1</t>
+    <t>99_99_99</t>
   </si>
   <si>
     <t>机器人奖池比例</t>
@@ -605,7 +598,7 @@
     <t>VIP充值：充值金额与经验转换比例(充值金额_获得vip经验，最低支持0.01_1，美元)</t>
   </si>
   <si>
-    <t>1_30000</t>
+    <t>1_10</t>
   </si>
   <si>
     <t>积分大奖：实物奖励兑换码过期时间（天）</t>
@@ -638,9 +631,6 @@
     <t>新手奖励</t>
   </si>
   <si>
-    <t>1990000_21400</t>
-  </si>
-  <si>
     <t>手机短信区号（印度、巴基斯坦、菲律宾、巴西、尼日利亚）废弃</t>
   </si>
   <si>
@@ -674,13 +664,13 @@
     <t>隐私政策链接</t>
   </si>
   <si>
-    <t>https://chat.kinghush.com/privacy.html</t>
+    <t>http://chat.kinghush.com/privacy.html</t>
   </si>
   <si>
     <t>推广分享：分享1人得固定奖励</t>
   </si>
   <si>
-    <t>1990000_42000</t>
+    <t>1990000_100000</t>
   </si>
   <si>
     <t>推广分享：二维码图片配置(该资源放在资源服务器实时下载显示的)</t>
@@ -692,19 +682,19 @@
     <t>推广分享：周榜上榜条件设置(收益数量)</t>
   </si>
   <si>
-    <t>1990000_750000</t>
+    <t>1990000_4000000</t>
   </si>
   <si>
     <t>推广分享：有效用户达标条件（有效下注累计_数值|累计充值_数值）</t>
   </si>
   <si>
-    <t>AND(totalValidBets(4200000),totalRecharge(10,0))</t>
+    <t>AND(totalValidBets(2000000),totalRecharge(100000,0))</t>
   </si>
   <si>
     <t>财富轮盘：昨日输的金币兑换为积分的比例（昨日所输金币_获得积分）</t>
   </si>
   <si>
-    <t>125_1</t>
+    <t>2000_1</t>
   </si>
   <si>
     <t>财富轮盘：每次抽奖所消耗的积分</t>
@@ -767,18 +757,18 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="微软雅黑"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color theme="0" tint="-0.249977111117893"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
@@ -976,7 +966,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="38">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -985,42 +975,18 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -1178,12 +1144,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1345,7 +1305,7 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1369,16 +1329,16 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -1387,31 +1347,43 @@
     <xf numFmtId="0" fontId="23" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="28" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="28" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1447,89 +1419,66 @@
     <xf numFmtId="0" fontId="27" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="28" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="28" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="6" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" quotePrefix="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" quotePrefix="1">
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" quotePrefix="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" quotePrefix="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1854,1071 +1803,1059 @@
   <dimension ref="A1:W73"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
-    <col min="1" max="1" width="9" style="8"/>
-    <col min="2" max="2" width="96.9083333333333" style="8" customWidth="1"/>
-    <col min="3" max="4" width="28.375" style="8" customWidth="1"/>
-    <col min="5" max="5" width="11.5" style="8" customWidth="1"/>
-    <col min="6" max="6" width="9.625" style="8" customWidth="1"/>
-    <col min="7" max="7" width="23.375" style="8" customWidth="1"/>
-    <col min="8" max="8" width="12.75" style="8"/>
-    <col min="9" max="10" width="14.125" style="8"/>
-    <col min="11" max="11" width="9" style="8"/>
-    <col min="12" max="12" width="12.875" style="8"/>
-    <col min="13" max="13" width="9" style="8"/>
-    <col min="14" max="17" width="10.375" style="8"/>
-    <col min="18" max="18" width="9.25" style="8"/>
-    <col min="19" max="16384" width="9" style="8"/>
+    <col min="1" max="1" width="9" style="3"/>
+    <col min="2" max="2" width="96.9083333333333" style="3" customWidth="1"/>
+    <col min="3" max="4" width="28.375" style="3" customWidth="1"/>
+    <col min="5" max="5" width="11.5" style="3" customWidth="1"/>
+    <col min="6" max="6" width="9.625" style="3" customWidth="1"/>
+    <col min="7" max="7" width="23.375" style="3" customWidth="1"/>
+    <col min="8" max="8" width="12.75" style="3"/>
+    <col min="9" max="10" width="14.125" style="3"/>
+    <col min="11" max="11" width="9" style="3"/>
+    <col min="12" max="12" width="12.875" style="3"/>
+    <col min="13" max="13" width="9" style="3"/>
+    <col min="14" max="17" width="10.375" style="3"/>
+    <col min="18" max="18" width="9.25" style="3"/>
+    <col min="19" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10" t="s">
+      <c r="B1" s="5"/>
+      <c r="C1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="10" t="s">
+      <c r="D1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="10" t="s">
+      <c r="E1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="10" t="s">
+      <c r="F1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="10" t="s">
+      <c r="G1" s="5" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="11" t="s">
+      <c r="A2" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="10"/>
-      <c r="C2" s="10" t="s">
+      <c r="B2" s="5"/>
+      <c r="C2" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="12" t="s">
+      <c r="D2" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="E2" s="8" t="s">
+      <c r="E2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F2" s="10" t="s">
+      <c r="F2" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="G2" s="10"/>
+      <c r="G2" s="5"/>
     </row>
     <row r="3" spans="1:7">
-      <c r="A3" s="9" t="s">
+      <c r="A3" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="10"/>
-      <c r="C3" s="10" t="s">
+      <c r="B3" s="5"/>
+      <c r="C3" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="8" t="s">
+      <c r="D3" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="8" t="s">
+      <c r="E3" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="F3" s="8" t="s">
+      <c r="F3" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="G3" s="10"/>
+      <c r="G3" s="5"/>
     </row>
     <row r="4" spans="1:7">
-      <c r="A4" s="13"/>
-      <c r="B4" s="12"/>
-      <c r="C4" s="12"/>
-      <c r="G4" s="12"/>
+      <c r="A4" s="8"/>
+      <c r="B4" s="7"/>
+      <c r="C4" s="7"/>
+      <c r="G4" s="7"/>
     </row>
     <row r="5" spans="1:7">
-      <c r="A5" s="8">
+      <c r="A5" s="3">
         <v>1</v>
       </c>
-      <c r="B5" s="12" t="s">
+      <c r="B5" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="D5" s="12">
+      <c r="D5" s="7">
         <v>999</v>
       </c>
-      <c r="E5" s="12"/>
-      <c r="F5" s="12"/>
-      <c r="G5" s="12"/>
+      <c r="E5" s="7"/>
+      <c r="F5" s="7"/>
+      <c r="G5" s="7"/>
     </row>
     <row r="6" spans="1:7">
-      <c r="A6" s="8">
+      <c r="A6" s="3">
         <v>2</v>
       </c>
-      <c r="B6" s="12" t="s">
+      <c r="B6" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="D6" s="14">
+      <c r="D6" s="9">
+        <v>30000</v>
+      </c>
+      <c r="E6" s="7"/>
+      <c r="F6" s="7"/>
+      <c r="G6" s="7" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7" s="3">
+        <v>3</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="D7" s="7">
         <v>10000</v>
       </c>
-      <c r="E6" s="12"/>
-      <c r="F6" s="12"/>
-      <c r="G6" s="12" t="s">
+      <c r="E7" s="7"/>
+      <c r="F7" s="7"/>
+      <c r="G7" s="7" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
-      <c r="A7" s="8">
-        <v>3</v>
-      </c>
-      <c r="B7" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="D7" s="12">
-        <v>10000</v>
-      </c>
-      <c r="E7" s="12"/>
-      <c r="F7" s="12"/>
-      <c r="G7" s="12" t="s">
-        <v>17</v>
-      </c>
-    </row>
     <row r="8" spans="1:7">
-      <c r="A8" s="8">
+      <c r="A8" s="3">
         <v>4</v>
       </c>
-      <c r="B8" s="12" t="s">
+      <c r="B8" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="C8" s="12">
+      <c r="C8" s="7">
         <v>100</v>
       </c>
-      <c r="D8" s="12"/>
-      <c r="E8" s="12"/>
-      <c r="F8" s="12"/>
-      <c r="G8" s="12" t="s">
+      <c r="D8" s="7"/>
+      <c r="E8" s="7"/>
+      <c r="F8" s="7"/>
+      <c r="G8" s="7" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="9" spans="1:7">
-      <c r="A9" s="8">
+      <c r="A9" s="3">
         <v>5</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="C9" s="8">
+      <c r="C9" s="3">
         <v>4</v>
       </c>
-      <c r="G9" s="8" t="s">
+      <c r="G9" s="3" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="10" spans="1:7">
-      <c r="A10" s="8">
+      <c r="A10" s="3">
         <v>6</v>
       </c>
-      <c r="B10" s="12" t="s">
+      <c r="B10" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="C10" s="38" t="s">
+      <c r="C10" s="27" t="s">
         <v>24</v>
       </c>
-      <c r="D10" s="15"/>
-      <c r="E10" s="12"/>
-      <c r="F10" s="12"/>
-      <c r="G10" s="8" t="s">
+      <c r="D10" s="10"/>
+      <c r="E10" s="7"/>
+      <c r="F10" s="7"/>
+      <c r="G10" s="3" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="11" spans="1:7">
-      <c r="A11" s="8">
+      <c r="A11" s="3">
         <v>7</v>
       </c>
-      <c r="B11" s="12" t="s">
+      <c r="B11" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="C11" s="39" t="s">
+      <c r="C11" s="28" t="s">
         <v>27</v>
       </c>
-      <c r="D11" s="12"/>
-      <c r="E11" s="12"/>
-      <c r="F11" s="12"/>
-      <c r="G11" s="8" t="s">
+      <c r="D11" s="7"/>
+      <c r="E11" s="7"/>
+      <c r="F11" s="7"/>
+      <c r="G11" s="3" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="12" spans="1:7">
-      <c r="A12" s="8">
+      <c r="A12" s="3">
         <v>8</v>
       </c>
-      <c r="B12" s="12" t="s">
+      <c r="B12" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="C12" s="39" t="s">
+      <c r="C12" s="28" t="s">
         <v>29</v>
       </c>
-      <c r="D12" s="12"/>
-      <c r="E12" s="12"/>
-      <c r="F12" s="12"/>
-      <c r="G12" s="8" t="s">
+      <c r="D12" s="7"/>
+      <c r="E12" s="7"/>
+      <c r="F12" s="7"/>
+      <c r="G12" s="3" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="13" spans="1:7">
-      <c r="A13" s="8">
+      <c r="A13" s="3">
         <v>9</v>
       </c>
-      <c r="B13" s="12" t="s">
+      <c r="B13" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="C13" s="39" t="s">
+      <c r="C13" s="28" t="s">
         <v>31</v>
       </c>
-      <c r="D13" s="12"/>
-      <c r="E13" s="12"/>
-      <c r="F13" s="12"/>
-      <c r="G13" s="8" t="s">
+      <c r="D13" s="7"/>
+      <c r="E13" s="7"/>
+      <c r="F13" s="7"/>
+      <c r="G13" s="3" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="14" spans="1:7">
-      <c r="A14" s="8">
+      <c r="A14" s="3">
         <v>10</v>
       </c>
-      <c r="B14" s="12" t="s">
+      <c r="B14" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="C14" s="39" t="s">
+      <c r="C14" s="28" t="s">
         <v>33</v>
       </c>
-      <c r="D14" s="12"/>
-      <c r="E14" s="12"/>
-      <c r="F14" s="12"/>
-      <c r="G14" s="8" t="s">
+      <c r="D14" s="7"/>
+      <c r="E14" s="7"/>
+      <c r="F14" s="7"/>
+      <c r="G14" s="3" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="15" spans="1:7">
-      <c r="A15" s="8">
+      <c r="A15" s="3">
         <v>11</v>
       </c>
-      <c r="B15" s="8" t="s">
+      <c r="B15" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="D15" s="8">
+      <c r="D15" s="3">
         <f>2*3*5*3</f>
         <v>90</v>
       </c>
     </row>
     <row r="16" spans="1:7">
-      <c r="A16" s="8">
+      <c r="A16" s="3">
         <v>12</v>
       </c>
-      <c r="B16" s="8" t="s">
+      <c r="B16" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="D16" s="8">
+      <c r="D16" s="3">
         <v>3333</v>
       </c>
-      <c r="G16" s="8" t="s">
+      <c r="G16" s="3" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="17" spans="1:12">
-      <c r="A17" s="8">
+    <row r="17" spans="1:7">
+      <c r="A17" s="3">
         <v>13</v>
       </c>
-      <c r="B17" s="8" t="s">
+      <c r="B17" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="D17" s="8">
+      <c r="D17" s="3">
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:12">
-      <c r="A18" s="8">
+    <row r="18" spans="1:7">
+      <c r="A18" s="3">
         <v>14</v>
       </c>
-      <c r="B18" s="8" t="s">
+      <c r="B18" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C18" s="16" t="s">
+      <c r="C18" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="G18" s="8" t="s">
+      <c r="G18" s="3" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="19" spans="1:12">
-      <c r="A19" s="8">
+    <row r="19" spans="1:7">
+      <c r="A19" s="3">
         <v>15</v>
       </c>
-      <c r="B19" s="8" t="s">
+      <c r="B19" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="D19" s="8">
+      <c r="D19" s="3">
         <v>5</v>
       </c>
     </row>
-    <row r="20" spans="1:12">
-      <c r="A20" s="8">
+    <row r="20" spans="1:7">
+      <c r="A20" s="3">
         <v>16</v>
       </c>
-      <c r="B20" s="8" t="s">
+      <c r="B20" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="D20" s="8">
+      <c r="D20" s="3">
         <v>10</v>
       </c>
     </row>
-    <row r="21" spans="1:12">
-      <c r="A21" s="8">
+    <row r="21" spans="1:7">
+      <c r="A21" s="3">
         <v>17</v>
       </c>
-      <c r="B21" s="8" t="s">
+      <c r="B21" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="C21" s="8" t="s">
+      <c r="C21" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="G21" s="8" t="s">
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22" s="3">
+        <v>18</v>
+      </c>
+      <c r="B22" s="3" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="22" spans="1:12">
-      <c r="A22" s="8">
-        <v>18</v>
-      </c>
-      <c r="B22" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="D22" s="8">
+      <c r="D22" s="3">
         <f>7*24*60*60</f>
         <v>604800</v>
       </c>
     </row>
-    <row r="23" spans="1:12">
-      <c r="A23" s="8">
+    <row r="23" spans="1:7">
+      <c r="A23" s="3">
         <v>19</v>
       </c>
-      <c r="B23" s="8" t="s">
+      <c r="B23" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="C23" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="C23" s="8" t="s">
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24" s="3">
+        <v>20</v>
+      </c>
+      <c r="B24" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="G23" s="8" t="s">
+      <c r="D24" s="3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
+      <c r="A25" s="3">
+        <v>21</v>
+      </c>
+      <c r="B25" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="L23" s="8">
-        <f>60*24*30</f>
-        <v>43200</v>
-      </c>
-    </row>
-    <row r="24" spans="1:12">
-      <c r="A24" s="8">
-        <v>20</v>
-      </c>
-      <c r="B24" s="8" t="s">
+      <c r="C25" s="12" t="s">
         <v>50</v>
       </c>
-      <c r="D24" s="8">
+      <c r="G25" s="3" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7">
+      <c r="A26" s="3">
+        <v>22</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7">
+      <c r="A27" s="3">
+        <v>23</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="D27" s="3">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7">
+      <c r="A28" s="3">
+        <v>24</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="D28" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7">
+      <c r="A29" s="3">
+        <v>25</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7">
+      <c r="A30" s="3">
+        <v>26</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="C30" s="13"/>
+      <c r="D30" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7">
+      <c r="A31" s="3">
+        <v>27</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="D31" s="3">
+        <v>10000</v>
+      </c>
+      <c r="G31" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7">
+      <c r="A32" s="3">
+        <v>28</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="33" spans="1:23">
+      <c r="A33" s="3">
+        <v>29</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="D33" s="3">
         <v>10</v>
       </c>
     </row>
-    <row r="25" s="1" customFormat="1" spans="1:12">
-      <c r="A25" s="1">
-        <v>21</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="C25" s="17" t="s">
-        <v>52</v>
-      </c>
-      <c r="G25" s="1" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="26" s="1" customFormat="1" spans="1:12">
-      <c r="A26" s="1">
-        <v>22</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="G26" s="1" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="27" s="1" customFormat="1" spans="1:12">
-      <c r="A27" s="1">
-        <v>23</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="D27" s="1">
-        <v>10000</v>
-      </c>
-    </row>
-    <row r="28" s="1" customFormat="1" spans="1:12">
-      <c r="A28" s="1">
-        <v>24</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="D28" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="29" s="1" customFormat="1" spans="1:12">
-      <c r="A29" s="1">
-        <v>25</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="C29" s="1" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="30" spans="1:12">
-      <c r="A30" s="8">
-        <v>26</v>
-      </c>
-      <c r="B30" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="C30" s="18"/>
-      <c r="D30" s="8">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="31" spans="1:12">
-      <c r="A31" s="8">
-        <v>27</v>
-      </c>
-      <c r="B31" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="D31" s="8">
-        <v>10000</v>
-      </c>
-      <c r="G31" s="8" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="32" spans="1:12">
-      <c r="A32" s="8">
-        <v>28</v>
-      </c>
-      <c r="B32" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="C32" s="8" t="s">
+    <row r="34" s="1" customFormat="1" spans="1:23">
+      <c r="A34" s="14">
+        <v>30</v>
+      </c>
+      <c r="B34" s="14" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="33" spans="1:23">
-      <c r="A33" s="8">
-        <v>29</v>
-      </c>
-      <c r="B33" s="8" t="s">
+      <c r="C34" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="D33" s="8">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="34" s="2" customFormat="1" spans="1:23">
-      <c r="A34" s="19">
-        <v>30</v>
-      </c>
-      <c r="B34" s="19" t="s">
+    </row>
+    <row r="35" s="1" customFormat="1" spans="1:23">
+      <c r="A35" s="14">
+        <v>31</v>
+      </c>
+      <c r="B35" s="14" t="s">
         <v>67</v>
       </c>
-      <c r="C34" s="2" t="s">
+      <c r="E35" s="15">
+        <v>372460972.440945</v>
+      </c>
+      <c r="G35" s="1" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="35" s="2" customFormat="1" spans="1:23">
-      <c r="A35" s="19">
-        <v>31</v>
-      </c>
-      <c r="B35" s="19" t="s">
+      <c r="H35" s="15">
+        <v>8692.20472440945</v>
+      </c>
+      <c r="I35" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="E35" s="20">
-        <v>372460972.440945</v>
-      </c>
-      <c r="G35" s="2" t="s">
+      <c r="J35" s="1">
+        <v>1</v>
+      </c>
+      <c r="K35" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="H35" s="20">
-        <v>8692.20472440945</v>
-      </c>
-      <c r="I35" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="J35" s="2">
-        <v>1</v>
-      </c>
-      <c r="K35" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="L35" s="2">
+      <c r="L35" s="1">
         <f>J35*24*60*60*1000</f>
         <v>86400000</v>
       </c>
-      <c r="M35" s="2" t="s">
+      <c r="M35" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="36" spans="1:23">
+      <c r="A36" s="14">
+        <v>32</v>
+      </c>
+      <c r="B36" s="14" t="s">
+        <v>72</v>
+      </c>
+      <c r="C36" s="1" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="36" spans="1:23">
-      <c r="A36" s="19">
-        <v>32</v>
-      </c>
-      <c r="B36" s="19" t="s">
+    <row r="37" spans="1:23">
+      <c r="A37" s="16">
+        <v>33</v>
+      </c>
+      <c r="B37" s="16" t="s">
         <v>74</v>
       </c>
-      <c r="C36" s="2" t="s">
+      <c r="C37" s="17" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="37" spans="1:23">
-      <c r="A37" s="21">
-        <v>33</v>
-      </c>
-      <c r="B37" s="21" t="s">
+    <row r="38" s="2" customFormat="1" spans="1:23">
+      <c r="A38" s="18">
+        <v>34</v>
+      </c>
+      <c r="B38" s="18" t="s">
         <v>76</v>
       </c>
-      <c r="C37" s="22" t="s">
+      <c r="C38" s="2" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="38" s="3" customFormat="1" spans="1:23">
-      <c r="A38" s="23">
-        <v>34</v>
-      </c>
-      <c r="B38" s="23" t="s">
+      <c r="G38" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="C38" s="3" t="s">
+      <c r="H38" s="2">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="39" spans="1:23">
+      <c r="A39" s="16">
+        <v>35</v>
+      </c>
+      <c r="B39" s="16" t="s">
         <v>79</v>
       </c>
-      <c r="G38" s="3" t="s">
+      <c r="C39" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="H38" s="3">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="39" spans="1:23">
-      <c r="A39" s="21">
-        <v>35</v>
-      </c>
-      <c r="B39" s="21" t="s">
+      <c r="G39" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="C39" s="8" t="s">
-        <v>82</v>
-      </c>
-      <c r="G39" s="8" t="s">
-        <v>83</v>
-      </c>
-      <c r="H39" s="24">
+      <c r="H39" s="19">
         <f>ROUND(L35/(E35*H38/100/H35),0)</f>
         <v>2240</v>
       </c>
-      <c r="I39" s="8" t="s">
-        <v>73</v>
-      </c>
-      <c r="J39" s="8" t="s">
+      <c r="I39" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="J39" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="K39" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="L39" s="20">
+        <v>0.25</v>
+      </c>
+      <c r="M39" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="K39" s="25" t="s">
-        <v>85</v>
-      </c>
-      <c r="L39" s="25">
-        <v>0.25</v>
-      </c>
-      <c r="M39" s="8" t="s">
-        <v>86</v>
-      </c>
-      <c r="N39" s="8">
+      <c r="N39" s="3">
         <f>ROUND(P39*(1+2*L39),0)</f>
         <v>3360</v>
       </c>
-      <c r="O39" s="8">
+      <c r="O39" s="3">
         <f>ROUND(P39*(1+1*L39),0)</f>
         <v>2800</v>
       </c>
-      <c r="P39" s="8">
+      <c r="P39" s="3">
         <f>H39</f>
         <v>2240</v>
       </c>
-      <c r="Q39" s="8">
+      <c r="Q39" s="3">
         <f>ROUND(P39*(1-1*L39),0)</f>
         <v>1680</v>
       </c>
-      <c r="R39" s="8">
+      <c r="R39" s="3">
         <f>ROUND(P39*(1-2*L39),0)</f>
         <v>1120</v>
       </c>
-      <c r="S39" s="8" t="str">
+      <c r="S39" s="3" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,N39,1000)</f>
         <v>3360_1000</v>
       </c>
-      <c r="T39" s="8" t="str">
+      <c r="T39" s="3" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,O39,1000)</f>
         <v>2800_1000</v>
       </c>
-      <c r="U39" s="8" t="str">
+      <c r="U39" s="3" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,P39,1000)</f>
         <v>2240_1000</v>
       </c>
-      <c r="V39" s="8" t="str">
+      <c r="V39" s="3" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,Q39,1000)</f>
         <v>1680_1000</v>
       </c>
-      <c r="W39" s="8" t="str">
+      <c r="W39" s="3" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,R39,1000)</f>
         <v>1120_1000</v>
       </c>
     </row>
-    <row r="40" s="4" customFormat="1" spans="1:23">
-      <c r="A40" s="4">
+    <row r="40" spans="1:23">
+      <c r="A40" s="21">
         <v>40</v>
       </c>
-      <c r="B40" s="4" t="s">
+      <c r="B40" s="21" t="s">
+        <v>85</v>
+      </c>
+      <c r="D40" s="17">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="41" spans="1:23">
+      <c r="A41" s="21">
+        <v>41</v>
+      </c>
+      <c r="B41" s="21" t="s">
+        <v>86</v>
+      </c>
+      <c r="D41" s="17">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="42" spans="1:23">
+      <c r="A42" s="21">
+        <v>42</v>
+      </c>
+      <c r="B42" s="21" t="s">
         <v>87</v>
       </c>
-      <c r="D40" s="26">
+      <c r="D42" s="17">
+        <v>36000</v>
+      </c>
+    </row>
+    <row r="43" spans="1:23">
+      <c r="A43" s="21">
+        <v>43</v>
+      </c>
+      <c r="B43" s="21" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="41" s="4" customFormat="1" spans="1:23">
-      <c r="A41" s="4">
-        <v>41</v>
-      </c>
-      <c r="B41" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="D41" s="26">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="42" s="4" customFormat="1" spans="1:23">
-      <c r="A42" s="4">
-        <v>42</v>
-      </c>
-      <c r="B42" s="4" t="s">
+      <c r="D43" s="17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:23">
+      <c r="A44" s="21">
+        <v>44</v>
+      </c>
+      <c r="B44" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="D42" s="26">
-        <v>18000</v>
-      </c>
-    </row>
-    <row r="43" s="4" customFormat="1" spans="1:23">
-      <c r="A43" s="4">
-        <v>43</v>
-      </c>
-      <c r="B43" s="4" t="s">
+      <c r="D44" s="17">
+        <v>290000</v>
+      </c>
+    </row>
+    <row r="45" spans="1:23">
+      <c r="A45" s="21">
+        <v>45</v>
+      </c>
+      <c r="B45" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="D43" s="26">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="44" s="4" customFormat="1" spans="1:23">
-      <c r="A44" s="4">
-        <v>44</v>
-      </c>
-      <c r="B44" s="4" t="s">
+      <c r="C45" s="17" t="s">
         <v>91</v>
       </c>
-      <c r="D44" s="26">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="45" s="4" customFormat="1" spans="1:23">
-      <c r="A45" s="4">
-        <v>45</v>
-      </c>
-      <c r="B45" s="4" t="s">
+    </row>
+    <row r="46" spans="1:23">
+      <c r="A46" s="3">
+        <v>46</v>
+      </c>
+      <c r="B46" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="C45" s="26" t="s">
+      <c r="C46" s="17" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="46" s="5" customFormat="1" spans="1:23">
-      <c r="A46" s="5">
-        <v>46</v>
-      </c>
-      <c r="B46" s="5" t="s">
+    <row r="47" spans="1:23">
+      <c r="A47" s="3">
+        <v>47</v>
+      </c>
+      <c r="B47" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="C46" s="27" t="s">
+      <c r="D47" s="3">
+        <v>3</v>
+      </c>
+      <c r="H47" s="3" t="s">
         <v>95</v>
       </c>
-    </row>
-    <row r="47" s="4" customFormat="1" spans="1:23">
-      <c r="A47" s="4">
-        <v>47</v>
-      </c>
-      <c r="B47" s="4" t="s">
+      <c r="I47" s="3">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="48" spans="1:23">
+      <c r="A48" s="3">
+        <v>48</v>
+      </c>
+      <c r="B48" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="D47" s="4">
-        <v>3</v>
-      </c>
-      <c r="H47" s="4" t="s">
+      <c r="C48" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="I47" s="4">
-        <v>6000</v>
-      </c>
-    </row>
-    <row r="48" s="4" customFormat="1" spans="1:23">
-      <c r="A48" s="4">
-        <v>48</v>
-      </c>
-      <c r="B48" s="4" t="s">
+      <c r="G48" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="C48" s="4" t="s">
+      <c r="H48" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="G48" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="H48" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="I48" s="4">
+      <c r="I48" s="3">
         <v>30</v>
       </c>
-      <c r="J48" s="4">
+      <c r="J48" s="3">
         <f>I47/(24*60/I49)*100/(I48/1+I48/1)</f>
         <v>104.166666666667</v>
       </c>
     </row>
-    <row r="49" s="4" customFormat="1" spans="1:9">
-      <c r="A49" s="4">
+    <row r="49" spans="1:9">
+      <c r="A49" s="3">
         <v>49</v>
       </c>
-      <c r="B49" s="4" t="s">
+      <c r="B49" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="C49" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="H49" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="C49" s="4" t="s">
+      <c r="I49" s="3">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9">
+      <c r="A50" s="3">
+        <v>50</v>
+      </c>
+      <c r="B50" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="H49" s="4" t="s">
+      <c r="C50" s="17"/>
+      <c r="I50" s="3">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="51" s="1" customFormat="1" spans="1:9">
+      <c r="A51" s="1">
+        <v>51</v>
+      </c>
+      <c r="B51" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="I49" s="4">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="50" spans="1:9">
-      <c r="A50" s="8">
-        <v>50</v>
-      </c>
-      <c r="B50" s="8" t="s">
+      <c r="C51" s="22" t="s">
         <v>105</v>
       </c>
-      <c r="C50" s="28" t="s">
+      <c r="I51" s="1">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9">
+      <c r="A52" s="3">
+        <v>52</v>
+      </c>
+      <c r="B52" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="I50" s="8">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="51" s="2" customFormat="1" spans="1:9">
-      <c r="A51" s="2">
-        <v>51</v>
-      </c>
-      <c r="B51" s="2" t="s">
+      <c r="D52" s="12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9">
+      <c r="A53" s="3">
+        <v>53</v>
+      </c>
+      <c r="B53" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="C51" s="29" t="s">
+      <c r="D53" s="12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9">
+      <c r="A54" s="3">
+        <v>54</v>
+      </c>
+      <c r="B54" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="I51" s="2">
-        <v>1200</v>
-      </c>
-    </row>
-    <row r="52" s="5" customFormat="1" spans="1:9">
-      <c r="A52" s="5">
-        <v>52</v>
-      </c>
-      <c r="B52" s="5" t="s">
+      <c r="D54" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" customFormat="1" spans="1:9">
+      <c r="A55" s="3">
+        <v>55</v>
+      </c>
+      <c r="B55" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="D52" s="30">
-        <v>30000</v>
-      </c>
-    </row>
-    <row r="53" s="6" customFormat="1" spans="1:9">
-      <c r="A53" s="6">
-        <v>53</v>
-      </c>
-      <c r="B53" s="6" t="s">
+      <c r="C55" s="3"/>
+      <c r="D55" s="3">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9">
+      <c r="A56" s="3">
+        <v>56</v>
+      </c>
+      <c r="B56" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="D53" s="31">
-        <v>30000</v>
-      </c>
-    </row>
-    <row r="54" s="5" customFormat="1" spans="1:9">
-      <c r="A54" s="5">
-        <v>54</v>
-      </c>
-      <c r="B54" s="5" t="s">
+      <c r="C56" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="D54" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="55" customFormat="1" spans="1:9">
-      <c r="A55" s="8">
-        <v>55</v>
-      </c>
-      <c r="B55" s="8" t="s">
+    </row>
+    <row r="57" s="1" customFormat="1" spans="1:9">
+      <c r="A57" s="1">
+        <v>60</v>
+      </c>
+      <c r="B57" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="C55" s="8"/>
-      <c r="D55" s="8">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="56" s="5" customFormat="1" spans="1:9">
-      <c r="A56" s="5">
-        <v>56</v>
-      </c>
-      <c r="B56" s="5" t="s">
+      <c r="C57" s="23" t="s">
         <v>113</v>
       </c>
-      <c r="C56" s="5" t="s">
+    </row>
+    <row r="58" spans="1:9">
+      <c r="A58" s="3">
+        <v>61</v>
+      </c>
+      <c r="B58" s="3" t="s">
         <v>114</v>
       </c>
-    </row>
-    <row r="57" s="2" customFormat="1" spans="1:9">
-      <c r="A57" s="2">
-        <v>60</v>
-      </c>
-      <c r="B57" s="2" t="s">
+      <c r="C58" s="24" t="s">
         <v>115</v>
       </c>
-      <c r="C57" s="32" t="s">
+    </row>
+    <row r="59" spans="1:9">
+      <c r="A59" s="3">
+        <v>62</v>
+      </c>
+      <c r="B59" s="3" t="s">
         <v>116</v>
       </c>
-    </row>
-    <row r="58" spans="1:9">
-      <c r="A58" s="8">
-        <v>61</v>
-      </c>
-      <c r="B58" s="8" t="s">
+      <c r="C59" s="12" t="s">
         <v>117</v>
       </c>
-      <c r="C58" s="33" t="s">
+    </row>
+    <row r="60" spans="1:9">
+      <c r="A60" s="3">
+        <v>63</v>
+      </c>
+      <c r="B60" s="3" t="s">
         <v>118</v>
       </c>
-    </row>
-    <row r="59" s="6" customFormat="1" spans="1:9">
-      <c r="A59" s="6">
-        <v>62</v>
-      </c>
-      <c r="B59" s="6" t="s">
+      <c r="C60" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="C59" s="31" t="s">
+    </row>
+    <row r="61" spans="1:9">
+      <c r="A61" s="3">
+        <v>64</v>
+      </c>
+      <c r="B61" s="3" t="s">
         <v>120</v>
       </c>
-    </row>
-    <row r="60" s="6" customFormat="1" spans="1:9">
-      <c r="A60" s="6">
-        <v>63</v>
-      </c>
-      <c r="B60" s="6" t="s">
+      <c r="C61" s="17" t="s">
         <v>121</v>
       </c>
-      <c r="C60" s="6" t="s">
+    </row>
+    <row r="62" spans="1:9">
+      <c r="A62" s="3">
+        <v>65</v>
+      </c>
+      <c r="B62" s="3" t="s">
         <v>122</v>
       </c>
-    </row>
-    <row r="61" s="6" customFormat="1" spans="1:9">
-      <c r="A61" s="6">
-        <v>64</v>
-      </c>
-      <c r="B61" s="6" t="s">
+      <c r="C62" s="17" t="s">
         <v>123</v>
       </c>
-      <c r="C61" s="34" t="s">
+    </row>
+    <row r="63" spans="1:9">
+      <c r="A63" s="3">
+        <v>70</v>
+      </c>
+      <c r="B63" s="3" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="62" s="6" customFormat="1" spans="1:9">
-      <c r="A62" s="6">
-        <v>65</v>
-      </c>
-      <c r="B62" s="6" t="s">
+      <c r="C63" s="17" t="s">
         <v>125</v>
       </c>
-      <c r="C62" s="34" t="s">
+      <c r="D63" s="17"/>
+    </row>
+    <row r="64" spans="1:9">
+      <c r="A64" s="3">
+        <v>71</v>
+      </c>
+      <c r="B64" s="3" t="s">
         <v>126</v>
       </c>
-    </row>
-    <row r="63" s="7" customFormat="1" spans="1:9">
-      <c r="A63" s="7">
-        <v>70</v>
-      </c>
-      <c r="B63" s="7" t="s">
+      <c r="C64" s="17"/>
+      <c r="D64" s="17">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="65" spans="1:20">
+      <c r="A65" s="3">
+        <v>72</v>
+      </c>
+      <c r="B65" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="C63" s="35" t="s">
+      <c r="C65" s="17" t="s">
         <v>128</v>
       </c>
-      <c r="D63" s="35"/>
-    </row>
-    <row r="64" s="7" customFormat="1" spans="1:9">
-      <c r="A64" s="7">
-        <v>71</v>
-      </c>
-      <c r="B64" s="7" t="s">
+    </row>
+    <row r="66" spans="1:20">
+      <c r="A66" s="25">
+        <v>80</v>
+      </c>
+      <c r="B66" s="25" t="s">
         <v>129</v>
       </c>
-      <c r="C64" s="35"/>
-      <c r="D64" s="35">
-        <v>5000</v>
-      </c>
-    </row>
-    <row r="65" s="7" customFormat="1" spans="1:20">
-      <c r="A65" s="7">
-        <v>72</v>
-      </c>
-      <c r="B65" s="7" t="s">
+      <c r="C66" s="25"/>
+      <c r="D66" s="25">
+        <v>259200</v>
+      </c>
+      <c r="E66" s="6"/>
+      <c r="F66" s="6"/>
+      <c r="G66" s="6"/>
+      <c r="H66" s="6"/>
+      <c r="I66" s="6"/>
+      <c r="J66" s="6"/>
+      <c r="K66" s="6"/>
+      <c r="L66" s="6"/>
+      <c r="M66" s="6"/>
+      <c r="N66" s="6"/>
+      <c r="O66" s="6"/>
+      <c r="P66" s="6"/>
+      <c r="Q66" s="6"/>
+      <c r="R66" s="6"/>
+      <c r="S66" s="6"/>
+      <c r="T66" s="6"/>
+    </row>
+    <row r="67" spans="1:20">
+      <c r="A67" s="3">
+        <v>90</v>
+      </c>
+      <c r="B67" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="C65" s="35" t="s">
+      <c r="D67" s="3">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="68" spans="1:20">
+      <c r="A68" s="3">
+        <v>100</v>
+      </c>
+      <c r="B68" s="3" t="s">
         <v>131</v>
       </c>
-    </row>
-    <row r="66" spans="1:20">
-      <c r="A66" s="36">
-        <v>80</v>
-      </c>
-      <c r="B66" s="36" t="s">
+      <c r="C68" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="C66" s="36"/>
-      <c r="D66" s="36">
-        <v>259200</v>
-      </c>
-      <c r="E66" s="11"/>
-      <c r="F66" s="11"/>
-      <c r="G66" s="11"/>
-      <c r="H66" s="11"/>
-      <c r="I66" s="11"/>
-      <c r="J66" s="11"/>
-      <c r="K66" s="11"/>
-      <c r="L66" s="11"/>
-      <c r="M66" s="11"/>
-      <c r="N66" s="11"/>
-      <c r="O66" s="11"/>
-      <c r="P66" s="11"/>
-      <c r="Q66" s="11"/>
-      <c r="R66" s="11"/>
-      <c r="S66" s="11"/>
-      <c r="T66" s="11"/>
-    </row>
-    <row r="67" s="1" customFormat="1" spans="1:20">
-      <c r="A67" s="1">
-        <v>90</v>
-      </c>
-      <c r="B67" s="1" t="s">
+    </row>
+    <row r="69" spans="1:20">
+      <c r="A69" s="3">
+        <v>101</v>
+      </c>
+      <c r="B69" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="D67" s="1">
-        <v>150000</v>
-      </c>
-    </row>
-    <row r="68" spans="1:20">
-      <c r="A68" s="8">
-        <v>100</v>
-      </c>
-      <c r="B68" s="8" t="s">
+      <c r="C69" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="C68" s="8" t="s">
+    </row>
+    <row r="70" spans="1:20">
+      <c r="A70" s="3">
+        <v>102</v>
+      </c>
+      <c r="B70" s="3" t="s">
         <v>135</v>
       </c>
-    </row>
-    <row r="69" spans="1:20">
-      <c r="A69" s="8">
-        <v>101</v>
-      </c>
-      <c r="B69" s="8" t="s">
+      <c r="D70" s="26">
+        <v>1022503</v>
+      </c>
+    </row>
+    <row r="71" spans="1:20">
+      <c r="A71" s="3">
+        <v>110</v>
+      </c>
+      <c r="B71" s="21" t="s">
         <v>136</v>
       </c>
-      <c r="C69" s="8" t="s">
+      <c r="D71" s="17">
+        <f>8400</f>
+        <v>8400</v>
+      </c>
+    </row>
+    <row r="72" spans="1:20">
+      <c r="A72" s="3">
+        <v>111</v>
+      </c>
+      <c r="B72" s="3" t="s">
         <v>137</v>
       </c>
-    </row>
-    <row r="70" spans="1:20">
-      <c r="A70" s="8">
-        <v>102</v>
-      </c>
-      <c r="B70" s="8" t="s">
+      <c r="D72" s="3">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="73" spans="1:20">
+      <c r="A73" s="3">
+        <v>112</v>
+      </c>
+      <c r="B73" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="D70" s="37">
-        <v>1022503</v>
-      </c>
-    </row>
-    <row r="71" s="4" customFormat="1" spans="1:20">
-      <c r="A71" s="4">
-        <v>110</v>
-      </c>
-      <c r="B71" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="D71" s="26">
-        <v>4200</v>
-      </c>
-    </row>
-    <row r="72" spans="1:20">
-      <c r="A72" s="8">
-        <v>111</v>
-      </c>
-      <c r="B72" s="8" t="s">
-        <v>140</v>
-      </c>
-      <c r="D72" s="8">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="73" spans="1:20">
-      <c r="A73" s="8">
-        <v>112</v>
-      </c>
-      <c r="B73" s="8" t="s">
-        <v>141</v>
-      </c>
-      <c r="D73" s="8">
+      <c r="D73" s="3">
         <v>300000</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="C57" r:id="rId3" display="https://aws-s3-jjg-asset-bucket.s3.ap-southeast-1.amazonaws.com/tanchuang_res/english/tc_sc_1.png" tooltip="https://aws-s3-jjg-asset-bucket.s3.ap-southeast-1.amazonaws.com/tanchuang_res/english/tc_sc_1.png"/>
-    <hyperlink ref="C58" r:id="rId4" display="https://chat.kinghush.com/privacy.html"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/gm/resources/sample/global.xlsx
+++ b/gm/resources/sample/global.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="11925"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="globalConfig" sheetId="1" r:id="rId1"/>
@@ -317,7 +317,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="141">
   <si>
     <t>sid</t>
   </si>
@@ -734,6 +734,12 @@
   </si>
   <si>
     <t>创建房间-Slot游戏新增超时提出的倒计时，单位毫秒</t>
+  </si>
+  <si>
+    <t>俄罗斯轮盘数字红黑区分</t>
+  </si>
+  <si>
+    <t>1_3_5_7_9_12_14_16_18_19_21_23_25_27_30_32_34_36;2_4_6_8_10_11_13_15_17_20_22_24_26_28_29_31_33_35</t>
   </si>
 </sst>
 </file>
@@ -1800,7 +1806,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:W73"/>
+  <dimension ref="A1:W76"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="9" style="3"/>
@@ -2853,6 +2859,18 @@
         <v>300000</v>
       </c>
     </row>
+    <row r="74" spans="1:20">
+      <c r="A74" s="3">
+        <v>113</v>
+      </c>
+      <c r="B74" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="C74" s="3" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="76" ht="14.25"/>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="C57" r:id="rId3" display="https://aws-s3-jjg-asset-bucket.s3.ap-southeast-1.amazonaws.com/tanchuang_res/english/tc_sc_1.png" tooltip="https://aws-s3-jjg-asset-bucket.s3.ap-southeast-1.amazonaws.com/tanchuang_res/english/tc_sc_1.png"/>

--- a/gm/resources/sample/global.xlsx
+++ b/gm/resources/sample/global.xlsx
@@ -318,7 +318,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="144">
   <si>
     <t>sid</t>
   </si>
@@ -744,6 +744,12 @@
   </si>
   <si>
     <t>创建房间-Slot游戏新增超时提出的倒计时，单位毫秒</t>
+  </si>
+  <si>
+    <t>活动-分享按钮：活动参与条件，不满足时分享失败|奖励道具ID_道具数量|每天账号领取次数_相同设备最多领取次数_注册IP地址领取次数_登录IP地址领取次数</t>
+  </si>
+  <si>
+    <t>bindPhone()|1990000_30000|1_5_20_100</t>
   </si>
 </sst>
 </file>
@@ -1851,12 +1857,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:W73"/>
+  <dimension ref="A1:W74"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="9" style="8"/>
-    <col min="2" max="2" width="96.9083333333333" style="8" customWidth="1"/>
-    <col min="3" max="4" width="28.375" style="8" customWidth="1"/>
+    <col min="2" max="2" width="134.125" style="8" customWidth="1"/>
+    <col min="3" max="3" width="36.5" style="8" customWidth="1"/>
+    <col min="4" max="4" width="28.375" style="8" customWidth="1"/>
     <col min="5" max="5" width="11.5" style="8" customWidth="1"/>
     <col min="6" max="6" width="9.625" style="8" customWidth="1"/>
     <col min="7" max="7" width="23.375" style="8" customWidth="1"/>
@@ -2915,6 +2922,17 @@
         <v>300000</v>
       </c>
     </row>
+    <row r="74" spans="1:20">
+      <c r="A74" s="8">
+        <v>113</v>
+      </c>
+      <c r="B74" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="C74" s="8" t="s">
+        <v>143</v>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="C57" r:id="rId3" display="https://aws-s3-jjg-asset-bucket.s3.ap-southeast-1.amazonaws.com/tanchuang_res/english/tc_sc_1.png" tooltip="https://aws-s3-jjg-asset-bucket.s3.ap-southeast-1.amazonaws.com/tanchuang_res/english/tc_sc_1.png"/>

--- a/gm/resources/sample/global.xlsx
+++ b/gm/resources/sample/global.xlsx
@@ -551,7 +551,7 @@
     <t>官方派奖：充值转换积分比例 ：充值金额（290,000 越南盾 = 1 积分 )</t>
   </si>
   <si>
-    <t>1_1</t>
+    <t>1_10</t>
   </si>
   <si>
     <t>官方派奖：转盘1次数_转盘2次数_转盘3次数（真人抽奖后机器人跟着的抽奖次数，填10，表示玩家抽1次，机器人抽10次）</t>
@@ -566,7 +566,7 @@
     <t>官方派奖：机器人中奖间隔（毫秒_权重|毫秒_权重）</t>
   </si>
   <si>
-    <t>3360_1000|2800_1000|2240_1000|1680_1000|1120_1000</t>
+    <t>33600_1000|28000_1000|22400_1000|16800_1000|11200_1000</t>
   </si>
   <si>
     <t>平均中奖间隔</t>
@@ -599,7 +599,7 @@
     <t>积分大奖：积分保底奖励（积分数量_奖励道具ID_奖励道具数量）</t>
   </si>
   <si>
-    <t>300_1990000_2170|600_1990000_4300|1200_1990000_8600|3600_1990000_17300|10800_1990000_26000|32400_1990000_34000</t>
+    <t>300_1990000_25100|600_1990000_50200|1200_1990000_100400|2400_1990000_200900|3600_1990000_301300|4800_1990000_401800</t>
   </si>
   <si>
     <t>VIP充值：充值金额与经验转换比例(充值金额_获得vip经验，最低支持0.01_1，美元)</t>
@@ -638,7 +638,7 @@
     <t>新手奖励</t>
   </si>
   <si>
-    <t>1990000_21400</t>
+    <t>1990000_214300</t>
   </si>
   <si>
     <t>手机短信区号（印度、巴基斯坦、菲律宾、巴西、尼日利亚）废弃</t>
@@ -680,7 +680,7 @@
     <t>推广分享：分享1人得固定奖励</t>
   </si>
   <si>
-    <t>1990000_42000</t>
+    <t>1990000_210000</t>
   </si>
   <si>
     <t>推广分享：二维码图片配置(该资源放在资源服务器实时下载显示的)</t>
@@ -692,7 +692,7 @@
     <t>推广分享：周榜上榜条件设置(收益数量)</t>
   </si>
   <si>
-    <t>1990000_750000</t>
+    <t>1990000_7500000</t>
   </si>
   <si>
     <t>推广分享：有效用户达标条件（有效下注累计_数值|累计充值_数值）</t>
@@ -704,7 +704,7 @@
     <t>财富轮盘：昨日输的金币兑换为积分的比例（昨日所输金币_获得积分）</t>
   </si>
   <si>
-    <t>125_1</t>
+    <t>50_1</t>
   </si>
   <si>
     <t>财富轮盘：每次抽奖所消耗的积分</t>

--- a/gm/resources/sample/global.xlsx
+++ b/gm/resources/sample/global.xlsx
@@ -617,7 +617,7 @@
     <t>积分大奖：占用榜单的机器人条件，触发的倒计时，单位秒【倒计时下限_倒计时上限_最小增长积分_前X名用机器人占榜】</t>
   </si>
   <si>
-    <t>600_1200_105_30</t>
+    <t>90_210_120_45</t>
   </si>
   <si>
     <t>目标积分 / （24*60/时间间隔分）*100/(总排名/MAX(1,(当前名次*(当前名次-1)))+总排名/当前名次) =增长积分</t>

--- a/gm/resources/sample/global.xlsx
+++ b/gm/resources/sample/global.xlsx
@@ -746,10 +746,10 @@
     <t>创建房间-Slot游戏新增超时提出的倒计时，单位毫秒</t>
   </si>
   <si>
-    <t>活动-分享按钮：活动参与条件，不满足时分享失败|奖励道具ID_道具数量|每天账号领取次数_相同设备最多领取次数_注册IP地址领取次数_登录IP地址领取次数</t>
-  </si>
-  <si>
-    <t>bindPhone()|1990000_30000|1_5_20_100</t>
+    <t>活动-分享按钮：活动参与条件，不满足时分享失败|奖励道具ID_道具数量|每天账号领取次数_相同设备最多领取次数_注册IP地址领取次数_登录IP地址领取次数|领取奖励条件</t>
+  </si>
+  <si>
+    <t>bindPhone()|1990000_30000|1_5_20_100|accountTotalRecharge(200000)</t>
   </si>
 </sst>
 </file>

--- a/gm/resources/sample/global.xlsx
+++ b/gm/resources/sample/global.xlsx
@@ -318,7 +318,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="145">
   <si>
     <t>sid</t>
   </si>
@@ -749,7 +749,10 @@
     <t>活动-分享按钮：活动参与条件，不满足时分享失败|奖励道具ID_道具数量|每天账号领取次数_相同设备最多领取次数_注册IP地址领取次数_登录IP地址领取次数|领取奖励条件</t>
   </si>
   <si>
-    <t>bindPhone()|1990000_30000|1_5_20_100|accountTotalRecharge(200000)</t>
+    <t>bindPhone()|1990000_30000|1_5_20_100|accountTotalRecharge(100)</t>
+  </si>
+  <si>
+    <t>创建房间-房间时间上限，房间时长不能超过此值，单位：小时</t>
   </si>
 </sst>
 </file>
@@ -1857,7 +1860,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:W74"/>
+  <dimension ref="A1:W75"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="9" style="8"/>
@@ -2933,6 +2936,17 @@
         <v>143</v>
       </c>
     </row>
+    <row r="75" spans="1:20">
+      <c r="A75" s="8">
+        <v>114</v>
+      </c>
+      <c r="B75" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="D75" s="8">
+        <v>168</v>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="C57" r:id="rId3" display="https://aws-s3-jjg-asset-bucket.s3.ap-southeast-1.amazonaws.com/tanchuang_res/english/tc_sc_1.png" tooltip="https://aws-s3-jjg-asset-bucket.s3.ap-southeast-1.amazonaws.com/tanchuang_res/english/tc_sc_1.png"/>

--- a/gm/resources/sample/global.xlsx
+++ b/gm/resources/sample/global.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="11925"/>
   </bookViews>
   <sheets>
     <sheet name="globalConfig" sheetId="1" r:id="rId1"/>
@@ -317,7 +317,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="142">
   <si>
     <t>sid</t>
   </si>
@@ -736,10 +736,13 @@
     <t>创建房间-Slot游戏新增超时提出的倒计时，单位毫秒</t>
   </si>
   <si>
-    <t>俄罗斯轮盘数字红黑区分</t>
-  </si>
-  <si>
-    <t>1_3_5_7_9_12_14_16_18_19_21_23_25_27_30_32_34_36;2_4_6_8_10_11_13_15_17_20_22_24_26_28_29_31_33_35</t>
+    <t>活动-分享按钮：活动参与条件，不满足时分享失败|奖励道具ID_道具数量|每天账号领取次数_相同设备最多领取次数_注册IP地址领取次数_登录IP地址领取次数|领取奖励条件</t>
+  </si>
+  <si>
+    <t>bindPhone()|1990000_30000|1_5_20_100|accountTotalRecharge(100)</t>
+  </si>
+  <si>
+    <t>创建房间-房间时间上限，房间时长不能超过此值，单位：小时</t>
   </si>
 </sst>
 </file>
@@ -961,12 +964,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1806,7 +1809,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:W76"/>
+  <dimension ref="A1:W75"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="9" style="3"/>
@@ -2870,7 +2873,17 @@
         <v>140</v>
       </c>
     </row>
-    <row r="76" ht="14.25"/>
+    <row r="75" spans="1:20">
+      <c r="A75" s="3">
+        <v>114</v>
+      </c>
+      <c r="B75" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="D75" s="3">
+        <v>168</v>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="C57" r:id="rId3" display="https://aws-s3-jjg-asset-bucket.s3.ap-southeast-1.amazonaws.com/tanchuang_res/english/tc_sc_1.png" tooltip="https://aws-s3-jjg-asset-bucket.s3.ap-southeast-1.amazonaws.com/tanchuang_res/english/tc_sc_1.png"/>

--- a/gm/resources/sample/global.xlsx
+++ b/gm/resources/sample/global.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="11925"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="globalConfig" sheetId="1" r:id="rId1"/>
@@ -749,7 +749,7 @@
     <t>活动-分享按钮：活动参与条件，不满足时分享失败|奖励道具ID_道具数量|每天账号领取次数_相同设备最多领取次数_注册IP地址领取次数_登录IP地址领取次数|领取奖励条件</t>
   </si>
   <si>
-    <t>bindPhone()|1990000_30000|1_5_20_100|accountTotalRecharge(100)</t>
+    <t>bindPhone()|1990000_3000|1_5_20_100|accountTotalRecharge(100)</t>
   </si>
   <si>
     <t>创建房间-房间时间上限，房间时长不能超过此值，单位：小时</t>

--- a/gm/resources/sample/global.xlsx
+++ b/gm/resources/sample/global.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="11925"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="globalConfig" sheetId="1" r:id="rId1"/>
@@ -312,12 +312,36 @@
         </r>
       </text>
     </comment>
+    <comment ref="D77" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+1-可以重复触发
+-1—不能重复触发
+</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="146">
   <si>
     <t>sid</t>
   </si>
@@ -743,6 +767,18 @@
   </si>
   <si>
     <t>创建房间-房间时间上限，房间时长不能超过此值，单位：小时</t>
+  </si>
+  <si>
+    <t>截图分享-在slot游戏中中奖达到多少倍触发截图分享</t>
+  </si>
+  <si>
+    <t>截图分享-在slot游戏中退出房间后重新进入房间获得X倍奖励是否触发截图分享（在当日分享次数足够时）</t>
+  </si>
+  <si>
+    <t>截图分享-在slot游戏中同一用户每日最多触发多少次截图分享</t>
+  </si>
+  <si>
+    <t>充值挑战活动：福利中充值返利的金币数量=预算价值*此值</t>
   </si>
 </sst>
 </file>
@@ -964,12 +1000,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1809,7 +1845,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:W75"/>
+  <dimension ref="A1:W79"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="9" style="3"/>
@@ -2884,6 +2920,50 @@
         <v>168</v>
       </c>
     </row>
+    <row r="76" spans="1:20">
+      <c r="A76" s="3">
+        <v>120</v>
+      </c>
+      <c r="B76" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="D76" s="3">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="77" spans="1:20">
+      <c r="A77" s="3">
+        <v>121</v>
+      </c>
+      <c r="B77" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="D77" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="78" spans="1:20">
+      <c r="A78" s="3">
+        <v>122</v>
+      </c>
+      <c r="B78" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="D78" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="79" spans="1:20">
+      <c r="A79" s="3">
+        <v>123</v>
+      </c>
+      <c r="B79" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="D79" s="3">
+        <v>30000</v>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="C57" r:id="rId3" display="https://aws-s3-jjg-asset-bucket.s3.ap-southeast-1.amazonaws.com/tanchuang_res/english/tc_sc_1.png" tooltip="https://aws-s3-jjg-asset-bucket.s3.ap-southeast-1.amazonaws.com/tanchuang_res/english/tc_sc_1.png"/>

--- a/gm/resources/sample/global.xlsx
+++ b/gm/resources/sample/global.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="11925"/>
   </bookViews>
   <sheets>
     <sheet name="globalConfig" sheetId="1" r:id="rId1"/>
@@ -617,7 +617,7 @@
     <t>积分大奖：占用榜单的机器人条件，触发的倒计时，单位秒【倒计时下限_倒计时上限_最小增长积分_前X名用机器人占榜】</t>
   </si>
   <si>
-    <t>90_210_120_45</t>
+    <t>90_210_60_45</t>
   </si>
   <si>
     <t>目标积分 / （24*60/时间间隔分）*100/(总排名/MAX(1,(当前名次*(当前名次-1)))+总排名/当前名次) =增长积分</t>
@@ -974,12 +974,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>

--- a/gm/resources/sample/global.xlsx
+++ b/gm/resources/sample/global.xlsx
@@ -312,36 +312,12 @@
         </r>
       </text>
     </comment>
-    <comment ref="D77" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>Administrator:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">
-1-可以重复触发
--1—不能重复触发
-</t>
-        </r>
-      </text>
-    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="141">
   <si>
     <t>sid</t>
   </si>
@@ -760,25 +736,10 @@
     <t>创建房间-Slot游戏新增超时提出的倒计时，单位毫秒</t>
   </si>
   <si>
-    <t>活动-分享按钮：活动参与条件，不满足时分享失败|奖励道具ID_道具数量|每天账号领取次数_相同设备最多领取次数_注册IP地址领取次数_登录IP地址领取次数|领取奖励条件</t>
-  </si>
-  <si>
-    <t>bindPhone()|1990000_30000|1_5_20_100|accountTotalRecharge(100)</t>
-  </si>
-  <si>
-    <t>创建房间-房间时间上限，房间时长不能超过此值，单位：小时</t>
-  </si>
-  <si>
-    <t>截图分享-在slot游戏中中奖达到多少倍触发截图分享</t>
-  </si>
-  <si>
-    <t>截图分享-在slot游戏中退出房间后重新进入房间获得X倍奖励是否触发截图分享（在当日分享次数足够时）</t>
-  </si>
-  <si>
-    <t>截图分享-在slot游戏中同一用户每日最多触发多少次截图分享</t>
-  </si>
-  <si>
-    <t>充值挑战活动：福利中充值返利的金币数量=预算价值*此值</t>
+    <t>俄罗斯轮盘数字红黑区分</t>
+  </si>
+  <si>
+    <t>1_3_5_7_9_12_14_16_18_19_21_23_25_27_30_32_34_36;2_4_6_8_10_11_13_15_17_20_22_24_26_28_29_31_33_35</t>
   </si>
 </sst>
 </file>
@@ -1845,7 +1806,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:W79"/>
+  <dimension ref="A1:W76"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="9" style="3"/>
@@ -2909,61 +2870,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="75" spans="1:20">
-      <c r="A75" s="3">
-        <v>114</v>
-      </c>
-      <c r="B75" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="D75" s="3">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="76" spans="1:20">
-      <c r="A76" s="3">
-        <v>120</v>
-      </c>
-      <c r="B76" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="D76" s="3">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="77" spans="1:20">
-      <c r="A77" s="3">
-        <v>121</v>
-      </c>
-      <c r="B77" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="D77" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="78" spans="1:20">
-      <c r="A78" s="3">
-        <v>122</v>
-      </c>
-      <c r="B78" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="D78" s="3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="79" spans="1:20">
-      <c r="A79" s="3">
-        <v>123</v>
-      </c>
-      <c r="B79" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="D79" s="3">
-        <v>30000</v>
-      </c>
-    </row>
+    <row r="76" ht="14.25"/>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="C57" r:id="rId3" display="https://aws-s3-jjg-asset-bucket.s3.ap-southeast-1.amazonaws.com/tanchuang_res/english/tc_sc_1.png" tooltip="https://aws-s3-jjg-asset-bucket.s3.ap-southeast-1.amazonaws.com/tanchuang_res/english/tc_sc_1.png"/>

--- a/gm/resources/sample/global.xlsx
+++ b/gm/resources/sample/global.xlsx
@@ -312,12 +312,36 @@
         </r>
       </text>
     </comment>
+    <comment ref="D77" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+1-可以重复触发
+-1—不能重复触发
+</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="146">
   <si>
     <t>sid</t>
   </si>
@@ -736,10 +760,25 @@
     <t>创建房间-Slot游戏新增超时提出的倒计时，单位毫秒</t>
   </si>
   <si>
-    <t>俄罗斯轮盘数字红黑区分</t>
-  </si>
-  <si>
-    <t>1_3_5_7_9_12_14_16_18_19_21_23_25_27_30_32_34_36;2_4_6_8_10_11_13_15_17_20_22_24_26_28_29_31_33_35</t>
+    <t>活动-分享按钮：活动参与条件，不满足时分享失败|奖励道具ID_道具数量|每天账号领取次数_相同设备最多领取次数_注册IP地址领取次数_登录IP地址领取次数|领取奖励条件</t>
+  </si>
+  <si>
+    <t>bindPhone()|1990000_30000|1_5_20_100|accountTotalRecharge(100)</t>
+  </si>
+  <si>
+    <t>创建房间-房间时间上限，房间时长不能超过此值，单位：小时</t>
+  </si>
+  <si>
+    <t>截图分享-在slot游戏中中奖达到多少倍触发截图分享</t>
+  </si>
+  <si>
+    <t>截图分享-在slot游戏中退出房间后重新进入房间获得X倍奖励是否触发截图分享（在当日分享次数足够时）</t>
+  </si>
+  <si>
+    <t>截图分享-在slot游戏中同一用户每日最多触发多少次截图分享</t>
+  </si>
+  <si>
+    <t>充值挑战活动：福利中充值返利的金币数量=预算价值*此值</t>
   </si>
 </sst>
 </file>
@@ -1806,7 +1845,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:W76"/>
+  <dimension ref="A1:W79"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="9" style="3"/>
@@ -2870,7 +2909,61 @@
         <v>140</v>
       </c>
     </row>
-    <row r="76" ht="14.25"/>
+    <row r="75" spans="1:20">
+      <c r="A75" s="3">
+        <v>114</v>
+      </c>
+      <c r="B75" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="D75" s="3">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="76" spans="1:20">
+      <c r="A76" s="3">
+        <v>120</v>
+      </c>
+      <c r="B76" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="D76" s="3">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="77" spans="1:20">
+      <c r="A77" s="3">
+        <v>121</v>
+      </c>
+      <c r="B77" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="D77" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="78" spans="1:20">
+      <c r="A78" s="3">
+        <v>122</v>
+      </c>
+      <c r="B78" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="D78" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="79" spans="1:20">
+      <c r="A79" s="3">
+        <v>123</v>
+      </c>
+      <c r="B79" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="D79" s="3">
+        <v>30000</v>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="C57" r:id="rId3" display="https://aws-s3-jjg-asset-bucket.s3.ap-southeast-1.amazonaws.com/tanchuang_res/english/tc_sc_1.png" tooltip="https://aws-s3-jjg-asset-bucket.s3.ap-southeast-1.amazonaws.com/tanchuang_res/english/tc_sc_1.png"/>

--- a/gm/resources/sample/global.xlsx
+++ b/gm/resources/sample/global.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="globalConfig" sheetId="1" r:id="rId1"/>
@@ -318,7 +318,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="149">
   <si>
     <t>sid</t>
   </si>
@@ -617,7 +617,7 @@
     <t>积分大奖：占用榜单的机器人条件，触发的倒计时，单位秒【倒计时下限_倒计时上限_最小增长积分_前X名用机器人占榜】</t>
   </si>
   <si>
-    <t>90_210_120_45</t>
+    <t>90_210_60_45</t>
   </si>
   <si>
     <t>目标积分 / （24*60/时间间隔分）*100/(总排名/MAX(1,(当前名次*(当前名次-1)))+总排名/当前名次) =增长积分</t>
@@ -753,6 +753,18 @@
   </si>
   <si>
     <t>创建房间-房间时间上限，房间时长不能超过此值，单位：小时</t>
+  </si>
+  <si>
+    <t>截图分享-在slot游戏中中奖达到多少倍触发截图分享</t>
+  </si>
+  <si>
+    <t>截图分享-在slot游戏中退出房间后重新进入房间获得X倍奖励是否触发截图分享（在当日分享次数足够时）</t>
+  </si>
+  <si>
+    <t>截图分享-在slot游戏中同一用户每日最多触发多少次截图分享</t>
+  </si>
+  <si>
+    <t>充值挑战活动：福利中充值返利的金币数量=预算价值*此值</t>
   </si>
 </sst>
 </file>
@@ -1860,7 +1872,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:W75"/>
+  <dimension ref="A1:W79"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="9" style="8"/>
@@ -2947,6 +2959,110 @@
         <v>168</v>
       </c>
     </row>
+    <row r="76" customFormat="1" spans="1:20">
+      <c r="A76" s="8">
+        <v>120</v>
+      </c>
+      <c r="B76" s="8" t="s">
+        <v>145</v>
+      </c>
+      <c r="C76" s="8"/>
+      <c r="D76" s="8">
+        <v>30</v>
+      </c>
+      <c r="E76" s="8"/>
+      <c r="F76" s="8"/>
+      <c r="G76" s="8"/>
+      <c r="H76" s="8"/>
+      <c r="I76" s="8"/>
+      <c r="J76" s="8"/>
+      <c r="K76" s="8"/>
+      <c r="L76" s="8"/>
+      <c r="M76" s="8"/>
+      <c r="N76" s="8"/>
+      <c r="O76" s="8"/>
+      <c r="P76" s="8"/>
+      <c r="Q76" s="8"/>
+      <c r="R76" s="8"/>
+    </row>
+    <row r="77" customFormat="1" spans="1:20">
+      <c r="A77" s="8">
+        <v>121</v>
+      </c>
+      <c r="B77" s="8" t="s">
+        <v>146</v>
+      </c>
+      <c r="C77" s="8"/>
+      <c r="D77" s="8">
+        <v>1</v>
+      </c>
+      <c r="E77" s="8"/>
+      <c r="F77" s="8"/>
+      <c r="G77" s="8"/>
+      <c r="H77" s="8"/>
+      <c r="I77" s="8"/>
+      <c r="J77" s="8"/>
+      <c r="K77" s="8"/>
+      <c r="L77" s="8"/>
+      <c r="M77" s="8"/>
+      <c r="N77" s="8"/>
+      <c r="O77" s="8"/>
+      <c r="P77" s="8"/>
+      <c r="Q77" s="8"/>
+      <c r="R77" s="8"/>
+    </row>
+    <row r="78" customFormat="1" spans="1:20">
+      <c r="A78" s="8">
+        <v>122</v>
+      </c>
+      <c r="B78" s="8" t="s">
+        <v>147</v>
+      </c>
+      <c r="C78" s="8"/>
+      <c r="D78" s="8">
+        <v>5</v>
+      </c>
+      <c r="E78" s="8"/>
+      <c r="F78" s="8"/>
+      <c r="G78" s="8"/>
+      <c r="H78" s="8"/>
+      <c r="I78" s="8"/>
+      <c r="J78" s="8"/>
+      <c r="K78" s="8"/>
+      <c r="L78" s="8"/>
+      <c r="M78" s="8"/>
+      <c r="N78" s="8"/>
+      <c r="O78" s="8"/>
+      <c r="P78" s="8"/>
+      <c r="Q78" s="8"/>
+      <c r="R78" s="8"/>
+    </row>
+    <row r="79" customFormat="1" spans="1:20">
+      <c r="A79" s="8">
+        <v>123</v>
+      </c>
+      <c r="B79" s="8" t="s">
+        <v>148</v>
+      </c>
+      <c r="C79" s="8"/>
+      <c r="D79" s="8">
+        <v>30000</v>
+      </c>
+      <c r="E79" s="8"/>
+      <c r="F79" s="8"/>
+      <c r="G79" s="8"/>
+      <c r="H79" s="8"/>
+      <c r="I79" s="8"/>
+      <c r="J79" s="8"/>
+      <c r="K79" s="8"/>
+      <c r="L79" s="8"/>
+      <c r="M79" s="8"/>
+      <c r="N79" s="8"/>
+      <c r="O79" s="8"/>
+      <c r="P79" s="8"/>
+      <c r="Q79" s="8"/>
+      <c r="R79" s="8"/>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="C57" r:id="rId3" display="https://aws-s3-jjg-asset-bucket.s3.ap-southeast-1.amazonaws.com/tanchuang_res/english/tc_sc_1.png" tooltip="https://aws-s3-jjg-asset-bucket.s3.ap-southeast-1.amazonaws.com/tanchuang_res/english/tc_sc_1.png"/>

--- a/gm/resources/sample/global.xlsx
+++ b/gm/resources/sample/global.xlsx
@@ -318,7 +318,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="150">
   <si>
     <t>sid</t>
   </si>
@@ -765,6 +765,9 @@
   </si>
   <si>
     <t>充值挑战活动：福利中充值返利的金币数量=预算价值*此值</t>
+  </si>
+  <si>
+    <t>礼包码输入错误后需要等待的时间（单位：秒）</t>
   </si>
 </sst>
 </file>
@@ -1872,7 +1875,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:W79"/>
+  <dimension ref="A1:W80"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="9" style="8"/>
@@ -3063,6 +3066,17 @@
       <c r="Q79" s="8"/>
       <c r="R79" s="8"/>
     </row>
+    <row r="80" spans="1:20">
+      <c r="A80" s="8">
+        <v>124</v>
+      </c>
+      <c r="B80" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="D80" s="8">
+        <v>10</v>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="C57" r:id="rId3" display="https://aws-s3-jjg-asset-bucket.s3.ap-southeast-1.amazonaws.com/tanchuang_res/english/tc_sc_1.png" tooltip="https://aws-s3-jjg-asset-bucket.s3.ap-southeast-1.amazonaws.com/tanchuang_res/english/tc_sc_1.png"/>

--- a/gm/resources/sample/global.xlsx
+++ b/gm/resources/sample/global.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="globalConfig" sheetId="1" r:id="rId1"/>
@@ -341,7 +341,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="147">
   <si>
     <t>sid</t>
   </si>
@@ -779,6 +779,9 @@
   </si>
   <si>
     <t>充值挑战活动：福利中充值返利的金币数量=预算价值*此值</t>
+  </si>
+  <si>
+    <t>礼包码输入错误后需要等待的时间（单位：秒）</t>
   </si>
 </sst>
 </file>
@@ -1845,7 +1848,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:W79"/>
+  <dimension ref="A1:W80"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="9" style="3"/>
@@ -2964,6 +2967,17 @@
         <v>30000</v>
       </c>
     </row>
+    <row r="80" spans="1:20">
+      <c r="A80" s="3">
+        <v>124</v>
+      </c>
+      <c r="B80" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="D80" s="3">
+        <v>600</v>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="C57" r:id="rId3" display="https://aws-s3-jjg-asset-bucket.s3.ap-southeast-1.amazonaws.com/tanchuang_res/english/tc_sc_1.png" tooltip="https://aws-s3-jjg-asset-bucket.s3.ap-southeast-1.amazonaws.com/tanchuang_res/english/tc_sc_1.png"/>

--- a/gm/resources/sample/global.xlsx
+++ b/gm/resources/sample/global.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="globalConfig" sheetId="1" r:id="rId1"/>
@@ -310,6 +310,29 @@
 -1:此类型的所有游戏
 100100：金矿大亨
 ……</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D77" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+1表示可以重复触发
+-1表示不能触发</t>
         </r>
       </text>
     </comment>
@@ -3023,7 +3046,7 @@
       </c>
       <c r="C78" s="8"/>
       <c r="D78" s="8">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E78" s="8"/>
       <c r="F78" s="8"/>

--- a/gm/resources/sample/global.xlsx
+++ b/gm/resources/sample/global.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="globalConfig" sheetId="1" r:id="rId1"/>
@@ -164,7 +164,7 @@
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
-值为空，表示不开启该活动</t>
+为空时表示不开此活动</t>
         </r>
       </text>
     </comment>
@@ -208,7 +208,8 @@
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
-值为0表示不返利</t>
+值为0表示不返利
+</t>
         </r>
       </text>
     </comment>
@@ -330,9 +331,8 @@
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
-1-可以重复触发
--1—不能重复触发
-</t>
+1表示可以重复触发
+-1表示不能触发</t>
         </r>
       </text>
     </comment>
@@ -341,7 +341,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="150">
   <si>
     <t>sid</t>
   </si>
@@ -475,7 +475,10 @@
     <t>我的赌场清除CD价值，每X秒需要Y钻石（道具ID_道具数量_单位时间秒）</t>
   </si>
   <si>
-    <t>1980000_1_60</t>
+    <t>1980000_500_60</t>
+  </si>
+  <si>
+    <t>钻石和金币等价，30000金币等于1$，设1分钟=0.02$=0.14￥=0.02*30000=600</t>
   </si>
   <si>
     <t>默认邮件有效期（秒）</t>
@@ -484,7 +487,10 @@
     <t>我的赌场购买一键领取的消耗（道具ID_道具数量_持续时间分钟）</t>
   </si>
   <si>
-    <t>1980000_200_1440</t>
+    <t>1980000_3000_1440</t>
+  </si>
+  <si>
+    <t>钻石和金币等价，30000金币等于1$，设1分钟=0.001$=0.007￥=1*0.001*30000=30</t>
   </si>
   <si>
     <t>收藏游戏数量上限</t>
@@ -493,7 +499,7 @@
     <t>摇钱树活动增长金额</t>
   </si>
   <si>
-    <t>0_12_100_250|12_24_100_250</t>
+    <t>0_12_5000_10000|12_24_5000_10000</t>
   </si>
   <si>
     <t>开始时间/时_结束时间/时（左闭右开）_每次增长值_每次增长下限|</t>
@@ -520,7 +526,7 @@
     <t>1022501_1</t>
   </si>
   <si>
-    <t>每次下注金币的万分比飞入储钱罐</t>
+    <t>储钱罐：每次下注金币的万分比飞入储钱罐</t>
   </si>
   <si>
     <t>创建房间-房间销毁时房主获得实际准备金的万分比</t>
@@ -568,13 +574,13 @@
     <t>官方派奖：充值转换积分比例 ：充值金额（290,000 越南盾 = 1 积分 )</t>
   </si>
   <si>
-    <t>208000_1</t>
+    <t>1_10</t>
   </si>
   <si>
     <t>官方派奖：转盘1次数_转盘2次数_转盘3次数（真人抽奖后机器人跟着的抽奖次数，填10，表示玩家抽1次，机器人抽10次）</t>
   </si>
   <si>
-    <t>99_99_99</t>
+    <t>1_1_1</t>
   </si>
   <si>
     <t>机器人奖池比例</t>
@@ -583,7 +589,7 @@
     <t>官方派奖：机器人中奖间隔（毫秒_权重|毫秒_权重）</t>
   </si>
   <si>
-    <t>3360_1000|2800_1000|2240_1000|1680_1000|1120_1000</t>
+    <t>33600_1000|28000_1000|22400_1000|16800_1000|11200_1000</t>
   </si>
   <si>
     <t>平均中奖间隔</t>
@@ -616,13 +622,13 @@
     <t>积分大奖：积分保底奖励（积分数量_奖励道具ID_奖励道具数量）</t>
   </si>
   <si>
-    <t>300_1990000_2170|600_1990000_4300|1200_1990000_8600|3600_1990000_17300|10800_1990000_26000|32400_1990000_34000</t>
+    <t>300_1990000_25100|600_1990000_50200|1200_1990000_100400|2400_1990000_200900|3600_1990000_301300|4800_1990000_401800</t>
   </si>
   <si>
     <t>VIP充值：充值金额与经验转换比例(充值金额_获得vip经验，最低支持0.01_1，美元)</t>
   </si>
   <si>
-    <t>1_10</t>
+    <t>1_30000</t>
   </si>
   <si>
     <t>积分大奖：实物奖励兑换码过期时间（天）</t>
@@ -634,7 +640,7 @@
     <t>积分大奖：占用榜单的机器人条件，触发的倒计时，单位秒【倒计时下限_倒计时上限_最小增长积分_前X名用机器人占榜】</t>
   </si>
   <si>
-    <t>600_1200_105_30</t>
+    <t>90_210_60_45</t>
   </si>
   <si>
     <t>目标积分 / （24*60/时间间隔分）*100/(总排名/MAX(1,(当前名次*(当前名次-1)))+总排名/当前名次) =增长积分</t>
@@ -655,6 +661,9 @@
     <t>新手奖励</t>
   </si>
   <si>
+    <t>1990000_214300</t>
+  </si>
+  <si>
     <t>手机短信区号（印度、巴基斯坦、菲律宾、巴西、尼日利亚）废弃</t>
   </si>
   <si>
@@ -688,13 +697,13 @@
     <t>隐私政策链接</t>
   </si>
   <si>
-    <t>http://chat.kinghush.com/privacy.html</t>
+    <t>https://chat.kinghush.com/privacy.html</t>
   </si>
   <si>
     <t>推广分享：分享1人得固定奖励</t>
   </si>
   <si>
-    <t>1990000_100000</t>
+    <t>1990000_210000</t>
   </si>
   <si>
     <t>推广分享：二维码图片配置(该资源放在资源服务器实时下载显示的)</t>
@@ -706,19 +715,19 @@
     <t>推广分享：周榜上榜条件设置(收益数量)</t>
   </si>
   <si>
-    <t>1990000_4000000</t>
+    <t>1990000_7500000</t>
   </si>
   <si>
     <t>推广分享：有效用户达标条件（有效下注累计_数值|累计充值_数值）</t>
   </si>
   <si>
-    <t>AND(totalValidBets(2000000),totalRecharge(100000,0))</t>
+    <t>AND(totalValidBets(4200000),totalRecharge(10,0))</t>
   </si>
   <si>
     <t>财富轮盘：昨日输的金币兑换为积分的比例（昨日所输金币_获得积分）</t>
   </si>
   <si>
-    <t>2000_1</t>
+    <t>50_1</t>
   </si>
   <si>
     <t>财富轮盘：每次抽奖所消耗的积分</t>
@@ -763,7 +772,7 @@
     <t>活动-分享按钮：活动参与条件，不满足时分享失败|奖励道具ID_道具数量|每天账号领取次数_相同设备最多领取次数_注册IP地址领取次数_登录IP地址领取次数|领取奖励条件</t>
   </si>
   <si>
-    <t>bindPhone()|1990000_30000|1_5_20_100|accountTotalRecharge(100)</t>
+    <t>bindPhone()|1990000_3000|1_5_20_100|accountTotalRecharge(100)</t>
   </si>
   <si>
     <t>创建房间-房间时间上限，房间时长不能超过此值，单位：小时</t>
@@ -805,18 +814,18 @@
     </font>
     <font>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="0" tint="-0.249977111117893"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
-      <name val="微软雅黑"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
@@ -1014,7 +1023,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="38">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1023,175 +1032,205 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1353,7 +1392,7 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1377,16 +1416,16 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -1395,43 +1434,31 @@
     <xf numFmtId="0" fontId="23" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="28" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1467,66 +1494,89 @@
     <xf numFmtId="0" fontId="27" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="28" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="6" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" quotePrefix="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" quotePrefix="1">
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" quotePrefix="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" quotePrefix="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1851,1136 +1901,1209 @@
   <dimension ref="A1:W80"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
-    <col min="1" max="1" width="9" style="3"/>
-    <col min="2" max="2" width="96.9083333333333" style="3" customWidth="1"/>
-    <col min="3" max="4" width="28.375" style="3" customWidth="1"/>
-    <col min="5" max="5" width="11.5" style="3" customWidth="1"/>
-    <col min="6" max="6" width="9.625" style="3" customWidth="1"/>
-    <col min="7" max="7" width="23.375" style="3" customWidth="1"/>
-    <col min="8" max="8" width="12.75" style="3"/>
-    <col min="9" max="10" width="14.125" style="3"/>
-    <col min="11" max="11" width="9" style="3"/>
-    <col min="12" max="12" width="12.875" style="3"/>
-    <col min="13" max="13" width="9" style="3"/>
-    <col min="14" max="17" width="10.375" style="3"/>
-    <col min="18" max="18" width="9.25" style="3"/>
-    <col min="19" max="16384" width="9" style="3"/>
+    <col min="1" max="1" width="9" style="8"/>
+    <col min="2" max="2" width="134.125" style="8" customWidth="1"/>
+    <col min="3" max="3" width="36.5" style="8" customWidth="1"/>
+    <col min="4" max="4" width="28.375" style="8" customWidth="1"/>
+    <col min="5" max="5" width="11.5" style="8" customWidth="1"/>
+    <col min="6" max="6" width="9.625" style="8" customWidth="1"/>
+    <col min="7" max="7" width="23.375" style="8" customWidth="1"/>
+    <col min="8" max="8" width="12.75" style="8"/>
+    <col min="9" max="10" width="14.125" style="8"/>
+    <col min="11" max="11" width="9" style="8"/>
+    <col min="12" max="12" width="12.875" style="8"/>
+    <col min="13" max="13" width="9" style="8"/>
+    <col min="14" max="17" width="10.375" style="8"/>
+    <col min="18" max="18" width="9.25" style="8"/>
+    <col min="19" max="16384" width="9" style="8"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5" t="s">
+      <c r="B1" s="10"/>
+      <c r="C1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="G1" s="10" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="5"/>
-      <c r="C2" s="5" t="s">
+      <c r="B2" s="10"/>
+      <c r="C2" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="7" t="s">
+      <c r="D2" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="E2" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="F2" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="G2" s="5"/>
+      <c r="G2" s="10"/>
     </row>
     <row r="3" spans="1:7">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="5"/>
-      <c r="C3" s="5" t="s">
+      <c r="B3" s="10"/>
+      <c r="C3" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="F3" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="G3" s="5"/>
+      <c r="G3" s="10"/>
     </row>
     <row r="4" spans="1:7">
-      <c r="A4" s="8"/>
-      <c r="B4" s="7"/>
-      <c r="C4" s="7"/>
-      <c r="G4" s="7"/>
+      <c r="A4" s="13"/>
+      <c r="B4" s="12"/>
+      <c r="C4" s="12"/>
+      <c r="G4" s="12"/>
     </row>
     <row r="5" spans="1:7">
-      <c r="A5" s="3">
+      <c r="A5" s="8">
         <v>1</v>
       </c>
-      <c r="B5" s="7" t="s">
+      <c r="B5" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="D5" s="7">
+      <c r="D5" s="12">
         <v>999</v>
       </c>
-      <c r="E5" s="7"/>
-      <c r="F5" s="7"/>
-      <c r="G5" s="7"/>
+      <c r="E5" s="12"/>
+      <c r="F5" s="12"/>
+      <c r="G5" s="12"/>
     </row>
     <row r="6" spans="1:7">
-      <c r="A6" s="3">
+      <c r="A6" s="8">
         <v>2</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="B6" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="D6" s="9">
-        <v>30000</v>
-      </c>
-      <c r="E6" s="7"/>
-      <c r="F6" s="7"/>
-      <c r="G6" s="7" t="s">
+      <c r="D6" s="14">
+        <v>10000</v>
+      </c>
+      <c r="E6" s="12"/>
+      <c r="F6" s="12"/>
+      <c r="G6" s="12" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="7" spans="1:7">
-      <c r="A7" s="3">
+      <c r="A7" s="8">
         <v>3</v>
       </c>
-      <c r="B7" s="7" t="s">
+      <c r="B7" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="D7" s="7">
+      <c r="D7" s="12">
         <v>10000</v>
       </c>
-      <c r="E7" s="7"/>
-      <c r="F7" s="7"/>
-      <c r="G7" s="7" t="s">
+      <c r="E7" s="12"/>
+      <c r="F7" s="12"/>
+      <c r="G7" s="12" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="8" spans="1:7">
-      <c r="A8" s="3">
+      <c r="A8" s="8">
         <v>4</v>
       </c>
-      <c r="B8" s="7" t="s">
+      <c r="B8" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="C8" s="7">
+      <c r="C8" s="12">
         <v>100</v>
       </c>
-      <c r="D8" s="7"/>
-      <c r="E8" s="7"/>
-      <c r="F8" s="7"/>
-      <c r="G8" s="7" t="s">
+      <c r="D8" s="12"/>
+      <c r="E8" s="12"/>
+      <c r="F8" s="12"/>
+      <c r="G8" s="12" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="9" spans="1:7">
-      <c r="A9" s="3">
+      <c r="A9" s="8">
         <v>5</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="C9" s="3">
+      <c r="C9" s="8">
         <v>4</v>
       </c>
-      <c r="G9" s="3" t="s">
+      <c r="G9" s="8" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="10" spans="1:7">
-      <c r="A10" s="3">
+      <c r="A10" s="8">
         <v>6</v>
       </c>
-      <c r="B10" s="7" t="s">
+      <c r="B10" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="C10" s="27" t="s">
+      <c r="C10" s="38" t="s">
         <v>24</v>
       </c>
-      <c r="D10" s="10"/>
-      <c r="E10" s="7"/>
-      <c r="F10" s="7"/>
-      <c r="G10" s="3" t="s">
+      <c r="D10" s="15"/>
+      <c r="E10" s="12"/>
+      <c r="F10" s="12"/>
+      <c r="G10" s="8" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="11" spans="1:7">
-      <c r="A11" s="3">
+      <c r="A11" s="8">
         <v>7</v>
       </c>
-      <c r="B11" s="7" t="s">
+      <c r="B11" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="C11" s="28" t="s">
+      <c r="C11" s="39" t="s">
         <v>27</v>
       </c>
-      <c r="D11" s="7"/>
-      <c r="E11" s="7"/>
-      <c r="F11" s="7"/>
-      <c r="G11" s="3" t="s">
+      <c r="D11" s="12"/>
+      <c r="E11" s="12"/>
+      <c r="F11" s="12"/>
+      <c r="G11" s="8" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="12" spans="1:7">
-      <c r="A12" s="3">
+      <c r="A12" s="8">
         <v>8</v>
       </c>
-      <c r="B12" s="7" t="s">
+      <c r="B12" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="C12" s="28" t="s">
+      <c r="C12" s="39" t="s">
         <v>29</v>
       </c>
-      <c r="D12" s="7"/>
-      <c r="E12" s="7"/>
-      <c r="F12" s="7"/>
-      <c r="G12" s="3" t="s">
+      <c r="D12" s="12"/>
+      <c r="E12" s="12"/>
+      <c r="F12" s="12"/>
+      <c r="G12" s="8" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="13" spans="1:7">
-      <c r="A13" s="3">
+      <c r="A13" s="8">
         <v>9</v>
       </c>
-      <c r="B13" s="7" t="s">
+      <c r="B13" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="C13" s="28" t="s">
+      <c r="C13" s="39" t="s">
         <v>31</v>
       </c>
-      <c r="D13" s="7"/>
-      <c r="E13" s="7"/>
-      <c r="F13" s="7"/>
-      <c r="G13" s="3" t="s">
+      <c r="D13" s="12"/>
+      <c r="E13" s="12"/>
+      <c r="F13" s="12"/>
+      <c r="G13" s="8" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="14" spans="1:7">
-      <c r="A14" s="3">
+      <c r="A14" s="8">
         <v>10</v>
       </c>
-      <c r="B14" s="7" t="s">
+      <c r="B14" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="C14" s="28" t="s">
+      <c r="C14" s="39" t="s">
         <v>33</v>
       </c>
-      <c r="D14" s="7"/>
-      <c r="E14" s="7"/>
-      <c r="F14" s="7"/>
-      <c r="G14" s="3" t="s">
+      <c r="D14" s="12"/>
+      <c r="E14" s="12"/>
+      <c r="F14" s="12"/>
+      <c r="G14" s="8" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="15" spans="1:7">
-      <c r="A15" s="3">
+      <c r="A15" s="8">
         <v>11</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="B15" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="D15" s="3">
+      <c r="D15" s="8">
         <f>2*3*5*3</f>
         <v>90</v>
       </c>
     </row>
     <row r="16" spans="1:7">
-      <c r="A16" s="3">
+      <c r="A16" s="8">
         <v>12</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="B16" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="D16" s="3">
+      <c r="D16" s="8">
         <v>3333</v>
       </c>
-      <c r="G16" s="3" t="s">
+      <c r="G16" s="8" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="17" spans="1:7">
-      <c r="A17" s="3">
+    <row r="17" spans="1:12">
+      <c r="A17" s="8">
         <v>13</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="B17" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="D17" s="3">
+      <c r="D17" s="8">
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:7">
-      <c r="A18" s="3">
+    <row r="18" spans="1:12">
+      <c r="A18" s="8">
         <v>14</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="B18" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="C18" s="11" t="s">
+      <c r="C18" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="G18" s="3" t="s">
+      <c r="G18" s="8" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="19" spans="1:7">
-      <c r="A19" s="3">
+    <row r="19" spans="1:12">
+      <c r="A19" s="8">
         <v>15</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="B19" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="D19" s="3">
+      <c r="D19" s="8">
         <v>5</v>
       </c>
     </row>
-    <row r="20" spans="1:7">
-      <c r="A20" s="3">
+    <row r="20" spans="1:12">
+      <c r="A20" s="8">
         <v>16</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="B20" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="D20" s="3">
+      <c r="D20" s="8">
         <v>10</v>
       </c>
     </row>
-    <row r="21" spans="1:7">
-      <c r="A21" s="3">
+    <row r="21" spans="1:12">
+      <c r="A21" s="8">
         <v>17</v>
       </c>
-      <c r="B21" s="3" t="s">
+      <c r="B21" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="C21" s="3" t="s">
+      <c r="C21" s="8" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="22" spans="1:7">
-      <c r="A22" s="3">
+      <c r="G21" s="8" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12">
+      <c r="A22" s="8">
         <v>18</v>
       </c>
-      <c r="B22" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="D22" s="3">
+      <c r="B22" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="D22" s="8">
         <f>7*24*60*60</f>
         <v>604800</v>
       </c>
     </row>
-    <row r="23" spans="1:7">
-      <c r="A23" s="3">
+    <row r="23" spans="1:12">
+      <c r="A23" s="8">
         <v>19</v>
       </c>
-      <c r="B23" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="C23" s="3" t="s">
+      <c r="B23" s="8" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="24" spans="1:7">
-      <c r="A24" s="3">
+      <c r="C23" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="G23" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="L23" s="8">
+        <f>60*24*30</f>
+        <v>43200</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12">
+      <c r="A24" s="8">
         <v>20</v>
       </c>
-      <c r="B24" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="D24" s="3">
+      <c r="B24" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="D24" s="8">
         <v>10</v>
       </c>
     </row>
-    <row r="25" spans="1:7">
-      <c r="A25" s="3">
+    <row r="25" s="1" customFormat="1" spans="1:12">
+      <c r="A25" s="1">
         <v>21</v>
       </c>
-      <c r="B25" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="C25" s="12" t="s">
-        <v>50</v>
-      </c>
-      <c r="G25" s="3" t="s">
+      <c r="B25" s="1" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="26" spans="1:7">
-      <c r="A26" s="3">
+      <c r="C25" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="G25" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="26" s="1" customFormat="1" spans="1:12">
+      <c r="A26" s="1">
         <v>22</v>
       </c>
-      <c r="B26" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="C26" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="G26" s="3" t="s">
+      <c r="B26" s="1" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="27" spans="1:7">
-      <c r="A27" s="3">
+      <c r="C26" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="G26" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="27" s="1" customFormat="1" spans="1:12">
+      <c r="A27" s="1">
         <v>23</v>
       </c>
-      <c r="B27" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="D27" s="3">
+      <c r="B27" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D27" s="1">
         <v>10000</v>
       </c>
     </row>
-    <row r="28" spans="1:7">
-      <c r="A28" s="3">
+    <row r="28" s="1" customFormat="1" spans="1:12">
+      <c r="A28" s="1">
         <v>24</v>
       </c>
-      <c r="B28" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="D28" s="3">
+      <c r="B28" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="D28" s="1">
         <v>100</v>
       </c>
     </row>
-    <row r="29" spans="1:7">
-      <c r="A29" s="3">
+    <row r="29" s="1" customFormat="1" spans="1:12">
+      <c r="A29" s="1">
         <v>25</v>
       </c>
-      <c r="B29" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="C29" s="3" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7">
-      <c r="A30" s="3">
+      <c r="B29" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12">
+      <c r="A30" s="8">
         <v>26</v>
       </c>
-      <c r="B30" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="C30" s="13"/>
-      <c r="D30" s="3">
+      <c r="B30" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="C30" s="18"/>
+      <c r="D30" s="8">
         <v>100</v>
       </c>
     </row>
-    <row r="31" spans="1:7">
-      <c r="A31" s="3">
+    <row r="31" spans="1:12">
+      <c r="A31" s="8">
         <v>27</v>
       </c>
-      <c r="B31" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="D31" s="3">
+      <c r="B31" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="D31" s="8">
         <v>10000</v>
       </c>
-      <c r="G31" s="3" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7">
-      <c r="A32" s="3">
+      <c r="G31" s="8" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12">
+      <c r="A32" s="8">
         <v>28</v>
       </c>
-      <c r="B32" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="C32" s="3" t="s">
-        <v>63</v>
+      <c r="B32" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="C32" s="8" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="33" spans="1:23">
-      <c r="A33" s="3">
+      <c r="A33" s="8">
         <v>29</v>
       </c>
-      <c r="B33" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="D33" s="3">
+      <c r="B33" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="D33" s="8">
         <v>10</v>
       </c>
     </row>
-    <row r="34" s="1" customFormat="1" spans="1:23">
-      <c r="A34" s="14">
+    <row r="34" s="2" customFormat="1" spans="1:23">
+      <c r="A34" s="19">
         <v>30</v>
       </c>
-      <c r="B34" s="14" t="s">
-        <v>65</v>
-      </c>
-      <c r="C34" s="1" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="35" s="1" customFormat="1" spans="1:23">
-      <c r="A35" s="14">
+      <c r="B34" s="19" t="s">
+        <v>67</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="35" s="2" customFormat="1" spans="1:23">
+      <c r="A35" s="19">
         <v>31</v>
       </c>
-      <c r="B35" s="14" t="s">
-        <v>67</v>
-      </c>
-      <c r="E35" s="15">
+      <c r="B35" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="E35" s="20">
         <v>372460972.440945</v>
       </c>
-      <c r="G35" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="H35" s="15">
+      <c r="G35" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="H35" s="20">
         <v>8692.20472440945</v>
       </c>
-      <c r="I35" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="J35" s="1">
+      <c r="I35" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="J35" s="2">
         <v>1</v>
       </c>
-      <c r="K35" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="L35" s="1">
+      <c r="K35" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="L35" s="2">
         <f>J35*24*60*60*1000</f>
         <v>86400000</v>
       </c>
-      <c r="M35" s="1" t="s">
-        <v>71</v>
+      <c r="M35" s="2" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="36" spans="1:23">
-      <c r="A36" s="14">
+      <c r="A36" s="19">
         <v>32</v>
       </c>
-      <c r="B36" s="14" t="s">
-        <v>72</v>
-      </c>
-      <c r="C36" s="1" t="s">
-        <v>73</v>
+      <c r="B36" s="19" t="s">
+        <v>74</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="37" spans="1:23">
-      <c r="A37" s="16">
+      <c r="A37" s="21">
         <v>33</v>
       </c>
-      <c r="B37" s="16" t="s">
-        <v>74</v>
-      </c>
-      <c r="C37" s="17" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="38" s="2" customFormat="1" spans="1:23">
-      <c r="A38" s="18">
+      <c r="B37" s="21" t="s">
+        <v>76</v>
+      </c>
+      <c r="C37" s="22" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="38" s="3" customFormat="1" spans="1:23">
+      <c r="A38" s="23">
         <v>34</v>
       </c>
-      <c r="B38" s="18" t="s">
-        <v>76</v>
-      </c>
-      <c r="C38" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="G38" s="2" t="s">
+      <c r="B38" s="23" t="s">
         <v>78</v>
       </c>
-      <c r="H38" s="2">
+      <c r="C38" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="G38" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="H38" s="3">
         <v>90</v>
       </c>
     </row>
     <row r="39" spans="1:23">
-      <c r="A39" s="16">
+      <c r="A39" s="21">
         <v>35</v>
       </c>
-      <c r="B39" s="16" t="s">
-        <v>79</v>
-      </c>
-      <c r="C39" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="G39" s="3" t="s">
+      <c r="B39" s="21" t="s">
         <v>81</v>
       </c>
-      <c r="H39" s="19">
+      <c r="C39" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="G39" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="H39" s="24">
         <f>ROUND(L35/(E35*H38/100/H35),0)</f>
         <v>2240</v>
       </c>
-      <c r="I39" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="J39" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="K39" s="20" t="s">
-        <v>83</v>
-      </c>
-      <c r="L39" s="20">
+      <c r="I39" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="J39" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="K39" s="25" t="s">
+        <v>85</v>
+      </c>
+      <c r="L39" s="25">
         <v>0.25</v>
       </c>
-      <c r="M39" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="N39" s="3">
+      <c r="M39" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="N39" s="8">
         <f>ROUND(P39*(1+2*L39),0)</f>
         <v>3360</v>
       </c>
-      <c r="O39" s="3">
+      <c r="O39" s="8">
         <f>ROUND(P39*(1+1*L39),0)</f>
         <v>2800</v>
       </c>
-      <c r="P39" s="3">
+      <c r="P39" s="8">
         <f>H39</f>
         <v>2240</v>
       </c>
-      <c r="Q39" s="3">
+      <c r="Q39" s="8">
         <f>ROUND(P39*(1-1*L39),0)</f>
         <v>1680</v>
       </c>
-      <c r="R39" s="3">
+      <c r="R39" s="8">
         <f>ROUND(P39*(1-2*L39),0)</f>
         <v>1120</v>
       </c>
-      <c r="S39" s="3" t="str">
+      <c r="S39" s="8" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,N39,1000)</f>
         <v>3360_1000</v>
       </c>
-      <c r="T39" s="3" t="str">
+      <c r="T39" s="8" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,O39,1000)</f>
         <v>2800_1000</v>
       </c>
-      <c r="U39" s="3" t="str">
+      <c r="U39" s="8" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,P39,1000)</f>
         <v>2240_1000</v>
       </c>
-      <c r="V39" s="3" t="str">
+      <c r="V39" s="8" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,Q39,1000)</f>
         <v>1680_1000</v>
       </c>
-      <c r="W39" s="3" t="str">
+      <c r="W39" s="8" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,R39,1000)</f>
         <v>1120_1000</v>
       </c>
     </row>
-    <row r="40" spans="1:23">
-      <c r="A40" s="21">
+    <row r="40" s="4" customFormat="1" spans="1:23">
+      <c r="A40" s="4">
         <v>40</v>
       </c>
-      <c r="B40" s="21" t="s">
-        <v>85</v>
-      </c>
-      <c r="D40" s="17">
+      <c r="B40" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="D40" s="26">
         <v>88</v>
       </c>
     </row>
-    <row r="41" spans="1:23">
-      <c r="A41" s="21">
+    <row r="41" s="4" customFormat="1" spans="1:23">
+      <c r="A41" s="4">
         <v>41</v>
       </c>
-      <c r="B41" s="21" t="s">
-        <v>86</v>
-      </c>
-      <c r="D41" s="17">
-        <v>1200</v>
-      </c>
-    </row>
-    <row r="42" spans="1:23">
-      <c r="A42" s="21">
+      <c r="B41" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="D41" s="26">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="42" s="4" customFormat="1" spans="1:23">
+      <c r="A42" s="4">
         <v>42</v>
       </c>
-      <c r="B42" s="21" t="s">
-        <v>87</v>
-      </c>
-      <c r="D42" s="17">
-        <v>36000</v>
-      </c>
-    </row>
-    <row r="43" spans="1:23">
-      <c r="A43" s="21">
+      <c r="B42" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="D42" s="26">
+        <v>18000</v>
+      </c>
+    </row>
+    <row r="43" s="4" customFormat="1" spans="1:23">
+      <c r="A43" s="4">
         <v>43</v>
       </c>
-      <c r="B43" s="21" t="s">
-        <v>88</v>
-      </c>
-      <c r="D43" s="17">
+      <c r="B43" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="D43" s="26">
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:23">
-      <c r="A44" s="21">
+    <row r="44" s="4" customFormat="1" spans="1:23">
+      <c r="A44" s="4">
         <v>44</v>
       </c>
-      <c r="B44" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="D44" s="17">
-        <v>290000</v>
-      </c>
-    </row>
-    <row r="45" spans="1:23">
-      <c r="A45" s="21">
+      <c r="B44" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="D44" s="26">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="45" s="4" customFormat="1" spans="1:23">
+      <c r="A45" s="4">
         <v>45</v>
       </c>
-      <c r="B45" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="C45" s="17" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="46" spans="1:23">
-      <c r="A46" s="3">
+      <c r="B45" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="C45" s="26" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="46" s="5" customFormat="1" spans="1:23">
+      <c r="A46" s="5">
         <v>46</v>
       </c>
-      <c r="B46" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="C46" s="17" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="47" spans="1:23">
-      <c r="A47" s="3">
+      <c r="B46" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="C46" s="27" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="47" s="4" customFormat="1" spans="1:23">
+      <c r="A47" s="4">
         <v>47</v>
       </c>
-      <c r="B47" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="D47" s="3">
+      <c r="B47" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="D47" s="4">
         <v>3</v>
       </c>
-      <c r="H47" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="I47" s="3">
+      <c r="H47" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="I47" s="4">
         <v>6000</v>
       </c>
     </row>
-    <row r="48" spans="1:23">
-      <c r="A48" s="3">
+    <row r="48" s="4" customFormat="1" spans="1:23">
+      <c r="A48" s="4">
         <v>48</v>
       </c>
-      <c r="B48" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="C48" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="G48" s="3" t="s">
+      <c r="B48" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="H48" s="3" t="s">
+      <c r="C48" s="4" t="s">
         <v>99</v>
       </c>
-      <c r="I48" s="3">
+      <c r="G48" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="H48" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="I48" s="4">
         <v>30</v>
       </c>
-      <c r="J48" s="3">
+      <c r="J48" s="4">
         <f>I47/(24*60/I49)*100/(I48/1+I48/1)</f>
         <v>104.166666666667</v>
       </c>
     </row>
-    <row r="49" spans="1:9">
-      <c r="A49" s="3">
+    <row r="49" s="4" customFormat="1" spans="1:9">
+      <c r="A49" s="4">
         <v>49</v>
       </c>
-      <c r="B49" s="3" t="s">
+      <c r="B49" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="C49" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="H49" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="I49" s="4">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9">
+      <c r="A50" s="8">
+        <v>50</v>
+      </c>
+      <c r="B50" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="C50" s="28" t="s">
+        <v>106</v>
+      </c>
+      <c r="I50" s="8">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="51" s="2" customFormat="1" spans="1:9">
+      <c r="A51" s="2">
+        <v>51</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="C51" s="29" t="s">
+        <v>108</v>
+      </c>
+      <c r="I51" s="2">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="52" s="5" customFormat="1" spans="1:9">
+      <c r="A52" s="5">
+        <v>52</v>
+      </c>
+      <c r="B52" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="D52" s="30">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="53" s="6" customFormat="1" spans="1:9">
+      <c r="A53" s="6">
+        <v>53</v>
+      </c>
+      <c r="B53" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="D53" s="31">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="54" s="5" customFormat="1" spans="1:9">
+      <c r="A54" s="5">
+        <v>54</v>
+      </c>
+      <c r="B54" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="D54" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" customFormat="1" spans="1:9">
+      <c r="A55" s="8">
+        <v>55</v>
+      </c>
+      <c r="B55" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="C55" s="8"/>
+      <c r="D55" s="8">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="56" s="5" customFormat="1" spans="1:9">
+      <c r="A56" s="5">
+        <v>56</v>
+      </c>
+      <c r="B56" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="C56" s="5" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="57" s="2" customFormat="1" spans="1:9">
+      <c r="A57" s="2">
+        <v>60</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="C57" s="32" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9">
+      <c r="A58" s="8">
+        <v>61</v>
+      </c>
+      <c r="B58" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="C58" s="33" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="59" s="6" customFormat="1" spans="1:9">
+      <c r="A59" s="6">
+        <v>62</v>
+      </c>
+      <c r="B59" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="C59" s="31" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="60" s="6" customFormat="1" spans="1:9">
+      <c r="A60" s="6">
+        <v>63</v>
+      </c>
+      <c r="B60" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="C60" s="6" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="61" s="6" customFormat="1" spans="1:9">
+      <c r="A61" s="6">
+        <v>64</v>
+      </c>
+      <c r="B61" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="C61" s="34" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="62" s="6" customFormat="1" spans="1:9">
+      <c r="A62" s="6">
+        <v>65</v>
+      </c>
+      <c r="B62" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="C62" s="34" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="63" s="7" customFormat="1" spans="1:9">
+      <c r="A63" s="7">
+        <v>70</v>
+      </c>
+      <c r="B63" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="C63" s="35" t="s">
+        <v>128</v>
+      </c>
+      <c r="D63" s="35"/>
+    </row>
+    <row r="64" s="7" customFormat="1" spans="1:9">
+      <c r="A64" s="7">
+        <v>71</v>
+      </c>
+      <c r="B64" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="C64" s="35"/>
+      <c r="D64" s="35">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="65" s="7" customFormat="1" spans="1:20">
+      <c r="A65" s="7">
+        <v>72</v>
+      </c>
+      <c r="B65" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="C65" s="35" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="66" spans="1:20">
+      <c r="A66" s="36">
+        <v>80</v>
+      </c>
+      <c r="B66" s="36" t="s">
+        <v>132</v>
+      </c>
+      <c r="C66" s="36"/>
+      <c r="D66" s="36">
+        <v>259200</v>
+      </c>
+      <c r="E66" s="11"/>
+      <c r="F66" s="11"/>
+      <c r="G66" s="11"/>
+      <c r="H66" s="11"/>
+      <c r="I66" s="11"/>
+      <c r="J66" s="11"/>
+      <c r="K66" s="11"/>
+      <c r="L66" s="11"/>
+      <c r="M66" s="11"/>
+      <c r="N66" s="11"/>
+      <c r="O66" s="11"/>
+      <c r="P66" s="11"/>
+      <c r="Q66" s="11"/>
+      <c r="R66" s="11"/>
+      <c r="S66" s="11"/>
+      <c r="T66" s="11"/>
+    </row>
+    <row r="67" s="1" customFormat="1" spans="1:20">
+      <c r="A67" s="1">
+        <v>90</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="D67" s="1">
+        <v>150000</v>
+      </c>
+    </row>
+    <row r="68" spans="1:20">
+      <c r="A68" s="8">
         <v>100</v>
       </c>
-      <c r="C49" s="3" t="s">
+      <c r="B68" s="8" t="s">
+        <v>134</v>
+      </c>
+      <c r="C68" s="8" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="69" spans="1:20">
+      <c r="A69" s="8">
         <v>101</v>
       </c>
-      <c r="H49" s="3" t="s">
+      <c r="B69" s="8" t="s">
+        <v>136</v>
+      </c>
+      <c r="C69" s="8" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="70" spans="1:20">
+      <c r="A70" s="8">
         <v>102</v>
       </c>
-      <c r="I49" s="3">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="50" spans="1:9">
-      <c r="A50" s="3">
-        <v>50</v>
-      </c>
-      <c r="B50" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="C50" s="17"/>
-      <c r="I50" s="3">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="51" s="1" customFormat="1" spans="1:9">
-      <c r="A51" s="1">
-        <v>51</v>
-      </c>
-      <c r="B51" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="C51" s="22" t="s">
-        <v>105</v>
-      </c>
-      <c r="I51" s="1">
-        <v>1200</v>
-      </c>
-    </row>
-    <row r="52" spans="1:9">
-      <c r="A52" s="3">
-        <v>52</v>
-      </c>
-      <c r="B52" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="D52" s="12">
+      <c r="B70" s="8" t="s">
+        <v>138</v>
+      </c>
+      <c r="D70" s="37">
+        <v>1022503</v>
+      </c>
+    </row>
+    <row r="71" s="4" customFormat="1" spans="1:20">
+      <c r="A71" s="4">
+        <v>110</v>
+      </c>
+      <c r="B71" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="D71" s="26">
+        <v>4200</v>
+      </c>
+    </row>
+    <row r="72" spans="1:20">
+      <c r="A72" s="8">
+        <v>111</v>
+      </c>
+      <c r="B72" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="D72" s="8">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="73" spans="1:20">
+      <c r="A73" s="8">
+        <v>112</v>
+      </c>
+      <c r="B73" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="D73" s="8">
+        <v>300000</v>
+      </c>
+    </row>
+    <row r="74" spans="1:20">
+      <c r="A74" s="8">
+        <v>113</v>
+      </c>
+      <c r="B74" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="C74" s="8" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="75" spans="1:20">
+      <c r="A75" s="8">
+        <v>114</v>
+      </c>
+      <c r="B75" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="D75" s="8">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="76" customFormat="1" spans="1:20">
+      <c r="A76" s="8">
+        <v>120</v>
+      </c>
+      <c r="B76" s="8" t="s">
+        <v>145</v>
+      </c>
+      <c r="C76" s="8"/>
+      <c r="D76" s="8">
+        <v>30</v>
+      </c>
+      <c r="E76" s="8"/>
+      <c r="F76" s="8"/>
+      <c r="G76" s="8"/>
+      <c r="H76" s="8"/>
+      <c r="I76" s="8"/>
+      <c r="J76" s="8"/>
+      <c r="K76" s="8"/>
+      <c r="L76" s="8"/>
+      <c r="M76" s="8"/>
+      <c r="N76" s="8"/>
+      <c r="O76" s="8"/>
+      <c r="P76" s="8"/>
+      <c r="Q76" s="8"/>
+      <c r="R76" s="8"/>
+    </row>
+    <row r="77" customFormat="1" spans="1:20">
+      <c r="A77" s="8">
+        <v>121</v>
+      </c>
+      <c r="B77" s="8" t="s">
+        <v>146</v>
+      </c>
+      <c r="C77" s="8"/>
+      <c r="D77" s="8">
         <v>1</v>
       </c>
-    </row>
-    <row r="53" spans="1:9">
-      <c r="A53" s="3">
-        <v>53</v>
-      </c>
-      <c r="B53" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="D53" s="12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="54" spans="1:9">
-      <c r="A54" s="3">
-        <v>54</v>
-      </c>
-      <c r="B54" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="D54" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="55" customFormat="1" spans="1:9">
-      <c r="A55" s="3">
-        <v>55</v>
-      </c>
-      <c r="B55" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="C55" s="3"/>
-      <c r="D55" s="3">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="56" spans="1:9">
-      <c r="A56" s="3">
-        <v>56</v>
-      </c>
-      <c r="B56" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="C56" s="3" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="57" s="1" customFormat="1" spans="1:9">
-      <c r="A57" s="1">
-        <v>60</v>
-      </c>
-      <c r="B57" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="C57" s="23" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="58" spans="1:9">
-      <c r="A58" s="3">
-        <v>61</v>
-      </c>
-      <c r="B58" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="C58" s="24" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="59" spans="1:9">
-      <c r="A59" s="3">
-        <v>62</v>
-      </c>
-      <c r="B59" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="C59" s="12" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="60" spans="1:9">
-      <c r="A60" s="3">
-        <v>63</v>
-      </c>
-      <c r="B60" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="C60" s="3" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="61" spans="1:9">
-      <c r="A61" s="3">
-        <v>64</v>
-      </c>
-      <c r="B61" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="C61" s="17" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="62" spans="1:9">
-      <c r="A62" s="3">
-        <v>65</v>
-      </c>
-      <c r="B62" s="3" t="s">
+      <c r="E77" s="8"/>
+      <c r="F77" s="8"/>
+      <c r="G77" s="8"/>
+      <c r="H77" s="8"/>
+      <c r="I77" s="8"/>
+      <c r="J77" s="8"/>
+      <c r="K77" s="8"/>
+      <c r="L77" s="8"/>
+      <c r="M77" s="8"/>
+      <c r="N77" s="8"/>
+      <c r="O77" s="8"/>
+      <c r="P77" s="8"/>
+      <c r="Q77" s="8"/>
+      <c r="R77" s="8"/>
+    </row>
+    <row r="78" customFormat="1" spans="1:20">
+      <c r="A78" s="8">
         <v>122</v>
       </c>
-      <c r="C62" s="17" t="s">
+      <c r="B78" s="8" t="s">
+        <v>147</v>
+      </c>
+      <c r="C78" s="8"/>
+      <c r="D78" s="8">
+        <v>5</v>
+      </c>
+      <c r="E78" s="8"/>
+      <c r="F78" s="8"/>
+      <c r="G78" s="8"/>
+      <c r="H78" s="8"/>
+      <c r="I78" s="8"/>
+      <c r="J78" s="8"/>
+      <c r="K78" s="8"/>
+      <c r="L78" s="8"/>
+      <c r="M78" s="8"/>
+      <c r="N78" s="8"/>
+      <c r="O78" s="8"/>
+      <c r="P78" s="8"/>
+      <c r="Q78" s="8"/>
+      <c r="R78" s="8"/>
+    </row>
+    <row r="79" customFormat="1" spans="1:20">
+      <c r="A79" s="8">
         <v>123</v>
       </c>
-    </row>
-    <row r="63" spans="1:9">
-      <c r="A63" s="3">
-        <v>70</v>
-      </c>
-      <c r="B63" s="3" t="s">
+      <c r="B79" s="8" t="s">
+        <v>148</v>
+      </c>
+      <c r="C79" s="8"/>
+      <c r="D79" s="8">
+        <v>30000</v>
+      </c>
+      <c r="E79" s="8"/>
+      <c r="F79" s="8"/>
+      <c r="G79" s="8"/>
+      <c r="H79" s="8"/>
+      <c r="I79" s="8"/>
+      <c r="J79" s="8"/>
+      <c r="K79" s="8"/>
+      <c r="L79" s="8"/>
+      <c r="M79" s="8"/>
+      <c r="N79" s="8"/>
+      <c r="O79" s="8"/>
+      <c r="P79" s="8"/>
+      <c r="Q79" s="8"/>
+      <c r="R79" s="8"/>
+    </row>
+    <row r="80" spans="1:20">
+      <c r="A80" s="8">
         <v>124</v>
       </c>
-      <c r="C63" s="17" t="s">
-        <v>125</v>
-      </c>
-      <c r="D63" s="17"/>
-    </row>
-    <row r="64" spans="1:9">
-      <c r="A64" s="3">
-        <v>71</v>
-      </c>
-      <c r="B64" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="C64" s="17"/>
-      <c r="D64" s="17">
-        <v>5000</v>
-      </c>
-    </row>
-    <row r="65" spans="1:20">
-      <c r="A65" s="3">
-        <v>72</v>
-      </c>
-      <c r="B65" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="C65" s="17" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="66" spans="1:20">
-      <c r="A66" s="25">
-        <v>80</v>
-      </c>
-      <c r="B66" s="25" t="s">
-        <v>129</v>
-      </c>
-      <c r="C66" s="25"/>
-      <c r="D66" s="25">
-        <v>259200</v>
-      </c>
-      <c r="E66" s="6"/>
-      <c r="F66" s="6"/>
-      <c r="G66" s="6"/>
-      <c r="H66" s="6"/>
-      <c r="I66" s="6"/>
-      <c r="J66" s="6"/>
-      <c r="K66" s="6"/>
-      <c r="L66" s="6"/>
-      <c r="M66" s="6"/>
-      <c r="N66" s="6"/>
-      <c r="O66" s="6"/>
-      <c r="P66" s="6"/>
-      <c r="Q66" s="6"/>
-      <c r="R66" s="6"/>
-      <c r="S66" s="6"/>
-      <c r="T66" s="6"/>
-    </row>
-    <row r="67" spans="1:20">
-      <c r="A67" s="3">
-        <v>90</v>
-      </c>
-      <c r="B67" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="D67" s="3">
-        <v>100000</v>
-      </c>
-    </row>
-    <row r="68" spans="1:20">
-      <c r="A68" s="3">
-        <v>100</v>
-      </c>
-      <c r="B68" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="C68" s="3" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="69" spans="1:20">
-      <c r="A69" s="3">
-        <v>101</v>
-      </c>
-      <c r="B69" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="C69" s="3" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="70" spans="1:20">
-      <c r="A70" s="3">
-        <v>102</v>
-      </c>
-      <c r="B70" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="D70" s="26">
-        <v>1022503</v>
-      </c>
-    </row>
-    <row r="71" spans="1:20">
-      <c r="A71" s="3">
-        <v>110</v>
-      </c>
-      <c r="B71" s="21" t="s">
-        <v>136</v>
-      </c>
-      <c r="D71" s="17">
-        <f>8400</f>
-        <v>8400</v>
-      </c>
-    </row>
-    <row r="72" spans="1:20">
-      <c r="A72" s="3">
-        <v>111</v>
-      </c>
-      <c r="B72" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="D72" s="3">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="73" spans="1:20">
-      <c r="A73" s="3">
-        <v>112</v>
-      </c>
-      <c r="B73" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="D73" s="3">
-        <v>300000</v>
-      </c>
-    </row>
-    <row r="74" spans="1:20">
-      <c r="A74" s="3">
-        <v>113</v>
-      </c>
-      <c r="B74" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="C74" s="3" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="75" spans="1:20">
-      <c r="A75" s="3">
-        <v>114</v>
-      </c>
-      <c r="B75" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="D75" s="3">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="76" spans="1:20">
-      <c r="A76" s="3">
-        <v>120</v>
-      </c>
-      <c r="B76" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="D76" s="3">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="77" spans="1:20">
-      <c r="A77" s="3">
-        <v>121</v>
-      </c>
-      <c r="B77" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="D77" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="78" spans="1:20">
-      <c r="A78" s="3">
-        <v>122</v>
-      </c>
-      <c r="B78" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="D78" s="3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="79" spans="1:20">
-      <c r="A79" s="3">
-        <v>123</v>
-      </c>
-      <c r="B79" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="D79" s="3">
-        <v>30000</v>
-      </c>
-    </row>
-    <row r="80" spans="1:20">
-      <c r="A80" s="3">
-        <v>124</v>
-      </c>
-      <c r="B80" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="D80" s="3">
-        <v>600</v>
+      <c r="B80" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="D80" s="8">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="C57" r:id="rId3" display="https://aws-s3-jjg-asset-bucket.s3.ap-southeast-1.amazonaws.com/tanchuang_res/english/tc_sc_1.png" tooltip="https://aws-s3-jjg-asset-bucket.s3.ap-southeast-1.amazonaws.com/tanchuang_res/english/tc_sc_1.png"/>
+    <hyperlink ref="C58" r:id="rId4" display="https://chat.kinghush.com/privacy.html"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/gm/resources/sample/global.xlsx
+++ b/gm/resources/sample/global.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="globalConfig" sheetId="1" r:id="rId1"/>
@@ -3046,7 +3046,7 @@
       </c>
       <c r="C78" s="8"/>
       <c r="D78" s="8">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E78" s="8"/>
       <c r="F78" s="8"/>
